--- a/STOK.xlsx
+++ b/STOK.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="118">
   <si>
     <t>BAYRAMPAŞA DEPODAKİ ELSAN AYRINTI  DÖKÜMÜ</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>İTÜ</t>
+  </si>
+  <si>
+    <t>UYARLAR</t>
   </si>
 </sst>
 </file>
@@ -2515,6 +2518,45 @@
     <xf numFmtId="165" fontId="15" fillId="5" borderId="24" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="5" borderId="33" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="33" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="64" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="35" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="5" borderId="33" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="64" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2533,6 +2575,12 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2629,56 +2677,11 @@
     <xf numFmtId="0" fontId="26" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="33" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="5" borderId="33" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="5" borderId="33" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="5" borderId="64" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="5" borderId="35" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="5" borderId="33" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="64" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -2939,1104 +2942,1104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="327" t="s">
+      <c r="A1" s="340" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="328"/>
-      <c r="C1" s="328"/>
-      <c r="D1" s="328"/>
-      <c r="E1" s="328"/>
-      <c r="F1" s="328"/>
-      <c r="G1" s="328"/>
-      <c r="H1" s="328"/>
-      <c r="I1" s="328"/>
-      <c r="J1" s="328"/>
-      <c r="K1" s="328"/>
-      <c r="L1" s="328"/>
-      <c r="M1" s="328"/>
-      <c r="N1" s="328"/>
-      <c r="O1" s="328"/>
-      <c r="P1" s="328"/>
-      <c r="Q1" s="328"/>
-      <c r="R1" s="328"/>
-      <c r="S1" s="328"/>
-      <c r="T1" s="328"/>
-      <c r="U1" s="328"/>
-      <c r="V1" s="328"/>
-      <c r="W1" s="328"/>
-      <c r="X1" s="328"/>
-      <c r="Y1" s="328"/>
-      <c r="Z1" s="328"/>
-      <c r="AA1" s="328"/>
-      <c r="AB1" s="328"/>
-      <c r="AC1" s="328"/>
+      <c r="B1" s="341"/>
+      <c r="C1" s="341"/>
+      <c r="D1" s="341"/>
+      <c r="E1" s="341"/>
+      <c r="F1" s="341"/>
+      <c r="G1" s="341"/>
+      <c r="H1" s="341"/>
+      <c r="I1" s="341"/>
+      <c r="J1" s="341"/>
+      <c r="K1" s="341"/>
+      <c r="L1" s="341"/>
+      <c r="M1" s="341"/>
+      <c r="N1" s="341"/>
+      <c r="O1" s="341"/>
+      <c r="P1" s="341"/>
+      <c r="Q1" s="341"/>
+      <c r="R1" s="341"/>
+      <c r="S1" s="341"/>
+      <c r="T1" s="341"/>
+      <c r="U1" s="341"/>
+      <c r="V1" s="341"/>
+      <c r="W1" s="341"/>
+      <c r="X1" s="341"/>
+      <c r="Y1" s="341"/>
+      <c r="Z1" s="341"/>
+      <c r="AA1" s="341"/>
+      <c r="AB1" s="341"/>
+      <c r="AC1" s="341"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A2" s="329"/>
-      <c r="B2" s="326"/>
-      <c r="C2" s="326"/>
-      <c r="D2" s="326"/>
-      <c r="E2" s="326"/>
-      <c r="F2" s="326"/>
-      <c r="G2" s="326"/>
-      <c r="H2" s="326"/>
-      <c r="I2" s="326"/>
-      <c r="J2" s="326"/>
-      <c r="K2" s="326"/>
-      <c r="L2" s="326"/>
-      <c r="M2" s="326"/>
-      <c r="N2" s="326"/>
-      <c r="O2" s="326"/>
-      <c r="P2" s="326"/>
-      <c r="Q2" s="326"/>
-      <c r="R2" s="326"/>
-      <c r="S2" s="326"/>
-      <c r="T2" s="326"/>
-      <c r="U2" s="326"/>
-      <c r="V2" s="326"/>
-      <c r="W2" s="326"/>
-      <c r="X2" s="326"/>
-      <c r="Y2" s="326"/>
-      <c r="Z2" s="326"/>
-      <c r="AA2" s="326"/>
-      <c r="AB2" s="326"/>
-      <c r="AC2" s="326"/>
+      <c r="A2" s="342"/>
+      <c r="B2" s="339"/>
+      <c r="C2" s="339"/>
+      <c r="D2" s="339"/>
+      <c r="E2" s="339"/>
+      <c r="F2" s="339"/>
+      <c r="G2" s="339"/>
+      <c r="H2" s="339"/>
+      <c r="I2" s="339"/>
+      <c r="J2" s="339"/>
+      <c r="K2" s="339"/>
+      <c r="L2" s="339"/>
+      <c r="M2" s="339"/>
+      <c r="N2" s="339"/>
+      <c r="O2" s="339"/>
+      <c r="P2" s="339"/>
+      <c r="Q2" s="339"/>
+      <c r="R2" s="339"/>
+      <c r="S2" s="339"/>
+      <c r="T2" s="339"/>
+      <c r="U2" s="339"/>
+      <c r="V2" s="339"/>
+      <c r="W2" s="339"/>
+      <c r="X2" s="339"/>
+      <c r="Y2" s="339"/>
+      <c r="Z2" s="339"/>
+      <c r="AA2" s="339"/>
+      <c r="AB2" s="339"/>
+      <c r="AC2" s="339"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1.8</v>
       </c>
-      <c r="B3" s="324"/>
+      <c r="B3" s="337"/>
       <c r="C3" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D3" s="324"/>
+      <c r="D3" s="337"/>
       <c r="E3" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F3" s="324"/>
+      <c r="F3" s="337"/>
       <c r="G3" s="2">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H3" s="324"/>
+      <c r="H3" s="337"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="324"/>
+      <c r="J3" s="337"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="324"/>
+      <c r="L3" s="337"/>
       <c r="M3" s="2"/>
-      <c r="N3" s="324"/>
+      <c r="N3" s="337"/>
       <c r="O3" s="2"/>
-      <c r="P3" s="324"/>
+      <c r="P3" s="337"/>
       <c r="Q3" s="2"/>
-      <c r="R3" s="324"/>
+      <c r="R3" s="337"/>
       <c r="S3" s="2"/>
-      <c r="T3" s="324"/>
+      <c r="T3" s="337"/>
       <c r="U3" s="2"/>
-      <c r="V3" s="324"/>
+      <c r="V3" s="337"/>
       <c r="W3" s="2"/>
-      <c r="X3" s="324"/>
+      <c r="X3" s="337"/>
       <c r="Y3" s="2"/>
-      <c r="Z3" s="324"/>
+      <c r="Z3" s="337"/>
       <c r="AA3" s="2"/>
-      <c r="AB3" s="326"/>
+      <c r="AB3" s="339"/>
     </row>
     <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
-      <c r="B4" s="325"/>
+      <c r="B4" s="338"/>
       <c r="C4" s="5"/>
-      <c r="D4" s="325"/>
+      <c r="D4" s="338"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="325"/>
+      <c r="F4" s="338"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="325"/>
+      <c r="H4" s="338"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="325"/>
+      <c r="J4" s="338"/>
       <c r="K4" s="5"/>
-      <c r="L4" s="325"/>
+      <c r="L4" s="338"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="325"/>
+      <c r="N4" s="338"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="325"/>
+      <c r="P4" s="338"/>
       <c r="Q4" s="5"/>
-      <c r="R4" s="325"/>
+      <c r="R4" s="338"/>
       <c r="S4" s="5"/>
-      <c r="T4" s="325"/>
+      <c r="T4" s="338"/>
       <c r="U4" s="5"/>
-      <c r="V4" s="325"/>
+      <c r="V4" s="338"/>
       <c r="W4" s="5"/>
-      <c r="X4" s="325"/>
+      <c r="X4" s="338"/>
       <c r="Y4" s="5"/>
-      <c r="Z4" s="325"/>
+      <c r="Z4" s="338"/>
       <c r="AA4" s="5"/>
-      <c r="AB4" s="326"/>
+      <c r="AB4" s="339"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>2035.8</v>
       </c>
-      <c r="B5" s="325"/>
+      <c r="B5" s="338"/>
       <c r="C5" s="7">
         <v>2018.1</v>
       </c>
-      <c r="D5" s="325"/>
+      <c r="D5" s="338"/>
       <c r="E5" s="7">
         <v>2056.1</v>
       </c>
-      <c r="F5" s="325"/>
+      <c r="F5" s="338"/>
       <c r="G5" s="7">
         <v>1995.7</v>
       </c>
-      <c r="H5" s="325"/>
+      <c r="H5" s="338"/>
       <c r="I5" s="7"/>
-      <c r="J5" s="325"/>
+      <c r="J5" s="338"/>
       <c r="K5" s="7"/>
-      <c r="L5" s="325"/>
+      <c r="L5" s="338"/>
       <c r="M5" s="7"/>
-      <c r="N5" s="325"/>
+      <c r="N5" s="338"/>
       <c r="O5" s="7"/>
-      <c r="P5" s="325"/>
+      <c r="P5" s="338"/>
       <c r="Q5" s="7"/>
-      <c r="R5" s="325"/>
+      <c r="R5" s="338"/>
       <c r="S5" s="7"/>
-      <c r="T5" s="325"/>
+      <c r="T5" s="338"/>
       <c r="U5" s="7"/>
-      <c r="V5" s="325"/>
+      <c r="V5" s="338"/>
       <c r="W5" s="7"/>
-      <c r="X5" s="325"/>
+      <c r="X5" s="338"/>
       <c r="Y5" s="7"/>
-      <c r="Z5" s="325"/>
+      <c r="Z5" s="338"/>
       <c r="AA5" s="7"/>
-      <c r="AB5" s="326"/>
+      <c r="AB5" s="339"/>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
-      <c r="B6" s="325"/>
+      <c r="B6" s="338"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="325"/>
+      <c r="D6" s="338"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="325"/>
+      <c r="F6" s="338"/>
       <c r="G6" s="7"/>
-      <c r="H6" s="325"/>
+      <c r="H6" s="338"/>
       <c r="I6" s="7"/>
-      <c r="J6" s="325"/>
+      <c r="J6" s="338"/>
       <c r="K6" s="7"/>
-      <c r="L6" s="325"/>
+      <c r="L6" s="338"/>
       <c r="M6" s="7"/>
-      <c r="N6" s="325"/>
+      <c r="N6" s="338"/>
       <c r="O6" s="7"/>
-      <c r="P6" s="325"/>
+      <c r="P6" s="338"/>
       <c r="Q6" s="7"/>
-      <c r="R6" s="325"/>
+      <c r="R6" s="338"/>
       <c r="S6" s="7"/>
-      <c r="T6" s="325"/>
+      <c r="T6" s="338"/>
       <c r="U6" s="7"/>
-      <c r="V6" s="325"/>
+      <c r="V6" s="338"/>
       <c r="W6" s="7"/>
-      <c r="X6" s="325"/>
+      <c r="X6" s="338"/>
       <c r="Y6" s="7"/>
-      <c r="Z6" s="325"/>
+      <c r="Z6" s="338"/>
       <c r="AA6" s="7"/>
-      <c r="AB6" s="326"/>
+      <c r="AB6" s="339"/>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
-      <c r="B7" s="325"/>
+      <c r="B7" s="338"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="325"/>
+      <c r="D7" s="338"/>
       <c r="E7" s="7"/>
-      <c r="F7" s="325"/>
+      <c r="F7" s="338"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="325"/>
+      <c r="H7" s="338"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="325"/>
+      <c r="J7" s="338"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="325"/>
+      <c r="L7" s="338"/>
       <c r="M7" s="7"/>
-      <c r="N7" s="325"/>
+      <c r="N7" s="338"/>
       <c r="O7" s="7"/>
-      <c r="P7" s="325"/>
+      <c r="P7" s="338"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="325"/>
+      <c r="R7" s="338"/>
       <c r="S7" s="7"/>
-      <c r="T7" s="325"/>
+      <c r="T7" s="338"/>
       <c r="U7" s="7"/>
-      <c r="V7" s="325"/>
+      <c r="V7" s="338"/>
       <c r="W7" s="7"/>
-      <c r="X7" s="325"/>
+      <c r="X7" s="338"/>
       <c r="Y7" s="7"/>
-      <c r="Z7" s="325"/>
+      <c r="Z7" s="338"/>
       <c r="AA7" s="7"/>
-      <c r="AB7" s="326"/>
+      <c r="AB7" s="339"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
-      <c r="B8" s="325"/>
+      <c r="B8" s="338"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="325"/>
+      <c r="D8" s="338"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="325"/>
+      <c r="F8" s="338"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="325"/>
+      <c r="H8" s="338"/>
       <c r="I8" s="7"/>
-      <c r="J8" s="325"/>
+      <c r="J8" s="338"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="325"/>
+      <c r="L8" s="338"/>
       <c r="M8" s="7"/>
-      <c r="N8" s="325"/>
+      <c r="N8" s="338"/>
       <c r="O8" s="7"/>
-      <c r="P8" s="325"/>
+      <c r="P8" s="338"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="325"/>
+      <c r="R8" s="338"/>
       <c r="S8" s="7"/>
-      <c r="T8" s="325"/>
+      <c r="T8" s="338"/>
       <c r="U8" s="7"/>
-      <c r="V8" s="325"/>
+      <c r="V8" s="338"/>
       <c r="W8" s="7"/>
-      <c r="X8" s="325"/>
+      <c r="X8" s="338"/>
       <c r="Y8" s="7"/>
-      <c r="Z8" s="325"/>
+      <c r="Z8" s="338"/>
       <c r="AA8" s="7"/>
-      <c r="AB8" s="326"/>
+      <c r="AB8" s="339"/>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
-      <c r="B9" s="325"/>
+      <c r="B9" s="338"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="325"/>
+      <c r="D9" s="338"/>
       <c r="E9" s="7"/>
-      <c r="F9" s="325"/>
+      <c r="F9" s="338"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="325"/>
+      <c r="H9" s="338"/>
       <c r="I9" s="7"/>
-      <c r="J9" s="325"/>
+      <c r="J9" s="338"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="325"/>
+      <c r="L9" s="338"/>
       <c r="M9" s="7"/>
-      <c r="N9" s="325"/>
+      <c r="N9" s="338"/>
       <c r="O9" s="7"/>
-      <c r="P9" s="325"/>
+      <c r="P9" s="338"/>
       <c r="Q9" s="7"/>
-      <c r="R9" s="325"/>
+      <c r="R9" s="338"/>
       <c r="S9" s="7"/>
-      <c r="T9" s="325"/>
+      <c r="T9" s="338"/>
       <c r="U9" s="7"/>
-      <c r="V9" s="325"/>
+      <c r="V9" s="338"/>
       <c r="W9" s="7"/>
-      <c r="X9" s="325"/>
+      <c r="X9" s="338"/>
       <c r="Y9" s="7"/>
-      <c r="Z9" s="325"/>
+      <c r="Z9" s="338"/>
       <c r="AA9" s="7"/>
-      <c r="AB9" s="326"/>
+      <c r="AB9" s="339"/>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
-      <c r="B10" s="325"/>
+      <c r="B10" s="338"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="325"/>
+      <c r="D10" s="338"/>
       <c r="E10" s="7"/>
-      <c r="F10" s="325"/>
+      <c r="F10" s="338"/>
       <c r="G10" s="7"/>
-      <c r="H10" s="325"/>
+      <c r="H10" s="338"/>
       <c r="I10" s="7"/>
-      <c r="J10" s="325"/>
+      <c r="J10" s="338"/>
       <c r="K10" s="7"/>
-      <c r="L10" s="325"/>
+      <c r="L10" s="338"/>
       <c r="M10" s="7"/>
-      <c r="N10" s="325"/>
+      <c r="N10" s="338"/>
       <c r="O10" s="7"/>
-      <c r="P10" s="325"/>
+      <c r="P10" s="338"/>
       <c r="Q10" s="7"/>
-      <c r="R10" s="325"/>
+      <c r="R10" s="338"/>
       <c r="S10" s="7"/>
-      <c r="T10" s="325"/>
+      <c r="T10" s="338"/>
       <c r="U10" s="7"/>
-      <c r="V10" s="325"/>
+      <c r="V10" s="338"/>
       <c r="W10" s="7"/>
-      <c r="X10" s="325"/>
+      <c r="X10" s="338"/>
       <c r="Y10" s="7"/>
-      <c r="Z10" s="325"/>
+      <c r="Z10" s="338"/>
       <c r="AA10" s="7"/>
-      <c r="AB10" s="326"/>
+      <c r="AB10" s="339"/>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
-      <c r="B11" s="325"/>
+      <c r="B11" s="338"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="325"/>
+      <c r="D11" s="338"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="325"/>
+      <c r="F11" s="338"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="325"/>
+      <c r="H11" s="338"/>
       <c r="I11" s="7"/>
-      <c r="J11" s="325"/>
+      <c r="J11" s="338"/>
       <c r="K11" s="7"/>
-      <c r="L11" s="325"/>
+      <c r="L11" s="338"/>
       <c r="M11" s="7"/>
-      <c r="N11" s="325"/>
+      <c r="N11" s="338"/>
       <c r="O11" s="7"/>
-      <c r="P11" s="325"/>
+      <c r="P11" s="338"/>
       <c r="Q11" s="7"/>
-      <c r="R11" s="325"/>
+      <c r="R11" s="338"/>
       <c r="S11" s="7"/>
-      <c r="T11" s="325"/>
+      <c r="T11" s="338"/>
       <c r="U11" s="7"/>
-      <c r="V11" s="325"/>
+      <c r="V11" s="338"/>
       <c r="W11" s="7"/>
-      <c r="X11" s="325"/>
+      <c r="X11" s="338"/>
       <c r="Y11" s="7"/>
-      <c r="Z11" s="325"/>
+      <c r="Z11" s="338"/>
       <c r="AA11" s="7"/>
-      <c r="AB11" s="326"/>
+      <c r="AB11" s="339"/>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
-      <c r="B12" s="325"/>
+      <c r="B12" s="338"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="325"/>
+      <c r="D12" s="338"/>
       <c r="E12" s="7"/>
-      <c r="F12" s="325"/>
+      <c r="F12" s="338"/>
       <c r="G12" s="7"/>
-      <c r="H12" s="325"/>
+      <c r="H12" s="338"/>
       <c r="I12" s="7"/>
-      <c r="J12" s="325"/>
+      <c r="J12" s="338"/>
       <c r="K12" s="7"/>
-      <c r="L12" s="325"/>
+      <c r="L12" s="338"/>
       <c r="M12" s="7"/>
-      <c r="N12" s="325"/>
+      <c r="N12" s="338"/>
       <c r="O12" s="7"/>
-      <c r="P12" s="325"/>
+      <c r="P12" s="338"/>
       <c r="Q12" s="7"/>
-      <c r="R12" s="325"/>
+      <c r="R12" s="338"/>
       <c r="S12" s="7"/>
-      <c r="T12" s="325"/>
+      <c r="T12" s="338"/>
       <c r="U12" s="7"/>
-      <c r="V12" s="325"/>
+      <c r="V12" s="338"/>
       <c r="W12" s="7"/>
-      <c r="X12" s="325"/>
+      <c r="X12" s="338"/>
       <c r="Y12" s="7"/>
-      <c r="Z12" s="325"/>
+      <c r="Z12" s="338"/>
       <c r="AA12" s="7"/>
-      <c r="AB12" s="326"/>
+      <c r="AB12" s="339"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
-      <c r="B13" s="325"/>
+      <c r="B13" s="338"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="325"/>
+      <c r="D13" s="338"/>
       <c r="E13" s="7"/>
-      <c r="F13" s="325"/>
+      <c r="F13" s="338"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="325"/>
+      <c r="H13" s="338"/>
       <c r="I13" s="7"/>
-      <c r="J13" s="325"/>
+      <c r="J13" s="338"/>
       <c r="K13" s="7"/>
-      <c r="L13" s="325"/>
+      <c r="L13" s="338"/>
       <c r="M13" s="7"/>
-      <c r="N13" s="325"/>
+      <c r="N13" s="338"/>
       <c r="O13" s="7"/>
-      <c r="P13" s="325"/>
+      <c r="P13" s="338"/>
       <c r="Q13" s="7"/>
-      <c r="R13" s="325"/>
+      <c r="R13" s="338"/>
       <c r="S13" s="7"/>
-      <c r="T13" s="325"/>
+      <c r="T13" s="338"/>
       <c r="U13" s="7"/>
-      <c r="V13" s="325"/>
+      <c r="V13" s="338"/>
       <c r="W13" s="7"/>
-      <c r="X13" s="325"/>
+      <c r="X13" s="338"/>
       <c r="Y13" s="7"/>
-      <c r="Z13" s="325"/>
+      <c r="Z13" s="338"/>
       <c r="AA13" s="7"/>
-      <c r="AB13" s="326"/>
+      <c r="AB13" s="339"/>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
-      <c r="B14" s="325"/>
+      <c r="B14" s="338"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="325"/>
+      <c r="D14" s="338"/>
       <c r="E14" s="7"/>
-      <c r="F14" s="325"/>
+      <c r="F14" s="338"/>
       <c r="G14" s="7"/>
-      <c r="H14" s="325"/>
+      <c r="H14" s="338"/>
       <c r="I14" s="7"/>
-      <c r="J14" s="325"/>
+      <c r="J14" s="338"/>
       <c r="K14" s="7"/>
-      <c r="L14" s="325"/>
+      <c r="L14" s="338"/>
       <c r="M14" s="7"/>
-      <c r="N14" s="325"/>
+      <c r="N14" s="338"/>
       <c r="O14" s="7"/>
-      <c r="P14" s="325"/>
+      <c r="P14" s="338"/>
       <c r="Q14" s="7"/>
-      <c r="R14" s="325"/>
+      <c r="R14" s="338"/>
       <c r="S14" s="7"/>
-      <c r="T14" s="325"/>
+      <c r="T14" s="338"/>
       <c r="U14" s="7"/>
-      <c r="V14" s="325"/>
+      <c r="V14" s="338"/>
       <c r="W14" s="7"/>
-      <c r="X14" s="325"/>
+      <c r="X14" s="338"/>
       <c r="Y14" s="7"/>
-      <c r="Z14" s="325"/>
+      <c r="Z14" s="338"/>
       <c r="AA14" s="7"/>
-      <c r="AB14" s="326"/>
+      <c r="AB14" s="339"/>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
-      <c r="B15" s="325"/>
+      <c r="B15" s="338"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="325"/>
+      <c r="D15" s="338"/>
       <c r="E15" s="7"/>
-      <c r="F15" s="325"/>
+      <c r="F15" s="338"/>
       <c r="G15" s="7"/>
-      <c r="H15" s="325"/>
+      <c r="H15" s="338"/>
       <c r="I15" s="7"/>
-      <c r="J15" s="325"/>
+      <c r="J15" s="338"/>
       <c r="K15" s="7"/>
-      <c r="L15" s="325"/>
+      <c r="L15" s="338"/>
       <c r="M15" s="7"/>
-      <c r="N15" s="325"/>
+      <c r="N15" s="338"/>
       <c r="O15" s="7"/>
-      <c r="P15" s="325"/>
+      <c r="P15" s="338"/>
       <c r="Q15" s="7"/>
-      <c r="R15" s="325"/>
+      <c r="R15" s="338"/>
       <c r="S15" s="7"/>
-      <c r="T15" s="325"/>
+      <c r="T15" s="338"/>
       <c r="U15" s="7"/>
-      <c r="V15" s="325"/>
+      <c r="V15" s="338"/>
       <c r="W15" s="7"/>
-      <c r="X15" s="325"/>
+      <c r="X15" s="338"/>
       <c r="Y15" s="7"/>
-      <c r="Z15" s="325"/>
+      <c r="Z15" s="338"/>
       <c r="AA15" s="7"/>
-      <c r="AB15" s="326"/>
+      <c r="AB15" s="339"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="325"/>
+      <c r="B16" s="338"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="325"/>
+      <c r="D16" s="338"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="325"/>
+      <c r="F16" s="338"/>
       <c r="G16" s="7"/>
-      <c r="H16" s="325"/>
+      <c r="H16" s="338"/>
       <c r="I16" s="7"/>
-      <c r="J16" s="325"/>
+      <c r="J16" s="338"/>
       <c r="K16" s="7"/>
-      <c r="L16" s="325"/>
+      <c r="L16" s="338"/>
       <c r="M16" s="7"/>
-      <c r="N16" s="325"/>
+      <c r="N16" s="338"/>
       <c r="O16" s="7"/>
-      <c r="P16" s="325"/>
+      <c r="P16" s="338"/>
       <c r="Q16" s="7"/>
-      <c r="R16" s="325"/>
+      <c r="R16" s="338"/>
       <c r="S16" s="7"/>
-      <c r="T16" s="325"/>
+      <c r="T16" s="338"/>
       <c r="U16" s="7"/>
-      <c r="V16" s="325"/>
+      <c r="V16" s="338"/>
       <c r="W16" s="7"/>
-      <c r="X16" s="325"/>
+      <c r="X16" s="338"/>
       <c r="Y16" s="7"/>
-      <c r="Z16" s="325"/>
+      <c r="Z16" s="338"/>
       <c r="AA16" s="7"/>
-      <c r="AB16" s="326"/>
+      <c r="AB16" s="339"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
-      <c r="B17" s="325"/>
+      <c r="B17" s="338"/>
       <c r="C17" s="7"/>
-      <c r="D17" s="325"/>
+      <c r="D17" s="338"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="325"/>
+      <c r="F17" s="338"/>
       <c r="G17" s="7"/>
-      <c r="H17" s="325"/>
+      <c r="H17" s="338"/>
       <c r="I17" s="7"/>
-      <c r="J17" s="325"/>
+      <c r="J17" s="338"/>
       <c r="K17" s="7"/>
-      <c r="L17" s="325"/>
+      <c r="L17" s="338"/>
       <c r="M17" s="7"/>
-      <c r="N17" s="325"/>
+      <c r="N17" s="338"/>
       <c r="O17" s="7"/>
-      <c r="P17" s="325"/>
+      <c r="P17" s="338"/>
       <c r="Q17" s="7"/>
-      <c r="R17" s="325"/>
+      <c r="R17" s="338"/>
       <c r="S17" s="7"/>
-      <c r="T17" s="325"/>
+      <c r="T17" s="338"/>
       <c r="U17" s="7"/>
-      <c r="V17" s="325"/>
+      <c r="V17" s="338"/>
       <c r="W17" s="7"/>
-      <c r="X17" s="325"/>
+      <c r="X17" s="338"/>
       <c r="Y17" s="7"/>
-      <c r="Z17" s="325"/>
+      <c r="Z17" s="338"/>
       <c r="AA17" s="7"/>
-      <c r="AB17" s="326"/>
+      <c r="AB17" s="339"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
-      <c r="B18" s="325"/>
+      <c r="B18" s="338"/>
       <c r="C18" s="7"/>
-      <c r="D18" s="325"/>
+      <c r="D18" s="338"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="325"/>
+      <c r="F18" s="338"/>
       <c r="G18" s="7"/>
-      <c r="H18" s="325"/>
+      <c r="H18" s="338"/>
       <c r="I18" s="7"/>
-      <c r="J18" s="325"/>
+      <c r="J18" s="338"/>
       <c r="K18" s="7"/>
-      <c r="L18" s="325"/>
+      <c r="L18" s="338"/>
       <c r="M18" s="7"/>
-      <c r="N18" s="325"/>
+      <c r="N18" s="338"/>
       <c r="O18" s="7"/>
-      <c r="P18" s="325"/>
+      <c r="P18" s="338"/>
       <c r="Q18" s="7"/>
-      <c r="R18" s="325"/>
+      <c r="R18" s="338"/>
       <c r="S18" s="7"/>
-      <c r="T18" s="325"/>
+      <c r="T18" s="338"/>
       <c r="U18" s="7"/>
-      <c r="V18" s="325"/>
+      <c r="V18" s="338"/>
       <c r="W18" s="7"/>
-      <c r="X18" s="325"/>
+      <c r="X18" s="338"/>
       <c r="Y18" s="7"/>
-      <c r="Z18" s="325"/>
+      <c r="Z18" s="338"/>
       <c r="AA18" s="7"/>
-      <c r="AB18" s="326"/>
+      <c r="AB18" s="339"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
-      <c r="B19" s="325"/>
+      <c r="B19" s="338"/>
       <c r="C19" s="7"/>
-      <c r="D19" s="325"/>
+      <c r="D19" s="338"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="325"/>
+      <c r="F19" s="338"/>
       <c r="G19" s="7"/>
-      <c r="H19" s="325"/>
+      <c r="H19" s="338"/>
       <c r="I19" s="7"/>
-      <c r="J19" s="325"/>
+      <c r="J19" s="338"/>
       <c r="K19" s="7"/>
-      <c r="L19" s="325"/>
+      <c r="L19" s="338"/>
       <c r="M19" s="7"/>
-      <c r="N19" s="325"/>
+      <c r="N19" s="338"/>
       <c r="O19" s="7"/>
-      <c r="P19" s="325"/>
+      <c r="P19" s="338"/>
       <c r="Q19" s="7"/>
-      <c r="R19" s="325"/>
+      <c r="R19" s="338"/>
       <c r="S19" s="7"/>
-      <c r="T19" s="325"/>
+      <c r="T19" s="338"/>
       <c r="U19" s="7"/>
-      <c r="V19" s="325"/>
+      <c r="V19" s="338"/>
       <c r="W19" s="7"/>
-      <c r="X19" s="325"/>
+      <c r="X19" s="338"/>
       <c r="Y19" s="7"/>
-      <c r="Z19" s="325"/>
+      <c r="Z19" s="338"/>
       <c r="AA19" s="7"/>
-      <c r="AB19" s="326"/>
+      <c r="AB19" s="339"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
-      <c r="B20" s="325"/>
+      <c r="B20" s="338"/>
       <c r="C20" s="7"/>
-      <c r="D20" s="325"/>
+      <c r="D20" s="338"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="325"/>
+      <c r="F20" s="338"/>
       <c r="G20" s="7"/>
-      <c r="H20" s="325"/>
+      <c r="H20" s="338"/>
       <c r="I20" s="7"/>
-      <c r="J20" s="325"/>
+      <c r="J20" s="338"/>
       <c r="K20" s="7"/>
-      <c r="L20" s="325"/>
+      <c r="L20" s="338"/>
       <c r="M20" s="7"/>
-      <c r="N20" s="325"/>
+      <c r="N20" s="338"/>
       <c r="O20" s="7"/>
-      <c r="P20" s="325"/>
+      <c r="P20" s="338"/>
       <c r="Q20" s="7"/>
-      <c r="R20" s="325"/>
+      <c r="R20" s="338"/>
       <c r="S20" s="7"/>
-      <c r="T20" s="325"/>
+      <c r="T20" s="338"/>
       <c r="U20" s="7"/>
-      <c r="V20" s="325"/>
+      <c r="V20" s="338"/>
       <c r="W20" s="7"/>
-      <c r="X20" s="325"/>
+      <c r="X20" s="338"/>
       <c r="Y20" s="7"/>
-      <c r="Z20" s="325"/>
+      <c r="Z20" s="338"/>
       <c r="AA20" s="7"/>
-      <c r="AB20" s="326"/>
+      <c r="AB20" s="339"/>
     </row>
     <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
-      <c r="B21" s="325"/>
+      <c r="B21" s="338"/>
       <c r="C21" s="7"/>
-      <c r="D21" s="325"/>
+      <c r="D21" s="338"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="325"/>
+      <c r="F21" s="338"/>
       <c r="G21" s="7"/>
-      <c r="H21" s="325"/>
+      <c r="H21" s="338"/>
       <c r="I21" s="7"/>
-      <c r="J21" s="325"/>
+      <c r="J21" s="338"/>
       <c r="K21" s="7"/>
-      <c r="L21" s="325"/>
+      <c r="L21" s="338"/>
       <c r="M21" s="7"/>
-      <c r="N21" s="325"/>
+      <c r="N21" s="338"/>
       <c r="O21" s="7"/>
-      <c r="P21" s="325"/>
+      <c r="P21" s="338"/>
       <c r="Q21" s="7"/>
-      <c r="R21" s="325"/>
+      <c r="R21" s="338"/>
       <c r="S21" s="7"/>
-      <c r="T21" s="325"/>
+      <c r="T21" s="338"/>
       <c r="U21" s="7"/>
-      <c r="V21" s="325"/>
+      <c r="V21" s="338"/>
       <c r="W21" s="7"/>
-      <c r="X21" s="325"/>
+      <c r="X21" s="338"/>
       <c r="Y21" s="7"/>
-      <c r="Z21" s="325"/>
+      <c r="Z21" s="338"/>
       <c r="AA21" s="7"/>
-      <c r="AB21" s="326"/>
+      <c r="AB21" s="339"/>
     </row>
     <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
-      <c r="B22" s="325"/>
+      <c r="B22" s="338"/>
       <c r="C22" s="7"/>
-      <c r="D22" s="325"/>
+      <c r="D22" s="338"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="325"/>
+      <c r="F22" s="338"/>
       <c r="G22" s="7"/>
-      <c r="H22" s="325"/>
+      <c r="H22" s="338"/>
       <c r="I22" s="7"/>
-      <c r="J22" s="325"/>
+      <c r="J22" s="338"/>
       <c r="K22" s="7"/>
-      <c r="L22" s="325"/>
+      <c r="L22" s="338"/>
       <c r="M22" s="7"/>
-      <c r="N22" s="325"/>
+      <c r="N22" s="338"/>
       <c r="O22" s="7"/>
-      <c r="P22" s="325"/>
+      <c r="P22" s="338"/>
       <c r="Q22" s="7"/>
-      <c r="R22" s="325"/>
+      <c r="R22" s="338"/>
       <c r="S22" s="7"/>
-      <c r="T22" s="325"/>
+      <c r="T22" s="338"/>
       <c r="U22" s="7"/>
-      <c r="V22" s="325"/>
+      <c r="V22" s="338"/>
       <c r="W22" s="7"/>
-      <c r="X22" s="325"/>
+      <c r="X22" s="338"/>
       <c r="Y22" s="7"/>
-      <c r="Z22" s="325"/>
+      <c r="Z22" s="338"/>
       <c r="AA22" s="7"/>
-      <c r="AB22" s="326"/>
+      <c r="AB22" s="339"/>
     </row>
     <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
-      <c r="B23" s="325"/>
+      <c r="B23" s="338"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="325"/>
+      <c r="D23" s="338"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="325"/>
+      <c r="F23" s="338"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="325"/>
+      <c r="H23" s="338"/>
       <c r="I23" s="7"/>
-      <c r="J23" s="325"/>
+      <c r="J23" s="338"/>
       <c r="K23" s="7"/>
-      <c r="L23" s="325"/>
+      <c r="L23" s="338"/>
       <c r="M23" s="7"/>
-      <c r="N23" s="325"/>
+      <c r="N23" s="338"/>
       <c r="O23" s="7"/>
-      <c r="P23" s="325"/>
+      <c r="P23" s="338"/>
       <c r="Q23" s="7"/>
-      <c r="R23" s="325"/>
+      <c r="R23" s="338"/>
       <c r="S23" s="7"/>
-      <c r="T23" s="325"/>
+      <c r="T23" s="338"/>
       <c r="U23" s="7"/>
-      <c r="V23" s="325"/>
+      <c r="V23" s="338"/>
       <c r="W23" s="7"/>
-      <c r="X23" s="325"/>
+      <c r="X23" s="338"/>
       <c r="Y23" s="7"/>
-      <c r="Z23" s="325"/>
+      <c r="Z23" s="338"/>
       <c r="AA23" s="7"/>
-      <c r="AB23" s="326"/>
+      <c r="AB23" s="339"/>
     </row>
     <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
-      <c r="B24" s="325"/>
+      <c r="B24" s="338"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="325"/>
+      <c r="D24" s="338"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="325"/>
+      <c r="F24" s="338"/>
       <c r="G24" s="7"/>
-      <c r="H24" s="325"/>
+      <c r="H24" s="338"/>
       <c r="I24" s="7"/>
-      <c r="J24" s="325"/>
+      <c r="J24" s="338"/>
       <c r="K24" s="7"/>
-      <c r="L24" s="325"/>
+      <c r="L24" s="338"/>
       <c r="M24" s="7"/>
-      <c r="N24" s="325"/>
+      <c r="N24" s="338"/>
       <c r="O24" s="7"/>
-      <c r="P24" s="325"/>
+      <c r="P24" s="338"/>
       <c r="Q24" s="7"/>
-      <c r="R24" s="325"/>
+      <c r="R24" s="338"/>
       <c r="S24" s="7"/>
-      <c r="T24" s="325"/>
+      <c r="T24" s="338"/>
       <c r="U24" s="7"/>
-      <c r="V24" s="325"/>
+      <c r="V24" s="338"/>
       <c r="W24" s="7"/>
-      <c r="X24" s="325"/>
+      <c r="X24" s="338"/>
       <c r="Y24" s="7"/>
-      <c r="Z24" s="325"/>
+      <c r="Z24" s="338"/>
       <c r="AA24" s="7"/>
-      <c r="AB24" s="326"/>
+      <c r="AB24" s="339"/>
     </row>
     <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
-      <c r="B25" s="325"/>
+      <c r="B25" s="338"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="325"/>
+      <c r="D25" s="338"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="325"/>
+      <c r="F25" s="338"/>
       <c r="G25" s="7"/>
-      <c r="H25" s="325"/>
+      <c r="H25" s="338"/>
       <c r="I25" s="7"/>
-      <c r="J25" s="325"/>
+      <c r="J25" s="338"/>
       <c r="K25" s="7"/>
-      <c r="L25" s="325"/>
+      <c r="L25" s="338"/>
       <c r="M25" s="7"/>
-      <c r="N25" s="325"/>
+      <c r="N25" s="338"/>
       <c r="O25" s="7"/>
-      <c r="P25" s="325"/>
+      <c r="P25" s="338"/>
       <c r="Q25" s="7"/>
-      <c r="R25" s="325"/>
+      <c r="R25" s="338"/>
       <c r="S25" s="7"/>
-      <c r="T25" s="325"/>
+      <c r="T25" s="338"/>
       <c r="U25" s="7"/>
-      <c r="V25" s="325"/>
+      <c r="V25" s="338"/>
       <c r="W25" s="7"/>
-      <c r="X25" s="325"/>
+      <c r="X25" s="338"/>
       <c r="Y25" s="7"/>
-      <c r="Z25" s="325"/>
+      <c r="Z25" s="338"/>
       <c r="AA25" s="7"/>
-      <c r="AB25" s="326"/>
+      <c r="AB25" s="339"/>
     </row>
     <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
-      <c r="B26" s="325"/>
+      <c r="B26" s="338"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="325"/>
+      <c r="D26" s="338"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="325"/>
+      <c r="F26" s="338"/>
       <c r="G26" s="7"/>
-      <c r="H26" s="325"/>
+      <c r="H26" s="338"/>
       <c r="I26" s="7"/>
-      <c r="J26" s="325"/>
+      <c r="J26" s="338"/>
       <c r="K26" s="7"/>
-      <c r="L26" s="325"/>
+      <c r="L26" s="338"/>
       <c r="M26" s="7"/>
-      <c r="N26" s="325"/>
+      <c r="N26" s="338"/>
       <c r="O26" s="7"/>
-      <c r="P26" s="325"/>
+      <c r="P26" s="338"/>
       <c r="Q26" s="7"/>
-      <c r="R26" s="325"/>
+      <c r="R26" s="338"/>
       <c r="S26" s="7"/>
-      <c r="T26" s="325"/>
+      <c r="T26" s="338"/>
       <c r="U26" s="7"/>
-      <c r="V26" s="325"/>
+      <c r="V26" s="338"/>
       <c r="W26" s="7"/>
-      <c r="X26" s="325"/>
+      <c r="X26" s="338"/>
       <c r="Y26" s="7"/>
-      <c r="Z26" s="325"/>
+      <c r="Z26" s="338"/>
       <c r="AA26" s="7"/>
-      <c r="AB26" s="326"/>
+      <c r="AB26" s="339"/>
     </row>
     <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
-      <c r="B27" s="325"/>
+      <c r="B27" s="338"/>
       <c r="C27" s="7"/>
-      <c r="D27" s="325"/>
+      <c r="D27" s="338"/>
       <c r="E27" s="7"/>
-      <c r="F27" s="325"/>
+      <c r="F27" s="338"/>
       <c r="G27" s="7"/>
-      <c r="H27" s="325"/>
+      <c r="H27" s="338"/>
       <c r="I27" s="7"/>
-      <c r="J27" s="325"/>
+      <c r="J27" s="338"/>
       <c r="K27" s="7"/>
-      <c r="L27" s="325"/>
+      <c r="L27" s="338"/>
       <c r="M27" s="7"/>
-      <c r="N27" s="325"/>
+      <c r="N27" s="338"/>
       <c r="O27" s="7"/>
-      <c r="P27" s="325"/>
+      <c r="P27" s="338"/>
       <c r="Q27" s="7"/>
-      <c r="R27" s="325"/>
+      <c r="R27" s="338"/>
       <c r="S27" s="7"/>
-      <c r="T27" s="325"/>
+      <c r="T27" s="338"/>
       <c r="U27" s="7"/>
-      <c r="V27" s="325"/>
+      <c r="V27" s="338"/>
       <c r="W27" s="7"/>
-      <c r="X27" s="325"/>
+      <c r="X27" s="338"/>
       <c r="Y27" s="7"/>
-      <c r="Z27" s="325"/>
+      <c r="Z27" s="338"/>
       <c r="AA27" s="7"/>
-      <c r="AB27" s="326"/>
+      <c r="AB27" s="339"/>
     </row>
     <row r="28" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
-      <c r="B28" s="325"/>
+      <c r="B28" s="338"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="325"/>
+      <c r="D28" s="338"/>
       <c r="E28" s="7"/>
-      <c r="F28" s="325"/>
+      <c r="F28" s="338"/>
       <c r="G28" s="7"/>
-      <c r="H28" s="325"/>
+      <c r="H28" s="338"/>
       <c r="I28" s="7"/>
-      <c r="J28" s="325"/>
+      <c r="J28" s="338"/>
       <c r="K28" s="7"/>
-      <c r="L28" s="325"/>
+      <c r="L28" s="338"/>
       <c r="M28" s="7"/>
-      <c r="N28" s="325"/>
+      <c r="N28" s="338"/>
       <c r="O28" s="7"/>
-      <c r="P28" s="325"/>
+      <c r="P28" s="338"/>
       <c r="Q28" s="7"/>
-      <c r="R28" s="325"/>
+      <c r="R28" s="338"/>
       <c r="S28" s="7"/>
-      <c r="T28" s="325"/>
+      <c r="T28" s="338"/>
       <c r="U28" s="7"/>
-      <c r="V28" s="325"/>
+      <c r="V28" s="338"/>
       <c r="W28" s="7"/>
-      <c r="X28" s="325"/>
+      <c r="X28" s="338"/>
       <c r="Y28" s="7"/>
-      <c r="Z28" s="325"/>
+      <c r="Z28" s="338"/>
       <c r="AA28" s="7"/>
-      <c r="AB28" s="326"/>
+      <c r="AB28" s="339"/>
     </row>
     <row r="29" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
-      <c r="B29" s="325"/>
+      <c r="B29" s="338"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="325"/>
+      <c r="D29" s="338"/>
       <c r="E29" s="7"/>
-      <c r="F29" s="325"/>
+      <c r="F29" s="338"/>
       <c r="G29" s="7"/>
-      <c r="H29" s="325"/>
+      <c r="H29" s="338"/>
       <c r="I29" s="7"/>
-      <c r="J29" s="325"/>
+      <c r="J29" s="338"/>
       <c r="K29" s="7"/>
-      <c r="L29" s="325"/>
+      <c r="L29" s="338"/>
       <c r="M29" s="7"/>
-      <c r="N29" s="325"/>
+      <c r="N29" s="338"/>
       <c r="O29" s="7"/>
-      <c r="P29" s="325"/>
+      <c r="P29" s="338"/>
       <c r="Q29" s="7"/>
-      <c r="R29" s="325"/>
+      <c r="R29" s="338"/>
       <c r="S29" s="7"/>
-      <c r="T29" s="325"/>
+      <c r="T29" s="338"/>
       <c r="U29" s="7"/>
-      <c r="V29" s="325"/>
+      <c r="V29" s="338"/>
       <c r="W29" s="7"/>
-      <c r="X29" s="325"/>
+      <c r="X29" s="338"/>
       <c r="Y29" s="7"/>
-      <c r="Z29" s="325"/>
+      <c r="Z29" s="338"/>
       <c r="AA29" s="7"/>
-      <c r="AB29" s="326"/>
+      <c r="AB29" s="339"/>
     </row>
     <row r="30" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
-      <c r="B30" s="325"/>
+      <c r="B30" s="338"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="325"/>
+      <c r="D30" s="338"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="325"/>
+      <c r="F30" s="338"/>
       <c r="G30" s="7"/>
-      <c r="H30" s="325"/>
+      <c r="H30" s="338"/>
       <c r="I30" s="7"/>
-      <c r="J30" s="325"/>
+      <c r="J30" s="338"/>
       <c r="K30" s="7"/>
-      <c r="L30" s="325"/>
+      <c r="L30" s="338"/>
       <c r="M30" s="7"/>
-      <c r="N30" s="325"/>
+      <c r="N30" s="338"/>
       <c r="O30" s="7"/>
-      <c r="P30" s="325"/>
+      <c r="P30" s="338"/>
       <c r="Q30" s="7"/>
-      <c r="R30" s="325"/>
+      <c r="R30" s="338"/>
       <c r="S30" s="7"/>
-      <c r="T30" s="325"/>
+      <c r="T30" s="338"/>
       <c r="U30" s="7"/>
-      <c r="V30" s="325"/>
+      <c r="V30" s="338"/>
       <c r="W30" s="7"/>
-      <c r="X30" s="325"/>
+      <c r="X30" s="338"/>
       <c r="Y30" s="7"/>
-      <c r="Z30" s="325"/>
+      <c r="Z30" s="338"/>
       <c r="AA30" s="7"/>
-      <c r="AB30" s="326"/>
+      <c r="AB30" s="339"/>
     </row>
     <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
-      <c r="B31" s="325"/>
+      <c r="B31" s="338"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="325"/>
+      <c r="D31" s="338"/>
       <c r="E31" s="7"/>
-      <c r="F31" s="325"/>
+      <c r="F31" s="338"/>
       <c r="G31" s="7"/>
-      <c r="H31" s="325"/>
+      <c r="H31" s="338"/>
       <c r="I31" s="7"/>
-      <c r="J31" s="325"/>
+      <c r="J31" s="338"/>
       <c r="K31" s="7"/>
-      <c r="L31" s="325"/>
+      <c r="L31" s="338"/>
       <c r="M31" s="7"/>
-      <c r="N31" s="325"/>
+      <c r="N31" s="338"/>
       <c r="O31" s="7"/>
-      <c r="P31" s="325"/>
+      <c r="P31" s="338"/>
       <c r="Q31" s="7"/>
-      <c r="R31" s="325"/>
+      <c r="R31" s="338"/>
       <c r="S31" s="7"/>
-      <c r="T31" s="325"/>
+      <c r="T31" s="338"/>
       <c r="U31" s="7"/>
-      <c r="V31" s="325"/>
+      <c r="V31" s="338"/>
       <c r="W31" s="7"/>
-      <c r="X31" s="325"/>
+      <c r="X31" s="338"/>
       <c r="Y31" s="7"/>
-      <c r="Z31" s="325"/>
+      <c r="Z31" s="338"/>
       <c r="AA31" s="7"/>
-      <c r="AB31" s="326"/>
+      <c r="AB31" s="339"/>
     </row>
     <row r="32" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
-      <c r="B32" s="325"/>
+      <c r="B32" s="338"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="325"/>
+      <c r="D32" s="338"/>
       <c r="E32" s="7"/>
-      <c r="F32" s="325"/>
+      <c r="F32" s="338"/>
       <c r="G32" s="7"/>
-      <c r="H32" s="325"/>
+      <c r="H32" s="338"/>
       <c r="I32" s="7"/>
-      <c r="J32" s="325"/>
+      <c r="J32" s="338"/>
       <c r="K32" s="7"/>
-      <c r="L32" s="325"/>
+      <c r="L32" s="338"/>
       <c r="M32" s="7"/>
-      <c r="N32" s="325"/>
+      <c r="N32" s="338"/>
       <c r="O32" s="7"/>
-      <c r="P32" s="325"/>
+      <c r="P32" s="338"/>
       <c r="Q32" s="7"/>
-      <c r="R32" s="325"/>
+      <c r="R32" s="338"/>
       <c r="S32" s="7"/>
-      <c r="T32" s="325"/>
+      <c r="T32" s="338"/>
       <c r="U32" s="7"/>
-      <c r="V32" s="325"/>
+      <c r="V32" s="338"/>
       <c r="W32" s="7"/>
-      <c r="X32" s="325"/>
+      <c r="X32" s="338"/>
       <c r="Y32" s="7"/>
-      <c r="Z32" s="325"/>
+      <c r="Z32" s="338"/>
       <c r="AA32" s="7"/>
-      <c r="AB32" s="326"/>
+      <c r="AB32" s="339"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
-      <c r="B33" s="325"/>
+      <c r="B33" s="338"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="325"/>
+      <c r="D33" s="338"/>
       <c r="E33" s="7"/>
-      <c r="F33" s="325"/>
+      <c r="F33" s="338"/>
       <c r="G33" s="7"/>
-      <c r="H33" s="325"/>
+      <c r="H33" s="338"/>
       <c r="I33" s="7"/>
-      <c r="J33" s="325"/>
+      <c r="J33" s="338"/>
       <c r="K33" s="7"/>
-      <c r="L33" s="325"/>
+      <c r="L33" s="338"/>
       <c r="M33" s="7"/>
-      <c r="N33" s="325"/>
+      <c r="N33" s="338"/>
       <c r="O33" s="7"/>
-      <c r="P33" s="325"/>
+      <c r="P33" s="338"/>
       <c r="Q33" s="7"/>
-      <c r="R33" s="325"/>
+      <c r="R33" s="338"/>
       <c r="S33" s="7"/>
-      <c r="T33" s="325"/>
+      <c r="T33" s="338"/>
       <c r="U33" s="7"/>
-      <c r="V33" s="325"/>
+      <c r="V33" s="338"/>
       <c r="W33" s="7"/>
-      <c r="X33" s="325"/>
+      <c r="X33" s="338"/>
       <c r="Y33" s="7"/>
-      <c r="Z33" s="325"/>
+      <c r="Z33" s="338"/>
       <c r="AA33" s="7"/>
-      <c r="AB33" s="326"/>
+      <c r="AB33" s="339"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
-      <c r="B34" s="325"/>
+      <c r="B34" s="338"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="325"/>
+      <c r="D34" s="338"/>
       <c r="E34" s="7"/>
-      <c r="F34" s="325"/>
+      <c r="F34" s="338"/>
       <c r="G34" s="7"/>
-      <c r="H34" s="325"/>
+      <c r="H34" s="338"/>
       <c r="I34" s="7"/>
-      <c r="J34" s="325"/>
+      <c r="J34" s="338"/>
       <c r="K34" s="7"/>
-      <c r="L34" s="325"/>
+      <c r="L34" s="338"/>
       <c r="M34" s="7"/>
-      <c r="N34" s="325"/>
+      <c r="N34" s="338"/>
       <c r="O34" s="7"/>
-      <c r="P34" s="325"/>
+      <c r="P34" s="338"/>
       <c r="Q34" s="7"/>
-      <c r="R34" s="325"/>
+      <c r="R34" s="338"/>
       <c r="S34" s="7"/>
-      <c r="T34" s="325"/>
+      <c r="T34" s="338"/>
       <c r="U34" s="7"/>
-      <c r="V34" s="325"/>
+      <c r="V34" s="338"/>
       <c r="W34" s="7"/>
-      <c r="X34" s="325"/>
+      <c r="X34" s="338"/>
       <c r="Y34" s="7"/>
-      <c r="Z34" s="325"/>
+      <c r="Z34" s="338"/>
       <c r="AA34" s="7"/>
-      <c r="AB34" s="326"/>
+      <c r="AB34" s="339"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
-      <c r="B35" s="325"/>
+      <c r="B35" s="338"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="325"/>
+      <c r="D35" s="338"/>
       <c r="E35" s="7"/>
-      <c r="F35" s="325"/>
+      <c r="F35" s="338"/>
       <c r="G35" s="7"/>
-      <c r="H35" s="325"/>
+      <c r="H35" s="338"/>
       <c r="I35" s="7"/>
-      <c r="J35" s="325"/>
+      <c r="J35" s="338"/>
       <c r="K35" s="7"/>
-      <c r="L35" s="325"/>
+      <c r="L35" s="338"/>
       <c r="M35" s="7"/>
-      <c r="N35" s="325"/>
+      <c r="N35" s="338"/>
       <c r="O35" s="7"/>
-      <c r="P35" s="325"/>
+      <c r="P35" s="338"/>
       <c r="Q35" s="7"/>
-      <c r="R35" s="325"/>
+      <c r="R35" s="338"/>
       <c r="S35" s="7"/>
-      <c r="T35" s="325"/>
+      <c r="T35" s="338"/>
       <c r="U35" s="7"/>
-      <c r="V35" s="325"/>
+      <c r="V35" s="338"/>
       <c r="W35" s="7"/>
-      <c r="X35" s="325"/>
+      <c r="X35" s="338"/>
       <c r="Y35" s="7"/>
-      <c r="Z35" s="325"/>
+      <c r="Z35" s="338"/>
       <c r="AA35" s="7"/>
-      <c r="AB35" s="326"/>
+      <c r="AB35" s="339"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
-      <c r="B36" s="325"/>
+      <c r="B36" s="338"/>
       <c r="C36" s="5"/>
-      <c r="D36" s="325"/>
+      <c r="D36" s="338"/>
       <c r="E36" s="5"/>
-      <c r="F36" s="325"/>
+      <c r="F36" s="338"/>
       <c r="G36" s="5"/>
-      <c r="H36" s="325"/>
+      <c r="H36" s="338"/>
       <c r="I36" s="5"/>
-      <c r="J36" s="325"/>
+      <c r="J36" s="338"/>
       <c r="K36" s="5"/>
-      <c r="L36" s="325"/>
+      <c r="L36" s="338"/>
       <c r="M36" s="5"/>
-      <c r="N36" s="325"/>
+      <c r="N36" s="338"/>
       <c r="O36" s="5"/>
-      <c r="P36" s="325"/>
+      <c r="P36" s="338"/>
       <c r="Q36" s="5"/>
-      <c r="R36" s="325"/>
+      <c r="R36" s="338"/>
       <c r="S36" s="5"/>
-      <c r="T36" s="325"/>
+      <c r="T36" s="338"/>
       <c r="U36" s="5"/>
-      <c r="V36" s="325"/>
+      <c r="V36" s="338"/>
       <c r="W36" s="5"/>
-      <c r="X36" s="325"/>
+      <c r="X36" s="338"/>
       <c r="Y36" s="5"/>
-      <c r="Z36" s="325"/>
+      <c r="Z36" s="338"/>
       <c r="AA36" s="5"/>
-      <c r="AB36" s="326"/>
+      <c r="AB36" s="339"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
@@ -4194,19 +4197,19 @@
     </row>
     <row r="39" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="318">
+      <c r="A40" s="331">
         <f>SUM(A38:AC38)</f>
         <v>8105.7</v>
       </c>
-      <c r="B40" s="319"/>
-      <c r="C40" s="319"/>
-      <c r="D40" s="320"/>
+      <c r="B40" s="332"/>
+      <c r="C40" s="332"/>
+      <c r="D40" s="333"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="321"/>
-      <c r="B41" s="322"/>
-      <c r="C41" s="322"/>
-      <c r="D41" s="323"/>
+      <c r="A41" s="334"/>
+      <c r="B41" s="335"/>
+      <c r="C41" s="335"/>
+      <c r="D41" s="336"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8595,19 +8598,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="330" t="s">
+      <c r="A1" s="345" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="331"/>
-      <c r="C1" s="331"/>
-      <c r="D1" s="331"/>
-      <c r="E1" s="331"/>
-      <c r="F1" s="331"/>
-      <c r="G1" s="331"/>
-      <c r="H1" s="331"/>
-      <c r="I1" s="331"/>
-      <c r="J1" s="331"/>
-      <c r="K1" s="332"/>
+      <c r="B1" s="346"/>
+      <c r="C1" s="346"/>
+      <c r="D1" s="346"/>
+      <c r="E1" s="346"/>
+      <c r="F1" s="346"/>
+      <c r="G1" s="346"/>
+      <c r="H1" s="346"/>
+      <c r="I1" s="346"/>
+      <c r="J1" s="346"/>
+      <c r="K1" s="347"/>
       <c r="L1" s="65"/>
       <c r="M1" s="65"/>
       <c r="N1" s="65"/>
@@ -8623,11 +8626,11 @@
       <c r="X1" s="65"/>
     </row>
     <row r="2" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="342" t="s">
+      <c r="A2" s="357" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="343"/>
-      <c r="C2" s="344"/>
+      <c r="B2" s="358"/>
+      <c r="C2" s="359"/>
       <c r="D2" s="112" t="s">
         <v>27</v>
       </c>
@@ -8670,10 +8673,10 @@
       <c r="A3" s="117" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="348" t="s">
+      <c r="B3" s="363" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="349"/>
+      <c r="C3" s="364"/>
       <c r="D3" s="118">
         <v>102</v>
       </c>
@@ -8708,10 +8711,10 @@
       <c r="A4" s="123" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="350" t="s">
+      <c r="B4" s="365" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="351"/>
+      <c r="C4" s="366"/>
       <c r="D4" s="124">
         <v>102</v>
       </c>
@@ -8746,10 +8749,10 @@
       <c r="A5" s="123" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="350" t="s">
+      <c r="B5" s="365" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="351"/>
+      <c r="C5" s="366"/>
       <c r="D5" s="124">
         <v>102</v>
       </c>
@@ -8784,10 +8787,10 @@
       <c r="A6" s="129" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="355" t="s">
+      <c r="B6" s="370" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="356"/>
+      <c r="C6" s="371"/>
       <c r="D6" s="130"/>
       <c r="E6" s="131">
         <f>SUM(F6:K6)</f>
@@ -8817,12 +8820,12 @@
       <c r="X6" s="74"/>
     </row>
     <row r="7" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="339" t="s">
+      <c r="A7" s="354" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="340"/>
-      <c r="C7" s="340"/>
-      <c r="D7" s="341"/>
+      <c r="B7" s="355"/>
+      <c r="C7" s="355"/>
+      <c r="D7" s="356"/>
       <c r="E7" s="135">
         <f>SUM(F7:K7)</f>
         <v>50.314999999999998</v>
@@ -8866,11 +8869,11 @@
       <c r="X7" s="65"/>
     </row>
     <row r="8" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="357" t="s">
+      <c r="A8" s="372" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="358"/>
-      <c r="C8" s="359"/>
+      <c r="B8" s="373"/>
+      <c r="C8" s="374"/>
       <c r="D8" s="113" t="s">
         <v>27</v>
       </c>
@@ -8964,11 +8967,11 @@
       </c>
       <c r="E10" s="125">
         <f t="shared" si="1"/>
-        <v>6.06</v>
+        <v>2.0999999999999996</v>
       </c>
       <c r="F10" s="177">
         <f>'STOK DETAY'!I6</f>
-        <v>6.06</v>
+        <v>2.0999999999999996</v>
       </c>
       <c r="G10" s="178"/>
       <c r="H10" s="178"/>
@@ -9410,7 +9413,7 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" si="1"/>
-        <v>8.4649999999999999</v>
+        <v>0</v>
       </c>
       <c r="F21" s="145">
         <f>'STOK DETAY'!X6</f>
@@ -9422,7 +9425,7 @@
       </c>
       <c r="H21" s="146">
         <f>'STOK DETAY'!Z6</f>
-        <v>8.4649999999999999</v>
+        <v>0</v>
       </c>
       <c r="I21" s="146"/>
       <c r="J21" s="146"/>
@@ -9456,7 +9459,7 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="1"/>
-        <v>8.4400000000000013</v>
+        <v>0</v>
       </c>
       <c r="F22" s="145">
         <f>'STOK DETAY'!AA6</f>
@@ -9468,7 +9471,7 @@
       </c>
       <c r="H22" s="146">
         <f>'STOK DETAY'!AC6</f>
-        <v>8.4400000000000013</v>
+        <v>0</v>
       </c>
       <c r="I22" s="146"/>
       <c r="J22" s="146"/>
@@ -9502,7 +9505,7 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="1"/>
-        <v>8.4550000000000001</v>
+        <v>0</v>
       </c>
       <c r="F23" s="145">
         <f>'STOK DETAY'!AD6</f>
@@ -9514,7 +9517,7 @@
       </c>
       <c r="H23" s="146">
         <f>'STOK DETAY'!AF6</f>
-        <v>8.4550000000000001</v>
+        <v>0</v>
       </c>
       <c r="I23" s="146"/>
       <c r="J23" s="146"/>
@@ -9548,7 +9551,7 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="1"/>
-        <v>8.6300000000000061</v>
+        <v>0</v>
       </c>
       <c r="F24" s="145">
         <f>'STOK DETAY'!AG6</f>
@@ -9556,7 +9559,7 @@
       </c>
       <c r="G24" s="146">
         <f>'STOK DETAY'!AH6</f>
-        <v>8.6300000000000061</v>
+        <v>0</v>
       </c>
       <c r="H24" s="146">
         <f>'STOK DETAY'!AI6</f>
@@ -9594,7 +9597,7 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="1"/>
-        <v>8.350000000000005</v>
+        <v>0</v>
       </c>
       <c r="F25" s="194">
         <f>'STOK DETAY'!AJ6</f>
@@ -9602,7 +9605,7 @@
       </c>
       <c r="G25" s="146">
         <f>'STOK DETAY'!AK6</f>
-        <v>8.350000000000005</v>
+        <v>0</v>
       </c>
       <c r="H25" s="146">
         <f>'STOK DETAY'!AL6</f>
@@ -9640,15 +9643,15 @@
       </c>
       <c r="E26" s="125">
         <f t="shared" si="1"/>
-        <v>17.159999999999997</v>
+        <v>48.69</v>
       </c>
       <c r="F26" s="145">
         <f>'STOK DETAY'!AM6</f>
-        <v>0</v>
+        <v>48.69</v>
       </c>
       <c r="G26" s="146">
         <f>'STOK DETAY'!AN6</f>
-        <v>17.159999999999997</v>
+        <v>0</v>
       </c>
       <c r="H26" s="146">
         <f>'STOK DETAY'!AO6</f>
@@ -9686,7 +9689,7 @@
       </c>
       <c r="E27" s="125">
         <f t="shared" si="1"/>
-        <v>8.9250000000000007</v>
+        <v>0</v>
       </c>
       <c r="F27" s="145">
         <f>'STOK DETAY'!AP6</f>
@@ -9694,7 +9697,7 @@
       </c>
       <c r="G27" s="146">
         <f>'STOK DETAY'!AQ6</f>
-        <v>8.9250000000000007</v>
+        <v>0</v>
       </c>
       <c r="H27" s="146">
         <f>'STOK DETAY'!AR6</f>
@@ -9732,7 +9735,7 @@
       </c>
       <c r="E28" s="125">
         <f t="shared" si="1"/>
-        <v>16.895000000000007</v>
+        <v>0</v>
       </c>
       <c r="F28" s="145">
         <f>'STOK DETAY'!AS6</f>
@@ -9744,7 +9747,7 @@
       </c>
       <c r="H28" s="146">
         <f>'STOK DETAY'!AU6</f>
-        <v>16.895000000000007</v>
+        <v>0</v>
       </c>
       <c r="I28" s="146"/>
       <c r="J28" s="146"/>
@@ -9778,7 +9781,7 @@
       </c>
       <c r="E29" s="125">
         <f t="shared" si="1"/>
-        <v>25.679999999999989</v>
+        <v>0</v>
       </c>
       <c r="F29" s="145">
         <f>'STOK DETAY'!AV6</f>
@@ -9790,7 +9793,7 @@
       </c>
       <c r="H29" s="146">
         <f>'STOK DETAY'!AX6</f>
-        <v>25.679999999999989</v>
+        <v>0</v>
       </c>
       <c r="I29" s="146"/>
       <c r="J29" s="146"/>
@@ -9824,7 +9827,7 @@
       </c>
       <c r="E30" s="125">
         <f t="shared" si="1"/>
-        <v>16.680000000000007</v>
+        <v>8.3200000000000074</v>
       </c>
       <c r="F30" s="145">
         <f>'STOK DETAY'!AY6</f>
@@ -9832,7 +9835,7 @@
       </c>
       <c r="G30" s="146">
         <f>'STOK DETAY'!AZ6</f>
-        <v>16.68</v>
+        <v>8.32</v>
       </c>
       <c r="H30" s="146">
         <f>'STOK DETAY'!BA6</f>
@@ -10383,7 +10386,7 @@
         <v>1.85</v>
       </c>
       <c r="B43" s="148" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C43" s="143" t="s">
         <v>14</v>
@@ -10730,27 +10733,27 @@
       <c r="X51" s="74"/>
     </row>
     <row r="52" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="339" t="s">
+      <c r="A52" s="354" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="340"/>
-      <c r="C52" s="340"/>
-      <c r="D52" s="341"/>
+      <c r="B52" s="355"/>
+      <c r="C52" s="355"/>
+      <c r="D52" s="356"/>
       <c r="E52" s="135">
         <f t="shared" si="1"/>
-        <v>923.0150000000001</v>
+        <v>848.38499999999999</v>
       </c>
       <c r="F52" s="136">
         <f t="shared" ref="F52:K52" si="2">SUM(F9:F51)</f>
-        <v>307.86</v>
+        <v>352.59000000000003</v>
       </c>
       <c r="G52" s="137">
         <f t="shared" si="2"/>
-        <v>107.04000000000002</v>
+        <v>55.615000000000002</v>
       </c>
       <c r="H52" s="137">
         <f>SUM(H9:H51)</f>
-        <v>144.785</v>
+        <v>76.849999999999994</v>
       </c>
       <c r="I52" s="137">
         <f t="shared" si="2"/>
@@ -10779,11 +10782,11 @@
       <c r="X52" s="65"/>
     </row>
     <row r="53" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="342" t="s">
+      <c r="A53" s="357" t="s">
         <v>12</v>
       </c>
-      <c r="B53" s="343"/>
-      <c r="C53" s="344"/>
+      <c r="B53" s="358"/>
+      <c r="C53" s="359"/>
       <c r="D53" s="112" t="s">
         <v>27</v>
       </c>
@@ -10953,11 +10956,11 @@
       </c>
       <c r="E57" s="125">
         <f t="shared" si="3"/>
-        <v>24.160000000000004</v>
+        <v>0</v>
       </c>
       <c r="F57" s="145">
         <f>'STOK DETAY'!CP6</f>
-        <v>24.160000000000004</v>
+        <v>0</v>
       </c>
       <c r="G57" s="146">
         <f>'STOK DETAY'!CQ6</f>
@@ -11464,19 +11467,19 @@
       <c r="X69" s="74"/>
     </row>
     <row r="70" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A70" s="336" t="s">
+      <c r="A70" s="351" t="s">
         <v>4</v>
       </c>
-      <c r="B70" s="337"/>
-      <c r="C70" s="337"/>
-      <c r="D70" s="338"/>
+      <c r="B70" s="352"/>
+      <c r="C70" s="352"/>
+      <c r="D70" s="353"/>
       <c r="E70" s="135">
         <f t="shared" si="3"/>
-        <v>217.083</v>
+        <v>192.923</v>
       </c>
       <c r="F70" s="136">
         <f t="shared" ref="F70:K70" si="4">SUM(F54:F69)</f>
-        <v>104.35300000000001</v>
+        <v>80.192999999999998</v>
       </c>
       <c r="G70" s="137">
         <f t="shared" si="4"/>
@@ -11513,11 +11516,11 @@
       <c r="X70" s="65"/>
     </row>
     <row r="71" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A71" s="342" t="s">
+      <c r="A71" s="357" t="s">
         <v>10</v>
       </c>
-      <c r="B71" s="343"/>
-      <c r="C71" s="345"/>
+      <c r="B71" s="358"/>
+      <c r="C71" s="360"/>
       <c r="D71" s="152" t="s">
         <v>27</v>
       </c>
@@ -11560,8 +11563,8 @@
       <c r="A72" s="153">
         <v>0.3</v>
       </c>
-      <c r="B72" s="360"/>
-      <c r="C72" s="361"/>
+      <c r="B72" s="375"/>
+      <c r="C72" s="376"/>
       <c r="D72" s="154">
         <v>511</v>
       </c>
@@ -11596,8 +11599,8 @@
       <c r="A73" s="123">
         <v>0.5</v>
       </c>
-      <c r="B73" s="362"/>
-      <c r="C73" s="363"/>
+      <c r="B73" s="343"/>
+      <c r="C73" s="344"/>
       <c r="D73" s="154">
         <v>511</v>
       </c>
@@ -11632,8 +11635,8 @@
       <c r="A74" s="123">
         <v>0.55000000000000004</v>
       </c>
-      <c r="B74" s="362"/>
-      <c r="C74" s="363"/>
+      <c r="B74" s="343"/>
+      <c r="C74" s="344"/>
       <c r="D74" s="154">
         <v>511</v>
       </c>
@@ -11668,8 +11671,8 @@
       <c r="A75" s="123">
         <v>0.6</v>
       </c>
-      <c r="B75" s="362"/>
-      <c r="C75" s="363"/>
+      <c r="B75" s="343"/>
+      <c r="C75" s="344"/>
       <c r="D75" s="154">
         <v>101</v>
       </c>
@@ -11704,8 +11707,8 @@
       <c r="A76" s="123">
         <v>0.7</v>
       </c>
-      <c r="B76" s="362"/>
-      <c r="C76" s="363"/>
+      <c r="B76" s="343"/>
+      <c r="C76" s="344"/>
       <c r="D76" s="154">
         <v>101</v>
       </c>
@@ -11743,8 +11746,8 @@
       <c r="A77" s="123">
         <v>1</v>
       </c>
-      <c r="B77" s="362"/>
-      <c r="C77" s="363"/>
+      <c r="B77" s="343"/>
+      <c r="C77" s="344"/>
       <c r="D77" s="154">
         <v>511</v>
       </c>
@@ -11779,8 +11782,8 @@
       <c r="A78" s="123">
         <v>1.2</v>
       </c>
-      <c r="B78" s="362"/>
-      <c r="C78" s="363"/>
+      <c r="B78" s="343"/>
+      <c r="C78" s="344"/>
       <c r="D78" s="154">
         <v>511</v>
       </c>
@@ -11815,8 +11818,8 @@
       <c r="A79" s="123">
         <v>1.3</v>
       </c>
-      <c r="B79" s="362"/>
-      <c r="C79" s="363"/>
+      <c r="B79" s="343"/>
+      <c r="C79" s="344"/>
       <c r="D79" s="154">
         <v>511</v>
       </c>
@@ -11851,8 +11854,8 @@
       <c r="A80" s="123">
         <v>1.4</v>
       </c>
-      <c r="B80" s="362"/>
-      <c r="C80" s="363"/>
+      <c r="B80" s="343"/>
+      <c r="C80" s="344"/>
       <c r="D80" s="154">
         <v>511</v>
       </c>
@@ -11887,8 +11890,8 @@
       <c r="A81" s="123">
         <v>1.6</v>
       </c>
-      <c r="B81" s="362"/>
-      <c r="C81" s="363"/>
+      <c r="B81" s="343"/>
+      <c r="C81" s="344"/>
       <c r="D81" s="154">
         <v>511</v>
       </c>
@@ -11923,8 +11926,8 @@
       <c r="A82" s="123">
         <v>1.7</v>
       </c>
-      <c r="B82" s="362"/>
-      <c r="C82" s="363"/>
+      <c r="B82" s="343"/>
+      <c r="C82" s="344"/>
       <c r="D82" s="154">
         <v>511</v>
       </c>
@@ -11959,8 +11962,8 @@
       <c r="A83" s="158">
         <v>3.5</v>
       </c>
-      <c r="B83" s="346"/>
-      <c r="C83" s="347"/>
+      <c r="B83" s="361"/>
+      <c r="C83" s="362"/>
       <c r="D83" s="159">
         <v>511</v>
       </c>
@@ -11992,12 +11995,12 @@
       <c r="X83" s="74"/>
     </row>
     <row r="84" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A84" s="352" t="s">
+      <c r="A84" s="367" t="s">
         <v>4</v>
       </c>
-      <c r="B84" s="353"/>
-      <c r="C84" s="353"/>
-      <c r="D84" s="354"/>
+      <c r="B84" s="368"/>
+      <c r="C84" s="368"/>
+      <c r="D84" s="369"/>
       <c r="E84" s="135">
         <f t="shared" si="5"/>
         <v>588.67000000000007</v>
@@ -12041,27 +12044,27 @@
       <c r="X84" s="65"/>
     </row>
     <row r="85" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A85" s="333" t="s">
+      <c r="A85" s="348" t="s">
         <v>1</v>
       </c>
-      <c r="B85" s="334"/>
-      <c r="C85" s="334"/>
-      <c r="D85" s="335"/>
+      <c r="B85" s="349"/>
+      <c r="C85" s="349"/>
+      <c r="D85" s="350"/>
       <c r="E85" s="161">
         <f t="shared" si="5"/>
-        <v>1779.0829999999996</v>
+        <v>1680.2930000000001</v>
       </c>
       <c r="F85" s="162">
         <f t="shared" ref="F85:K85" si="7">F7+F52+F70+F84</f>
-        <v>412.21300000000002</v>
+        <v>432.78300000000002</v>
       </c>
       <c r="G85" s="163">
         <f t="shared" si="7"/>
-        <v>575.11500000000001</v>
+        <v>523.69000000000005</v>
       </c>
       <c r="H85" s="163">
         <f>H7+H52+H70+H84</f>
-        <v>329.01499999999999</v>
+        <v>261.08000000000004</v>
       </c>
       <c r="I85" s="163">
         <f t="shared" si="7"/>
@@ -30114,16 +30117,6 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="26">
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A85:D85"/>
     <mergeCell ref="A70:D70"/>
@@ -30140,6 +30133,16 @@
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
   </mergeCells>
   <conditionalFormatting sqref="F72:K83 F9:K69 F3:K6">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -30165,8 +30168,7 @@
     <col min="1" max="1" width="22.7109375" style="50" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" style="19" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" style="22" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="230" customWidth="1"/>
-    <col min="5" max="6" width="12.7109375" style="174" customWidth="1"/>
+    <col min="4" max="6" width="12.7109375" style="174" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" style="230" customWidth="1"/>
     <col min="8" max="10" width="12.7109375" style="45" customWidth="1"/>
     <col min="11" max="12" width="12.7109375" style="237" customWidth="1"/>
@@ -30177,41 +30179,41 @@
     <col min="18" max="18" width="12.7109375" style="237" customWidth="1"/>
     <col min="19" max="19" width="12.7109375" style="72" customWidth="1"/>
     <col min="20" max="20" width="12.7109375" style="45" customWidth="1"/>
-    <col min="21" max="21" width="12.7109375" style="107" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="237" customWidth="1"/>
     <col min="22" max="22" width="12.7109375" style="255" customWidth="1"/>
     <col min="23" max="23" width="12.7109375" style="305" customWidth="1"/>
     <col min="24" max="24" width="12.7109375" style="237" customWidth="1"/>
     <col min="25" max="25" width="12.7109375" style="255" customWidth="1"/>
-    <col min="26" max="26" width="12.7109375" style="299" customWidth="1"/>
+    <col min="26" max="26" width="12.7109375" style="305" customWidth="1"/>
     <col min="27" max="27" width="12.7109375" style="237" customWidth="1"/>
     <col min="28" max="28" width="12.7109375" style="255" customWidth="1"/>
     <col min="29" max="29" width="12.7109375" style="305" customWidth="1"/>
     <col min="30" max="30" width="12.7109375" style="237" customWidth="1"/>
     <col min="31" max="31" width="12.7109375" style="255" customWidth="1"/>
-    <col min="32" max="32" width="12.7109375" style="299" customWidth="1"/>
+    <col min="32" max="32" width="12.7109375" style="305" customWidth="1"/>
     <col min="33" max="33" width="12.7109375" style="237" customWidth="1"/>
-    <col min="34" max="34" width="12.7109375" style="371" customWidth="1"/>
+    <col min="34" max="34" width="12.7109375" style="255" customWidth="1"/>
     <col min="35" max="35" width="12.7109375" style="305" customWidth="1"/>
     <col min="36" max="36" width="12.7109375" style="237" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="371" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="255" customWidth="1"/>
     <col min="38" max="38" width="12.7109375" style="305" customWidth="1"/>
-    <col min="39" max="39" width="12.7109375" style="237" customWidth="1"/>
-    <col min="40" max="40" width="12.7109375" style="371" customWidth="1"/>
+    <col min="39" max="39" width="12.7109375" style="107" customWidth="1"/>
+    <col min="40" max="40" width="12.7109375" style="255" customWidth="1"/>
     <col min="41" max="41" width="12.7109375" style="305" customWidth="1"/>
     <col min="42" max="42" width="12.7109375" style="237" customWidth="1"/>
-    <col min="43" max="43" width="12.7109375" style="371" customWidth="1"/>
+    <col min="43" max="43" width="12.7109375" style="255" customWidth="1"/>
     <col min="44" max="44" width="12.7109375" style="305" customWidth="1"/>
     <col min="45" max="45" width="12.7109375" style="237" customWidth="1"/>
     <col min="46" max="46" width="12.7109375" style="255" customWidth="1"/>
-    <col min="47" max="47" width="12.7109375" style="299" customWidth="1"/>
+    <col min="47" max="47" width="12.7109375" style="305" customWidth="1"/>
     <col min="48" max="48" width="12.7109375" style="237" customWidth="1"/>
     <col min="49" max="49" width="12.7109375" style="255" customWidth="1"/>
-    <col min="50" max="50" width="12.7109375" style="299" customWidth="1"/>
+    <col min="50" max="50" width="12.7109375" style="305" customWidth="1"/>
     <col min="51" max="51" width="12.7109375" style="237" customWidth="1"/>
-    <col min="52" max="52" width="12.7109375" style="371" customWidth="1"/>
+    <col min="52" max="52" width="12.7109375" style="323" customWidth="1"/>
     <col min="53" max="53" width="12.7109375" style="305" customWidth="1"/>
     <col min="54" max="54" width="12.7109375" style="237" customWidth="1"/>
-    <col min="55" max="55" width="12.7109375" style="371" customWidth="1"/>
+    <col min="55" max="55" width="12.7109375" style="323" customWidth="1"/>
     <col min="56" max="56" width="12.7109375" style="305" customWidth="1"/>
     <col min="57" max="57" width="12.7109375" style="237" customWidth="1"/>
     <col min="58" max="58" width="12.7109375" style="255" customWidth="1"/>
@@ -30235,7 +30237,7 @@
     <col min="76" max="76" width="12.7109375" style="63" customWidth="1"/>
     <col min="77" max="77" width="12.7109375" style="107" customWidth="1"/>
     <col min="78" max="78" width="12.7109375" style="261" customWidth="1"/>
-    <col min="79" max="79" width="12.7109375" style="378" customWidth="1"/>
+    <col min="79" max="79" width="12.7109375" style="330" customWidth="1"/>
     <col min="80" max="80" width="12.7109375" style="69" customWidth="1"/>
     <col min="81" max="81" width="12.7109375" style="237" customWidth="1"/>
     <col min="82" max="82" width="12.7109375" style="69" customWidth="1"/>
@@ -30277,14 +30279,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:124" s="19" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="364" t="s">
+      <c r="A1" s="377" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="364"/>
+      <c r="B1" s="377"/>
       <c r="C1" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="225" t="s">
+      <c r="D1" s="171" t="s">
         <v>17</v>
       </c>
       <c r="E1" s="171" t="s">
@@ -30335,7 +30337,7 @@
       <c r="T1" s="193" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="190" t="s">
+      <c r="U1" s="231" t="s">
         <v>16</v>
       </c>
       <c r="V1" s="307" t="s">
@@ -30350,7 +30352,7 @@
       <c r="Y1" s="250" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="294" t="s">
+      <c r="Z1" s="300" t="s">
         <v>3</v>
       </c>
       <c r="AA1" s="231" t="s">
@@ -30368,13 +30370,13 @@
       <c r="AE1" s="250" t="s">
         <v>17</v>
       </c>
-      <c r="AF1" s="294" t="s">
+      <c r="AF1" s="300" t="s">
         <v>3</v>
       </c>
       <c r="AG1" s="231" t="s">
         <v>16</v>
       </c>
-      <c r="AH1" s="366" t="s">
+      <c r="AH1" s="250" t="s">
         <v>17</v>
       </c>
       <c r="AI1" s="300" t="s">
@@ -30383,16 +30385,16 @@
       <c r="AJ1" s="231" t="s">
         <v>16</v>
       </c>
-      <c r="AK1" s="366" t="s">
+      <c r="AK1" s="250" t="s">
         <v>17</v>
       </c>
       <c r="AL1" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="AM1" s="231" t="s">
+      <c r="AM1" s="190" t="s">
         <v>16</v>
       </c>
-      <c r="AN1" s="366" t="s">
+      <c r="AN1" s="250" t="s">
         <v>17</v>
       </c>
       <c r="AO1" s="300" t="s">
@@ -30401,7 +30403,7 @@
       <c r="AP1" s="231" t="s">
         <v>16</v>
       </c>
-      <c r="AQ1" s="366" t="s">
+      <c r="AQ1" s="250" t="s">
         <v>17</v>
       </c>
       <c r="AR1" s="300" t="s">
@@ -30413,7 +30415,7 @@
       <c r="AT1" s="250" t="s">
         <v>17</v>
       </c>
-      <c r="AU1" s="294" t="s">
+      <c r="AU1" s="300" t="s">
         <v>3</v>
       </c>
       <c r="AV1" s="231" t="s">
@@ -30422,13 +30424,13 @@
       <c r="AW1" s="250" t="s">
         <v>17</v>
       </c>
-      <c r="AX1" s="294" t="s">
+      <c r="AX1" s="300" t="s">
         <v>3</v>
       </c>
       <c r="AY1" s="231" t="s">
         <v>16</v>
       </c>
-      <c r="AZ1" s="366" t="s">
+      <c r="AZ1" s="318" t="s">
         <v>17</v>
       </c>
       <c r="BA1" s="310" t="s">
@@ -30437,7 +30439,7 @@
       <c r="BB1" s="231" t="s">
         <v>16</v>
       </c>
-      <c r="BC1" s="366" t="s">
+      <c r="BC1" s="318" t="s">
         <v>17</v>
       </c>
       <c r="BD1" s="300" t="s">
@@ -30509,7 +30511,7 @@
       <c r="BZ1" s="256" t="s">
         <v>6</v>
       </c>
-      <c r="CA1" s="372" t="s">
+      <c r="CA1" s="324" t="s">
         <v>6</v>
       </c>
       <c r="CB1" s="70" t="s">
@@ -30649,12 +30651,12 @@
       </c>
     </row>
     <row r="2" spans="1:124" s="19" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="364"/>
-      <c r="B2" s="364"/>
+      <c r="A2" s="377"/>
+      <c r="B2" s="377"/>
       <c r="C2" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="225" t="s">
+      <c r="D2" s="171" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="171" t="s">
@@ -30705,7 +30707,7 @@
       <c r="T2" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="190" t="s">
+      <c r="U2" s="231" t="s">
         <v>7</v>
       </c>
       <c r="V2" s="307" t="s">
@@ -30720,7 +30722,7 @@
       <c r="Y2" s="250" t="s">
         <v>7</v>
       </c>
-      <c r="Z2" s="294" t="s">
+      <c r="Z2" s="300" t="s">
         <v>7</v>
       </c>
       <c r="AA2" s="231" t="s">
@@ -30738,13 +30740,13 @@
       <c r="AE2" s="250" t="s">
         <v>7</v>
       </c>
-      <c r="AF2" s="294" t="s">
+      <c r="AF2" s="300" t="s">
         <v>7</v>
       </c>
       <c r="AG2" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="AH2" s="366" t="s">
+      <c r="AH2" s="250" t="s">
         <v>7</v>
       </c>
       <c r="AI2" s="300" t="s">
@@ -30753,16 +30755,16 @@
       <c r="AJ2" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="AK2" s="366" t="s">
+      <c r="AK2" s="250" t="s">
         <v>7</v>
       </c>
       <c r="AL2" s="300" t="s">
         <v>7</v>
       </c>
-      <c r="AM2" s="231" t="s">
+      <c r="AM2" s="190" t="s">
         <v>7</v>
       </c>
-      <c r="AN2" s="366" t="s">
+      <c r="AN2" s="250" t="s">
         <v>7</v>
       </c>
       <c r="AO2" s="300" t="s">
@@ -30771,7 +30773,7 @@
       <c r="AP2" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="AQ2" s="366" t="s">
+      <c r="AQ2" s="250" t="s">
         <v>7</v>
       </c>
       <c r="AR2" s="300" t="s">
@@ -30783,7 +30785,7 @@
       <c r="AT2" s="250" t="s">
         <v>7</v>
       </c>
-      <c r="AU2" s="294" t="s">
+      <c r="AU2" s="300" t="s">
         <v>7</v>
       </c>
       <c r="AV2" s="231" t="s">
@@ -30792,13 +30794,13 @@
       <c r="AW2" s="250" t="s">
         <v>7</v>
       </c>
-      <c r="AX2" s="294" t="s">
+      <c r="AX2" s="300" t="s">
         <v>7</v>
       </c>
       <c r="AY2" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="AZ2" s="366" t="s">
+      <c r="AZ2" s="318" t="s">
         <v>7</v>
       </c>
       <c r="BA2" s="310" t="s">
@@ -30807,7 +30809,7 @@
       <c r="BB2" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="BC2" s="366" t="s">
+      <c r="BC2" s="318" t="s">
         <v>7</v>
       </c>
       <c r="BD2" s="300" t="s">
@@ -30879,7 +30881,7 @@
       <c r="BZ2" s="256" t="s">
         <v>7</v>
       </c>
-      <c r="CA2" s="373" t="s">
+      <c r="CA2" s="325" t="s">
         <v>7</v>
       </c>
       <c r="CB2" s="70" t="s">
@@ -31019,12 +31021,12 @@
       </c>
     </row>
     <row r="3" spans="1:124" s="19" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="364"/>
-      <c r="B3" s="364"/>
+      <c r="A3" s="377"/>
+      <c r="B3" s="377"/>
       <c r="C3" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="225" t="s">
+      <c r="D3" s="171" t="s">
         <v>18</v>
       </c>
       <c r="E3" s="171" t="s">
@@ -31075,7 +31077,7 @@
       <c r="T3" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="U3" s="190" t="s">
+      <c r="U3" s="231" t="s">
         <v>14</v>
       </c>
       <c r="V3" s="307" t="s">
@@ -31090,7 +31092,7 @@
       <c r="Y3" s="250" t="s">
         <v>14</v>
       </c>
-      <c r="Z3" s="294" t="s">
+      <c r="Z3" s="300" t="s">
         <v>14</v>
       </c>
       <c r="AA3" s="231" t="s">
@@ -31108,13 +31110,13 @@
       <c r="AE3" s="250" t="s">
         <v>14</v>
       </c>
-      <c r="AF3" s="294" t="s">
+      <c r="AF3" s="300" t="s">
         <v>14</v>
       </c>
       <c r="AG3" s="231" t="s">
         <v>14</v>
       </c>
-      <c r="AH3" s="366" t="s">
+      <c r="AH3" s="250" t="s">
         <v>14</v>
       </c>
       <c r="AI3" s="300" t="s">
@@ -31123,16 +31125,16 @@
       <c r="AJ3" s="231" t="s">
         <v>14</v>
       </c>
-      <c r="AK3" s="366" t="s">
+      <c r="AK3" s="250" t="s">
         <v>14</v>
       </c>
       <c r="AL3" s="300" t="s">
         <v>14</v>
       </c>
-      <c r="AM3" s="231" t="s">
+      <c r="AM3" s="190" t="s">
         <v>14</v>
       </c>
-      <c r="AN3" s="366" t="s">
+      <c r="AN3" s="250" t="s">
         <v>14</v>
       </c>
       <c r="AO3" s="300" t="s">
@@ -31141,7 +31143,7 @@
       <c r="AP3" s="231" t="s">
         <v>14</v>
       </c>
-      <c r="AQ3" s="366" t="s">
+      <c r="AQ3" s="250" t="s">
         <v>14</v>
       </c>
       <c r="AR3" s="300" t="s">
@@ -31153,7 +31155,7 @@
       <c r="AT3" s="250" t="s">
         <v>14</v>
       </c>
-      <c r="AU3" s="294" t="s">
+      <c r="AU3" s="300" t="s">
         <v>14</v>
       </c>
       <c r="AV3" s="231" t="s">
@@ -31162,13 +31164,13 @@
       <c r="AW3" s="250" t="s">
         <v>14</v>
       </c>
-      <c r="AX3" s="294" t="s">
+      <c r="AX3" s="300" t="s">
         <v>14</v>
       </c>
       <c r="AY3" s="231" t="s">
         <v>14</v>
       </c>
-      <c r="AZ3" s="366" t="s">
+      <c r="AZ3" s="318" t="s">
         <v>14</v>
       </c>
       <c r="BA3" s="310" t="s">
@@ -31177,7 +31179,7 @@
       <c r="BB3" s="231" t="s">
         <v>14</v>
       </c>
-      <c r="BC3" s="366" t="s">
+      <c r="BC3" s="318" t="s">
         <v>14</v>
       </c>
       <c r="BD3" s="300" t="s">
@@ -31249,7 +31251,7 @@
       <c r="BZ3" s="256" t="s">
         <v>14</v>
       </c>
-      <c r="CA3" s="373" t="s">
+      <c r="CA3" s="325" t="s">
         <v>14</v>
       </c>
       <c r="CB3" s="70" t="s">
@@ -31389,12 +31391,12 @@
       </c>
     </row>
     <row r="4" spans="1:124" s="20" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="364"/>
-      <c r="B4" s="364"/>
+      <c r="A4" s="377"/>
+      <c r="B4" s="377"/>
       <c r="C4" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="226">
+      <c r="D4" s="172">
         <v>0.4</v>
       </c>
       <c r="E4" s="172">
@@ -31445,7 +31447,7 @@
       <c r="T4" s="192">
         <v>0.47499999999999998</v>
       </c>
-      <c r="U4" s="104">
+      <c r="U4" s="233">
         <v>0.5</v>
       </c>
       <c r="V4" s="251">
@@ -31460,7 +31462,7 @@
       <c r="Y4" s="251">
         <v>0.55000000000000004</v>
       </c>
-      <c r="Z4" s="295">
+      <c r="Z4" s="301">
         <v>0.55000000000000004</v>
       </c>
       <c r="AA4" s="233">
@@ -31478,13 +31480,13 @@
       <c r="AE4" s="251">
         <v>0.65</v>
       </c>
-      <c r="AF4" s="295">
+      <c r="AF4" s="301">
         <v>0.65</v>
       </c>
       <c r="AG4" s="233">
         <v>0.7</v>
       </c>
-      <c r="AH4" s="367">
+      <c r="AH4" s="251">
         <v>0.7</v>
       </c>
       <c r="AI4" s="301">
@@ -31493,16 +31495,16 @@
       <c r="AJ4" s="233">
         <v>0.75</v>
       </c>
-      <c r="AK4" s="367">
+      <c r="AK4" s="251">
         <v>0.75</v>
       </c>
       <c r="AL4" s="301">
         <v>0.75</v>
       </c>
-      <c r="AM4" s="233">
+      <c r="AM4" s="104">
         <v>0.8</v>
       </c>
-      <c r="AN4" s="367">
+      <c r="AN4" s="251">
         <v>0.8</v>
       </c>
       <c r="AO4" s="301">
@@ -31511,7 +31513,7 @@
       <c r="AP4" s="233">
         <v>0.85</v>
       </c>
-      <c r="AQ4" s="367">
+      <c r="AQ4" s="251">
         <v>0.85</v>
       </c>
       <c r="AR4" s="301">
@@ -31523,7 +31525,7 @@
       <c r="AT4" s="251">
         <v>0.9</v>
       </c>
-      <c r="AU4" s="295">
+      <c r="AU4" s="301">
         <v>0.9</v>
       </c>
       <c r="AV4" s="233">
@@ -31532,13 +31534,13 @@
       <c r="AW4" s="251">
         <v>0.95</v>
       </c>
-      <c r="AX4" s="295">
+      <c r="AX4" s="301">
         <v>0.95</v>
       </c>
       <c r="AY4" s="233">
         <v>1</v>
       </c>
-      <c r="AZ4" s="367">
+      <c r="AZ4" s="319">
         <v>1</v>
       </c>
       <c r="BA4" s="301">
@@ -31547,7 +31549,7 @@
       <c r="BB4" s="233">
         <v>1.05</v>
       </c>
-      <c r="BC4" s="367">
+      <c r="BC4" s="319">
         <v>1.05</v>
       </c>
       <c r="BD4" s="301">
@@ -31619,7 +31621,7 @@
       <c r="BZ4" s="257">
         <v>1.45</v>
       </c>
-      <c r="CA4" s="374">
+      <c r="CA4" s="326">
         <v>1.5</v>
       </c>
       <c r="CB4" s="67">
@@ -31759,10 +31761,10 @@
       </c>
     </row>
     <row r="5" spans="1:124" ht="6.75" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A5" s="364"/>
-      <c r="B5" s="364"/>
+      <c r="A5" s="377"/>
+      <c r="B5" s="377"/>
       <c r="C5" s="48"/>
-      <c r="D5" s="243"/>
+      <c r="D5" s="58"/>
       <c r="E5" s="317"/>
       <c r="F5" s="317"/>
       <c r="G5" s="227"/>
@@ -31779,41 +31781,41 @@
       <c r="R5" s="234"/>
       <c r="S5" s="58"/>
       <c r="T5" s="43"/>
-      <c r="U5" s="105"/>
+      <c r="U5" s="234"/>
       <c r="V5" s="252"/>
       <c r="W5" s="302"/>
       <c r="X5" s="234"/>
       <c r="Y5" s="252"/>
-      <c r="Z5" s="296"/>
+      <c r="Z5" s="302"/>
       <c r="AA5" s="234"/>
       <c r="AB5" s="252"/>
       <c r="AC5" s="302"/>
       <c r="AD5" s="234"/>
       <c r="AE5" s="252"/>
-      <c r="AF5" s="296"/>
+      <c r="AF5" s="302"/>
       <c r="AG5" s="234"/>
-      <c r="AH5" s="368"/>
+      <c r="AH5" s="252"/>
       <c r="AI5" s="302"/>
       <c r="AJ5" s="234"/>
-      <c r="AK5" s="368"/>
+      <c r="AK5" s="252"/>
       <c r="AL5" s="302"/>
-      <c r="AM5" s="234"/>
-      <c r="AN5" s="368"/>
+      <c r="AM5" s="105"/>
+      <c r="AN5" s="252"/>
       <c r="AO5" s="302"/>
       <c r="AP5" s="234"/>
-      <c r="AQ5" s="368"/>
+      <c r="AQ5" s="252"/>
       <c r="AR5" s="302"/>
       <c r="AS5" s="234"/>
       <c r="AT5" s="252"/>
-      <c r="AU5" s="296"/>
+      <c r="AU5" s="302"/>
       <c r="AV5" s="234"/>
       <c r="AW5" s="252"/>
-      <c r="AX5" s="296"/>
+      <c r="AX5" s="302"/>
       <c r="AY5" s="234"/>
-      <c r="AZ5" s="368"/>
+      <c r="AZ5" s="320"/>
       <c r="BA5" s="302"/>
       <c r="BB5" s="234"/>
-      <c r="BC5" s="368"/>
+      <c r="BC5" s="320"/>
       <c r="BD5" s="302"/>
       <c r="BE5" s="234"/>
       <c r="BF5" s="252"/>
@@ -31837,7 +31839,7 @@
       <c r="BX5" s="61"/>
       <c r="BY5" s="105"/>
       <c r="BZ5" s="258"/>
-      <c r="CA5" s="375"/>
+      <c r="CA5" s="327"/>
       <c r="CB5" s="68"/>
       <c r="CC5" s="234"/>
       <c r="CD5" s="68"/>
@@ -31882,490 +31884,490 @@
       </c>
       <c r="C6" s="78">
         <f>SUM(D6:DT6)</f>
-        <v>1779.0830000000001</v>
-      </c>
-      <c r="D6" s="228">
-        <f>SUM(D8:D1048576)</f>
+        <v>1680.2930000000001</v>
+      </c>
+      <c r="D6" s="79">
+        <f t="shared" ref="D6:AI6" si="0">SUM(D8:D1048576)</f>
         <v>8.7850000000000001</v>
       </c>
       <c r="E6" s="79">
-        <f>SUM(E8:E1048576)</f>
+        <f t="shared" si="0"/>
         <v>8.39</v>
       </c>
       <c r="F6" s="79">
-        <f>SUM(F8:F1048576)</f>
+        <f t="shared" si="0"/>
         <v>33.14</v>
       </c>
       <c r="G6" s="228">
-        <f>SUM(G8:G1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H6" s="80">
-        <f>SUM(H8:H1048576)</f>
+        <f t="shared" si="0"/>
         <v>92.75</v>
       </c>
       <c r="I6" s="80">
-        <f>SUM(I8:I1048576)</f>
-        <v>6.06</v>
+        <f t="shared" si="0"/>
+        <v>2.0999999999999996</v>
       </c>
       <c r="J6" s="80">
-        <f>SUM(J8:J1048576)</f>
+        <f t="shared" si="0"/>
         <v>32.06</v>
       </c>
       <c r="K6" s="235">
-        <f>SUM(K8:K1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L6" s="235">
-        <f>SUM(L8:L1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M6" s="80">
-        <f>SUM(M8:M1048576)</f>
+        <f t="shared" si="0"/>
         <v>89.04</v>
       </c>
       <c r="N6" s="80">
-        <f>SUM(N8:N1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O6" s="265">
-        <f>SUM(O8:O1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P6" s="235">
-        <f>SUM(P8:P1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q6" s="303">
-        <f>SUM(Q8:Q1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R6" s="235">
-        <f>SUM(R8:R1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S6" s="79">
-        <f>SUM(S8:S1048576)</f>
+        <f t="shared" si="0"/>
         <v>5.8900000000000006</v>
       </c>
       <c r="T6" s="80">
-        <f>SUM(T8:T1048576)</f>
+        <f t="shared" si="0"/>
         <v>24.22</v>
       </c>
-      <c r="U6" s="191">
-        <f>SUM(U8:U1048576)</f>
+      <c r="U6" s="235">
+        <f t="shared" si="0"/>
         <v>7.9936057773011271E-15</v>
       </c>
       <c r="V6" s="253">
-        <f>SUM(V8:V1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W6" s="303">
-        <f>SUM(W8:W1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X6" s="235">
-        <f>SUM(X8:X1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y6" s="253">
-        <f>SUM(Y8:Y1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Z6" s="297">
-        <f>SUM(Z8:Z1048576)</f>
-        <v>8.4649999999999999</v>
+      <c r="Z6" s="303">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="AA6" s="235">
-        <f>SUM(AA8:AA1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB6" s="253">
-        <f>SUM(AB8:AB1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC6" s="303">
-        <f>SUM(AC8:AC1048576)</f>
-        <v>8.4400000000000013</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="AD6" s="235">
-        <f>SUM(AD8:AD1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE6" s="253">
-        <f>SUM(AE8:AE1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AF6" s="297">
-        <f>SUM(AF8:AF1048576)</f>
-        <v>8.4550000000000001</v>
+      <c r="AF6" s="303">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="AG6" s="235">
-        <f>SUM(AG8:AG1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH6" s="369">
-        <f>SUM(AH8:AH1048576)</f>
-        <v>8.6300000000000061</v>
+      <c r="AH6" s="253">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="AI6" s="303">
-        <f>SUM(AI8:AI1048576)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AJ6" s="235">
-        <f>SUM(AJ8:AJ1048576)</f>
+        <f t="shared" ref="AJ6:BO6" si="1">SUM(AJ8:AJ1048576)</f>
         <v>0</v>
       </c>
-      <c r="AK6" s="369">
-        <f>SUM(AK8:AK1048576)</f>
-        <v>8.350000000000005</v>
+      <c r="AK6" s="253">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="AL6" s="303">
-        <f>SUM(AL8:AL1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AM6" s="235">
-        <f>SUM(AM8:AM1048576)</f>
+      <c r="AM6" s="191">
+        <f t="shared" si="1"/>
+        <v>48.69</v>
+      </c>
+      <c r="AN6" s="253">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN6" s="369">
-        <f>SUM(AN8:AN1048576)</f>
-        <v>17.159999999999997</v>
-      </c>
       <c r="AO6" s="303">
-        <f>SUM(AO8:AO1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AP6" s="235">
-        <f>SUM(AP8:AP1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AQ6" s="369">
-        <f>SUM(AQ8:AQ1048576)</f>
-        <v>8.9250000000000007</v>
+      <c r="AQ6" s="253">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="AR6" s="303">
-        <f>SUM(AR8:AR1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AS6" s="235">
-        <f>SUM(AS8:AS1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AT6" s="253">
-        <f>SUM(AT8:AT1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AU6" s="297">
-        <f>SUM(AU8:AU1048576)</f>
-        <v>16.895000000000007</v>
+      <c r="AU6" s="303">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="AV6" s="235">
-        <f>SUM(AV8:AV1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AW6" s="253">
-        <f>SUM(AW8:AW1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AX6" s="297">
-        <f>SUM(AX8:AX1048576)</f>
-        <v>25.679999999999989</v>
+      <c r="AX6" s="303">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="AY6" s="235">
-        <f>SUM(AY8:AY1048576)</f>
+        <f t="shared" si="1"/>
         <v>7.1054273576010019E-15</v>
       </c>
-      <c r="AZ6" s="369">
-        <f>SUM(AZ8:AZ1048576)</f>
-        <v>16.68</v>
+      <c r="AZ6" s="321">
+        <f t="shared" si="1"/>
+        <v>8.32</v>
       </c>
       <c r="BA6" s="303">
-        <f>SUM(BA8:BA1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="BB6" s="235">
-        <f>SUM(BB8:BB1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BC6" s="369">
-        <f>SUM(BC8:BC1048576)</f>
+      <c r="BC6" s="321">
+        <f t="shared" si="1"/>
         <v>33.25</v>
       </c>
       <c r="BD6" s="303">
-        <f>SUM(BD8:BD1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="BE6" s="235">
-        <f>SUM(BE8:BE1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="BF6" s="253">
-        <f>SUM(BF8:BF1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="BG6" s="297">
-        <f>SUM(BG8:BG1048576)</f>
+        <f t="shared" si="1"/>
         <v>8.6549999999999994</v>
       </c>
       <c r="BH6" s="244">
-        <f>SUM(BH8:BH1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="BI6" s="253">
-        <f>SUM(BI8:BI1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="BJ6" s="314">
-        <f>SUM(BJ8:BJ1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="BK6" s="235">
-        <f>SUM(BK8:BK1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="BL6" s="253">
-        <f>SUM(BL8:BL1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="BM6" s="168">
-        <f>SUM(BM8:BM1048576)</f>
+        <f t="shared" si="1"/>
         <v>16.925000000000001</v>
       </c>
       <c r="BN6" s="235">
-        <f>SUM(BN8:BN1048576)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="BO6" s="253">
-        <f>SUM(BO8:BO1048576)</f>
+        <f t="shared" si="1"/>
         <v>8.1550000000000011</v>
       </c>
       <c r="BP6" s="297">
-        <f>SUM(BP8:BP1048576)</f>
+        <f t="shared" ref="BP6:CU6" si="2">SUM(BP8:BP1048576)</f>
         <v>17.184999999999999</v>
       </c>
       <c r="BQ6" s="235">
-        <f>SUM(BQ8:BQ1048576)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BR6" s="253">
-        <f>SUM(BR8:BR1048576)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BS6" s="297">
-        <f>SUM(BS8:BS1048576)</f>
+        <f t="shared" si="2"/>
         <v>34.085000000000001</v>
       </c>
       <c r="BT6" s="82">
-        <f>SUM(BT8:BT1048576)</f>
+        <f t="shared" si="2"/>
         <v>47.559999999999988</v>
       </c>
       <c r="BU6" s="83">
-        <f>SUM(BU8:BU1048576)</f>
+        <f t="shared" si="2"/>
         <v>8.44</v>
       </c>
       <c r="BV6" s="108">
-        <f>SUM(BV8:BV1048576)</f>
+        <f t="shared" si="2"/>
         <v>1.75</v>
       </c>
       <c r="BW6" s="244">
-        <f>SUM(BW8:BW1048576)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="BX6" s="83">
-        <f>SUM(BX8:BX1048576)</f>
+        <f t="shared" si="2"/>
         <v>110.34</v>
       </c>
       <c r="BY6" s="191">
-        <f>SUM(BY8:BY1048576)</f>
+        <f t="shared" si="2"/>
         <v>16.170000000000002</v>
       </c>
       <c r="BZ6" s="259">
-        <f>SUM(BZ8:BZ1048576)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CA6" s="376">
-        <f>SUM(CA8:CA1048576)</f>
+      <c r="CA6" s="328">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="CB6" s="85">
-        <f>SUM(CB8:CB1048576)</f>
+        <f t="shared" si="2"/>
         <v>27.65</v>
       </c>
       <c r="CC6" s="235">
-        <f>SUM(CC8:CC1048576)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="CD6" s="85">
-        <f>SUM(CD8:CD1048576)</f>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="CE6" s="244">
-        <f>SUM(CE8:CE1048576)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="CF6" s="265">
-        <f>SUM(CF8:CF1048576)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="CG6" s="84">
-        <f>SUM(CG8:CG1048576)</f>
+        <f t="shared" si="2"/>
         <v>21.650000000000002</v>
       </c>
       <c r="CH6" s="244">
-        <f>SUM(CH8:CH1048576)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="CI6" s="84">
-        <f>SUM(CI8:CI1048576)</f>
+        <f t="shared" si="2"/>
         <v>45.4</v>
       </c>
       <c r="CJ6" s="86">
-        <f>SUM(CJ8:CJ1048576)</f>
+        <f t="shared" si="2"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="CK6" s="83">
-        <f>SUM(CK8:CK1048576)</f>
+        <f t="shared" si="2"/>
         <v>89.45</v>
       </c>
       <c r="CL6" s="205">
-        <f>SUM(CL8:CL1048576)</f>
+        <f t="shared" si="2"/>
         <v>21.45</v>
       </c>
       <c r="CM6" s="81">
-        <f>SUM(CM8:CM1048576)</f>
+        <f t="shared" si="2"/>
         <v>54.058</v>
       </c>
       <c r="CN6" s="265">
-        <f>SUM(CN8:CN1048576)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="CO6" s="271">
-        <f>SUM(CO8:CO1048576)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="CP6" s="82">
-        <f>SUM(CP8:CP1048576)</f>
-        <v>24.160000000000004</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="CQ6" s="228">
-        <f>SUM(CQ8:CQ1048576)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="CR6" s="291">
-        <f>SUM(CR8:CR1048576)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="CS6" s="235">
-        <f>SUM(CS8:CS1048576)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="CT6" s="253">
-        <f>SUM(CT8:CT1048576)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="CU6" s="277">
-        <f>SUM(CU8:CU1048576)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="CV6" s="271">
-        <f>SUM(CV8:CV1048576)</f>
+        <f t="shared" ref="CV6:DT6" si="3">SUM(CV8:CV1048576)</f>
         <v>0</v>
       </c>
       <c r="CW6" s="244">
-        <f>SUM(CW8:CW1048576)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="CX6" s="79">
-        <f>SUM(CX8:CX1048576)</f>
+        <f t="shared" si="3"/>
         <v>13.32</v>
       </c>
       <c r="CY6" s="81">
-        <f>SUM(CY8:CY1048576)</f>
+        <f t="shared" si="3"/>
         <v>8.9849999999999994</v>
       </c>
       <c r="CZ6" s="265">
-        <f>SUM(CZ8:CZ1048576)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="DA6" s="265">
-        <f>SUM(DA8:DA1048576)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="DB6" s="235">
-        <f>SUM(DB8:DB1048576)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="DC6" s="271">
-        <f>SUM(DC8:DC1048576)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="DD6" s="86">
-        <f>SUM(DD8:DD1048576)</f>
+        <f t="shared" si="3"/>
         <v>93.39</v>
       </c>
       <c r="DE6" s="80">
-        <f>SUM(DE8:DE1048576)</f>
+        <f t="shared" si="3"/>
         <v>14.9</v>
       </c>
       <c r="DF6" s="86">
-        <f>SUM(DF8:DF1048576)</f>
+        <f t="shared" si="3"/>
         <v>6.02</v>
       </c>
       <c r="DG6" s="109">
-        <f>SUM(DG8:DG1048576)</f>
+        <f t="shared" si="3"/>
         <v>2.25</v>
       </c>
       <c r="DH6" s="108">
-        <f>SUM(DH8:DH1048576)</f>
+        <f t="shared" si="3"/>
         <v>3.28</v>
       </c>
       <c r="DI6" s="99">
-        <f>SUM(DI8:DI1048576)</f>
+        <f t="shared" si="3"/>
         <v>63.54</v>
       </c>
       <c r="DJ6" s="99">
-        <f>SUM(DJ8:DJ1048576)</f>
+        <f t="shared" si="3"/>
         <v>10.45</v>
       </c>
       <c r="DK6" s="283">
-        <f>SUM(DK8:DK1048576)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="DL6" s="212">
-        <f>SUM(DL8:DL1048576)</f>
+        <f t="shared" si="3"/>
         <v>404.44</v>
       </c>
       <c r="DM6" s="277">
-        <f>SUM(DM8:DM1048576)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="DN6" s="99">
-        <f>SUM(DN8:DN1048576)</f>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="DO6" s="99">
-        <f>SUM(DO8:DO1048576)</f>
+        <f t="shared" si="3"/>
         <v>14.7</v>
       </c>
       <c r="DP6" s="99">
-        <f>SUM(DP8:DP1048576)</f>
+        <f t="shared" si="3"/>
         <v>2.85</v>
       </c>
       <c r="DQ6" s="99">
-        <f>SUM(DQ8:DQ1048576)</f>
+        <f t="shared" si="3"/>
         <v>6.83</v>
       </c>
       <c r="DR6" s="99">
-        <f>SUM(DR8:DR1048576)</f>
+        <f t="shared" si="3"/>
         <v>9.2200000000000006</v>
       </c>
       <c r="DS6" s="99">
-        <f>SUM(DS8:DS1048576)</f>
+        <f t="shared" si="3"/>
         <v>18.5</v>
       </c>
       <c r="DT6" s="99">
-        <f>SUM(DT8:DT1048576)</f>
+        <f t="shared" si="3"/>
         <v>52.36</v>
       </c>
     </row>
@@ -32373,7 +32375,7 @@
       <c r="A7" s="51"/>
       <c r="B7" s="27"/>
       <c r="C7" s="28"/>
-      <c r="D7" s="229"/>
+      <c r="D7" s="173"/>
       <c r="E7" s="173"/>
       <c r="F7" s="173"/>
       <c r="G7" s="229"/>
@@ -32390,41 +32392,41 @@
       <c r="R7" s="236"/>
       <c r="S7" s="111"/>
       <c r="T7" s="44"/>
-      <c r="U7" s="106"/>
+      <c r="U7" s="236"/>
       <c r="V7" s="254"/>
       <c r="W7" s="304"/>
       <c r="X7" s="236"/>
       <c r="Y7" s="254"/>
-      <c r="Z7" s="298"/>
+      <c r="Z7" s="304"/>
       <c r="AA7" s="236"/>
       <c r="AB7" s="254"/>
       <c r="AC7" s="304"/>
       <c r="AD7" s="236"/>
       <c r="AE7" s="254"/>
-      <c r="AF7" s="298"/>
+      <c r="AF7" s="304"/>
       <c r="AG7" s="236"/>
-      <c r="AH7" s="370"/>
+      <c r="AH7" s="254"/>
       <c r="AI7" s="304"/>
       <c r="AJ7" s="236"/>
-      <c r="AK7" s="370"/>
+      <c r="AK7" s="254"/>
       <c r="AL7" s="304"/>
-      <c r="AM7" s="236"/>
-      <c r="AN7" s="370"/>
+      <c r="AM7" s="106"/>
+      <c r="AN7" s="254"/>
       <c r="AO7" s="304"/>
       <c r="AP7" s="236"/>
-      <c r="AQ7" s="370"/>
+      <c r="AQ7" s="254"/>
       <c r="AR7" s="304"/>
       <c r="AS7" s="236"/>
       <c r="AT7" s="254"/>
-      <c r="AU7" s="298"/>
+      <c r="AU7" s="304"/>
       <c r="AV7" s="236"/>
       <c r="AW7" s="254"/>
-      <c r="AX7" s="298"/>
+      <c r="AX7" s="304"/>
       <c r="AY7" s="236"/>
-      <c r="AZ7" s="370"/>
+      <c r="AZ7" s="322"/>
       <c r="BA7" s="304"/>
       <c r="BB7" s="236"/>
-      <c r="BC7" s="370"/>
+      <c r="BC7" s="322"/>
       <c r="BD7" s="304"/>
       <c r="BE7" s="236"/>
       <c r="BF7" s="254"/>
@@ -32448,7 +32450,7 @@
       <c r="BX7" s="62"/>
       <c r="BY7" s="106"/>
       <c r="BZ7" s="260"/>
-      <c r="CA7" s="377"/>
+      <c r="CA7" s="329"/>
       <c r="CB7" s="76"/>
       <c r="CC7" s="236"/>
       <c r="CD7" s="76"/>
@@ -32503,10 +32505,10 @@
         <v>13</v>
       </c>
       <c r="C8" s="18">
-        <f t="shared" ref="C8:C79" si="0">SUM(D8:EQ8)</f>
+        <f t="shared" ref="C8:C79" si="4">SUM(D8:EQ8)</f>
         <v>2009.373</v>
       </c>
-      <c r="D8" s="230">
+      <c r="D8" s="174">
         <v>25.675000000000001</v>
       </c>
       <c r="E8" s="174">
@@ -32551,7 +32553,7 @@
       <c r="T8" s="45">
         <v>24.22</v>
       </c>
-      <c r="U8" s="107">
+      <c r="U8" s="237">
         <v>65.760000000000005</v>
       </c>
       <c r="X8" s="237">
@@ -32572,25 +32574,25 @@
       <c r="AG8" s="237">
         <v>0</v>
       </c>
-      <c r="AH8" s="371">
+      <c r="AH8" s="255">
         <v>0</v>
       </c>
       <c r="AJ8" s="237">
         <v>0</v>
       </c>
-      <c r="AK8" s="371">
+      <c r="AK8" s="255">
         <v>0</v>
       </c>
-      <c r="AM8" s="237">
+      <c r="AM8" s="107">
         <v>0</v>
       </c>
-      <c r="AN8" s="371">
+      <c r="AN8" s="255">
         <v>0</v>
       </c>
       <c r="AP8" s="237">
         <v>0</v>
       </c>
-      <c r="AQ8" s="371">
+      <c r="AQ8" s="255">
         <v>0</v>
       </c>
       <c r="AS8" s="237">
@@ -32608,13 +32610,13 @@
       <c r="AY8" s="237">
         <v>0</v>
       </c>
-      <c r="AZ8" s="371">
+      <c r="AZ8" s="323">
         <v>0</v>
       </c>
       <c r="BB8" s="237">
         <v>0</v>
       </c>
-      <c r="BC8" s="371">
+      <c r="BC8" s="323">
         <v>0</v>
       </c>
       <c r="BE8" s="237">
@@ -32671,7 +32673,7 @@
       <c r="BZ8" s="261">
         <v>0</v>
       </c>
-      <c r="CA8" s="378">
+      <c r="CA8" s="330">
         <v>0</v>
       </c>
       <c r="CB8" s="69">
@@ -32809,7 +32811,7 @@
         <v>113</v>
       </c>
       <c r="C9" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0.03</v>
       </c>
       <c r="BA9" s="305">
@@ -32824,7 +32826,7 @@
         <v>83</v>
       </c>
       <c r="C10" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-43.445</v>
       </c>
       <c r="BE10" s="237">
@@ -32842,10 +32844,10 @@
         <v>84</v>
       </c>
       <c r="C11" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-25.9</v>
       </c>
-      <c r="U11" s="107">
+      <c r="U11" s="237">
         <f>-8.475-8.58</f>
         <v>-17.055</v>
       </c>
@@ -32861,7 +32863,7 @@
         <v>85</v>
       </c>
       <c r="C12" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-16.080000000000002</v>
       </c>
       <c r="R12" s="237">
@@ -32879,7 +32881,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>993.31500000000005</v>
       </c>
       <c r="AG13" s="237">
@@ -32888,7 +32890,7 @@
       <c r="AJ13" s="237">
         <v>70.025000000000006</v>
       </c>
-      <c r="AM13" s="237">
+      <c r="AM13" s="107">
         <v>66.03</v>
       </c>
       <c r="AP13" s="237">
@@ -32928,7 +32930,7 @@
         <v>16</v>
       </c>
       <c r="C14" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>167.98</v>
       </c>
       <c r="AA14" s="237">
@@ -32950,7 +32952,7 @@
         <v>86</v>
       </c>
       <c r="C15" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-796.76</v>
       </c>
       <c r="AG15" s="237">
@@ -32959,7 +32961,7 @@
       <c r="AJ15" s="237">
         <v>-70.025000000000006</v>
       </c>
-      <c r="AM15" s="237">
+      <c r="AM15" s="107">
         <v>-66.03</v>
       </c>
       <c r="AP15" s="237">
@@ -32990,7 +32992,7 @@
         <v>87</v>
       </c>
       <c r="C16" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-230.61500000000001</v>
       </c>
       <c r="P16" s="237">
@@ -33014,7 +33016,7 @@
         <v>91</v>
       </c>
       <c r="C17" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-8.69</v>
       </c>
       <c r="AD17" s="237">
@@ -33029,7 +33031,7 @@
         <v>88</v>
       </c>
       <c r="C18" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-16.39</v>
       </c>
       <c r="N18" s="45">
@@ -33047,7 +33049,7 @@
         <v>89</v>
       </c>
       <c r="C19" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-7.6849999999999996</v>
       </c>
       <c r="AD19" s="237">
@@ -33062,7 +33064,7 @@
         <v>90</v>
       </c>
       <c r="C20" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-34.004999999999995</v>
       </c>
       <c r="AD20" s="237">
@@ -33080,7 +33082,7 @@
         <v>90</v>
       </c>
       <c r="C21" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-4.9400000000000004</v>
       </c>
       <c r="N21" s="45">
@@ -33095,22 +33097,22 @@
         <v>17</v>
       </c>
       <c r="C22" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>288.53499999999997</v>
       </c>
       <c r="AB22" s="255">
         <v>33.28</v>
       </c>
-      <c r="AH22" s="371">
+      <c r="AH22" s="255">
         <v>28.57</v>
       </c>
-      <c r="AK22" s="371">
+      <c r="AK22" s="255">
         <v>33.734999999999999</v>
       </c>
-      <c r="AN22" s="371">
+      <c r="AN22" s="255">
         <v>34.26</v>
       </c>
-      <c r="AQ22" s="371">
+      <c r="AQ22" s="255">
         <v>33.39</v>
       </c>
       <c r="AT22" s="255">
@@ -33134,7 +33136,7 @@
         <v>92</v>
       </c>
       <c r="C23" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-92.259999999999991</v>
       </c>
       <c r="P23" s="237">
@@ -33143,13 +33145,13 @@
       <c r="AB23" s="255">
         <v>-8.2200000000000006</v>
       </c>
-      <c r="AH23" s="371">
+      <c r="AH23" s="255">
         <v>-7.12</v>
       </c>
-      <c r="AK23" s="371">
+      <c r="AK23" s="255">
         <v>-16.844999999999999</v>
       </c>
-      <c r="AN23" s="371">
+      <c r="AN23" s="255">
         <v>-8.4949999999999992</v>
       </c>
       <c r="BO23" s="255">
@@ -33167,19 +33169,19 @@
         <v>90</v>
       </c>
       <c r="C24" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-98.229999999999976</v>
       </c>
       <c r="AB24" s="255">
         <v>-16.72</v>
       </c>
-      <c r="AH24" s="371">
+      <c r="AH24" s="255">
         <v>-14.3</v>
       </c>
-      <c r="AN24" s="371">
+      <c r="AN24" s="255">
         <v>-16.97</v>
       </c>
-      <c r="AQ24" s="371">
+      <c r="AQ24" s="255">
         <v>-16.649999999999999</v>
       </c>
       <c r="AT24" s="255">
@@ -33197,19 +33199,19 @@
         <v>89</v>
       </c>
       <c r="C25" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-49.64</v>
       </c>
-      <c r="AH25" s="371">
+      <c r="AH25" s="255">
         <v>-7.15</v>
       </c>
-      <c r="AK25" s="371">
+      <c r="AK25" s="255">
         <v>-8.4250000000000007</v>
       </c>
-      <c r="AN25" s="371">
+      <c r="AN25" s="255">
         <v>-8.7949999999999999</v>
       </c>
-      <c r="AQ25" s="371">
+      <c r="AQ25" s="255">
         <v>-8.36</v>
       </c>
       <c r="AT25" s="255">
@@ -33224,7 +33226,7 @@
         <v>93</v>
       </c>
       <c r="C26" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-8.07</v>
       </c>
       <c r="R26" s="237">
@@ -33239,10 +33241,10 @@
         <v>88</v>
       </c>
       <c r="C27" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-8.4649999999999999</v>
       </c>
-      <c r="AK27" s="371">
+      <c r="AK27" s="255">
         <v>-8.4649999999999999</v>
       </c>
     </row>
@@ -33254,10 +33256,10 @@
         <v>91</v>
       </c>
       <c r="C28" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-16.79</v>
       </c>
-      <c r="AQ28" s="371">
+      <c r="AQ28" s="255">
         <v>-8.3800000000000008</v>
       </c>
       <c r="AW28" s="255">
@@ -33272,7 +33274,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>185.95999999999998</v>
       </c>
       <c r="E29" s="174">
@@ -33296,7 +33298,7 @@
         <v>94</v>
       </c>
       <c r="C30" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-34.055</v>
       </c>
       <c r="F30" s="174">
@@ -33311,10 +33313,10 @@
         <v>95</v>
       </c>
       <c r="C31" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-98.41</v>
       </c>
-      <c r="D31" s="230">
+      <c r="D31" s="174">
         <v>-25.675000000000001</v>
       </c>
       <c r="E31" s="174">
@@ -33332,7 +33334,7 @@
         <v>96</v>
       </c>
       <c r="C32" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-36.659999999999997</v>
       </c>
       <c r="DC32" s="273">
@@ -33347,7 +33349,7 @@
         <v>98</v>
       </c>
       <c r="C33" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-15.975</v>
       </c>
       <c r="BB33" s="237">
@@ -33362,10 +33364,10 @@
         <v>97</v>
       </c>
       <c r="C34" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-8.48</v>
       </c>
-      <c r="U34" s="107">
+      <c r="U34" s="237">
         <v>-8.48</v>
       </c>
     </row>
@@ -33377,7 +33379,7 @@
         <v>93</v>
       </c>
       <c r="C35" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-7.58</v>
       </c>
       <c r="BB35" s="237">
@@ -33392,7 +33394,7 @@
         <v>93</v>
       </c>
       <c r="C36" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-8.11</v>
       </c>
       <c r="BB36" s="237">
@@ -33407,7 +33409,7 @@
         <v>17</v>
       </c>
       <c r="C37" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>193.27</v>
       </c>
       <c r="AB37" s="255">
@@ -33416,13 +33418,13 @@
       <c r="AE37" s="255">
         <v>27.53</v>
       </c>
-      <c r="AH37" s="371">
+      <c r="AH37" s="255">
         <v>34.17</v>
       </c>
-      <c r="AK37" s="371">
+      <c r="AK37" s="255">
         <v>34.085000000000001</v>
       </c>
-      <c r="AN37" s="371">
+      <c r="AN37" s="255">
         <v>32.604999999999997</v>
       </c>
       <c r="AT37" s="255">
@@ -33437,7 +33439,7 @@
         <v>17</v>
       </c>
       <c r="C38" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-103.66500000000001</v>
       </c>
       <c r="CE38" s="247">
@@ -33452,7 +33454,7 @@
         <v>99</v>
       </c>
       <c r="C39" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-6.9249999999999998</v>
       </c>
       <c r="CR39" s="293">
@@ -33470,7 +33472,7 @@
         <v>92</v>
       </c>
       <c r="C40" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-96.424999999999983</v>
       </c>
       <c r="AB40" s="255">
@@ -33479,13 +33481,13 @@
       <c r="AE40" s="255">
         <v>-14.04</v>
       </c>
-      <c r="AH40" s="371">
+      <c r="AH40" s="255">
         <v>-17.02</v>
       </c>
-      <c r="AK40" s="371">
+      <c r="AK40" s="255">
         <v>-17.05</v>
       </c>
-      <c r="AN40" s="371">
+      <c r="AN40" s="255">
         <v>-16.285</v>
       </c>
       <c r="AT40" s="255">
@@ -33500,7 +33502,7 @@
         <v>91</v>
       </c>
       <c r="C41" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-16.814999999999998</v>
       </c>
       <c r="AY41" s="237">
@@ -33518,17 +33520,17 @@
         <v>89</v>
       </c>
       <c r="C42" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-42.534999999999997</v>
       </c>
       <c r="AB42" s="255">
         <v>-8.4450000000000003</v>
       </c>
-      <c r="AH42" s="371">
+      <c r="AH42" s="255">
         <f>-8.585-8.565</f>
         <v>-17.149999999999999</v>
       </c>
-      <c r="AK42" s="371">
+      <c r="AK42" s="255">
         <v>-8.57</v>
       </c>
       <c r="AW42" s="255">
@@ -33543,10 +33545,10 @@
         <v>100</v>
       </c>
       <c r="C43" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-16.695</v>
       </c>
-      <c r="AN43" s="371">
+      <c r="AN43" s="255">
         <v>-8.1050000000000004</v>
       </c>
       <c r="AT43" s="255">
@@ -33561,10 +33563,10 @@
         <v>101</v>
       </c>
       <c r="C44" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-81.894999999999996</v>
       </c>
-      <c r="U44" s="107">
+      <c r="U44" s="237">
         <v>-15.88</v>
       </c>
       <c r="BT44" s="35">
@@ -33579,7 +33581,7 @@
         <v>102</v>
       </c>
       <c r="C45" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-16.754999999999999</v>
       </c>
       <c r="AB45" s="255">
@@ -33594,10 +33596,10 @@
         <v>103</v>
       </c>
       <c r="C46" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>92.83</v>
       </c>
-      <c r="Z46" s="299">
+      <c r="Z46" s="305">
         <v>8.4649999999999999</v>
       </c>
       <c r="AC46" s="305">
@@ -33611,7 +33613,7 @@
       <c r="AR46" s="305">
         <v>33.494999999999997</v>
       </c>
-      <c r="AX46" s="299">
+      <c r="AX46" s="305">
         <f>8.59+8.585</f>
         <v>17.175000000000001</v>
       </c>
@@ -33624,7 +33626,7 @@
         <v>104</v>
       </c>
       <c r="C47" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-65.025000000000006</v>
       </c>
       <c r="BT47" s="35">
@@ -33639,10 +33641,10 @@
         <v>107</v>
       </c>
       <c r="C48" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-8.2149999999999999</v>
       </c>
-      <c r="AN48" s="371">
+      <c r="AN48" s="255">
         <v>-8.2149999999999999</v>
       </c>
     </row>
@@ -33654,7 +33656,7 @@
         <v>91</v>
       </c>
       <c r="C49" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-40.055</v>
       </c>
       <c r="O49" s="267">
@@ -33678,7 +33680,7 @@
         <v>105</v>
       </c>
       <c r="C50" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-55.505000000000003</v>
       </c>
       <c r="AC50" s="305">
@@ -33702,7 +33704,7 @@
         <v>89</v>
       </c>
       <c r="C51" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-16.93</v>
       </c>
       <c r="O51" s="267">
@@ -33720,7 +33722,7 @@
         <v>101</v>
       </c>
       <c r="C52" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-41.335000000000001</v>
       </c>
       <c r="BT52" s="35">
@@ -33738,16 +33740,16 @@
         <v>103</v>
       </c>
       <c r="C53" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>166.6</v>
       </c>
-      <c r="AF53" s="299">
+      <c r="AF53" s="305">
         <v>33.950000000000003</v>
       </c>
       <c r="AR53" s="305">
         <v>32.505000000000003</v>
       </c>
-      <c r="AU53" s="299">
+      <c r="AU53" s="305">
         <v>34.045000000000002</v>
       </c>
       <c r="BA53" s="305">
@@ -33765,7 +33767,7 @@
         <v>83</v>
       </c>
       <c r="C54" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-82.89</v>
       </c>
       <c r="AR54" s="305">
@@ -33789,7 +33791,7 @@
         <v>91</v>
       </c>
       <c r="C55" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-5.4450000000000003</v>
       </c>
       <c r="N55" s="45">
@@ -33804,16 +33806,16 @@
         <v>106</v>
       </c>
       <c r="C56" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-49.494999999999997</v>
       </c>
-      <c r="Z56" s="299">
+      <c r="Z56" s="305">
         <v>-8.4649999999999999</v>
       </c>
-      <c r="AF56" s="299">
+      <c r="AF56" s="305">
         <v>-8.5</v>
       </c>
-      <c r="AK56" s="371">
+      <c r="AK56" s="255">
         <v>-8.4649999999999999</v>
       </c>
       <c r="AR56" s="305">
@@ -33831,16 +33833,16 @@
         <v>108</v>
       </c>
       <c r="C57" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-33.68</v>
       </c>
       <c r="AC57" s="305">
         <v>-8.4700000000000006</v>
       </c>
-      <c r="AF57" s="299">
+      <c r="AF57" s="305">
         <v>-8.4749999999999996</v>
       </c>
-      <c r="AU57" s="299">
+      <c r="AU57" s="305">
         <v>-8.5749999999999993</v>
       </c>
       <c r="BE57" s="237">
@@ -33855,13 +33857,13 @@
         <v>109</v>
       </c>
       <c r="C58" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-15.93</v>
       </c>
       <c r="AR58" s="305">
         <v>-7.3449999999999998</v>
       </c>
-      <c r="AX58" s="299">
+      <c r="AX58" s="305">
         <v>-8.5850000000000009</v>
       </c>
     </row>
@@ -33873,10 +33875,10 @@
         <v>98</v>
       </c>
       <c r="C59" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-49.765000000000001</v>
       </c>
-      <c r="AU59" s="299">
+      <c r="AU59" s="305">
         <f>-8.525-8.385</f>
         <v>-16.91</v>
       </c>
@@ -33899,7 +33901,7 @@
         <v>110</v>
       </c>
       <c r="C60" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-8.08</v>
       </c>
       <c r="BX60" s="63">
@@ -33914,19 +33916,19 @@
         <v>103</v>
       </c>
       <c r="C61" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>247.55000000000004</v>
       </c>
-      <c r="Z61" s="299">
+      <c r="Z61" s="305">
         <v>17.065000000000001</v>
       </c>
       <c r="AL61" s="305">
         <v>8.5050000000000008</v>
       </c>
-      <c r="AU61" s="299">
+      <c r="AU61" s="305">
         <v>34.090000000000003</v>
       </c>
-      <c r="AX61" s="299">
+      <c r="AX61" s="305">
         <v>34.134999999999998</v>
       </c>
       <c r="BA61" s="305">
@@ -33959,10 +33961,10 @@
         <v>111</v>
       </c>
       <c r="C62" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-8.4849999999999994</v>
       </c>
-      <c r="AF62" s="299">
+      <c r="AF62" s="305">
         <v>-8.4849999999999994</v>
       </c>
     </row>
@@ -33974,16 +33976,16 @@
         <v>89</v>
       </c>
       <c r="C63" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-25.655000000000001</v>
       </c>
       <c r="AL63" s="305">
         <v>-8.5050000000000008</v>
       </c>
-      <c r="AU63" s="299">
+      <c r="AU63" s="305">
         <v>-8.56</v>
       </c>
-      <c r="AX63" s="299">
+      <c r="AX63" s="305">
         <v>-8.59</v>
       </c>
     </row>
@@ -33995,10 +33997,10 @@
         <v>100</v>
       </c>
       <c r="C64" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-8.5449999999999999</v>
       </c>
-      <c r="Z64" s="299">
+      <c r="Z64" s="305">
         <v>-8.5449999999999999</v>
       </c>
     </row>
@@ -34010,13 +34012,13 @@
         <v>97</v>
       </c>
       <c r="C65" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-17.009999999999998</v>
       </c>
-      <c r="Z65" s="299">
+      <c r="Z65" s="305">
         <v>-8.52</v>
       </c>
-      <c r="AF65" s="299">
+      <c r="AF65" s="305">
         <v>-8.49</v>
       </c>
     </row>
@@ -34028,7 +34030,7 @@
         <v>112</v>
       </c>
       <c r="C66" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-24.2</v>
       </c>
       <c r="CG66" s="56">
@@ -34043,10 +34045,10 @@
         <v>89</v>
       </c>
       <c r="C67" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-50.300000000000011</v>
       </c>
-      <c r="AX67" s="299">
+      <c r="AX67" s="305">
         <v>-8.56</v>
       </c>
       <c r="BA67" s="305">
@@ -34067,7 +34069,7 @@
         <v>106</v>
       </c>
       <c r="C68" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-17.130000000000003</v>
       </c>
       <c r="BA68" s="305">
@@ -34085,10 +34087,10 @@
         <v>107</v>
       </c>
       <c r="C69" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-17.005000000000003</v>
       </c>
-      <c r="AX69" s="299">
+      <c r="AX69" s="305">
         <v>-8.4250000000000007</v>
       </c>
       <c r="BA69" s="305">
@@ -34103,13 +34105,13 @@
         <v>91</v>
       </c>
       <c r="C70" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-17.14</v>
       </c>
-      <c r="AU70" s="299">
+      <c r="AU70" s="305">
         <v>-8.5649999999999995</v>
       </c>
-      <c r="AX70" s="299">
+      <c r="AX70" s="305">
         <v>-8.5749999999999993</v>
       </c>
     </row>
@@ -34121,10 +34123,10 @@
         <v>89</v>
       </c>
       <c r="C71" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-7.8849999999999998</v>
       </c>
-      <c r="U71" s="107">
+      <c r="U71" s="237">
         <v>-7.8849999999999998</v>
       </c>
     </row>
@@ -34136,7 +34138,7 @@
         <v>105</v>
       </c>
       <c r="C72" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-25.840000000000003</v>
       </c>
       <c r="BG72" s="299">
@@ -34155,10 +34157,10 @@
         <v>92</v>
       </c>
       <c r="C73" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-25.524999999999999</v>
       </c>
-      <c r="AU73" s="299">
+      <c r="AU73" s="305">
         <v>-25.524999999999999</v>
       </c>
     </row>
@@ -34170,13 +34172,13 @@
         <v>84</v>
       </c>
       <c r="C74" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>82.53</v>
       </c>
       <c r="BX74" s="63">
         <v>49.62</v>
       </c>
-      <c r="CA74" s="378">
+      <c r="CA74" s="330">
         <v>32.909999999999997</v>
       </c>
     </row>
@@ -34188,13 +34190,13 @@
         <v>103</v>
       </c>
       <c r="C75" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>85.32</v>
       </c>
       <c r="Q75" s="305">
         <v>8.3949999999999996</v>
       </c>
-      <c r="AF75" s="299">
+      <c r="AF75" s="305">
         <v>33.909999999999997</v>
       </c>
       <c r="BA75" s="305">
@@ -34212,10 +34214,10 @@
         <v>92</v>
       </c>
       <c r="C76" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-42.555</v>
       </c>
-      <c r="AF76" s="299">
+      <c r="AF76" s="305">
         <v>-25.414999999999999</v>
       </c>
       <c r="BA76" s="305">
@@ -34230,10 +34232,10 @@
         <v>84</v>
       </c>
       <c r="C77" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>17.059999999999999</v>
       </c>
-      <c r="CA77" s="378">
+      <c r="CA77" s="330">
         <v>17.059999999999999</v>
       </c>
     </row>
@@ -34245,7 +34247,7 @@
         <v>105</v>
       </c>
       <c r="C78" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-8.6</v>
       </c>
       <c r="BG78" s="299">
@@ -34260,7 +34262,7 @@
         <v>89</v>
       </c>
       <c r="C79" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>-17.015000000000001</v>
       </c>
       <c r="Q79" s="305">
@@ -34278,10 +34280,10 @@
         <v>91</v>
       </c>
       <c r="C80" s="18">
-        <f t="shared" ref="C80:C112" si="1">SUM(D80:EQ80)</f>
+        <f t="shared" ref="C80:C112" si="5">SUM(D80:EQ80)</f>
         <v>-8.4949999999999992</v>
       </c>
-      <c r="AF80" s="299">
+      <c r="AF80" s="305">
         <v>-8.4949999999999992</v>
       </c>
     </row>
@@ -34293,10 +34295,10 @@
         <v>116</v>
       </c>
       <c r="C81" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-49.97</v>
       </c>
-      <c r="CA81" s="378">
+      <c r="CA81" s="330">
         <v>-49.97</v>
       </c>
     </row>
@@ -34308,10 +34310,10 @@
         <v>103</v>
       </c>
       <c r="C82" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>118.51</v>
       </c>
-      <c r="Z82" s="299">
+      <c r="Z82" s="305">
         <f>8.465+8.48</f>
         <v>16.945</v>
       </c>
@@ -34319,13 +34321,13 @@
         <f>8.465+8.44</f>
         <v>16.905000000000001</v>
       </c>
-      <c r="AF82" s="299">
+      <c r="AF82" s="305">
         <v>33.695</v>
       </c>
-      <c r="AU82" s="299">
+      <c r="AU82" s="305">
         <v>33.86</v>
       </c>
-      <c r="AX82" s="299">
+      <c r="AX82" s="305">
         <f>8.545+8.56</f>
         <v>17.105</v>
       </c>
@@ -34338,7 +34340,7 @@
         <v>103</v>
       </c>
       <c r="C83" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>25.215</v>
       </c>
       <c r="AI83" s="305">
@@ -34359,7 +34361,7 @@
         <v>114</v>
       </c>
       <c r="C84" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-8.2100000000000009</v>
       </c>
       <c r="N84" s="45">
@@ -34374,10 +34376,10 @@
         <v>17</v>
       </c>
       <c r="C85" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>300.28499999999997</v>
       </c>
-      <c r="D85" s="230">
+      <c r="D85" s="174">
         <v>17.09</v>
       </c>
       <c r="E85" s="174">
@@ -34389,22 +34391,22 @@
       <c r="S85" s="72">
         <v>15.47</v>
       </c>
-      <c r="AH85" s="371">
+      <c r="AH85" s="255">
         <v>34.340000000000003</v>
       </c>
-      <c r="AK85" s="371">
+      <c r="AK85" s="255">
         <v>33.475000000000001</v>
       </c>
-      <c r="AN85" s="371">
+      <c r="AN85" s="255">
         <v>33.755000000000003</v>
       </c>
-      <c r="AQ85" s="371">
+      <c r="AQ85" s="255">
         <v>35.299999999999997</v>
       </c>
-      <c r="AZ85" s="371">
+      <c r="AZ85" s="323">
         <v>33.47</v>
       </c>
-      <c r="BC85" s="371">
+      <c r="BC85" s="323">
         <v>33.25</v>
       </c>
     </row>
@@ -34416,10 +34418,10 @@
         <v>115</v>
       </c>
       <c r="C86" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-73.42</v>
       </c>
-      <c r="D86" s="230">
+      <c r="D86" s="174">
         <v>-8.3049999999999997</v>
       </c>
       <c r="E86" s="174">
@@ -34437,7 +34439,7 @@
         <v>83</v>
       </c>
       <c r="C87" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-8.4</v>
       </c>
       <c r="AO87" s="305">
@@ -34452,13 +34454,13 @@
         <v>89</v>
       </c>
       <c r="C88" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-13.975</v>
       </c>
       <c r="S88" s="72">
         <v>-5.43</v>
       </c>
-      <c r="U88" s="107">
+      <c r="U88" s="237">
         <v>-8.5449999999999999</v>
       </c>
     </row>
@@ -34470,10 +34472,10 @@
         <v>107</v>
       </c>
       <c r="C89" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-8.42</v>
       </c>
-      <c r="AF89" s="299">
+      <c r="AF89" s="305">
         <v>-8.42</v>
       </c>
     </row>
@@ -34485,25 +34487,25 @@
         <v>100</v>
       </c>
       <c r="C90" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-46.264999999999993</v>
       </c>
       <c r="S90" s="72">
         <v>-4.1500000000000004</v>
       </c>
-      <c r="U90" s="107">
+      <c r="U90" s="237">
         <v>-7.915</v>
       </c>
-      <c r="AF90" s="299">
+      <c r="AF90" s="305">
         <v>-8.4499999999999993</v>
       </c>
-      <c r="AH90" s="371">
+      <c r="AH90" s="255">
         <v>-8.6199999999999992</v>
       </c>
-      <c r="AK90" s="371">
+      <c r="AK90" s="255">
         <v>-8.3849999999999998</v>
       </c>
-      <c r="AQ90" s="371">
+      <c r="AQ90" s="255">
         <v>-8.7449999999999992</v>
       </c>
     </row>
@@ -34515,13 +34517,13 @@
         <v>92</v>
       </c>
       <c r="C91" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-33.754999999999995</v>
       </c>
-      <c r="AU91" s="299">
+      <c r="AU91" s="305">
         <v>-16.965</v>
       </c>
-      <c r="AZ91" s="371">
+      <c r="AZ91" s="323">
         <v>-16.79</v>
       </c>
     </row>
@@ -34533,19 +34535,19 @@
         <v>92</v>
       </c>
       <c r="C92" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-68.054999999999993</v>
       </c>
-      <c r="AH92" s="371">
+      <c r="AH92" s="255">
         <v>-17.09</v>
       </c>
-      <c r="AK92" s="371">
+      <c r="AK92" s="255">
         <v>-16.739999999999998</v>
       </c>
-      <c r="AN92" s="371">
+      <c r="AN92" s="255">
         <v>-16.594999999999999</v>
       </c>
-      <c r="AQ92" s="371">
+      <c r="AQ92" s="255">
         <v>-17.63</v>
       </c>
     </row>
@@ -34557,16 +34559,16 @@
         <v>84</v>
       </c>
       <c r="C93" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-42.129999999999995</v>
       </c>
-      <c r="Z93" s="299">
+      <c r="Z93" s="305">
         <v>-8.48</v>
       </c>
       <c r="AC93" s="305">
         <v>-8.4649999999999999</v>
       </c>
-      <c r="AF93" s="299">
+      <c r="AF93" s="305">
         <v>-8.3699999999999992</v>
       </c>
       <c r="AI93" s="305">
@@ -34577,1118 +34579,1239 @@
       </c>
     </row>
     <row r="94" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A94" s="50">
+        <v>46155</v>
+      </c>
+      <c r="B94" s="19" t="s">
+        <v>88</v>
+      </c>
       <c r="C94" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
+        <v>-17.844999999999999</v>
+      </c>
+      <c r="AN94" s="255">
+        <v>-8.92</v>
+      </c>
+      <c r="AQ94" s="255">
+        <v>-8.9250000000000007</v>
+      </c>
+    </row>
+    <row r="95" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A95" s="50">
+        <v>46156</v>
+      </c>
+      <c r="B95" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C95" s="18">
+        <f t="shared" si="5"/>
+        <v>-3.96</v>
+      </c>
+      <c r="I95" s="45">
+        <v>-3.96</v>
+      </c>
+    </row>
+    <row r="96" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A96" s="50">
+        <v>46156</v>
+      </c>
+      <c r="B96" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C96" s="18">
+        <f t="shared" si="5"/>
+        <v>-16.98</v>
+      </c>
+      <c r="AH96" s="255">
+        <v>-8.6300000000000008</v>
+      </c>
+      <c r="AK96" s="255">
+        <v>-8.35</v>
+      </c>
+    </row>
+    <row r="97" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="A97" s="50">
+        <v>46157</v>
+      </c>
+      <c r="B97" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C97" s="18">
+        <f t="shared" si="5"/>
+        <v>-33.72</v>
+      </c>
+      <c r="Z97" s="305">
+        <v>-8.4649999999999999</v>
+      </c>
+      <c r="AC97" s="305">
+        <v>-8.44</v>
+      </c>
+      <c r="AF97" s="305">
+        <v>-8.4550000000000001</v>
+      </c>
+      <c r="AZ97" s="323">
+        <v>-8.36</v>
+      </c>
+    </row>
+    <row r="98" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="A98" s="50">
+        <v>46157</v>
+      </c>
+      <c r="B98" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C98" s="18">
+        <f t="shared" si="5"/>
+        <v>-33.709999999999994</v>
+      </c>
+      <c r="AN98" s="255">
+        <v>-8.24</v>
+      </c>
+      <c r="AU98" s="305">
+        <v>-16.895</v>
+      </c>
+      <c r="AX98" s="305">
+        <v>-8.5749999999999993</v>
+      </c>
+    </row>
+    <row r="99" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="A99" s="50">
+        <v>46157</v>
+      </c>
+      <c r="B99" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C99" s="18">
+        <f t="shared" si="5"/>
+        <v>-24.16</v>
+      </c>
+      <c r="CP99" s="35">
+        <v>-24.16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="A100" s="50">
+        <v>46157</v>
+      </c>
+      <c r="B100" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C100" s="18">
+        <f t="shared" si="5"/>
+        <v>-17.105</v>
+      </c>
+      <c r="AX100" s="305">
+        <v>-17.105</v>
+      </c>
+    </row>
+    <row r="101" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="A101" s="50">
+        <v>46161</v>
+      </c>
+      <c r="B101" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" s="18">
+        <f t="shared" si="5"/>
+        <v>197.405</v>
+      </c>
+      <c r="AM101" s="107">
+        <v>197.405</v>
+      </c>
+    </row>
+    <row r="102" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="A102" s="50">
+        <v>46162</v>
+      </c>
+      <c r="B102" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C102" s="18">
+        <f t="shared" si="5"/>
+        <v>-66.085000000000008</v>
+      </c>
+      <c r="AM102" s="107">
+        <f>-33.07-33.015</f>
+        <v>-66.085000000000008</v>
+      </c>
+    </row>
+    <row r="103" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="A103" s="50">
+        <v>46162</v>
+      </c>
+      <c r="B103" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C103" s="18">
+        <f t="shared" si="5"/>
+        <v>-66.19</v>
+      </c>
+      <c r="AM103" s="107">
+        <v>-66.19</v>
+      </c>
+    </row>
+    <row r="104" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="A104" s="50">
+        <v>46162</v>
+      </c>
+      <c r="B104" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C104" s="18">
+        <f t="shared" si="5"/>
+        <v>-16.440000000000001</v>
+      </c>
+      <c r="AM104" s="107">
+        <v>-16.440000000000001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="C105" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="C95" s="18">
-        <f t="shared" si="1"/>
+    <row r="106" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="C106" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="C96" s="18">
-        <f t="shared" si="1"/>
+    <row r="107" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="C107" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C97" s="18">
-        <f t="shared" si="1"/>
+    <row r="108" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="C108" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C98" s="18">
-        <f t="shared" si="1"/>
+    <row r="109" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="C109" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C99" s="18">
-        <f t="shared" si="1"/>
+    <row r="110" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="C110" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C100" s="18">
-        <f t="shared" si="1"/>
+    <row r="111" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="C111" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C101" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C102" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C103" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C104" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C105" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C106" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C107" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C108" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C109" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C110" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C111" s="18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:94" x14ac:dyDescent="0.25">
       <c r="C112" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C113" s="18">
-        <f t="shared" ref="C113:C144" si="2">SUM(D113:EQ113)</f>
+        <f t="shared" ref="C113:C144" si="6">SUM(D113:EQ113)</f>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C114" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C115" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C116" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C117" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C118" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C119" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C120" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C121" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C122" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C123" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C124" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C125" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C126" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C127" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C128" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C129" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C130" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C131" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C132" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C133" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C134" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C135" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C136" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C137" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C138" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C139" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C140" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="141" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C141" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="142" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C142" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="143" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C143" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="144" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C144" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="145" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C145" s="18">
-        <f t="shared" ref="C145:C176" si="3">SUM(D145:EQ145)</f>
+        <f t="shared" ref="C145:C176" si="7">SUM(D145:EQ145)</f>
         <v>0</v>
       </c>
     </row>
     <row r="146" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C146" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="147" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C147" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="148" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C148" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="149" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C149" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C150" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="151" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C151" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="152" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C152" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="153" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C153" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="154" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C154" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="155" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C155" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="156" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C156" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="157" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C157" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="158" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C158" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="159" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C159" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="160" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C160" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="161" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C161" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="162" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C162" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="163" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C163" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="164" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C164" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="165" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C165" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="166" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C166" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="167" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C167" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="168" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C168" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="169" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C169" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="170" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C170" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="171" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C171" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="172" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C172" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="173" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C173" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="174" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C174" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="175" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C175" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="176" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C176" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="177" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C177" s="18">
-        <f t="shared" ref="C177:C208" si="4">SUM(D177:EQ177)</f>
+        <f t="shared" ref="C177:C208" si="8">SUM(D177:EQ177)</f>
         <v>0</v>
       </c>
     </row>
     <row r="178" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C178" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="179" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C179" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="180" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C180" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="181" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C181" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="182" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C182" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="183" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C183" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="184" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C184" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="185" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C185" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C186" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="187" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C187" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="188" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C188" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="189" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C189" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="190" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C190" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="191" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C191" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="192" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C192" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="193" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C193" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="194" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C194" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="195" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C195" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="196" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C196" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="197" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C197" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="198" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C198" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="199" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C199" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="200" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C200" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="201" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C201" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="202" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C202" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="203" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C203" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="204" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C204" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="205" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C205" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="206" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C206" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="207" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C207" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="208" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C208" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="209" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C209" s="18">
-        <f t="shared" ref="C209:C240" si="5">SUM(D209:EQ209)</f>
+        <f t="shared" ref="C209:C240" si="9">SUM(D209:EQ209)</f>
         <v>0</v>
       </c>
     </row>
     <row r="210" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C210" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="211" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C211" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="212" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C212" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="213" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C213" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="214" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C214" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="215" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C215" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="216" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C216" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="217" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C217" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="218" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C218" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="219" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C219" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="220" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C220" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="221" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C221" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="222" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C222" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="223" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C223" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="224" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C224" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="225" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C225" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="226" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C226" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="227" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C227" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="228" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C228" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="229" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C229" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="230" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C230" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="231" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C231" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="232" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C232" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="233" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C233" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="234" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C234" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="235" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C235" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="236" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C236" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="237" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C237" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="238" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C238" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="239" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C239" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="240" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C240" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
     <row r="241" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C241" s="18">
-        <f t="shared" ref="C241:C272" si="6">SUM(D241:EQ241)</f>
+        <f t="shared" ref="C241:C272" si="10">SUM(D241:EQ241)</f>
         <v>0</v>
       </c>
     </row>
     <row r="242" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C242" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="243" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C243" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="244" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C244" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="245" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C245" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="246" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C246" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="247" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C247" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="248" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C248" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="249" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C249" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="250" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C250" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="251" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C251" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="252" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C252" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="253" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C253" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="254" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C254" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="255" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C255" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="256" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C256" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="257" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C257" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="258" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C258" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="259" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C259" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="260" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C260" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="261" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C261" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="262" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C262" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="263" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C263" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="264" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C264" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="265" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C265" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="266" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C266" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="267" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C267" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="268" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C268" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="269" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C269" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="270" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C270" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="271" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C271" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="272" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C272" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
     <row r="273" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C273" s="18">
-        <f t="shared" ref="C273:C279" si="7">SUM(D273:EQ273)</f>
+        <f t="shared" ref="C273:C279" si="11">SUM(D273:EQ273)</f>
         <v>0</v>
       </c>
     </row>
     <row r="274" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C274" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="275" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C275" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="276" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C276" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="277" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C277" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="278" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C278" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
     <row r="279" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C279" s="18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -35732,16 +35855,16 @@
     </row>
     <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="89"/>
-      <c r="B3" s="365" t="s">
+      <c r="B3" s="378" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="365"/>
+      <c r="C3" s="378"/>
       <c r="D3" s="89"/>
     </row>
     <row r="4" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="89"/>
-      <c r="B4" s="365"/>
-      <c r="C4" s="365"/>
+      <c r="B4" s="378"/>
+      <c r="C4" s="378"/>
       <c r="D4" s="89"/>
     </row>
     <row r="5" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -36136,7 +36259,7 @@
       </c>
       <c r="D7" s="127">
         <f>'STOK DETAY'!I6</f>
-        <v>6.06</v>
+        <v>2.0999999999999996</v>
       </c>
       <c r="E7" s="127"/>
       <c r="F7" s="127"/>
@@ -36145,7 +36268,7 @@
       <c r="I7" s="127"/>
       <c r="J7" s="146">
         <f t="shared" si="0"/>
-        <v>6.06</v>
+        <v>2.0999999999999996</v>
       </c>
       <c r="K7" s="74"/>
       <c r="L7" s="74"/>
@@ -36563,14 +36686,14 @@
       </c>
       <c r="F18" s="146">
         <f>'STOK DETAY'!Z6</f>
-        <v>8.4649999999999999</v>
+        <v>0</v>
       </c>
       <c r="G18" s="146"/>
       <c r="H18" s="146"/>
       <c r="I18" s="146"/>
       <c r="J18" s="146">
         <f t="shared" si="0"/>
-        <v>8.4649999999999999</v>
+        <v>0</v>
       </c>
       <c r="K18" s="74"/>
       <c r="L18" s="74"/>
@@ -36606,14 +36729,14 @@
       </c>
       <c r="F19" s="146">
         <f>'STOK DETAY'!AC6</f>
-        <v>8.4400000000000013</v>
+        <v>0</v>
       </c>
       <c r="G19" s="146"/>
       <c r="H19" s="146"/>
       <c r="I19" s="146"/>
       <c r="J19" s="146">
         <f t="shared" si="0"/>
-        <v>8.4400000000000013</v>
+        <v>0</v>
       </c>
       <c r="K19" s="74"/>
       <c r="L19" s="74"/>
@@ -36649,14 +36772,14 @@
       </c>
       <c r="F20" s="146">
         <f>'STOK DETAY'!AF6</f>
-        <v>8.4550000000000001</v>
+        <v>0</v>
       </c>
       <c r="G20" s="146"/>
       <c r="H20" s="146"/>
       <c r="I20" s="146"/>
       <c r="J20" s="146">
         <f t="shared" si="0"/>
-        <v>8.4550000000000001</v>
+        <v>0</v>
       </c>
       <c r="K20" s="74"/>
       <c r="L20" s="74"/>
@@ -36688,7 +36811,7 @@
       </c>
       <c r="E21" s="146">
         <f>'STOK DETAY'!AH6</f>
-        <v>8.6300000000000061</v>
+        <v>0</v>
       </c>
       <c r="F21" s="146">
         <f>'STOK DETAY'!AI6</f>
@@ -36699,7 +36822,7 @@
       <c r="I21" s="146"/>
       <c r="J21" s="146">
         <f t="shared" si="0"/>
-        <v>8.6300000000000061</v>
+        <v>0</v>
       </c>
       <c r="K21" s="74"/>
       <c r="L21" s="74"/>
@@ -36731,7 +36854,7 @@
       </c>
       <c r="E22" s="146">
         <f>'STOK DETAY'!AK6</f>
-        <v>8.350000000000005</v>
+        <v>0</v>
       </c>
       <c r="F22" s="146">
         <f>'STOK DETAY'!AL6</f>
@@ -36742,7 +36865,7 @@
       <c r="I22" s="146"/>
       <c r="J22" s="146">
         <f t="shared" si="0"/>
-        <v>8.350000000000005</v>
+        <v>0</v>
       </c>
       <c r="K22" s="74"/>
       <c r="L22" s="74"/>
@@ -36770,11 +36893,11 @@
       </c>
       <c r="D23" s="146">
         <f>'STOK DETAY'!AM6</f>
-        <v>0</v>
+        <v>48.69</v>
       </c>
       <c r="E23" s="146">
         <f>'STOK DETAY'!AN6</f>
-        <v>17.159999999999997</v>
+        <v>0</v>
       </c>
       <c r="F23" s="146">
         <f>'STOK DETAY'!AO6</f>
@@ -36785,7 +36908,7 @@
       <c r="I23" s="146"/>
       <c r="J23" s="146">
         <f t="shared" si="0"/>
-        <v>17.159999999999997</v>
+        <v>48.69</v>
       </c>
       <c r="K23" s="74"/>
       <c r="L23" s="74"/>
@@ -36817,7 +36940,7 @@
       </c>
       <c r="E24" s="146">
         <f>'STOK DETAY'!AQ6</f>
-        <v>8.9250000000000007</v>
+        <v>0</v>
       </c>
       <c r="F24" s="146">
         <f>'STOK DETAY'!AR6</f>
@@ -36828,7 +36951,7 @@
       <c r="I24" s="146"/>
       <c r="J24" s="146">
         <f t="shared" si="0"/>
-        <v>8.9250000000000007</v>
+        <v>0</v>
       </c>
       <c r="K24" s="74"/>
       <c r="L24" s="74"/>
@@ -36864,14 +36987,14 @@
       </c>
       <c r="F25" s="146">
         <f>'STOK DETAY'!AU6</f>
-        <v>16.895000000000007</v>
+        <v>0</v>
       </c>
       <c r="G25" s="146"/>
       <c r="H25" s="146"/>
       <c r="I25" s="146"/>
       <c r="J25" s="146">
         <f t="shared" si="0"/>
-        <v>16.895000000000007</v>
+        <v>0</v>
       </c>
       <c r="K25" s="74"/>
       <c r="L25" s="74"/>
@@ -36907,14 +37030,14 @@
       </c>
       <c r="F26" s="146">
         <f>'STOK DETAY'!AX6</f>
-        <v>25.679999999999989</v>
+        <v>0</v>
       </c>
       <c r="G26" s="146"/>
       <c r="H26" s="146"/>
       <c r="I26" s="146"/>
       <c r="J26" s="146">
         <f t="shared" si="0"/>
-        <v>25.679999999999989</v>
+        <v>0</v>
       </c>
       <c r="K26" s="74"/>
       <c r="L26" s="74"/>
@@ -36946,7 +37069,7 @@
       </c>
       <c r="E27" s="146">
         <f>'STOK DETAY'!AZ6</f>
-        <v>16.68</v>
+        <v>8.32</v>
       </c>
       <c r="F27" s="146">
         <f>'STOK DETAY'!BA6</f>
@@ -36957,7 +37080,7 @@
       <c r="I27" s="146"/>
       <c r="J27" s="146">
         <f t="shared" si="0"/>
-        <v>16.680000000000007</v>
+        <v>8.3200000000000074</v>
       </c>
       <c r="K27" s="74"/>
       <c r="L27" s="74"/>
@@ -37906,7 +38029,7 @@
       </c>
       <c r="D52" s="146">
         <f>'STOK DETAY'!CP6</f>
-        <v>24.160000000000004</v>
+        <v>0</v>
       </c>
       <c r="E52" s="146">
         <f>'STOK DETAY'!CQ6</f>
@@ -37918,7 +38041,7 @@
       <c r="I52" s="146"/>
       <c r="J52" s="146">
         <f t="shared" si="1"/>
-        <v>24.160000000000004</v>
+        <v>0</v>
       </c>
       <c r="K52" s="74"/>
       <c r="L52" s="74"/>

--- a/STOK.xlsx
+++ b/STOK.xlsx
@@ -15,12 +15,12 @@
     <sheet name="ALÜMİNYUM STOK" sheetId="21" r:id="rId6"/>
     <sheet name="STOK" sheetId="22" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="144525" iterate="1"/>
+  <calcPr calcId="144525" iterate="1" fullPrecision="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="119">
   <si>
     <t>BAYRAMPAŞA DEPODAKİ ELSAN AYRINTI  DÖKÜMÜ</t>
   </si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t>UYARLAR</t>
+  </si>
+  <si>
+    <t>BİRLİK NİKELAJ</t>
   </si>
 </sst>
 </file>
@@ -5288,15 +5291,15 @@
     <row r="3" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17">
         <f>SUM(A5:A15)</f>
-        <v>245.37500000000003</v>
+        <v>245.375</v>
       </c>
       <c r="B3" s="17">
         <f>SUM(B5:B24)</f>
-        <v>231.34499999999997</v>
+        <v>231.345</v>
       </c>
       <c r="C3" s="17">
         <f>SUM(C5:C14)</f>
-        <v>193.92000000000002</v>
+        <v>193.92</v>
       </c>
       <c r="D3" s="17">
         <f>SUM(D5:D10)</f>
@@ -5308,11 +5311,11 @@
       </c>
       <c r="F3" s="17">
         <f>SUM(F5:F21)</f>
-        <v>476.91499999999991</v>
+        <v>476.91500000000002</v>
       </c>
       <c r="G3" s="17">
         <f>SUM(G5:G24)</f>
-        <v>449.11000000000007</v>
+        <v>449.11</v>
       </c>
       <c r="H3" s="17">
         <f>SUM(H5:H19)</f>
@@ -5324,7 +5327,7 @@
       </c>
       <c r="J3" s="17">
         <f>SUM(J5:J22)</f>
-        <v>514.27500000000009</v>
+        <v>514.27499999999998</v>
       </c>
       <c r="K3" s="17">
         <f>SUM(K5:K18)</f>
@@ -5348,15 +5351,15 @@
       </c>
       <c r="P3" s="17">
         <f>SUM(P5:P21)</f>
-        <v>502.09999999999991</v>
+        <v>502.1</v>
       </c>
       <c r="Q3" s="17">
         <f>SUM(Q5:Q28)</f>
-        <v>629.91999999999985</v>
+        <v>629.91999999999996</v>
       </c>
       <c r="R3" s="17">
         <f>SUM(R5:R27)</f>
-        <v>519.80500000000006</v>
+        <v>519.80499999999995</v>
       </c>
       <c r="S3" s="17">
         <f>SUM(S5:S15)</f>
@@ -5364,11 +5367,11 @@
       </c>
       <c r="T3" s="17">
         <f>SUM(T5:T33)</f>
-        <v>790.89999999999986</v>
+        <v>790.9</v>
       </c>
       <c r="U3" s="17">
         <f>SUM(U5:U29)</f>
-        <v>754.17500000000018</v>
+        <v>754.17499999999995</v>
       </c>
       <c r="V3" s="17">
         <f>SUM(V5:V8)</f>
@@ -5376,11 +5379,11 @@
       </c>
       <c r="W3" s="17">
         <f>SUM(W5:W16)</f>
-        <v>281.40999999999997</v>
+        <v>281.41000000000003</v>
       </c>
       <c r="X3" s="17">
         <f>SUM(X5:X29)</f>
-        <v>790.85000000000014</v>
+        <v>790.85</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -8720,12 +8723,12 @@
       </c>
       <c r="E4" s="125">
         <f>SUM(F4:K4)</f>
-        <v>8.39</v>
+        <v>0</v>
       </c>
       <c r="F4" s="126"/>
       <c r="G4" s="127">
         <f>'STOK DETAY'!E6</f>
-        <v>8.39</v>
+        <v>0</v>
       </c>
       <c r="H4" s="127"/>
       <c r="I4" s="127"/>
@@ -8828,7 +8831,7 @@
       <c r="D7" s="356"/>
       <c r="E7" s="135">
         <f>SUM(F7:K7)</f>
-        <v>50.314999999999998</v>
+        <v>41.924999999999997</v>
       </c>
       <c r="F7" s="136">
         <f>SUM(F3:F6)</f>
@@ -8836,7 +8839,7 @@
       </c>
       <c r="G7" s="137">
         <f t="shared" ref="G7:J7" si="0">SUM(G3:G6)</f>
-        <v>50.314999999999998</v>
+        <v>41.924999999999997</v>
       </c>
       <c r="H7" s="137">
         <f>SUM(H3:H6)</f>
@@ -8967,11 +8970,11 @@
       </c>
       <c r="E10" s="125">
         <f t="shared" si="1"/>
-        <v>2.0999999999999996</v>
+        <v>2.1</v>
       </c>
       <c r="F10" s="177">
         <f>'STOK DETAY'!I6</f>
-        <v>2.0999999999999996</v>
+        <v>2.1</v>
       </c>
       <c r="G10" s="178"/>
       <c r="H10" s="178"/>
@@ -9290,7 +9293,7 @@
       </c>
       <c r="E18" s="125">
         <f t="shared" si="1"/>
-        <v>5.8900000000000006</v>
+        <v>5.89</v>
       </c>
       <c r="F18" s="145">
         <f>'STOK DETAY'!R6</f>
@@ -9298,7 +9301,7 @@
       </c>
       <c r="G18" s="146">
         <f>'STOK DETAY'!S6</f>
-        <v>5.8900000000000006</v>
+        <v>5.89</v>
       </c>
       <c r="H18" s="146"/>
       <c r="I18" s="146"/>
@@ -9373,11 +9376,11 @@
       </c>
       <c r="E20" s="125">
         <f t="shared" si="1"/>
-        <v>7.9936057773011271E-15</v>
+        <v>0</v>
       </c>
       <c r="F20" s="145">
         <f>'STOK DETAY'!U6</f>
-        <v>7.9936057773011271E-15</v>
+        <v>0</v>
       </c>
       <c r="G20" s="146"/>
       <c r="H20" s="146"/>
@@ -9643,11 +9646,11 @@
       </c>
       <c r="E26" s="125">
         <f t="shared" si="1"/>
-        <v>48.69</v>
+        <v>0</v>
       </c>
       <c r="F26" s="145">
         <f>'STOK DETAY'!AM6</f>
-        <v>48.69</v>
+        <v>0</v>
       </c>
       <c r="G26" s="146">
         <f>'STOK DETAY'!AN6</f>
@@ -9827,15 +9830,15 @@
       </c>
       <c r="E30" s="125">
         <f t="shared" si="1"/>
-        <v>8.3200000000000074</v>
+        <v>0</v>
       </c>
       <c r="F30" s="145">
         <f>'STOK DETAY'!AY6</f>
-        <v>7.1054273576010019E-15</v>
+        <v>0</v>
       </c>
       <c r="G30" s="146">
         <f>'STOK DETAY'!AZ6</f>
-        <v>8.32</v>
+        <v>0</v>
       </c>
       <c r="H30" s="146">
         <f>'STOK DETAY'!BA6</f>
@@ -9873,7 +9876,7 @@
       </c>
       <c r="E31" s="125">
         <f t="shared" si="1"/>
-        <v>33.25</v>
+        <v>33.67</v>
       </c>
       <c r="F31" s="145">
         <f>'STOK DETAY'!BB6</f>
@@ -9881,7 +9884,7 @@
       </c>
       <c r="G31" s="146">
         <f>'STOK DETAY'!BC6</f>
-        <v>33.25</v>
+        <v>33.67</v>
       </c>
       <c r="H31" s="146">
         <f>'STOK DETAY'!BD6</f>
@@ -9919,11 +9922,11 @@
       </c>
       <c r="E32" s="125">
         <f t="shared" si="1"/>
-        <v>8.6549999999999994</v>
+        <v>32.975000000000001</v>
       </c>
       <c r="F32" s="145">
         <f>'STOK DETAY'!BE6</f>
-        <v>0</v>
+        <v>24.32</v>
       </c>
       <c r="G32" s="146">
         <f>'STOK DETAY'!BF6</f>
@@ -9965,14 +9968,14 @@
       </c>
       <c r="E33" s="125">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9.77</v>
       </c>
       <c r="F33" s="145">
         <f>'STOK DETAY'!BH6</f>
         <v>0</v>
       </c>
       <c r="G33" s="146">
-        <f>'STOK DETAY'!BK6</f>
+        <f>'STOK DETAY'!BL6</f>
         <v>0</v>
       </c>
       <c r="H33" s="146">
@@ -9980,7 +9983,10 @@
         <v>0</v>
       </c>
       <c r="I33" s="146"/>
-      <c r="J33" s="146"/>
+      <c r="J33" s="146">
+        <f>'STOK DETAY'!BK6</f>
+        <v>9.77</v>
+      </c>
       <c r="K33" s="147"/>
       <c r="L33" s="74"/>
       <c r="M33" s="74"/>
@@ -10014,15 +10020,15 @@
         <v>16.925000000000001</v>
       </c>
       <c r="F34" s="145">
-        <f>'STOK DETAY'!BK6</f>
-        <v>0</v>
-      </c>
-      <c r="G34" s="146">
         <f>'STOK DETAY'!BL6</f>
         <v>0</v>
       </c>
+      <c r="G34" s="146">
+        <f>'STOK DETAY'!BM6</f>
+        <v>0</v>
+      </c>
       <c r="H34" s="146">
-        <f>'STOK DETAY'!BM6</f>
+        <f>'STOK DETAY'!BN6</f>
         <v>16.925000000000001</v>
       </c>
       <c r="J34" s="146"/>
@@ -10056,19 +10062,19 @@
       </c>
       <c r="E35" s="125">
         <f t="shared" si="1"/>
-        <v>25.34</v>
+        <v>8.5950000000000006</v>
       </c>
       <c r="F35" s="145">
-        <f>'STOK DETAY'!BN6</f>
+        <f>'STOK DETAY'!BO6</f>
         <v>0</v>
       </c>
       <c r="G35" s="146">
-        <f>'STOK DETAY'!BO6</f>
-        <v>8.1550000000000011</v>
+        <f>'STOK DETAY'!BP6</f>
+        <v>0</v>
       </c>
       <c r="H35" s="146">
-        <f>'STOK DETAY'!BP6</f>
-        <v>17.184999999999999</v>
+        <f>'STOK DETAY'!BQ6</f>
+        <v>8.5950000000000006</v>
       </c>
       <c r="I35" s="146"/>
       <c r="J35" s="146"/>
@@ -10102,19 +10108,19 @@
       </c>
       <c r="E36" s="125">
         <f t="shared" si="1"/>
-        <v>34.085000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="F36" s="145">
-        <f>'STOK DETAY'!BQ6</f>
-        <v>0</v>
-      </c>
-      <c r="G36" s="146">
         <f>'STOK DETAY'!BR6</f>
         <v>0</v>
       </c>
+      <c r="G36" s="146">
+        <f>'STOK DETAY'!BS6</f>
+        <v>0</v>
+      </c>
       <c r="H36" s="146">
-        <f>'STOK DETAY'!BS6</f>
-        <v>34.085000000000001</v>
+        <f>'STOK DETAY'!BT6</f>
+        <v>8.57</v>
       </c>
       <c r="I36" s="146"/>
       <c r="J36" s="146"/>
@@ -10148,21 +10154,21 @@
       </c>
       <c r="E37" s="125">
         <f t="shared" si="1"/>
-        <v>57.749999999999986</v>
+        <v>57.75</v>
       </c>
       <c r="F37" s="145">
-        <f>'STOK DETAY'!BT6</f>
-        <v>47.559999999999988</v>
+        <f>'STOK DETAY'!BU6</f>
+        <v>47.56</v>
       </c>
       <c r="G37" s="146"/>
       <c r="H37" s="146"/>
       <c r="I37" s="146"/>
       <c r="J37" s="146">
-        <f>'STOK DETAY'!BU6</f>
+        <f>'STOK DETAY'!BV6</f>
         <v>8.44</v>
       </c>
       <c r="K37" s="147">
-        <f>'STOK DETAY'!BV6</f>
+        <f>'STOK DETAY'!BW6</f>
         <v>1.75</v>
       </c>
       <c r="L37" s="74"/>
@@ -10194,18 +10200,18 @@
       </c>
       <c r="E38" s="125">
         <f t="shared" si="1"/>
-        <v>110.34</v>
+        <v>77.099999999999994</v>
       </c>
       <c r="F38" s="145">
-        <f>'STOK DETAY'!BW6</f>
+        <f>'STOK DETAY'!BX6</f>
         <v>0</v>
       </c>
       <c r="G38" s="146"/>
       <c r="H38" s="146"/>
       <c r="I38" s="146"/>
       <c r="J38" s="146">
-        <f>'STOK DETAY'!BX6</f>
-        <v>110.34</v>
+        <f>'STOK DETAY'!BY6</f>
+        <v>77.099999999999994</v>
       </c>
       <c r="K38" s="147"/>
       <c r="L38" s="74"/>
@@ -10240,14 +10246,14 @@
         <v>16.170000000000002</v>
       </c>
       <c r="F39" s="145">
-        <f>'STOK DETAY'!BY6</f>
+        <f>'STOK DETAY'!BZ6</f>
         <v>16.170000000000002</v>
       </c>
       <c r="G39" s="146"/>
       <c r="H39" s="146"/>
       <c r="I39" s="146"/>
       <c r="J39" s="146">
-        <f>'STOK DETAY'!BZ6</f>
+        <f>'STOK DETAY'!CA6</f>
         <v>0</v>
       </c>
       <c r="K39" s="147"/>
@@ -10285,7 +10291,7 @@
       <c r="H40" s="146"/>
       <c r="I40" s="146"/>
       <c r="J40" s="146">
-        <f>'STOK DETAY'!CA6</f>
+        <f>'STOK DETAY'!CB6</f>
         <v>0</v>
       </c>
       <c r="K40" s="147"/>
@@ -10325,7 +10331,7 @@
       <c r="H41" s="146"/>
       <c r="I41" s="146"/>
       <c r="J41" s="146">
-        <f>'STOK DETAY'!CB6</f>
+        <f>'STOK DETAY'!CC6</f>
         <v>27.65</v>
       </c>
       <c r="K41" s="147"/>
@@ -10359,7 +10365,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="145">
-        <f>'STOK DETAY'!CC6</f>
+        <f>'STOK DETAY'!CD6</f>
         <v>0</v>
       </c>
       <c r="G42" s="146"/>
@@ -10403,7 +10409,7 @@
       <c r="H43" s="146"/>
       <c r="I43" s="146"/>
       <c r="J43" s="146">
-        <f>'STOK DETAY'!CD6</f>
+        <f>'STOK DETAY'!CE6</f>
         <v>28</v>
       </c>
       <c r="K43" s="147"/>
@@ -10437,7 +10443,7 @@
         <v>0</v>
       </c>
       <c r="F44" s="145">
-        <f>'STOK DETAY'!CE6</f>
+        <f>'STOK DETAY'!CF6</f>
         <v>0</v>
       </c>
       <c r="G44" s="146"/>
@@ -10475,7 +10481,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="145">
-        <f>'STOK DETAY'!CF6</f>
+        <f>'STOK DETAY'!CG6</f>
         <v>0</v>
       </c>
       <c r="G45" s="146"/>
@@ -10512,15 +10518,15 @@
       </c>
       <c r="E46" s="125">
         <f t="shared" si="1"/>
-        <v>21.650000000000002</v>
+        <v>21.65</v>
       </c>
       <c r="F46" s="145"/>
       <c r="G46" s="146"/>
       <c r="H46" s="146"/>
       <c r="I46" s="146"/>
       <c r="J46" s="146">
-        <f>'STOK DETAY'!CG6</f>
-        <v>21.650000000000002</v>
+        <f>'STOK DETAY'!CH6</f>
+        <v>21.65</v>
       </c>
       <c r="K46" s="147"/>
       <c r="L46" s="74"/>
@@ -10587,15 +10593,15 @@
       </c>
       <c r="E48" s="125">
         <f t="shared" si="1"/>
-        <v>45.4</v>
+        <v>24.4</v>
       </c>
       <c r="F48" s="145"/>
       <c r="G48" s="146"/>
       <c r="H48" s="146"/>
       <c r="I48" s="146"/>
       <c r="J48" s="146">
-        <f>'STOK DETAY'!CI6</f>
-        <v>45.4</v>
+        <f>'STOK DETAY'!CJ6</f>
+        <v>24.4</v>
       </c>
       <c r="K48" s="147"/>
       <c r="L48" s="74"/>
@@ -10633,7 +10639,7 @@
       <c r="G49" s="146"/>
       <c r="H49" s="146"/>
       <c r="I49" s="146">
-        <f>'STOK DETAY'!CJ6</f>
+        <f>'STOK DETAY'!CK6</f>
         <v>9.1999999999999993</v>
       </c>
       <c r="J49" s="146"/>
@@ -10674,7 +10680,7 @@
       <c r="H50" s="146"/>
       <c r="I50" s="146"/>
       <c r="J50" s="146">
-        <f>'STOK DETAY'!CK6</f>
+        <f>'STOK DETAY'!CL6</f>
         <v>89.45</v>
       </c>
       <c r="K50" s="147"/>
@@ -10714,7 +10720,7 @@
       <c r="H51" s="146"/>
       <c r="I51" s="146"/>
       <c r="J51" s="146">
-        <f>'STOK DETAY'!CL6</f>
+        <f>'STOK DETAY'!CM6</f>
         <v>21.45</v>
       </c>
       <c r="K51" s="147"/>
@@ -10741,19 +10747,19 @@
       <c r="D52" s="356"/>
       <c r="E52" s="135">
         <f t="shared" si="1"/>
-        <v>848.38499999999999</v>
+        <v>729.38499999999999</v>
       </c>
       <c r="F52" s="136">
         <f t="shared" ref="F52:K52" si="2">SUM(F9:F51)</f>
-        <v>352.59000000000003</v>
+        <v>328.22</v>
       </c>
       <c r="G52" s="137">
         <f t="shared" si="2"/>
-        <v>55.615000000000002</v>
+        <v>39.56</v>
       </c>
       <c r="H52" s="137">
         <f>SUM(H9:H51)</f>
-        <v>76.849999999999994</v>
+        <v>42.744999999999997</v>
       </c>
       <c r="I52" s="137">
         <f t="shared" si="2"/>
@@ -10761,7 +10767,7 @@
       </c>
       <c r="J52" s="137">
         <f t="shared" si="2"/>
-        <v>352.38</v>
+        <v>307.91000000000003</v>
       </c>
       <c r="K52" s="138">
         <f t="shared" si="2"/>
@@ -10843,7 +10849,7 @@
         <v>54.058</v>
       </c>
       <c r="F54" s="145">
-        <f>'STOK DETAY'!CM6</f>
+        <f>'STOK DETAY'!CN6</f>
         <v>54.058</v>
       </c>
       <c r="G54" s="146"/>
@@ -10881,7 +10887,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="145">
-        <f>'STOK DETAY'!CN6</f>
+        <f>'STOK DETAY'!CO6</f>
         <v>0</v>
       </c>
       <c r="G55" s="146"/>
@@ -10919,7 +10925,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="145">
-        <f>'STOK DETAY'!CO6</f>
+        <f>'STOK DETAY'!CP6</f>
         <v>0</v>
       </c>
       <c r="G56" s="146"/>
@@ -10959,11 +10965,11 @@
         <v>0</v>
       </c>
       <c r="F57" s="145">
-        <f>'STOK DETAY'!CP6</f>
+        <f>'STOK DETAY'!CQ6</f>
         <v>0</v>
       </c>
       <c r="G57" s="146">
-        <f>'STOK DETAY'!CQ6</f>
+        <f>'STOK DETAY'!CR6</f>
         <v>0</v>
       </c>
       <c r="H57" s="146"/>
@@ -11005,7 +11011,7 @@
       <c r="G58" s="146"/>
       <c r="H58" s="146"/>
       <c r="I58" s="146">
-        <f>'STOK DETAY'!CR6</f>
+        <f>'STOK DETAY'!CS6</f>
         <v>0</v>
       </c>
       <c r="J58" s="146"/>
@@ -11040,16 +11046,16 @@
         <v>0</v>
       </c>
       <c r="F59" s="145">
-        <f>'STOK DETAY'!CS6</f>
-        <v>0</v>
-      </c>
-      <c r="G59" s="146">
         <f>'STOK DETAY'!CT6</f>
         <v>0</v>
       </c>
+      <c r="G59" s="146">
+        <f>'STOK DETAY'!CU6</f>
+        <v>0</v>
+      </c>
       <c r="H59" s="146"/>
       <c r="I59" s="146">
-        <f>'STOK DETAY'!CU6</f>
+        <f>'STOK DETAY'!CV6</f>
         <v>0</v>
       </c>
       <c r="J59" s="146"/>
@@ -11084,7 +11090,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="145">
-        <f>'STOK DETAY'!CV6</f>
+        <f>'STOK DETAY'!CW6</f>
         <v>0</v>
       </c>
       <c r="G60" s="146"/>
@@ -11121,15 +11127,15 @@
       </c>
       <c r="E61" s="125">
         <f t="shared" si="3"/>
-        <v>13.32</v>
+        <v>6.6349999999999998</v>
       </c>
       <c r="F61" s="145">
-        <f>'STOK DETAY'!CW6</f>
+        <f>'STOK DETAY'!CX6</f>
         <v>0</v>
       </c>
       <c r="G61" s="146">
-        <f>'STOK DETAY'!CX6</f>
-        <v>13.32</v>
+        <f>'STOK DETAY'!CY6</f>
+        <v>6.6349999999999998</v>
       </c>
       <c r="H61" s="146"/>
       <c r="I61" s="146"/>
@@ -11167,7 +11173,7 @@
         <v>8.9849999999999994</v>
       </c>
       <c r="F62" s="145">
-        <f>'STOK DETAY'!CY6</f>
+        <f>'STOK DETAY'!CZ6</f>
         <v>8.9849999999999994</v>
       </c>
       <c r="G62" s="146"/>
@@ -11205,7 +11211,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="145">
-        <f>'STOK DETAY'!CZ6</f>
+        <f>'STOK DETAY'!DA6</f>
         <v>0</v>
       </c>
       <c r="G63" s="146"/>
@@ -11243,7 +11249,7 @@
         <v>0</v>
       </c>
       <c r="F64" s="145">
-        <f>'STOK DETAY'!DA6</f>
+        <f>'STOK DETAY'!DB6</f>
         <v>0</v>
       </c>
       <c r="G64" s="146"/>
@@ -11281,11 +11287,11 @@
         <v>0</v>
       </c>
       <c r="F65" s="145">
-        <f>'STOK DETAY'!DB6</f>
+        <f>'STOK DETAY'!DC6</f>
         <v>0</v>
       </c>
       <c r="G65" s="146">
-        <f>'STOK DETAY'!DC6</f>
+        <f>'STOK DETAY'!DD6</f>
         <v>0</v>
       </c>
       <c r="H65" s="146"/>
@@ -11327,7 +11333,7 @@
       <c r="G66" s="146"/>
       <c r="H66" s="146"/>
       <c r="I66" s="146">
-        <f>'STOK DETAY'!DD6</f>
+        <f>'STOK DETAY'!DE6</f>
         <v>93.39</v>
       </c>
       <c r="J66" s="146"/>
@@ -11364,7 +11370,7 @@
         <v>14.9</v>
       </c>
       <c r="F67" s="145">
-        <f>'STOK DETAY'!DE6</f>
+        <f>'STOK DETAY'!DF6</f>
         <v>14.9</v>
       </c>
       <c r="G67" s="146"/>
@@ -11407,7 +11413,7 @@
       <c r="G68" s="146"/>
       <c r="H68" s="146"/>
       <c r="I68" s="146">
-        <f>'STOK DETAY'!DF6</f>
+        <f>'STOK DETAY'!DG6</f>
         <v>6.02</v>
       </c>
       <c r="J68" s="146"/>
@@ -11444,7 +11450,7 @@
         <v>2.25</v>
       </c>
       <c r="F69" s="145">
-        <f>'STOK DETAY'!DG6</f>
+        <f>'STOK DETAY'!DH6</f>
         <v>2.25</v>
       </c>
       <c r="G69" s="146"/>
@@ -11475,7 +11481,7 @@
       <c r="D70" s="353"/>
       <c r="E70" s="135">
         <f t="shared" si="3"/>
-        <v>192.923</v>
+        <v>186.238</v>
       </c>
       <c r="F70" s="136">
         <f t="shared" ref="F70:K70" si="4">SUM(F54:F69)</f>
@@ -11483,7 +11489,7 @@
       </c>
       <c r="G70" s="137">
         <f t="shared" si="4"/>
-        <v>13.32</v>
+        <v>6.6349999999999998</v>
       </c>
       <c r="H70" s="137">
         <f>SUM(H54:H69)</f>
@@ -11575,7 +11581,7 @@
       <c r="F72" s="214"/>
       <c r="G72" s="215"/>
       <c r="H72" s="156">
-        <f>'STOK DETAY'!DH6</f>
+        <f>'STOK DETAY'!DI6</f>
         <v>3.28</v>
       </c>
       <c r="I72" s="156"/>
@@ -11611,7 +11617,7 @@
       <c r="F73" s="145"/>
       <c r="G73" s="216"/>
       <c r="H73" s="146">
-        <f>'STOK DETAY'!DI6</f>
+        <f>'STOK DETAY'!DJ6</f>
         <v>63.54</v>
       </c>
       <c r="I73" s="146"/>
@@ -11647,7 +11653,7 @@
       <c r="F74" s="145"/>
       <c r="G74" s="216"/>
       <c r="H74" s="146">
-        <f>'STOK DETAY'!DJ6</f>
+        <f>'STOK DETAY'!DK6</f>
         <v>10.45</v>
       </c>
       <c r="I74" s="146"/>
@@ -11684,7 +11690,7 @@
       <c r="G75" s="146"/>
       <c r="H75" s="146"/>
       <c r="I75" s="146">
-        <f>'STOK DETAY'!DK6</f>
+        <f>'STOK DETAY'!DL6</f>
         <v>0</v>
       </c>
       <c r="J75" s="146"/>
@@ -11718,12 +11724,12 @@
       </c>
       <c r="F76" s="217"/>
       <c r="G76" s="146">
-        <f>'STOK DETAY'!DL6</f>
+        <f>'STOK DETAY'!DM6</f>
         <v>404.44</v>
       </c>
       <c r="H76" s="146"/>
       <c r="I76" s="146">
-        <f>'STOK DETAY'!DM6</f>
+        <f>'STOK DETAY'!DN6</f>
         <v>0</v>
       </c>
       <c r="J76" s="146"/>
@@ -11758,7 +11764,7 @@
       <c r="F77" s="145"/>
       <c r="G77" s="216"/>
       <c r="H77" s="146">
-        <f>'STOK DETAY'!DN6</f>
+        <f>'STOK DETAY'!DO6</f>
         <v>2.5</v>
       </c>
       <c r="I77" s="146"/>
@@ -11794,7 +11800,7 @@
       <c r="F78" s="145"/>
       <c r="G78" s="216"/>
       <c r="H78" s="146">
-        <f>'STOK DETAY'!DO6</f>
+        <f>'STOK DETAY'!DP6</f>
         <v>14.7</v>
       </c>
       <c r="I78" s="146"/>
@@ -11830,7 +11836,7 @@
       <c r="F79" s="145"/>
       <c r="G79" s="216"/>
       <c r="H79" s="146">
-        <f>'STOK DETAY'!DP6</f>
+        <f>'STOK DETAY'!DQ6</f>
         <v>2.85</v>
       </c>
       <c r="I79" s="146"/>
@@ -11866,7 +11872,7 @@
       <c r="F80" s="145"/>
       <c r="G80" s="216"/>
       <c r="H80" s="146">
-        <f>'STOK DETAY'!DQ6</f>
+        <f>'STOK DETAY'!DR6</f>
         <v>6.83</v>
       </c>
       <c r="I80" s="146"/>
@@ -11902,7 +11908,7 @@
       <c r="F81" s="145"/>
       <c r="G81" s="216"/>
       <c r="H81" s="146">
-        <f>'STOK DETAY'!DR6</f>
+        <f>'STOK DETAY'!DS6</f>
         <v>9.2200000000000006</v>
       </c>
       <c r="I81" s="146"/>
@@ -11938,7 +11944,7 @@
       <c r="F82" s="145"/>
       <c r="G82" s="216"/>
       <c r="H82" s="146">
-        <f>'STOK DETAY'!DS6</f>
+        <f>'STOK DETAY'!DT6</f>
         <v>18.5</v>
       </c>
       <c r="I82" s="146"/>
@@ -11974,7 +11980,7 @@
       <c r="F83" s="132"/>
       <c r="G83" s="219"/>
       <c r="H83" s="133">
-        <f>'STOK DETAY'!DT6</f>
+        <f>'STOK DETAY'!DU6</f>
         <v>52.36</v>
       </c>
       <c r="I83" s="133"/>
@@ -12003,7 +12009,7 @@
       <c r="D84" s="369"/>
       <c r="E84" s="135">
         <f t="shared" si="5"/>
-        <v>588.67000000000007</v>
+        <v>588.66999999999996</v>
       </c>
       <c r="F84" s="136">
         <f t="shared" ref="F84:K84" si="6">SUM(F72:F83)</f>
@@ -12015,7 +12021,7 @@
       </c>
       <c r="H84" s="137">
         <f>SUM(H72:H83)</f>
-        <v>184.23000000000002</v>
+        <v>184.23</v>
       </c>
       <c r="I84" s="137">
         <f t="shared" si="6"/>
@@ -12052,19 +12058,19 @@
       <c r="D85" s="350"/>
       <c r="E85" s="161">
         <f t="shared" si="5"/>
-        <v>1680.2930000000001</v>
+        <v>1546.2180000000001</v>
       </c>
       <c r="F85" s="162">
         <f t="shared" ref="F85:K85" si="7">F7+F52+F70+F84</f>
-        <v>432.78300000000002</v>
+        <v>408.41300000000001</v>
       </c>
       <c r="G85" s="163">
         <f t="shared" si="7"/>
-        <v>523.69000000000005</v>
+        <v>492.56</v>
       </c>
       <c r="H85" s="163">
         <f>H7+H52+H70+H84</f>
-        <v>261.08000000000004</v>
+        <v>226.97499999999999</v>
       </c>
       <c r="I85" s="163">
         <f t="shared" si="7"/>
@@ -12072,7 +12078,7 @@
       </c>
       <c r="J85" s="163">
         <f t="shared" si="7"/>
-        <v>352.38</v>
+        <v>307.91000000000003</v>
       </c>
       <c r="K85" s="164">
         <f t="shared" si="7"/>
@@ -30162,13 +30168,15 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:DT279"/>
+  <dimension ref="A1:DU280"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" style="50" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" style="19" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" style="22" customWidth="1"/>
-    <col min="4" max="6" width="12.7109375" style="174" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="174" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="230" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="174" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" style="230" customWidth="1"/>
     <col min="8" max="10" width="12.7109375" style="45" customWidth="1"/>
     <col min="11" max="12" width="12.7109375" style="237" customWidth="1"/>
@@ -30197,7 +30205,7 @@
     <col min="36" max="36" width="12.7109375" style="237" customWidth="1"/>
     <col min="37" max="37" width="12.7109375" style="255" customWidth="1"/>
     <col min="38" max="38" width="12.7109375" style="305" customWidth="1"/>
-    <col min="39" max="39" width="12.7109375" style="107" customWidth="1"/>
+    <col min="39" max="39" width="12.7109375" style="237" customWidth="1"/>
     <col min="40" max="40" width="12.7109375" style="255" customWidth="1"/>
     <col min="41" max="41" width="12.7109375" style="305" customWidth="1"/>
     <col min="42" max="42" width="12.7109375" style="237" customWidth="1"/>
@@ -30210,75 +30218,76 @@
     <col min="49" max="49" width="12.7109375" style="255" customWidth="1"/>
     <col min="50" max="50" width="12.7109375" style="305" customWidth="1"/>
     <col min="51" max="51" width="12.7109375" style="237" customWidth="1"/>
-    <col min="52" max="52" width="12.7109375" style="323" customWidth="1"/>
+    <col min="52" max="52" width="12.7109375" style="255" customWidth="1"/>
     <col min="53" max="53" width="12.7109375" style="305" customWidth="1"/>
     <col min="54" max="54" width="12.7109375" style="237" customWidth="1"/>
     <col min="55" max="55" width="12.7109375" style="323" customWidth="1"/>
     <col min="56" max="56" width="12.7109375" style="305" customWidth="1"/>
-    <col min="57" max="57" width="12.7109375" style="237" customWidth="1"/>
+    <col min="57" max="57" width="12.7109375" style="107" customWidth="1"/>
     <col min="58" max="58" width="12.7109375" style="255" customWidth="1"/>
-    <col min="59" max="59" width="12.7109375" style="299" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="170" customWidth="1"/>
     <col min="60" max="60" width="12.7109375" style="247" customWidth="1"/>
     <col min="61" max="61" width="12.7109375" style="255" customWidth="1"/>
     <col min="62" max="62" width="12.7109375" style="316" customWidth="1"/>
-    <col min="63" max="63" width="12.7109375" style="237" customWidth="1"/>
-    <col min="64" max="64" width="12.7109375" style="255" customWidth="1"/>
-    <col min="65" max="65" width="12.7109375" style="170" customWidth="1"/>
-    <col min="66" max="66" width="12.7109375" style="237" customWidth="1"/>
-    <col min="67" max="67" width="12.7109375" style="255" customWidth="1"/>
-    <col min="68" max="68" width="12.7109375" style="299" customWidth="1"/>
-    <col min="69" max="69" width="12.7109375" style="237" customWidth="1"/>
-    <col min="70" max="70" width="12.7109375" style="255" customWidth="1"/>
-    <col min="71" max="71" width="12.7109375" style="299" customWidth="1"/>
-    <col min="72" max="72" width="12.7109375" style="35" customWidth="1"/>
-    <col min="73" max="73" width="12.7109375" style="63" customWidth="1"/>
-    <col min="74" max="74" width="12.7109375" style="199" customWidth="1"/>
-    <col min="75" max="75" width="12.7109375" style="247" customWidth="1"/>
-    <col min="76" max="76" width="12.7109375" style="63" customWidth="1"/>
-    <col min="77" max="77" width="12.7109375" style="107" customWidth="1"/>
-    <col min="78" max="78" width="12.7109375" style="261" customWidth="1"/>
-    <col min="79" max="79" width="12.7109375" style="330" customWidth="1"/>
-    <col min="80" max="80" width="12.7109375" style="69" customWidth="1"/>
-    <col min="81" max="81" width="12.7109375" style="237" customWidth="1"/>
-    <col min="82" max="82" width="12.7109375" style="69" customWidth="1"/>
-    <col min="83" max="83" width="12.7109375" style="247" customWidth="1"/>
-    <col min="84" max="84" width="12.7109375" style="267" customWidth="1"/>
-    <col min="85" max="85" width="12.7109375" style="56" customWidth="1"/>
-    <col min="86" max="86" width="12.7109375" style="247" customWidth="1"/>
-    <col min="87" max="87" width="12.7109375" style="56" customWidth="1"/>
-    <col min="88" max="88" width="12.7109375" style="26" customWidth="1"/>
-    <col min="89" max="89" width="12.7109375" style="63" customWidth="1"/>
-    <col min="90" max="90" width="12.7109375" style="207" customWidth="1"/>
-    <col min="91" max="91" width="12.7109375" style="40" customWidth="1"/>
-    <col min="92" max="92" width="12.7109375" style="267" customWidth="1"/>
-    <col min="93" max="93" width="12.7109375" style="273" customWidth="1"/>
-    <col min="94" max="94" width="12.7109375" style="35" customWidth="1"/>
-    <col min="95" max="95" width="12.7109375" style="248" customWidth="1"/>
-    <col min="96" max="96" width="12.7109375" style="293" customWidth="1"/>
-    <col min="97" max="97" width="12.7109375" style="237" customWidth="1"/>
-    <col min="98" max="98" width="12.7109375" style="255" customWidth="1"/>
-    <col min="99" max="99" width="12.7109375" style="279" customWidth="1"/>
-    <col min="100" max="100" width="12.7109375" style="273" customWidth="1"/>
-    <col min="101" max="101" width="12.7109375" style="247" customWidth="1"/>
-    <col min="102" max="102" width="12.7109375" style="72" customWidth="1"/>
-    <col min="103" max="103" width="12.7109375" style="40" customWidth="1"/>
-    <col min="104" max="105" width="12.7109375" style="267" customWidth="1"/>
-    <col min="106" max="106" width="12.7109375" style="237" customWidth="1"/>
-    <col min="107" max="107" width="12.7109375" style="273" customWidth="1"/>
-    <col min="108" max="108" width="12.7109375" style="26" customWidth="1"/>
-    <col min="109" max="109" width="12.7109375" style="45" customWidth="1"/>
-    <col min="110" max="110" width="12.7109375" style="26" customWidth="1"/>
-    <col min="111" max="111" width="12.7109375" style="107" customWidth="1"/>
-    <col min="112" max="112" width="12.7109375" style="103" customWidth="1"/>
-    <col min="113" max="114" width="12.7109375" style="98" customWidth="1"/>
-    <col min="115" max="115" width="12.7109375" style="282" customWidth="1"/>
-    <col min="116" max="116" width="12.7109375" style="211" customWidth="1"/>
-    <col min="117" max="117" width="12.7109375" style="279" customWidth="1"/>
-    <col min="118" max="124" width="12.7109375" style="98" customWidth="1"/>
-    <col min="125" max="16384" width="9.140625" style="21"/>
+    <col min="63" max="63" width="12.7109375" style="63" customWidth="1"/>
+    <col min="64" max="64" width="12.7109375" style="237" customWidth="1"/>
+    <col min="65" max="65" width="12.7109375" style="255" customWidth="1"/>
+    <col min="66" max="66" width="12.7109375" style="170" customWidth="1"/>
+    <col min="67" max="67" width="12.7109375" style="237" customWidth="1"/>
+    <col min="68" max="68" width="12.7109375" style="255" customWidth="1"/>
+    <col min="69" max="69" width="12.7109375" style="299" customWidth="1"/>
+    <col min="70" max="70" width="12.7109375" style="237" customWidth="1"/>
+    <col min="71" max="71" width="12.7109375" style="255" customWidth="1"/>
+    <col min="72" max="72" width="12.7109375" style="299" customWidth="1"/>
+    <col min="73" max="73" width="12.7109375" style="35" customWidth="1"/>
+    <col min="74" max="74" width="12.7109375" style="63" customWidth="1"/>
+    <col min="75" max="75" width="12.7109375" style="199" customWidth="1"/>
+    <col min="76" max="76" width="12.7109375" style="247" customWidth="1"/>
+    <col min="77" max="77" width="12.7109375" style="63" customWidth="1"/>
+    <col min="78" max="78" width="12.7109375" style="107" customWidth="1"/>
+    <col min="79" max="79" width="12.7109375" style="261" customWidth="1"/>
+    <col min="80" max="80" width="12.7109375" style="330" customWidth="1"/>
+    <col min="81" max="81" width="12.7109375" style="69" customWidth="1"/>
+    <col min="82" max="82" width="12.7109375" style="237" customWidth="1"/>
+    <col min="83" max="83" width="12.7109375" style="69" customWidth="1"/>
+    <col min="84" max="84" width="12.7109375" style="247" customWidth="1"/>
+    <col min="85" max="85" width="12.7109375" style="267" customWidth="1"/>
+    <col min="86" max="86" width="12.7109375" style="56" customWidth="1"/>
+    <col min="87" max="87" width="12.7109375" style="247" customWidth="1"/>
+    <col min="88" max="88" width="12.7109375" style="56" customWidth="1"/>
+    <col min="89" max="89" width="12.7109375" style="26" customWidth="1"/>
+    <col min="90" max="90" width="12.7109375" style="63" customWidth="1"/>
+    <col min="91" max="91" width="12.7109375" style="207" customWidth="1"/>
+    <col min="92" max="92" width="12.7109375" style="40" customWidth="1"/>
+    <col min="93" max="93" width="12.7109375" style="267" customWidth="1"/>
+    <col min="94" max="94" width="12.7109375" style="273" customWidth="1"/>
+    <col min="95" max="95" width="12.7109375" style="247" customWidth="1"/>
+    <col min="96" max="96" width="12.7109375" style="248" customWidth="1"/>
+    <col min="97" max="97" width="12.7109375" style="293" customWidth="1"/>
+    <col min="98" max="98" width="12.7109375" style="237" customWidth="1"/>
+    <col min="99" max="99" width="12.7109375" style="255" customWidth="1"/>
+    <col min="100" max="100" width="12.7109375" style="279" customWidth="1"/>
+    <col min="101" max="101" width="12.7109375" style="273" customWidth="1"/>
+    <col min="102" max="102" width="12.7109375" style="247" customWidth="1"/>
+    <col min="103" max="103" width="12.7109375" style="72" customWidth="1"/>
+    <col min="104" max="104" width="12.7109375" style="40" customWidth="1"/>
+    <col min="105" max="106" width="12.7109375" style="267" customWidth="1"/>
+    <col min="107" max="107" width="12.7109375" style="237" customWidth="1"/>
+    <col min="108" max="108" width="12.7109375" style="273" customWidth="1"/>
+    <col min="109" max="109" width="12.7109375" style="26" customWidth="1"/>
+    <col min="110" max="110" width="12.7109375" style="45" customWidth="1"/>
+    <col min="111" max="111" width="12.7109375" style="26" customWidth="1"/>
+    <col min="112" max="112" width="12.7109375" style="107" customWidth="1"/>
+    <col min="113" max="113" width="12.7109375" style="103" customWidth="1"/>
+    <col min="114" max="115" width="12.7109375" style="98" customWidth="1"/>
+    <col min="116" max="116" width="12.7109375" style="282" customWidth="1"/>
+    <col min="117" max="117" width="12.7109375" style="211" customWidth="1"/>
+    <col min="118" max="118" width="12.7109375" style="279" customWidth="1"/>
+    <col min="119" max="125" width="12.7109375" style="98" customWidth="1"/>
+    <col min="126" max="16384" width="9.140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" s="19" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:125" s="19" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="377" t="s">
         <v>15</v>
       </c>
@@ -30289,7 +30298,7 @@
       <c r="D1" s="171" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="171" t="s">
+      <c r="E1" s="225" t="s">
         <v>17</v>
       </c>
       <c r="F1" s="171" t="s">
@@ -30391,7 +30400,7 @@
       <c r="AL1" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="AM1" s="190" t="s">
+      <c r="AM1" s="231" t="s">
         <v>16</v>
       </c>
       <c r="AN1" s="250" t="s">
@@ -30430,7 +30439,7 @@
       <c r="AY1" s="231" t="s">
         <v>16</v>
       </c>
-      <c r="AZ1" s="318" t="s">
+      <c r="AZ1" s="250" t="s">
         <v>17</v>
       </c>
       <c r="BA1" s="310" t="s">
@@ -30445,13 +30454,13 @@
       <c r="BD1" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="BE1" s="231" t="s">
+      <c r="BE1" s="190" t="s">
         <v>16</v>
       </c>
       <c r="BF1" s="250" t="s">
         <v>17</v>
       </c>
-      <c r="BG1" s="294" t="s">
+      <c r="BG1" s="165" t="s">
         <v>3</v>
       </c>
       <c r="BH1" s="238" t="s">
@@ -30463,173 +30472,173 @@
       <c r="BJ1" s="311" t="s">
         <v>3</v>
       </c>
-      <c r="BK1" s="231" t="s">
+      <c r="BK1" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="BL1" s="231" t="s">
         <v>16</v>
       </c>
-      <c r="BL1" s="249" t="s">
+      <c r="BM1" s="249" t="s">
         <v>17</v>
       </c>
-      <c r="BM1" s="165" t="s">
+      <c r="BN1" s="165" t="s">
         <v>3</v>
       </c>
-      <c r="BN1" s="231" t="s">
+      <c r="BO1" s="231" t="s">
         <v>16</v>
       </c>
-      <c r="BO1" s="250" t="s">
+      <c r="BP1" s="250" t="s">
         <v>17</v>
       </c>
-      <c r="BP1" s="294" t="s">
+      <c r="BQ1" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="BQ1" s="231" t="s">
+      <c r="BR1" s="231" t="s">
         <v>16</v>
       </c>
-      <c r="BR1" s="250" t="s">
+      <c r="BS1" s="250" t="s">
         <v>17</v>
       </c>
-      <c r="BS1" s="294" t="s">
+      <c r="BT1" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="BT1" s="31" t="s">
+      <c r="BU1" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="BU1" s="200" t="s">
+      <c r="BV1" s="200" t="s">
         <v>6</v>
       </c>
-      <c r="BV1" s="201" t="s">
+      <c r="BW1" s="201" t="s">
         <v>5</v>
       </c>
-      <c r="BW1" s="238" t="s">
+      <c r="BX1" s="238" t="s">
         <v>16</v>
       </c>
-      <c r="BX1" s="59" t="s">
+      <c r="BY1" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="BY1" s="190" t="s">
+      <c r="BZ1" s="190" t="s">
         <v>16</v>
       </c>
-      <c r="BZ1" s="256" t="s">
+      <c r="CA1" s="256" t="s">
         <v>6</v>
       </c>
-      <c r="CA1" s="324" t="s">
+      <c r="CB1" s="324" t="s">
         <v>6</v>
       </c>
-      <c r="CB1" s="70" t="s">
+      <c r="CC1" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="CC1" s="231" t="s">
+      <c r="CD1" s="231" t="s">
         <v>16</v>
       </c>
-      <c r="CD1" s="75" t="s">
+      <c r="CE1" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="CE1" s="238" t="s">
+      <c r="CF1" s="238" t="s">
         <v>16</v>
       </c>
-      <c r="CF1" s="262" t="s">
+      <c r="CG1" s="262" t="s">
         <v>16</v>
       </c>
-      <c r="CG1" s="52" t="s">
+      <c r="CH1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="CH1" s="238" t="s">
+      <c r="CI1" s="238" t="s">
         <v>16</v>
       </c>
-      <c r="CI1" s="52" t="s">
+      <c r="CJ1" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="CJ1" s="208" t="s">
+      <c r="CK1" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="CK1" s="59" t="s">
+      <c r="CL1" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="CL1" s="202" t="s">
+      <c r="CM1" s="202" t="s">
         <v>6</v>
       </c>
-      <c r="CM1" s="36" t="s">
+      <c r="CN1" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="CN1" s="262" t="s">
+      <c r="CO1" s="262" t="s">
         <v>16</v>
       </c>
-      <c r="CO1" s="268" t="s">
+      <c r="CP1" s="268" t="s">
         <v>16</v>
       </c>
-      <c r="CP1" s="31" t="s">
+      <c r="CQ1" s="238" t="s">
         <v>16</v>
       </c>
-      <c r="CQ1" s="239" t="s">
+      <c r="CR1" s="239" t="s">
         <v>17</v>
       </c>
-      <c r="CR1" s="288" t="s">
+      <c r="CS1" s="288" t="s">
         <v>2</v>
       </c>
-      <c r="CS1" s="231" t="s">
+      <c r="CT1" s="231" t="s">
         <v>16</v>
       </c>
-      <c r="CT1" s="250" t="s">
+      <c r="CU1" s="250" t="s">
         <v>17</v>
       </c>
-      <c r="CU1" s="274" t="s">
+      <c r="CV1" s="274" t="s">
         <v>2</v>
       </c>
-      <c r="CV1" s="268" t="s">
+      <c r="CW1" s="268" t="s">
         <v>16</v>
       </c>
-      <c r="CW1" s="238" t="s">
+      <c r="CX1" s="238" t="s">
         <v>16</v>
       </c>
-      <c r="CX1" s="71" t="s">
+      <c r="CY1" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="CY1" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="CZ1" s="262" t="s">
+      <c r="CZ1" s="36" t="s">
         <v>16</v>
       </c>
       <c r="DA1" s="262" t="s">
         <v>16</v>
       </c>
-      <c r="DB1" s="231" t="s">
+      <c r="DB1" s="262" t="s">
         <v>16</v>
       </c>
-      <c r="DC1" s="287" t="s">
+      <c r="DC1" s="231" t="s">
+        <v>16</v>
+      </c>
+      <c r="DD1" s="287" t="s">
         <v>17</v>
       </c>
-      <c r="DD1" s="23" t="s">
+      <c r="DE1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="DE1" s="46" t="s">
+      <c r="DF1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="DF1" s="23" t="s">
+      <c r="DG1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="DG1" s="110" t="s">
+      <c r="DH1" s="110" t="s">
         <v>16</v>
       </c>
-      <c r="DH1" s="92" t="s">
-        <v>28</v>
-      </c>
-      <c r="DI1" s="93" t="s">
+      <c r="DI1" s="92" t="s">
         <v>28</v>
       </c>
       <c r="DJ1" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="DK1" s="280" t="s">
+      <c r="DK1" s="93" t="s">
+        <v>28</v>
+      </c>
+      <c r="DL1" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="DL1" s="209" t="s">
+      <c r="DM1" s="209" t="s">
         <v>17</v>
       </c>
-      <c r="DM1" s="274" t="s">
+      <c r="DN1" s="274" t="s">
         <v>2</v>
-      </c>
-      <c r="DN1" s="93" t="s">
-        <v>28</v>
       </c>
       <c r="DO1" s="93" t="s">
         <v>28</v>
@@ -30649,8 +30658,11 @@
       <c r="DT1" s="93" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:124" s="19" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DU1" s="93" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:125" s="19" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="377"/>
       <c r="B2" s="377"/>
       <c r="C2" s="49" t="s">
@@ -30659,7 +30671,7 @@
       <c r="D2" s="171" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="171" t="s">
+      <c r="E2" s="225" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="171" t="s">
@@ -30761,7 +30773,7 @@
       <c r="AL2" s="300" t="s">
         <v>7</v>
       </c>
-      <c r="AM2" s="190" t="s">
+      <c r="AM2" s="231" t="s">
         <v>7</v>
       </c>
       <c r="AN2" s="250" t="s">
@@ -30800,7 +30812,7 @@
       <c r="AY2" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="AZ2" s="318" t="s">
+      <c r="AZ2" s="250" t="s">
         <v>7</v>
       </c>
       <c r="BA2" s="310" t="s">
@@ -30815,13 +30827,13 @@
       <c r="BD2" s="300" t="s">
         <v>7</v>
       </c>
-      <c r="BE2" s="231" t="s">
+      <c r="BE2" s="190" t="s">
         <v>7</v>
       </c>
       <c r="BF2" s="250" t="s">
         <v>7</v>
       </c>
-      <c r="BG2" s="294" t="s">
+      <c r="BG2" s="165" t="s">
         <v>7</v>
       </c>
       <c r="BH2" s="238" t="s">
@@ -30833,173 +30845,173 @@
       <c r="BJ2" s="311" t="s">
         <v>7</v>
       </c>
-      <c r="BK2" s="231" t="s">
+      <c r="BK2" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="BL2" s="250" t="s">
+      <c r="BL2" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="BM2" s="165" t="s">
+      <c r="BM2" s="250" t="s">
         <v>7</v>
       </c>
-      <c r="BN2" s="231" t="s">
+      <c r="BN2" s="165" t="s">
         <v>7</v>
       </c>
-      <c r="BO2" s="250" t="s">
+      <c r="BO2" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="BP2" s="294" t="s">
+      <c r="BP2" s="250" t="s">
         <v>7</v>
       </c>
-      <c r="BQ2" s="231" t="s">
+      <c r="BQ2" s="294" t="s">
         <v>7</v>
       </c>
-      <c r="BR2" s="250" t="s">
+      <c r="BR2" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="BS2" s="294" t="s">
+      <c r="BS2" s="250" t="s">
         <v>7</v>
       </c>
-      <c r="BT2" s="31" t="s">
+      <c r="BT2" s="294" t="s">
         <v>7</v>
       </c>
-      <c r="BU2" s="59" t="s">
+      <c r="BU2" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="BV2" s="195" t="s">
+      <c r="BV2" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="BW2" s="238" t="s">
+      <c r="BW2" s="195" t="s">
         <v>7</v>
       </c>
-      <c r="BX2" s="59" t="s">
+      <c r="BX2" s="238" t="s">
         <v>7</v>
       </c>
-      <c r="BY2" s="190" t="s">
+      <c r="BY2" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="BZ2" s="256" t="s">
+      <c r="BZ2" s="190" t="s">
         <v>7</v>
       </c>
-      <c r="CA2" s="325" t="s">
+      <c r="CA2" s="256" t="s">
         <v>7</v>
       </c>
-      <c r="CB2" s="70" t="s">
+      <c r="CB2" s="325" t="s">
+        <v>7</v>
+      </c>
+      <c r="CC2" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="CC2" s="231" t="s">
+      <c r="CD2" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="CD2" s="75" t="s">
+      <c r="CE2" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="CE2" s="238" t="s">
+      <c r="CF2" s="238" t="s">
         <v>9</v>
       </c>
-      <c r="CF2" s="262" t="s">
+      <c r="CG2" s="262" t="s">
         <v>9</v>
       </c>
-      <c r="CG2" s="52" t="s">
+      <c r="CH2" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="CH2" s="238" t="s">
+      <c r="CI2" s="238" t="s">
         <v>9</v>
       </c>
-      <c r="CI2" s="52" t="s">
+      <c r="CJ2" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="CJ2" s="23" t="s">
+      <c r="CK2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="CK2" s="59" t="s">
+      <c r="CL2" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="CL2" s="202" t="s">
+      <c r="CM2" s="202" t="s">
         <v>9</v>
       </c>
-      <c r="CM2" s="36" t="s">
+      <c r="CN2" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="CN2" s="262" t="s">
+      <c r="CO2" s="262" t="s">
         <v>7</v>
       </c>
-      <c r="CO2" s="268" t="s">
+      <c r="CP2" s="268" t="s">
         <v>7</v>
       </c>
-      <c r="CP2" s="31" t="s">
+      <c r="CQ2" s="238" t="s">
         <v>7</v>
       </c>
-      <c r="CQ2" s="239" t="s">
+      <c r="CR2" s="239" t="s">
         <v>7</v>
       </c>
-      <c r="CR2" s="288" t="s">
+      <c r="CS2" s="288" t="s">
         <v>7</v>
       </c>
-      <c r="CS2" s="231" t="s">
+      <c r="CT2" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="CT2" s="250" t="s">
+      <c r="CU2" s="250" t="s">
         <v>7</v>
       </c>
-      <c r="CU2" s="274" t="s">
+      <c r="CV2" s="274" t="s">
         <v>7</v>
       </c>
-      <c r="CV2" s="268" t="s">
+      <c r="CW2" s="268" t="s">
         <v>7</v>
       </c>
-      <c r="CW2" s="238" t="s">
+      <c r="CX2" s="238" t="s">
         <v>7</v>
       </c>
-      <c r="CX2" s="71" t="s">
+      <c r="CY2" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="CY2" s="36" t="s">
-        <v>7</v>
-      </c>
-      <c r="CZ2" s="262" t="s">
+      <c r="CZ2" s="36" t="s">
         <v>7</v>
       </c>
       <c r="DA2" s="262" t="s">
         <v>7</v>
       </c>
-      <c r="DB2" s="231" t="s">
+      <c r="DB2" s="262" t="s">
         <v>7</v>
       </c>
-      <c r="DC2" s="287" t="s">
+      <c r="DC2" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="DD2" s="23" t="s">
+      <c r="DD2" s="287" t="s">
         <v>7</v>
       </c>
-      <c r="DE2" s="46" t="s">
+      <c r="DE2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="DF2" s="23" t="s">
+      <c r="DF2" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="DG2" s="110" t="s">
+      <c r="DG2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="DH2" s="92" t="s">
-        <v>28</v>
-      </c>
-      <c r="DI2" s="93" t="s">
+      <c r="DH2" s="110" t="s">
+        <v>7</v>
+      </c>
+      <c r="DI2" s="92" t="s">
         <v>28</v>
       </c>
       <c r="DJ2" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="DK2" s="280" t="s">
+      <c r="DK2" s="93" t="s">
+        <v>28</v>
+      </c>
+      <c r="DL2" s="280" t="s">
         <v>29</v>
       </c>
-      <c r="DL2" s="209" t="s">
+      <c r="DM2" s="209" t="s">
         <v>29</v>
       </c>
-      <c r="DM2" s="274" t="s">
+      <c r="DN2" s="274" t="s">
         <v>8</v>
-      </c>
-      <c r="DN2" s="93" t="s">
-        <v>28</v>
       </c>
       <c r="DO2" s="93" t="s">
         <v>28</v>
@@ -31019,8 +31031,11 @@
       <c r="DT2" s="93" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:124" s="19" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DU2" s="93" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:125" s="19" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="377"/>
       <c r="B3" s="377"/>
       <c r="C3" s="49" t="s">
@@ -31029,7 +31044,7 @@
       <c r="D3" s="171" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="171" t="s">
+      <c r="E3" s="225" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="171" t="s">
@@ -31131,7 +31146,7 @@
       <c r="AL3" s="300" t="s">
         <v>14</v>
       </c>
-      <c r="AM3" s="190" t="s">
+      <c r="AM3" s="231" t="s">
         <v>14</v>
       </c>
       <c r="AN3" s="250" t="s">
@@ -31170,7 +31185,7 @@
       <c r="AY3" s="231" t="s">
         <v>14</v>
       </c>
-      <c r="AZ3" s="318" t="s">
+      <c r="AZ3" s="250" t="s">
         <v>14</v>
       </c>
       <c r="BA3" s="310" t="s">
@@ -31185,13 +31200,13 @@
       <c r="BD3" s="300" t="s">
         <v>14</v>
       </c>
-      <c r="BE3" s="231" t="s">
+      <c r="BE3" s="190" t="s">
         <v>14</v>
       </c>
       <c r="BF3" s="250" t="s">
         <v>14</v>
       </c>
-      <c r="BG3" s="294" t="s">
+      <c r="BG3" s="165" t="s">
         <v>14</v>
       </c>
       <c r="BH3" s="238" t="s">
@@ -31203,172 +31218,172 @@
       <c r="BJ3" s="311" t="s">
         <v>14</v>
       </c>
-      <c r="BK3" s="231" t="s">
+      <c r="BK3" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="BL3" s="250" t="s">
+      <c r="BL3" s="231" t="s">
         <v>14</v>
       </c>
-      <c r="BM3" s="165" t="s">
+      <c r="BM3" s="250" t="s">
         <v>14</v>
       </c>
-      <c r="BN3" s="231" t="s">
+      <c r="BN3" s="165" t="s">
         <v>14</v>
       </c>
-      <c r="BO3" s="250" t="s">
+      <c r="BO3" s="231" t="s">
         <v>14</v>
       </c>
-      <c r="BP3" s="294" t="s">
+      <c r="BP3" s="250" t="s">
         <v>14</v>
       </c>
-      <c r="BQ3" s="231" t="s">
+      <c r="BQ3" s="294" t="s">
         <v>14</v>
       </c>
-      <c r="BR3" s="250" t="s">
+      <c r="BR3" s="231" t="s">
         <v>14</v>
       </c>
-      <c r="BS3" s="294" t="s">
+      <c r="BS3" s="250" t="s">
         <v>14</v>
       </c>
-      <c r="BT3" s="31" t="s">
+      <c r="BT3" s="294" t="s">
         <v>14</v>
       </c>
-      <c r="BU3" s="59" t="s">
+      <c r="BU3" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="BV3" s="195" t="s">
+      <c r="BV3" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="BW3" s="238" t="s">
+      <c r="BW3" s="195" t="s">
         <v>14</v>
       </c>
-      <c r="BX3" s="59" t="s">
+      <c r="BX3" s="238" t="s">
         <v>14</v>
       </c>
-      <c r="BY3" s="190" t="s">
+      <c r="BY3" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="BZ3" s="256" t="s">
+      <c r="BZ3" s="190" t="s">
         <v>14</v>
       </c>
-      <c r="CA3" s="325" t="s">
+      <c r="CA3" s="256" t="s">
         <v>14</v>
       </c>
-      <c r="CB3" s="70" t="s">
+      <c r="CB3" s="325" t="s">
         <v>14</v>
       </c>
-      <c r="CC3" s="231" t="s">
+      <c r="CC3" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="CD3" s="75" t="s">
+      <c r="CD3" s="231" t="s">
         <v>14</v>
       </c>
-      <c r="CE3" s="238" t="s">
+      <c r="CE3" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="CF3" s="262" t="s">
+      <c r="CF3" s="238" t="s">
         <v>14</v>
       </c>
-      <c r="CG3" s="52" t="s">
+      <c r="CG3" s="262" t="s">
         <v>14</v>
       </c>
-      <c r="CH3" s="238" t="s">
+      <c r="CH3" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="CI3" s="52" t="s">
+      <c r="CI3" s="238" t="s">
         <v>14</v>
       </c>
-      <c r="CJ3" s="23" t="s">
+      <c r="CJ3" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="CK3" s="59" t="s">
+      <c r="CK3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="CL3" s="202" t="s">
+      <c r="CL3" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="CM3" s="36" t="s">
+      <c r="CM3" s="202" t="s">
+        <v>14</v>
+      </c>
+      <c r="CN3" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="CN3" s="262" t="s">
+      <c r="CO3" s="262" t="s">
         <v>12</v>
       </c>
-      <c r="CO3" s="268" t="s">
+      <c r="CP3" s="268" t="s">
         <v>12</v>
       </c>
-      <c r="CP3" s="31" t="s">
+      <c r="CQ3" s="238" t="s">
         <v>12</v>
       </c>
-      <c r="CQ3" s="239" t="s">
+      <c r="CR3" s="239" t="s">
         <v>12</v>
       </c>
-      <c r="CR3" s="288" t="s">
+      <c r="CS3" s="288" t="s">
         <v>12</v>
       </c>
-      <c r="CS3" s="231" t="s">
+      <c r="CT3" s="231" t="s">
         <v>12</v>
       </c>
-      <c r="CT3" s="250" t="s">
+      <c r="CU3" s="250" t="s">
         <v>12</v>
       </c>
-      <c r="CU3" s="274" t="s">
+      <c r="CV3" s="274" t="s">
         <v>12</v>
       </c>
-      <c r="CV3" s="268" t="s">
+      <c r="CW3" s="268" t="s">
         <v>12</v>
       </c>
-      <c r="CW3" s="238" t="s">
+      <c r="CX3" s="238" t="s">
         <v>12</v>
       </c>
-      <c r="CX3" s="71" t="s">
+      <c r="CY3" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="CY3" s="36" t="s">
-        <v>12</v>
-      </c>
-      <c r="CZ3" s="262" t="s">
+      <c r="CZ3" s="36" t="s">
         <v>12</v>
       </c>
       <c r="DA3" s="262" t="s">
         <v>12</v>
       </c>
-      <c r="DB3" s="231" t="s">
+      <c r="DB3" s="262" t="s">
         <v>12</v>
       </c>
-      <c r="DC3" s="287" t="s">
+      <c r="DC3" s="231" t="s">
         <v>12</v>
       </c>
-      <c r="DD3" s="23" t="s">
+      <c r="DD3" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="DE3" s="46" t="s">
+      <c r="DE3" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="DF3" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="DF3" s="23" t="s">
+      <c r="DG3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="DG3" s="110" t="s">
+      <c r="DH3" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="DH3" s="92" t="s">
-        <v>10</v>
-      </c>
-      <c r="DI3" s="93" t="s">
+      <c r="DI3" s="92" t="s">
         <v>10</v>
       </c>
       <c r="DJ3" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="DK3" s="280" t="s">
+      <c r="DK3" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="DL3" s="209" t="s">
+      <c r="DL3" s="280" t="s">
         <v>10</v>
       </c>
-      <c r="DM3" s="274" t="s">
+      <c r="DM3" s="209" t="s">
         <v>10</v>
       </c>
-      <c r="DN3" s="93" t="s">
+      <c r="DN3" s="274" t="s">
         <v>10</v>
       </c>
       <c r="DO3" s="93" t="s">
@@ -31389,8 +31404,11 @@
       <c r="DT3" s="93" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:124" s="20" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DU3" s="93" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:125" s="20" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="377"/>
       <c r="B4" s="377"/>
       <c r="C4" s="49" t="s">
@@ -31399,7 +31417,7 @@
       <c r="D4" s="172">
         <v>0.4</v>
       </c>
-      <c r="E4" s="172">
+      <c r="E4" s="226">
         <v>0.5</v>
       </c>
       <c r="F4" s="172">
@@ -31501,7 +31519,7 @@
       <c r="AL4" s="301">
         <v>0.75</v>
       </c>
-      <c r="AM4" s="104">
+      <c r="AM4" s="233">
         <v>0.8</v>
       </c>
       <c r="AN4" s="251">
@@ -31540,7 +31558,7 @@
       <c r="AY4" s="233">
         <v>1</v>
       </c>
-      <c r="AZ4" s="319">
+      <c r="AZ4" s="251">
         <v>1</v>
       </c>
       <c r="BA4" s="301">
@@ -31555,13 +31573,13 @@
       <c r="BD4" s="301">
         <v>1.05</v>
       </c>
-      <c r="BE4" s="233">
+      <c r="BE4" s="104">
         <v>1.1000000000000001</v>
       </c>
       <c r="BF4" s="251">
         <v>1.1000000000000001</v>
       </c>
-      <c r="BG4" s="295">
+      <c r="BG4" s="166">
         <v>1.1000000000000001</v>
       </c>
       <c r="BH4" s="240">
@@ -31573,199 +31591,202 @@
       <c r="BJ4" s="312">
         <v>1.1499999999999999</v>
       </c>
-      <c r="BK4" s="233">
+      <c r="BK4" s="60">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="BL4" s="233">
         <v>1.2</v>
       </c>
-      <c r="BL4" s="251">
+      <c r="BM4" s="251">
         <v>1.2</v>
       </c>
-      <c r="BM4" s="166">
+      <c r="BN4" s="166">
         <v>1.2</v>
       </c>
-      <c r="BN4" s="233">
+      <c r="BO4" s="233">
         <v>1.25</v>
       </c>
-      <c r="BO4" s="251">
+      <c r="BP4" s="251">
         <v>1.25</v>
       </c>
-      <c r="BP4" s="295">
+      <c r="BQ4" s="295">
         <v>1.25</v>
       </c>
-      <c r="BQ4" s="233">
+      <c r="BR4" s="233">
         <v>1.3</v>
       </c>
-      <c r="BR4" s="251">
+      <c r="BS4" s="251">
         <v>1.3</v>
       </c>
-      <c r="BS4" s="295">
+      <c r="BT4" s="295">
         <v>1.3</v>
       </c>
-      <c r="BT4" s="32">
+      <c r="BU4" s="32">
         <v>1.35</v>
       </c>
-      <c r="BU4" s="60">
+      <c r="BV4" s="60">
         <v>1.35</v>
       </c>
-      <c r="BV4" s="196">
+      <c r="BW4" s="196">
         <v>1.35</v>
       </c>
-      <c r="BW4" s="240">
+      <c r="BX4" s="240">
         <v>1.4</v>
       </c>
-      <c r="BX4" s="60">
+      <c r="BY4" s="60">
         <v>1.4</v>
       </c>
-      <c r="BY4" s="104">
+      <c r="BZ4" s="104">
         <v>1.45</v>
       </c>
-      <c r="BZ4" s="257">
+      <c r="CA4" s="257">
         <v>1.45</v>
       </c>
-      <c r="CA4" s="326">
+      <c r="CB4" s="326">
         <v>1.5</v>
       </c>
-      <c r="CB4" s="67">
+      <c r="CC4" s="67">
         <v>1.55</v>
       </c>
-      <c r="CC4" s="233">
+      <c r="CD4" s="233">
         <v>1.6</v>
       </c>
-      <c r="CD4" s="67">
+      <c r="CE4" s="67">
         <v>1.85</v>
       </c>
-      <c r="CE4" s="240">
+      <c r="CF4" s="240">
         <v>1.9</v>
       </c>
-      <c r="CF4" s="263">
+      <c r="CG4" s="263">
         <v>2</v>
       </c>
-      <c r="CG4" s="53">
+      <c r="CH4" s="53">
         <v>2.2000000000000002</v>
       </c>
-      <c r="CH4" s="240">
+      <c r="CI4" s="240">
         <v>2.5</v>
       </c>
-      <c r="CI4" s="53">
+      <c r="CJ4" s="53">
         <v>2.6</v>
       </c>
-      <c r="CJ4" s="24">
+      <c r="CK4" s="24">
         <v>2.7</v>
       </c>
-      <c r="CK4" s="60">
+      <c r="CL4" s="60">
         <v>3</v>
       </c>
-      <c r="CL4" s="203">
+      <c r="CM4" s="203">
         <v>3.2</v>
       </c>
-      <c r="CM4" s="37">
+      <c r="CN4" s="37">
         <v>0.08</v>
       </c>
-      <c r="CN4" s="263">
+      <c r="CO4" s="263">
         <v>0.12</v>
       </c>
-      <c r="CO4" s="269">
+      <c r="CP4" s="269">
         <v>0.14000000000000001</v>
       </c>
-      <c r="CP4" s="32">
+      <c r="CQ4" s="240">
         <v>0.2</v>
       </c>
-      <c r="CQ4" s="241">
+      <c r="CR4" s="241">
         <v>0.2</v>
       </c>
-      <c r="CR4" s="289">
+      <c r="CS4" s="289">
         <v>0.23</v>
       </c>
-      <c r="CS4" s="233">
+      <c r="CT4" s="233">
         <v>0.25</v>
       </c>
-      <c r="CT4" s="251">
+      <c r="CU4" s="251">
         <v>0.25</v>
       </c>
-      <c r="CU4" s="275">
+      <c r="CV4" s="275">
         <v>0.25</v>
       </c>
-      <c r="CV4" s="269">
+      <c r="CW4" s="269">
         <v>0.28000000000000003</v>
       </c>
-      <c r="CW4" s="240">
+      <c r="CX4" s="240">
         <v>0.3</v>
       </c>
-      <c r="CX4" s="57">
+      <c r="CY4" s="57">
         <v>0.3</v>
       </c>
-      <c r="CY4" s="37">
+      <c r="CZ4" s="37">
         <v>0.32</v>
       </c>
-      <c r="CZ4" s="263">
+      <c r="DA4" s="263">
         <v>0.35</v>
       </c>
-      <c r="DA4" s="263">
+      <c r="DB4" s="263">
         <v>0.38</v>
       </c>
-      <c r="DB4" s="233">
+      <c r="DC4" s="233">
         <v>0.4</v>
       </c>
-      <c r="DC4" s="269">
+      <c r="DD4" s="269">
         <v>0.4</v>
       </c>
-      <c r="DD4" s="24">
+      <c r="DE4" s="24">
         <v>0.45</v>
       </c>
-      <c r="DE4" s="42">
+      <c r="DF4" s="42">
         <v>0.45</v>
       </c>
-      <c r="DF4" s="24">
+      <c r="DG4" s="24">
         <v>0.6</v>
       </c>
-      <c r="DG4" s="104">
+      <c r="DH4" s="104">
         <v>0.95</v>
       </c>
-      <c r="DH4" s="94">
+      <c r="DI4" s="94">
         <v>0.3</v>
       </c>
-      <c r="DI4" s="95">
+      <c r="DJ4" s="95">
         <v>0.5</v>
       </c>
-      <c r="DJ4" s="95">
+      <c r="DK4" s="95">
         <v>0.55000000000000004</v>
       </c>
-      <c r="DK4" s="281">
+      <c r="DL4" s="281">
         <v>0.6</v>
       </c>
-      <c r="DL4" s="210">
+      <c r="DM4" s="210">
         <v>0.7</v>
       </c>
-      <c r="DM4" s="275">
+      <c r="DN4" s="275">
         <v>0.7</v>
       </c>
-      <c r="DN4" s="95">
+      <c r="DO4" s="95">
         <v>1</v>
       </c>
-      <c r="DO4" s="95">
+      <c r="DP4" s="95">
         <v>1.2</v>
       </c>
-      <c r="DP4" s="95">
+      <c r="DQ4" s="95">
         <v>1.3</v>
       </c>
-      <c r="DQ4" s="95">
+      <c r="DR4" s="95">
         <v>1.4</v>
       </c>
-      <c r="DR4" s="95">
+      <c r="DS4" s="95">
         <v>1.6</v>
       </c>
-      <c r="DS4" s="95">
+      <c r="DT4" s="95">
         <v>1.7</v>
       </c>
-      <c r="DT4" s="95">
+      <c r="DU4" s="95">
         <v>3.5</v>
       </c>
     </row>
-    <row r="5" spans="1:124" ht="6.75" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="5" spans="1:125" ht="6.75" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A5" s="377"/>
       <c r="B5" s="377"/>
       <c r="C5" s="48"/>
       <c r="D5" s="58"/>
-      <c r="E5" s="317"/>
+      <c r="E5" s="227"/>
       <c r="F5" s="317"/>
       <c r="G5" s="227"/>
       <c r="H5" s="43"/>
@@ -31799,7 +31820,7 @@
       <c r="AJ5" s="234"/>
       <c r="AK5" s="252"/>
       <c r="AL5" s="302"/>
-      <c r="AM5" s="105"/>
+      <c r="AM5" s="234"/>
       <c r="AN5" s="252"/>
       <c r="AO5" s="302"/>
       <c r="AP5" s="234"/>
@@ -31812,70 +31833,71 @@
       <c r="AW5" s="252"/>
       <c r="AX5" s="302"/>
       <c r="AY5" s="234"/>
-      <c r="AZ5" s="320"/>
+      <c r="AZ5" s="252"/>
       <c r="BA5" s="302"/>
       <c r="BB5" s="234"/>
       <c r="BC5" s="320"/>
       <c r="BD5" s="302"/>
-      <c r="BE5" s="234"/>
+      <c r="BE5" s="105"/>
       <c r="BF5" s="252"/>
-      <c r="BG5" s="296"/>
+      <c r="BG5" s="167"/>
       <c r="BH5" s="242"/>
       <c r="BI5" s="252"/>
       <c r="BJ5" s="313"/>
-      <c r="BK5" s="234"/>
-      <c r="BL5" s="252"/>
-      <c r="BM5" s="167"/>
-      <c r="BN5" s="234"/>
-      <c r="BO5" s="252"/>
-      <c r="BP5" s="296"/>
-      <c r="BQ5" s="234"/>
-      <c r="BR5" s="252"/>
-      <c r="BS5" s="296"/>
-      <c r="BT5" s="33"/>
-      <c r="BU5" s="61"/>
-      <c r="BV5" s="197"/>
-      <c r="BW5" s="242"/>
-      <c r="BX5" s="61"/>
-      <c r="BY5" s="105"/>
-      <c r="BZ5" s="258"/>
-      <c r="CA5" s="327"/>
-      <c r="CB5" s="68"/>
-      <c r="CC5" s="234"/>
-      <c r="CD5" s="68"/>
-      <c r="CE5" s="242"/>
-      <c r="CF5" s="264"/>
-      <c r="CG5" s="54"/>
-      <c r="CH5" s="242"/>
-      <c r="CI5" s="54"/>
-      <c r="CJ5" s="25"/>
-      <c r="CK5" s="61"/>
-      <c r="CL5" s="204"/>
-      <c r="CM5" s="38"/>
-      <c r="CN5" s="264"/>
-      <c r="CO5" s="270"/>
-      <c r="CP5" s="33"/>
-      <c r="CQ5" s="243"/>
-      <c r="CR5" s="290"/>
-      <c r="CS5" s="234"/>
-      <c r="CT5" s="252"/>
-      <c r="CU5" s="276"/>
-      <c r="CV5" s="270"/>
-      <c r="CW5" s="242"/>
-      <c r="CX5" s="58"/>
-      <c r="CY5" s="38"/>
-      <c r="CZ5" s="264"/>
+      <c r="BK5" s="61"/>
+      <c r="BL5" s="234"/>
+      <c r="BM5" s="252"/>
+      <c r="BN5" s="167"/>
+      <c r="BO5" s="234"/>
+      <c r="BP5" s="252"/>
+      <c r="BQ5" s="296"/>
+      <c r="BR5" s="234"/>
+      <c r="BS5" s="252"/>
+      <c r="BT5" s="296"/>
+      <c r="BU5" s="33"/>
+      <c r="BV5" s="61"/>
+      <c r="BW5" s="197"/>
+      <c r="BX5" s="242"/>
+      <c r="BY5" s="61"/>
+      <c r="BZ5" s="105"/>
+      <c r="CA5" s="258"/>
+      <c r="CB5" s="327"/>
+      <c r="CC5" s="68"/>
+      <c r="CD5" s="234"/>
+      <c r="CE5" s="68"/>
+      <c r="CF5" s="242"/>
+      <c r="CG5" s="264"/>
+      <c r="CH5" s="54"/>
+      <c r="CI5" s="242"/>
+      <c r="CJ5" s="54"/>
+      <c r="CK5" s="25"/>
+      <c r="CL5" s="61"/>
+      <c r="CM5" s="204"/>
+      <c r="CN5" s="38"/>
+      <c r="CO5" s="264"/>
+      <c r="CP5" s="270"/>
+      <c r="CQ5" s="242"/>
+      <c r="CR5" s="243"/>
+      <c r="CS5" s="290"/>
+      <c r="CT5" s="234"/>
+      <c r="CU5" s="252"/>
+      <c r="CV5" s="276"/>
+      <c r="CW5" s="270"/>
+      <c r="CX5" s="242"/>
+      <c r="CY5" s="58"/>
+      <c r="CZ5" s="38"/>
       <c r="DA5" s="264"/>
-      <c r="DB5" s="234"/>
-      <c r="DC5" s="270"/>
-      <c r="DD5" s="25"/>
-      <c r="DE5" s="43"/>
-      <c r="DF5" s="25"/>
-      <c r="DG5" s="105"/>
-      <c r="DH5" s="96"/>
-      <c r="DI5" s="97"/>
-    </row>
-    <row r="6" spans="1:124" s="87" customFormat="1" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="DB5" s="264"/>
+      <c r="DC5" s="234"/>
+      <c r="DD5" s="270"/>
+      <c r="DE5" s="25"/>
+      <c r="DF5" s="43"/>
+      <c r="DG5" s="25"/>
+      <c r="DH5" s="105"/>
+      <c r="DI5" s="96"/>
+      <c r="DJ5" s="97"/>
+    </row>
+    <row r="6" spans="1:125" s="87" customFormat="1" ht="27.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="77" t="s">
         <v>11</v>
       </c>
@@ -31883,16 +31905,16 @@
         <v>26</v>
       </c>
       <c r="C6" s="78">
-        <f>SUM(D6:DT6)</f>
-        <v>1680.2930000000001</v>
+        <f>SUM(D6:DU6)</f>
+        <v>1546.2180000000001</v>
       </c>
       <c r="D6" s="79">
         <f t="shared" ref="D6:AI6" si="0">SUM(D8:D1048576)</f>
         <v>8.7850000000000001</v>
       </c>
-      <c r="E6" s="79">
+      <c r="E6" s="228">
         <f t="shared" si="0"/>
-        <v>8.39</v>
+        <v>0</v>
       </c>
       <c r="F6" s="79">
         <f t="shared" si="0"/>
@@ -31908,7 +31930,7 @@
       </c>
       <c r="I6" s="80">
         <f t="shared" si="0"/>
-        <v>2.0999999999999996</v>
+        <v>2.1</v>
       </c>
       <c r="J6" s="80">
         <f t="shared" si="0"/>
@@ -31948,7 +31970,7 @@
       </c>
       <c r="S6" s="79">
         <f t="shared" si="0"/>
-        <v>5.8900000000000006</v>
+        <v>5.89</v>
       </c>
       <c r="T6" s="80">
         <f t="shared" si="0"/>
@@ -31956,7 +31978,7 @@
       </c>
       <c r="U6" s="235">
         <f t="shared" si="0"/>
-        <v>7.9936057773011271E-15</v>
+        <v>0</v>
       </c>
       <c r="V6" s="253">
         <f t="shared" si="0"/>
@@ -32026,9 +32048,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AM6" s="191">
+      <c r="AM6" s="235">
         <f t="shared" si="1"/>
-        <v>48.69</v>
+        <v>0</v>
       </c>
       <c r="AN6" s="253">
         <f t="shared" si="1"/>
@@ -32076,11 +32098,11 @@
       </c>
       <c r="AY6" s="235">
         <f t="shared" si="1"/>
-        <v>7.1054273576010019E-15</v>
-      </c>
-      <c r="AZ6" s="321">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="253">
         <f t="shared" si="1"/>
-        <v>8.32</v>
+        <v>0</v>
       </c>
       <c r="BA6" s="303">
         <f t="shared" si="1"/>
@@ -32092,21 +32114,21 @@
       </c>
       <c r="BC6" s="321">
         <f t="shared" si="1"/>
-        <v>33.25</v>
+        <v>33.67</v>
       </c>
       <c r="BD6" s="303">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BE6" s="235">
+      <c r="BE6" s="191">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>24.32</v>
       </c>
       <c r="BF6" s="253">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BG6" s="297">
+      <c r="BG6" s="168">
         <f t="shared" si="1"/>
         <v>8.6549999999999994</v>
       </c>
@@ -32122,261 +32144,265 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BK6" s="235">
+      <c r="BK6" s="83">
+        <f t="shared" si="1"/>
+        <v>9.77</v>
+      </c>
+      <c r="BL6" s="235">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BL6" s="253">
+      <c r="BM6" s="253">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BM6" s="168">
+      <c r="BN6" s="168">
         <f t="shared" si="1"/>
         <v>16.925000000000001</v>
       </c>
-      <c r="BN6" s="235">
+      <c r="BO6" s="235">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BO6" s="253">
-        <f t="shared" si="1"/>
-        <v>8.1550000000000011</v>
-      </c>
-      <c r="BP6" s="297">
+      <c r="BP6" s="253">
         <f t="shared" ref="BP6:CU6" si="2">SUM(BP8:BP1048576)</f>
-        <v>17.184999999999999</v>
-      </c>
-      <c r="BQ6" s="235">
+        <v>0</v>
+      </c>
+      <c r="BQ6" s="297">
+        <f t="shared" si="2"/>
+        <v>8.5950000000000006</v>
+      </c>
+      <c r="BR6" s="235">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BR6" s="253">
+      <c r="BS6" s="253">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BS6" s="297">
+      <c r="BT6" s="297">
         <f t="shared" si="2"/>
-        <v>34.085000000000001</v>
-      </c>
-      <c r="BT6" s="82">
+        <v>8.57</v>
+      </c>
+      <c r="BU6" s="82">
         <f t="shared" si="2"/>
-        <v>47.559999999999988</v>
-      </c>
-      <c r="BU6" s="83">
+        <v>47.56</v>
+      </c>
+      <c r="BV6" s="83">
         <f t="shared" si="2"/>
         <v>8.44</v>
       </c>
-      <c r="BV6" s="108">
+      <c r="BW6" s="108">
         <f t="shared" si="2"/>
         <v>1.75</v>
       </c>
-      <c r="BW6" s="244">
+      <c r="BX6" s="244">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BX6" s="83">
+      <c r="BY6" s="83">
         <f t="shared" si="2"/>
-        <v>110.34</v>
-      </c>
-      <c r="BY6" s="191">
+        <v>77.099999999999994</v>
+      </c>
+      <c r="BZ6" s="191">
         <f t="shared" si="2"/>
         <v>16.170000000000002</v>
       </c>
-      <c r="BZ6" s="259">
+      <c r="CA6" s="259">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CA6" s="328">
+      <c r="CB6" s="328">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CB6" s="85">
+      <c r="CC6" s="85">
         <f t="shared" si="2"/>
         <v>27.65</v>
       </c>
-      <c r="CC6" s="235">
+      <c r="CD6" s="235">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CD6" s="85">
+      <c r="CE6" s="85">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="CE6" s="244">
+      <c r="CF6" s="244">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CF6" s="265">
+      <c r="CG6" s="265">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CG6" s="84">
+      <c r="CH6" s="84">
         <f t="shared" si="2"/>
-        <v>21.650000000000002</v>
-      </c>
-      <c r="CH6" s="244">
+        <v>21.65</v>
+      </c>
+      <c r="CI6" s="244">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CI6" s="84">
+      <c r="CJ6" s="84">
         <f t="shared" si="2"/>
-        <v>45.4</v>
-      </c>
-      <c r="CJ6" s="86">
+        <v>24.4</v>
+      </c>
+      <c r="CK6" s="86">
         <f t="shared" si="2"/>
         <v>9.1999999999999993</v>
       </c>
-      <c r="CK6" s="83">
+      <c r="CL6" s="83">
         <f t="shared" si="2"/>
         <v>89.45</v>
       </c>
-      <c r="CL6" s="205">
+      <c r="CM6" s="205">
         <f t="shared" si="2"/>
         <v>21.45</v>
       </c>
-      <c r="CM6" s="81">
+      <c r="CN6" s="81">
         <f t="shared" si="2"/>
         <v>54.058</v>
       </c>
-      <c r="CN6" s="265">
+      <c r="CO6" s="265">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CO6" s="271">
+      <c r="CP6" s="271">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CP6" s="82">
+      <c r="CQ6" s="244">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CQ6" s="228">
+      <c r="CR6" s="228">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CR6" s="291">
+      <c r="CS6" s="291">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CS6" s="235">
+      <c r="CT6" s="235">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CT6" s="253">
+      <c r="CU6" s="253">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="CU6" s="277">
-        <f t="shared" si="2"/>
+      <c r="CV6" s="277">
+        <f t="shared" ref="CV6:DU6" si="3">SUM(CV8:CV1048576)</f>
         <v>0</v>
       </c>
-      <c r="CV6" s="271">
-        <f t="shared" ref="CV6:DT6" si="3">SUM(CV8:CV1048576)</f>
-        <v>0</v>
-      </c>
-      <c r="CW6" s="244">
+      <c r="CW6" s="271">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="CX6" s="79">
+      <c r="CX6" s="244">
         <f t="shared" si="3"/>
-        <v>13.32</v>
-      </c>
-      <c r="CY6" s="81">
+        <v>0</v>
+      </c>
+      <c r="CY6" s="79">
+        <f t="shared" si="3"/>
+        <v>6.6349999999999998</v>
+      </c>
+      <c r="CZ6" s="81">
         <f t="shared" si="3"/>
         <v>8.9849999999999994</v>
-      </c>
-      <c r="CZ6" s="265">
-        <f t="shared" si="3"/>
-        <v>0</v>
       </c>
       <c r="DA6" s="265">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DB6" s="235">
+      <c r="DB6" s="265">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DC6" s="271">
+      <c r="DC6" s="235">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DD6" s="86">
+      <c r="DD6" s="271">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="DE6" s="86">
         <f t="shared" si="3"/>
         <v>93.39</v>
       </c>
-      <c r="DE6" s="80">
+      <c r="DF6" s="80">
         <f t="shared" si="3"/>
         <v>14.9</v>
       </c>
-      <c r="DF6" s="86">
+      <c r="DG6" s="86">
         <f t="shared" si="3"/>
         <v>6.02</v>
       </c>
-      <c r="DG6" s="109">
+      <c r="DH6" s="109">
         <f t="shared" si="3"/>
         <v>2.25</v>
       </c>
-      <c r="DH6" s="108">
+      <c r="DI6" s="108">
         <f t="shared" si="3"/>
         <v>3.28</v>
       </c>
-      <c r="DI6" s="99">
+      <c r="DJ6" s="99">
         <f t="shared" si="3"/>
         <v>63.54</v>
       </c>
-      <c r="DJ6" s="99">
+      <c r="DK6" s="99">
         <f t="shared" si="3"/>
         <v>10.45</v>
       </c>
-      <c r="DK6" s="283">
+      <c r="DL6" s="283">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DL6" s="212">
+      <c r="DM6" s="212">
         <f t="shared" si="3"/>
         <v>404.44</v>
       </c>
-      <c r="DM6" s="277">
+      <c r="DN6" s="277">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="DN6" s="99">
+      <c r="DO6" s="99">
         <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
-      <c r="DO6" s="99">
+      <c r="DP6" s="99">
         <f t="shared" si="3"/>
         <v>14.7</v>
       </c>
-      <c r="DP6" s="99">
+      <c r="DQ6" s="99">
         <f t="shared" si="3"/>
         <v>2.85</v>
       </c>
-      <c r="DQ6" s="99">
+      <c r="DR6" s="99">
         <f t="shared" si="3"/>
         <v>6.83</v>
       </c>
-      <c r="DR6" s="99">
+      <c r="DS6" s="99">
         <f t="shared" si="3"/>
         <v>9.2200000000000006</v>
       </c>
-      <c r="DS6" s="99">
+      <c r="DT6" s="99">
         <f t="shared" si="3"/>
         <v>18.5</v>
       </c>
-      <c r="DT6" s="99">
+      <c r="DU6" s="99">
         <f t="shared" si="3"/>
         <v>52.36</v>
       </c>
     </row>
-    <row r="7" spans="1:124" s="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:125" s="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="51"/>
       <c r="B7" s="27"/>
       <c r="C7" s="28"/>
       <c r="D7" s="173"/>
-      <c r="E7" s="173"/>
+      <c r="E7" s="229"/>
       <c r="F7" s="173"/>
       <c r="G7" s="229"/>
       <c r="H7" s="44"/>
@@ -32410,7 +32436,7 @@
       <c r="AJ7" s="236"/>
       <c r="AK7" s="254"/>
       <c r="AL7" s="304"/>
-      <c r="AM7" s="106"/>
+      <c r="AM7" s="236"/>
       <c r="AN7" s="254"/>
       <c r="AO7" s="304"/>
       <c r="AP7" s="236"/>
@@ -32423,81 +32449,82 @@
       <c r="AW7" s="254"/>
       <c r="AX7" s="304"/>
       <c r="AY7" s="236"/>
-      <c r="AZ7" s="322"/>
+      <c r="AZ7" s="254"/>
       <c r="BA7" s="304"/>
       <c r="BB7" s="236"/>
       <c r="BC7" s="322"/>
       <c r="BD7" s="304"/>
-      <c r="BE7" s="236"/>
+      <c r="BE7" s="106"/>
       <c r="BF7" s="254"/>
-      <c r="BG7" s="298"/>
+      <c r="BG7" s="169"/>
       <c r="BH7" s="245"/>
       <c r="BI7" s="254"/>
       <c r="BJ7" s="315"/>
-      <c r="BK7" s="236"/>
-      <c r="BL7" s="254"/>
-      <c r="BM7" s="169"/>
-      <c r="BN7" s="236"/>
-      <c r="BO7" s="254"/>
-      <c r="BP7" s="298"/>
-      <c r="BQ7" s="236"/>
-      <c r="BR7" s="254"/>
-      <c r="BS7" s="298"/>
-      <c r="BT7" s="34"/>
-      <c r="BU7" s="62"/>
-      <c r="BV7" s="198"/>
-      <c r="BW7" s="245"/>
-      <c r="BX7" s="62"/>
-      <c r="BY7" s="106"/>
-      <c r="BZ7" s="260"/>
-      <c r="CA7" s="329"/>
-      <c r="CB7" s="76"/>
-      <c r="CC7" s="236"/>
-      <c r="CD7" s="76"/>
-      <c r="CE7" s="245"/>
-      <c r="CF7" s="266"/>
-      <c r="CG7" s="55"/>
-      <c r="CH7" s="245"/>
-      <c r="CI7" s="55"/>
-      <c r="CJ7" s="29"/>
-      <c r="CK7" s="62"/>
-      <c r="CL7" s="206"/>
-      <c r="CM7" s="39"/>
-      <c r="CN7" s="266"/>
-      <c r="CO7" s="272"/>
-      <c r="CP7" s="34"/>
-      <c r="CQ7" s="246"/>
-      <c r="CR7" s="292"/>
-      <c r="CS7" s="236"/>
-      <c r="CT7" s="254"/>
-      <c r="CU7" s="278"/>
-      <c r="CV7" s="272"/>
-      <c r="CW7" s="245"/>
-      <c r="CX7" s="111"/>
-      <c r="CY7" s="39"/>
-      <c r="CZ7" s="266"/>
+      <c r="BK7" s="62"/>
+      <c r="BL7" s="236"/>
+      <c r="BM7" s="254"/>
+      <c r="BN7" s="169"/>
+      <c r="BO7" s="236"/>
+      <c r="BP7" s="254"/>
+      <c r="BQ7" s="298"/>
+      <c r="BR7" s="236"/>
+      <c r="BS7" s="254"/>
+      <c r="BT7" s="298"/>
+      <c r="BU7" s="34"/>
+      <c r="BV7" s="62"/>
+      <c r="BW7" s="198"/>
+      <c r="BX7" s="245"/>
+      <c r="BY7" s="62"/>
+      <c r="BZ7" s="106"/>
+      <c r="CA7" s="260"/>
+      <c r="CB7" s="329"/>
+      <c r="CC7" s="76"/>
+      <c r="CD7" s="236"/>
+      <c r="CE7" s="76"/>
+      <c r="CF7" s="245"/>
+      <c r="CG7" s="266"/>
+      <c r="CH7" s="55"/>
+      <c r="CI7" s="245"/>
+      <c r="CJ7" s="55"/>
+      <c r="CK7" s="29"/>
+      <c r="CL7" s="62"/>
+      <c r="CM7" s="206"/>
+      <c r="CN7" s="39"/>
+      <c r="CO7" s="266"/>
+      <c r="CP7" s="272"/>
+      <c r="CQ7" s="245"/>
+      <c r="CR7" s="246"/>
+      <c r="CS7" s="292"/>
+      <c r="CT7" s="236"/>
+      <c r="CU7" s="254"/>
+      <c r="CV7" s="278"/>
+      <c r="CW7" s="272"/>
+      <c r="CX7" s="245"/>
+      <c r="CY7" s="111"/>
+      <c r="CZ7" s="39"/>
       <c r="DA7" s="266"/>
-      <c r="DB7" s="236"/>
-      <c r="DC7" s="272"/>
-      <c r="DD7" s="29"/>
-      <c r="DE7" s="44"/>
-      <c r="DF7" s="29"/>
-      <c r="DG7" s="106"/>
-      <c r="DH7" s="100"/>
-      <c r="DI7" s="101"/>
-      <c r="DJ7" s="102"/>
-      <c r="DK7" s="284"/>
-      <c r="DL7" s="213"/>
-      <c r="DM7" s="285"/>
-      <c r="DN7" s="102"/>
+      <c r="DB7" s="266"/>
+      <c r="DC7" s="236"/>
+      <c r="DD7" s="272"/>
+      <c r="DE7" s="29"/>
+      <c r="DF7" s="44"/>
+      <c r="DG7" s="29"/>
+      <c r="DH7" s="106"/>
+      <c r="DI7" s="100"/>
+      <c r="DJ7" s="101"/>
+      <c r="DK7" s="102"/>
+      <c r="DL7" s="284"/>
+      <c r="DM7" s="213"/>
+      <c r="DN7" s="285"/>
       <c r="DO7" s="102"/>
       <c r="DP7" s="102"/>
       <c r="DQ7" s="102"/>
       <c r="DR7" s="102"/>
       <c r="DS7" s="102"/>
       <c r="DT7" s="102"/>
-    </row>
-    <row r="8" spans="1:124" x14ac:dyDescent="0.25">
+      <c r="DU7" s="102"/>
+    </row>
+    <row r="8" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A8" s="50">
         <v>46119</v>
       </c>
@@ -32505,13 +32532,13 @@
         <v>13</v>
       </c>
       <c r="C8" s="18">
-        <f t="shared" ref="C8:C79" si="4">SUM(D8:EQ8)</f>
+        <f t="shared" ref="C8:C71" si="4">SUM(D8:ER8)</f>
         <v>2009.373</v>
       </c>
       <c r="D8" s="174">
         <v>25.675000000000001</v>
       </c>
-      <c r="E8" s="174">
+      <c r="E8" s="230">
         <v>0</v>
       </c>
       <c r="F8" s="174">
@@ -32583,7 +32610,7 @@
       <c r="AK8" s="255">
         <v>0</v>
       </c>
-      <c r="AM8" s="107">
+      <c r="AM8" s="237">
         <v>0</v>
       </c>
       <c r="AN8" s="255">
@@ -32610,7 +32637,7 @@
       <c r="AY8" s="237">
         <v>0</v>
       </c>
-      <c r="AZ8" s="323">
+      <c r="AZ8" s="255">
         <v>0</v>
       </c>
       <c r="BB8" s="237">
@@ -32619,7 +32646,7 @@
       <c r="BC8" s="323">
         <v>0</v>
       </c>
-      <c r="BE8" s="237">
+      <c r="BE8" s="107">
         <v>34.340000000000003</v>
       </c>
       <c r="BF8" s="255">
@@ -32631,182 +32658,182 @@
       <c r="BI8" s="255">
         <v>0</v>
       </c>
-      <c r="BK8" s="237">
+      <c r="BL8" s="237">
         <v>0</v>
       </c>
-      <c r="BL8" s="255">
+      <c r="BM8" s="255">
         <v>0</v>
       </c>
-      <c r="BM8" s="170">
+      <c r="BN8" s="170">
         <v>8.5250000000000004</v>
       </c>
-      <c r="BN8" s="237">
+      <c r="BO8" s="237">
         <v>0</v>
       </c>
-      <c r="BO8" s="255">
+      <c r="BP8" s="255">
         <v>0</v>
       </c>
-      <c r="BQ8" s="237">
+      <c r="BR8" s="237">
         <v>0</v>
       </c>
-      <c r="BR8" s="255">
+      <c r="BS8" s="255">
         <v>0</v>
       </c>
-      <c r="BT8" s="35">
+      <c r="BU8" s="35">
         <v>211.39500000000001</v>
       </c>
-      <c r="BU8" s="63">
+      <c r="BV8" s="63">
         <v>8.44</v>
       </c>
-      <c r="BV8" s="199">
+      <c r="BW8" s="199">
         <v>1.75</v>
       </c>
-      <c r="BW8" s="247">
+      <c r="BX8" s="247">
         <v>0</v>
       </c>
-      <c r="BX8" s="63">
+      <c r="BY8" s="63">
         <v>68.8</v>
       </c>
-      <c r="BY8" s="107">
+      <c r="BZ8" s="107">
         <v>16.170000000000002</v>
       </c>
-      <c r="BZ8" s="261">
+      <c r="CA8" s="261">
         <v>0</v>
       </c>
-      <c r="CA8" s="330">
+      <c r="CB8" s="330">
         <v>0</v>
       </c>
-      <c r="CB8" s="69">
+      <c r="CC8" s="69">
         <v>27.65</v>
       </c>
-      <c r="CC8" s="237">
+      <c r="CD8" s="237">
         <v>0</v>
       </c>
-      <c r="CD8" s="69">
+      <c r="CE8" s="69">
         <v>28</v>
       </c>
-      <c r="CE8" s="247">
+      <c r="CF8" s="247">
         <v>103.66500000000001</v>
       </c>
-      <c r="CF8" s="267">
+      <c r="CG8" s="267">
         <v>0</v>
       </c>
-      <c r="CG8" s="56">
+      <c r="CH8" s="56">
         <v>45.85</v>
       </c>
-      <c r="CH8" s="247">
+      <c r="CI8" s="247">
         <v>0</v>
       </c>
-      <c r="CI8" s="56">
+      <c r="CJ8" s="56">
         <v>45.4</v>
       </c>
-      <c r="CJ8" s="26">
+      <c r="CK8" s="26">
         <v>9.1999999999999993</v>
       </c>
-      <c r="CK8" s="63">
+      <c r="CL8" s="63">
         <v>89.45</v>
       </c>
-      <c r="CL8" s="207">
+      <c r="CM8" s="207">
         <v>21.45</v>
       </c>
-      <c r="CM8" s="40">
+      <c r="CN8" s="40">
         <v>54.058</v>
       </c>
-      <c r="CN8" s="267">
+      <c r="CO8" s="267">
         <v>0</v>
       </c>
-      <c r="CO8" s="273">
+      <c r="CP8" s="273">
         <v>0</v>
       </c>
-      <c r="CP8" s="35">
+      <c r="CQ8" s="247">
         <v>32.700000000000003</v>
       </c>
-      <c r="CQ8" s="248">
+      <c r="CR8" s="248">
         <v>0</v>
       </c>
-      <c r="CR8" s="293">
+      <c r="CS8" s="293">
         <v>0.75</v>
       </c>
-      <c r="CS8" s="237">
+      <c r="CT8" s="237">
         <v>0</v>
       </c>
-      <c r="CU8" s="279">
+      <c r="CV8" s="279">
         <v>0</v>
       </c>
-      <c r="CV8" s="273">
+      <c r="CW8" s="273">
         <v>0</v>
       </c>
-      <c r="CW8" s="247">
+      <c r="CX8" s="247">
         <v>0</v>
       </c>
-      <c r="CX8" s="72">
+      <c r="CY8" s="72">
         <v>13.32</v>
       </c>
-      <c r="CY8" s="40">
+      <c r="CZ8" s="40">
         <v>8.9849999999999994</v>
-      </c>
-      <c r="CZ8" s="267">
-        <v>0</v>
       </c>
       <c r="DA8" s="267">
         <v>0</v>
       </c>
-      <c r="DB8" s="237">
+      <c r="DB8" s="267">
         <v>0</v>
       </c>
-      <c r="DD8" s="26">
+      <c r="DC8" s="237">
+        <v>0</v>
+      </c>
+      <c r="DE8" s="26">
         <v>93.39</v>
       </c>
-      <c r="DE8" s="45">
+      <c r="DF8" s="45">
         <v>14.9</v>
       </c>
-      <c r="DF8" s="26">
+      <c r="DG8" s="26">
         <v>6.02</v>
       </c>
-      <c r="DG8" s="107">
+      <c r="DH8" s="107">
         <v>2.25</v>
       </c>
-      <c r="DH8" s="103">
+      <c r="DI8" s="103">
         <v>3.28</v>
       </c>
-      <c r="DI8" s="98">
+      <c r="DJ8" s="98">
         <v>63.54</v>
       </c>
-      <c r="DJ8" s="98">
+      <c r="DK8" s="98">
         <v>10.45</v>
       </c>
-      <c r="DK8" s="282">
+      <c r="DL8" s="282">
         <v>0</v>
       </c>
-      <c r="DL8" s="211">
+      <c r="DM8" s="211">
         <v>404.44</v>
       </c>
-      <c r="DM8" s="279">
+      <c r="DN8" s="279">
         <v>0</v>
       </c>
-      <c r="DN8" s="98">
+      <c r="DO8" s="98">
         <v>2.5</v>
       </c>
-      <c r="DO8" s="98">
+      <c r="DP8" s="98">
         <v>14.7</v>
       </c>
-      <c r="DP8" s="98">
+      <c r="DQ8" s="98">
         <v>2.85</v>
       </c>
-      <c r="DQ8" s="98">
+      <c r="DR8" s="98">
         <v>6.83</v>
       </c>
-      <c r="DR8" s="98">
+      <c r="DS8" s="98">
         <v>9.2200000000000006</v>
       </c>
-      <c r="DS8" s="98">
+      <c r="DT8" s="98">
         <v>18.5</v>
       </c>
-      <c r="DT8" s="98">
+      <c r="DU8" s="98">
         <v>52.36</v>
       </c>
     </row>
-    <row r="9" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:125" x14ac:dyDescent="0.25">
       <c r="B9" s="19" t="s">
         <v>113</v>
       </c>
@@ -32818,7 +32845,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A10" s="50">
         <v>46120</v>
       </c>
@@ -32829,14 +32856,14 @@
         <f t="shared" si="4"/>
         <v>-43.445</v>
       </c>
-      <c r="BE10" s="237">
+      <c r="BE10" s="107">
         <v>-17.335000000000001</v>
       </c>
       <c r="BH10" s="247">
         <v>-26.11</v>
       </c>
     </row>
-    <row r="11" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A11" s="50">
         <v>46121</v>
       </c>
@@ -32851,11 +32878,11 @@
         <f>-8.475-8.58</f>
         <v>-17.055</v>
       </c>
-      <c r="BE11" s="237">
+      <c r="BE11" s="107">
         <v>-8.8450000000000006</v>
       </c>
     </row>
-    <row r="12" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A12" s="50">
         <v>46122</v>
       </c>
@@ -32864,7 +32891,7 @@
       </c>
       <c r="C12" s="18">
         <f t="shared" si="4"/>
-        <v>-16.080000000000002</v>
+        <v>-16.079999999999998</v>
       </c>
       <c r="R12" s="237">
         <v>-8.14</v>
@@ -32873,7 +32900,7 @@
         <v>-7.94</v>
       </c>
     </row>
-    <row r="13" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A13" s="50">
         <v>46122</v>
       </c>
@@ -32890,7 +32917,7 @@
       <c r="AJ13" s="237">
         <v>70.025000000000006</v>
       </c>
-      <c r="AM13" s="107">
+      <c r="AM13" s="237">
         <v>66.03</v>
       </c>
       <c r="AP13" s="237">
@@ -32908,21 +32935,21 @@
       <c r="BB13" s="237">
         <v>64.22</v>
       </c>
-      <c r="BE13" s="237">
+      <c r="BE13" s="107">
         <v>33.92</v>
       </c>
-      <c r="BK13" s="237">
+      <c r="BL13" s="237">
         <v>68.194999999999993</v>
       </c>
-      <c r="BN13" s="237">
+      <c r="BO13" s="237">
         <v>102.47</v>
       </c>
-      <c r="BQ13" s="306">
+      <c r="BR13" s="306">
         <f>178.405+41.14</f>
-        <v>219.54500000000002</v>
-      </c>
-    </row>
-    <row r="14" spans="1:124" x14ac:dyDescent="0.25">
+        <v>219.54499999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A14" s="50">
         <v>46122</v>
       </c>
@@ -32941,10 +32968,10 @@
       </c>
       <c r="AG14" s="237">
         <f>33.35+69.725</f>
-        <v>103.07499999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:124" x14ac:dyDescent="0.25">
+        <v>103.075</v>
+      </c>
+    </row>
+    <row r="15" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A15" s="50">
         <v>46122</v>
       </c>
@@ -32961,7 +32988,7 @@
       <c r="AJ15" s="237">
         <v>-70.025000000000006</v>
       </c>
-      <c r="AM15" s="107">
+      <c r="AM15" s="237">
         <v>-66.03</v>
       </c>
       <c r="AP15" s="237">
@@ -32973,18 +33000,18 @@
       <c r="AV15" s="237">
         <v>-71.19</v>
       </c>
-      <c r="BK15" s="237">
+      <c r="BL15" s="237">
         <v>-68.194999999999993</v>
       </c>
-      <c r="BN15" s="237">
+      <c r="BO15" s="237">
         <v>-102.47</v>
       </c>
-      <c r="BQ15" s="237">
+      <c r="BR15" s="237">
         <f>-41.14-178.405</f>
-        <v>-219.54500000000002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:124" x14ac:dyDescent="0.25">
+        <v>-219.54499999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A16" s="50">
         <v>46122</v>
       </c>
@@ -33008,7 +33035,7 @@
         <v>-65.765000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A17" s="50">
         <v>46122</v>
       </c>
@@ -33023,7 +33050,7 @@
         <v>-8.69</v>
       </c>
     </row>
-    <row r="18" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A18" s="50">
         <v>46123</v>
       </c>
@@ -33041,7 +33068,7 @@
         <v>-8.1950000000000003</v>
       </c>
     </row>
-    <row r="19" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A19" s="50">
         <v>46123</v>
       </c>
@@ -33056,7 +33083,7 @@
         <v>-7.6849999999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A20" s="50">
         <v>46123</v>
       </c>
@@ -33065,7 +33092,7 @@
       </c>
       <c r="C20" s="18">
         <f t="shared" si="4"/>
-        <v>-34.004999999999995</v>
+        <v>-34.005000000000003</v>
       </c>
       <c r="AD20" s="237">
         <v>-17.43</v>
@@ -33074,7 +33101,7 @@
         <v>-16.574999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A21" s="50">
         <v>46125</v>
       </c>
@@ -33089,7 +33116,7 @@
         <v>-4.9400000000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A22" s="50">
         <v>46125</v>
       </c>
@@ -33098,7 +33125,7 @@
       </c>
       <c r="C22" s="18">
         <f t="shared" si="4"/>
-        <v>288.53499999999997</v>
+        <v>288.53500000000003</v>
       </c>
       <c r="AB22" s="255">
         <v>33.28</v>
@@ -33121,14 +33148,14 @@
       <c r="AW22" s="255">
         <v>33.58</v>
       </c>
-      <c r="BO22" s="255">
+      <c r="BP22" s="255">
         <v>32.685000000000002</v>
       </c>
-      <c r="CT22" s="255">
+      <c r="CU22" s="255">
         <v>25.335000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A23" s="50">
         <v>46125</v>
       </c>
@@ -33137,7 +33164,7 @@
       </c>
       <c r="C23" s="18">
         <f t="shared" si="4"/>
-        <v>-92.259999999999991</v>
+        <v>-92.26</v>
       </c>
       <c r="P23" s="237">
         <v>-7.89</v>
@@ -33154,14 +33181,14 @@
       <c r="AN23" s="255">
         <v>-8.4949999999999992</v>
       </c>
-      <c r="BO23" s="255">
+      <c r="BP23" s="255">
         <v>-24.53</v>
       </c>
-      <c r="CT23" s="255">
+      <c r="CU23" s="255">
         <v>-19.16</v>
       </c>
     </row>
-    <row r="24" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A24" s="50">
         <v>46126</v>
       </c>
@@ -33170,7 +33197,7 @@
       </c>
       <c r="C24" s="18">
         <f t="shared" si="4"/>
-        <v>-98.229999999999976</v>
+        <v>-98.23</v>
       </c>
       <c r="AB24" s="255">
         <v>-16.72</v>
@@ -33191,7 +33218,7 @@
         <v>-16.8</v>
       </c>
     </row>
-    <row r="25" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A25" s="50">
         <v>46126</v>
       </c>
@@ -33218,7 +33245,7 @@
         <v>-16.91</v>
       </c>
     </row>
-    <row r="26" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A26" s="50">
         <v>46126</v>
       </c>
@@ -33233,7 +33260,7 @@
         <v>-8.07</v>
       </c>
     </row>
-    <row r="27" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A27" s="50">
         <v>46126</v>
       </c>
@@ -33248,7 +33275,7 @@
         <v>-8.4649999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A28" s="50">
         <v>46127</v>
       </c>
@@ -33266,7 +33293,7 @@
         <v>-8.41</v>
       </c>
     </row>
-    <row r="29" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A29" s="50">
         <v>46127</v>
       </c>
@@ -33275,9 +33302,9 @@
       </c>
       <c r="C29" s="18">
         <f t="shared" si="4"/>
-        <v>185.95999999999998</v>
-      </c>
-      <c r="E29" s="174">
+        <v>185.96</v>
+      </c>
+      <c r="E29" s="230">
         <v>34.344999999999999</v>
       </c>
       <c r="F29" s="174">
@@ -33286,11 +33313,11 @@
       <c r="G29" s="230">
         <v>46.98</v>
       </c>
-      <c r="DC29" s="273">
+      <c r="DD29" s="273">
         <v>36.659999999999997</v>
       </c>
     </row>
-    <row r="30" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A30" s="50">
         <v>46127</v>
       </c>
@@ -33305,7 +33332,7 @@
         <v>-34.055</v>
       </c>
     </row>
-    <row r="31" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A31" s="50">
         <v>46127</v>
       </c>
@@ -33319,14 +33346,14 @@
       <c r="D31" s="174">
         <v>-25.675000000000001</v>
       </c>
-      <c r="E31" s="174">
+      <c r="E31" s="230">
         <v>-25.754999999999999</v>
       </c>
       <c r="G31" s="230">
         <v>-46.98</v>
       </c>
     </row>
-    <row r="32" spans="1:107" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A32" s="50">
         <v>46127</v>
       </c>
@@ -33337,11 +33364,11 @@
         <f t="shared" si="4"/>
         <v>-36.659999999999997</v>
       </c>
-      <c r="DC32" s="273">
+      <c r="DD32" s="273">
         <v>-36.659999999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A33" s="50">
         <v>46127</v>
       </c>
@@ -33356,7 +33383,7 @@
         <v>-15.975</v>
       </c>
     </row>
-    <row r="34" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A34" s="50">
         <v>46128</v>
       </c>
@@ -33371,7 +33398,7 @@
         <v>-8.48</v>
       </c>
     </row>
-    <row r="35" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A35" s="50">
         <v>46130</v>
       </c>
@@ -33386,7 +33413,7 @@
         <v>-7.58</v>
       </c>
     </row>
-    <row r="36" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A36" s="50">
         <v>46132</v>
       </c>
@@ -33401,7 +33428,7 @@
         <v>-8.11</v>
       </c>
     </row>
-    <row r="37" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A37" s="50">
         <v>46132</v>
       </c>
@@ -33431,7 +33458,7 @@
         <v>31.09</v>
       </c>
     </row>
-    <row r="38" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A38" s="50">
         <v>46132</v>
       </c>
@@ -33442,11 +33469,11 @@
         <f t="shared" si="4"/>
         <v>-103.66500000000001</v>
       </c>
-      <c r="CE38" s="247">
+      <c r="CF38" s="247">
         <v>-103.66500000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A39" s="50">
         <v>46132</v>
       </c>
@@ -33457,14 +33484,14 @@
         <f t="shared" si="4"/>
         <v>-6.9249999999999998</v>
       </c>
-      <c r="CR39" s="293">
+      <c r="CS39" s="293">
         <v>-0.75</v>
       </c>
-      <c r="CT39" s="255">
+      <c r="CU39" s="255">
         <v>-6.1749999999999998</v>
       </c>
     </row>
-    <row r="40" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A40" s="50">
         <v>46132</v>
       </c>
@@ -33473,7 +33500,7 @@
       </c>
       <c r="C40" s="18">
         <f t="shared" si="4"/>
-        <v>-96.424999999999983</v>
+        <v>-96.424999999999997</v>
       </c>
       <c r="AB40" s="255">
         <v>-16.93</v>
@@ -33494,7 +33521,7 @@
         <v>-15.1</v>
       </c>
     </row>
-    <row r="41" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A41" s="50">
         <v>46133</v>
       </c>
@@ -33503,7 +33530,7 @@
       </c>
       <c r="C41" s="18">
         <f t="shared" si="4"/>
-        <v>-16.814999999999998</v>
+        <v>-16.815000000000001</v>
       </c>
       <c r="AY41" s="237">
         <v>-8.2449999999999992</v>
@@ -33512,7 +33539,7 @@
         <v>-8.57</v>
       </c>
     </row>
-    <row r="42" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A42" s="50">
         <v>46133</v>
       </c>
@@ -33537,7 +33564,7 @@
         <v>-8.3699999999999992</v>
       </c>
     </row>
-    <row r="43" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A43" s="50">
         <v>46133</v>
       </c>
@@ -33555,7 +33582,7 @@
         <v>-8.59</v>
       </c>
     </row>
-    <row r="44" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A44" s="50">
         <v>46133</v>
       </c>
@@ -33569,11 +33596,11 @@
       <c r="U44" s="237">
         <v>-15.88</v>
       </c>
-      <c r="BT44" s="35">
+      <c r="BU44" s="35">
         <v>-66.015000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A45" s="50">
         <v>46134</v>
       </c>
@@ -33588,7 +33615,7 @@
         <v>-16.754999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A46" s="50">
         <v>46134</v>
       </c>
@@ -33604,7 +33631,7 @@
       </c>
       <c r="AC46" s="305">
         <f>8.48+8.47</f>
-        <v>16.950000000000003</v>
+        <v>16.95</v>
       </c>
       <c r="AI46" s="305">
         <f>8.38+8.365</f>
@@ -33618,7 +33645,7 @@
         <v>17.175000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A47" s="50">
         <v>46135</v>
       </c>
@@ -33629,11 +33656,11 @@
         <f t="shared" si="4"/>
         <v>-65.025000000000006</v>
       </c>
-      <c r="BT47" s="35">
+      <c r="BU47" s="35">
         <v>-65.025000000000006</v>
       </c>
     </row>
-    <row r="48" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:99" x14ac:dyDescent="0.25">
       <c r="A48" s="50">
         <v>46135</v>
       </c>
@@ -33648,7 +33675,7 @@
         <v>-8.2149999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A49" s="50">
         <v>46136</v>
       </c>
@@ -33662,17 +33689,17 @@
       <c r="O49" s="267">
         <v>-5.9249999999999998</v>
       </c>
-      <c r="BE49" s="237">
+      <c r="BE49" s="107">
         <v>-16.995000000000001</v>
       </c>
       <c r="BH49" s="247">
         <v>-8.61</v>
       </c>
-      <c r="BM49" s="170">
+      <c r="BN49" s="170">
         <v>-8.5250000000000004</v>
       </c>
     </row>
-    <row r="50" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A50" s="50">
         <v>46136</v>
       </c>
@@ -33696,7 +33723,7 @@
         <v>-16.79</v>
       </c>
     </row>
-    <row r="51" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A51" s="50">
         <v>46136</v>
       </c>
@@ -33714,7 +33741,7 @@
         <v>-8.4</v>
       </c>
     </row>
-    <row r="52" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A52" s="50">
         <v>46136</v>
       </c>
@@ -33725,14 +33752,14 @@
         <f t="shared" si="4"/>
         <v>-41.335000000000001</v>
       </c>
-      <c r="BT52" s="35">
+      <c r="BU52" s="35">
         <v>-32.795000000000002</v>
       </c>
-      <c r="CP52" s="35">
+      <c r="CQ52" s="247">
         <v>-8.5399999999999991</v>
       </c>
     </row>
-    <row r="53" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A53" s="50">
         <v>46137</v>
       </c>
@@ -33759,7 +33786,7 @@
         <v>32.225000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A54" s="50">
         <v>46137</v>
       </c>
@@ -33779,11 +33806,11 @@
       <c r="BD54" s="305">
         <v>-32.225000000000001</v>
       </c>
-      <c r="BE54" s="237">
+      <c r="BE54" s="107">
         <v>-16.925000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A55" s="50">
         <v>46139</v>
       </c>
@@ -33798,7 +33825,7 @@
         <v>-5.4450000000000003</v>
       </c>
     </row>
-    <row r="56" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A56" s="50">
         <v>46139</v>
       </c>
@@ -33825,7 +33852,7 @@
         <v>-7.4</v>
       </c>
     </row>
-    <row r="57" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A57" s="50">
         <v>46140</v>
       </c>
@@ -33845,11 +33872,11 @@
       <c r="AU57" s="305">
         <v>-8.5749999999999993</v>
       </c>
-      <c r="BE57" s="237">
+      <c r="BE57" s="107">
         <v>-8.16</v>
       </c>
     </row>
-    <row r="58" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A58" s="50">
         <v>46140</v>
       </c>
@@ -33867,7 +33894,7 @@
         <v>-8.5850000000000009</v>
       </c>
     </row>
-    <row r="59" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A59" s="50">
         <v>46140</v>
       </c>
@@ -33887,13 +33914,13 @@
       </c>
       <c r="BA59" s="305">
         <f>-8.475-8.46</f>
-        <v>-16.935000000000002</v>
+        <v>-16.934999999999999</v>
       </c>
       <c r="BB59" s="237">
         <v>-8.09</v>
       </c>
     </row>
-    <row r="60" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A60" s="50">
         <v>46140</v>
       </c>
@@ -33904,11 +33931,11 @@
         <f t="shared" si="4"/>
         <v>-8.08</v>
       </c>
-      <c r="BX60" s="63">
+      <c r="BY60" s="63">
         <v>-8.08</v>
       </c>
     </row>
-    <row r="61" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A61" s="50">
         <v>46141</v>
       </c>
@@ -33917,7 +33944,7 @@
       </c>
       <c r="C61" s="18">
         <f t="shared" si="4"/>
-        <v>247.55000000000004</v>
+        <v>247.55</v>
       </c>
       <c r="Z61" s="305">
         <v>17.065000000000001</v>
@@ -33937,23 +33964,23 @@
       <c r="BD61" s="305">
         <v>16.940000000000001</v>
       </c>
-      <c r="BG61" s="299">
+      <c r="BG61" s="170">
         <v>17.145</v>
       </c>
       <c r="BJ61" s="316">
         <v>17.239999999999998</v>
       </c>
-      <c r="BM61" s="170">
+      <c r="BN61" s="170">
         <v>16.925000000000001</v>
       </c>
-      <c r="BP61" s="299">
+      <c r="BQ61" s="299">
         <v>17.184999999999999</v>
       </c>
-      <c r="BS61" s="299">
+      <c r="BT61" s="299">
         <v>34.085000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A62" s="50">
         <v>46141</v>
       </c>
@@ -33968,7 +33995,7 @@
         <v>-8.4849999999999994</v>
       </c>
     </row>
-    <row r="63" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A63" s="50">
         <v>46141</v>
       </c>
@@ -33989,7 +34016,7 @@
         <v>-8.59</v>
       </c>
     </row>
-    <row r="64" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:95" x14ac:dyDescent="0.25">
       <c r="A64" s="50">
         <v>46141</v>
       </c>
@@ -34004,7 +34031,7 @@
         <v>-8.5449999999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A65" s="50">
         <v>46141</v>
       </c>
@@ -34013,7 +34040,7 @@
       </c>
       <c r="C65" s="18">
         <f t="shared" si="4"/>
-        <v>-17.009999999999998</v>
+        <v>-17.010000000000002</v>
       </c>
       <c r="Z65" s="305">
         <v>-8.52</v>
@@ -34022,7 +34049,7 @@
         <v>-8.49</v>
       </c>
     </row>
-    <row r="66" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A66" s="50">
         <v>46142</v>
       </c>
@@ -34033,11 +34060,11 @@
         <f t="shared" si="4"/>
         <v>-24.2</v>
       </c>
-      <c r="CG66" s="56">
+      <c r="CH66" s="56">
         <v>-24.2</v>
       </c>
     </row>
-    <row r="67" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A67" s="50">
         <v>46142</v>
       </c>
@@ -34046,7 +34073,7 @@
       </c>
       <c r="C67" s="18">
         <f t="shared" si="4"/>
-        <v>-50.300000000000011</v>
+        <v>-50.3</v>
       </c>
       <c r="AX67" s="305">
         <v>-8.56</v>
@@ -34061,7 +34088,7 @@
         <v>-16.940000000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A68" s="50">
         <v>46142</v>
       </c>
@@ -34070,16 +34097,16 @@
       </c>
       <c r="C68" s="18">
         <f t="shared" si="4"/>
-        <v>-17.130000000000003</v>
+        <v>-17.13</v>
       </c>
       <c r="BA68" s="305">
         <v>-8.5850000000000009</v>
       </c>
-      <c r="BG68" s="299">
+      <c r="BG68" s="170">
         <v>-8.5449999999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A69" s="50">
         <v>46144</v>
       </c>
@@ -34088,7 +34115,7 @@
       </c>
       <c r="C69" s="18">
         <f t="shared" si="4"/>
-        <v>-17.005000000000003</v>
+        <v>-17.004999999999999</v>
       </c>
       <c r="AX69" s="305">
         <v>-8.4250000000000007</v>
@@ -34097,7 +34124,7 @@
         <v>-8.58</v>
       </c>
     </row>
-    <row r="70" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A70" s="50">
         <v>46146</v>
       </c>
@@ -34115,7 +34142,7 @@
         <v>-8.5749999999999993</v>
       </c>
     </row>
-    <row r="71" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A71" s="50">
         <v>46148</v>
       </c>
@@ -34130,7 +34157,7 @@
         <v>-7.8849999999999998</v>
       </c>
     </row>
-    <row r="72" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A72" s="50">
         <v>46148</v>
       </c>
@@ -34138,18 +34165,18 @@
         <v>105</v>
       </c>
       <c r="C72" s="18">
-        <f t="shared" si="4"/>
-        <v>-25.840000000000003</v>
-      </c>
-      <c r="BG72" s="299">
+        <f t="shared" ref="C72:C135" si="5">SUM(D72:ER72)</f>
+        <v>-25.84</v>
+      </c>
+      <c r="BG72" s="170">
         <v>-8.6</v>
       </c>
       <c r="BJ72" s="316">
         <f>-8.67-8.57</f>
-        <v>-17.240000000000002</v>
-      </c>
-    </row>
-    <row r="73" spans="1:85" x14ac:dyDescent="0.25">
+        <v>-17.239999999999998</v>
+      </c>
+    </row>
+    <row r="73" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A73" s="50">
         <v>46148</v>
       </c>
@@ -34157,14 +34184,14 @@
         <v>92</v>
       </c>
       <c r="C73" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-25.524999999999999</v>
       </c>
       <c r="AU73" s="305">
         <v>-25.524999999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A74" s="50">
         <v>46148</v>
       </c>
@@ -34172,17 +34199,17 @@
         <v>84</v>
       </c>
       <c r="C74" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>82.53</v>
       </c>
-      <c r="BX74" s="63">
+      <c r="BY74" s="63">
         <v>49.62</v>
       </c>
-      <c r="CA74" s="330">
+      <c r="CB74" s="330">
         <v>32.909999999999997</v>
       </c>
     </row>
-    <row r="75" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A75" s="50">
         <v>46148</v>
       </c>
@@ -34190,7 +34217,7 @@
         <v>103</v>
       </c>
       <c r="C75" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>85.32</v>
       </c>
       <c r="Q75" s="305">
@@ -34202,11 +34229,11 @@
       <c r="BA75" s="305">
         <v>25.76</v>
       </c>
-      <c r="BG75" s="299">
+      <c r="BG75" s="170">
         <v>17.254999999999999</v>
       </c>
     </row>
-    <row r="76" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A76" s="50">
         <v>46148</v>
       </c>
@@ -34214,7 +34241,7 @@
         <v>92</v>
       </c>
       <c r="C76" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-42.555</v>
       </c>
       <c r="AF76" s="305">
@@ -34224,7 +34251,7 @@
         <v>-17.14</v>
       </c>
     </row>
-    <row r="77" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A77" s="50">
         <v>46149</v>
       </c>
@@ -34232,14 +34259,14 @@
         <v>84</v>
       </c>
       <c r="C77" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>17.059999999999999</v>
       </c>
-      <c r="CA77" s="330">
+      <c r="CB77" s="330">
         <v>17.059999999999999</v>
       </c>
     </row>
-    <row r="78" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A78" s="50">
         <v>46149</v>
       </c>
@@ -34247,14 +34274,14 @@
         <v>105</v>
       </c>
       <c r="C78" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-8.6</v>
       </c>
-      <c r="BG78" s="299">
+      <c r="BG78" s="170">
         <v>-8.6</v>
       </c>
     </row>
-    <row r="79" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A79" s="50">
         <v>46149</v>
       </c>
@@ -34262,7 +34289,7 @@
         <v>89</v>
       </c>
       <c r="C79" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-17.015000000000001</v>
       </c>
       <c r="Q79" s="305">
@@ -34272,7 +34299,7 @@
         <v>-8.6199999999999992</v>
       </c>
     </row>
-    <row r="80" spans="1:85" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A80" s="50">
         <v>46149</v>
       </c>
@@ -34280,14 +34307,14 @@
         <v>91</v>
       </c>
       <c r="C80" s="18">
-        <f t="shared" ref="C80:C112" si="5">SUM(D80:EQ80)</f>
+        <f t="shared" si="5"/>
         <v>-8.4949999999999992</v>
       </c>
       <c r="AF80" s="305">
         <v>-8.4949999999999992</v>
       </c>
     </row>
-    <row r="81" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A81" s="50">
         <v>46149</v>
       </c>
@@ -34298,11 +34325,11 @@
         <f t="shared" si="5"/>
         <v>-49.97</v>
       </c>
-      <c r="CA81" s="330">
+      <c r="CB81" s="330">
         <v>-49.97</v>
       </c>
     </row>
-    <row r="82" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A82" s="50">
         <v>46153</v>
       </c>
@@ -34332,7 +34359,7 @@
         <v>17.105</v>
       </c>
     </row>
-    <row r="83" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A83" s="50">
         <v>46153</v>
       </c>
@@ -34353,7 +34380,7 @@
         <v>8.3949999999999996</v>
       </c>
     </row>
-    <row r="84" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A84" s="50">
         <v>46153</v>
       </c>
@@ -34368,7 +34395,7 @@
         <v>-8.2100000000000009</v>
       </c>
     </row>
-    <row r="85" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A85" s="50">
         <v>46153</v>
       </c>
@@ -34377,12 +34404,12 @@
       </c>
       <c r="C85" s="18">
         <f t="shared" si="5"/>
-        <v>300.28499999999997</v>
+        <v>300.28500000000003</v>
       </c>
       <c r="D85" s="174">
         <v>17.09</v>
       </c>
-      <c r="E85" s="174">
+      <c r="E85" s="230">
         <v>30.995000000000001</v>
       </c>
       <c r="F85" s="174">
@@ -34403,14 +34430,14 @@
       <c r="AQ85" s="255">
         <v>35.299999999999997</v>
       </c>
-      <c r="AZ85" s="323">
+      <c r="AZ85" s="255">
         <v>33.47</v>
       </c>
       <c r="BC85" s="323">
         <v>33.25</v>
       </c>
     </row>
-    <row r="86" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A86" s="50">
         <v>46154</v>
       </c>
@@ -34424,14 +34451,14 @@
       <c r="D86" s="174">
         <v>-8.3049999999999997</v>
       </c>
-      <c r="E86" s="174">
+      <c r="E86" s="230">
         <v>-31.195</v>
       </c>
       <c r="F86" s="174">
         <v>-33.92</v>
       </c>
     </row>
-    <row r="87" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A87" s="50">
         <v>46154</v>
       </c>
@@ -34446,7 +34473,7 @@
         <v>-8.4</v>
       </c>
     </row>
-    <row r="88" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A88" s="50">
         <v>46154</v>
       </c>
@@ -34464,7 +34491,7 @@
         <v>-8.5449999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A89" s="50">
         <v>46154</v>
       </c>
@@ -34479,7 +34506,7 @@
         <v>-8.42</v>
       </c>
     </row>
-    <row r="90" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A90" s="50">
         <v>46154</v>
       </c>
@@ -34488,7 +34515,7 @@
       </c>
       <c r="C90" s="18">
         <f t="shared" si="5"/>
-        <v>-46.264999999999993</v>
+        <v>-46.265000000000001</v>
       </c>
       <c r="S90" s="72">
         <v>-4.1500000000000004</v>
@@ -34509,7 +34536,7 @@
         <v>-8.7449999999999992</v>
       </c>
     </row>
-    <row r="91" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A91" s="50">
         <v>46154</v>
       </c>
@@ -34518,16 +34545,16 @@
       </c>
       <c r="C91" s="18">
         <f t="shared" si="5"/>
-        <v>-33.754999999999995</v>
+        <v>-33.755000000000003</v>
       </c>
       <c r="AU91" s="305">
         <v>-16.965</v>
       </c>
-      <c r="AZ91" s="323">
+      <c r="AZ91" s="255">
         <v>-16.79</v>
       </c>
     </row>
-    <row r="92" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A92" s="50">
         <v>46154</v>
       </c>
@@ -34536,7 +34563,7 @@
       </c>
       <c r="C92" s="18">
         <f t="shared" si="5"/>
-        <v>-68.054999999999993</v>
+        <v>-68.055000000000007</v>
       </c>
       <c r="AH92" s="255">
         <v>-17.09</v>
@@ -34551,7 +34578,7 @@
         <v>-17.63</v>
       </c>
     </row>
-    <row r="93" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A93" s="50">
         <v>46154</v>
       </c>
@@ -34560,7 +34587,7 @@
       </c>
       <c r="C93" s="18">
         <f t="shared" si="5"/>
-        <v>-42.129999999999995</v>
+        <v>-42.13</v>
       </c>
       <c r="Z93" s="305">
         <v>-8.48</v>
@@ -34578,7 +34605,7 @@
         <v>-8.3949999999999996</v>
       </c>
     </row>
-    <row r="94" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A94" s="50">
         <v>46155</v>
       </c>
@@ -34596,7 +34623,7 @@
         <v>-8.9250000000000007</v>
       </c>
     </row>
-    <row r="95" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A95" s="50">
         <v>46156</v>
       </c>
@@ -34611,7 +34638,7 @@
         <v>-3.96</v>
       </c>
     </row>
-    <row r="96" spans="1:79" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A96" s="50">
         <v>46156</v>
       </c>
@@ -34629,7 +34656,7 @@
         <v>-8.35</v>
       </c>
     </row>
-    <row r="97" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A97" s="50">
         <v>46157</v>
       </c>
@@ -34649,11 +34676,11 @@
       <c r="AF97" s="305">
         <v>-8.4550000000000001</v>
       </c>
-      <c r="AZ97" s="323">
+      <c r="AZ97" s="255">
         <v>-8.36</v>
       </c>
     </row>
-    <row r="98" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A98" s="50">
         <v>46157</v>
       </c>
@@ -34662,7 +34689,7 @@
       </c>
       <c r="C98" s="18">
         <f t="shared" si="5"/>
-        <v>-33.709999999999994</v>
+        <v>-33.71</v>
       </c>
       <c r="AN98" s="255">
         <v>-8.24</v>
@@ -34674,7 +34701,7 @@
         <v>-8.5749999999999993</v>
       </c>
     </row>
-    <row r="99" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A99" s="50">
         <v>46157</v>
       </c>
@@ -34685,11 +34712,11 @@
         <f t="shared" si="5"/>
         <v>-24.16</v>
       </c>
-      <c r="CP99" s="35">
+      <c r="CQ99" s="247">
         <v>-24.16</v>
       </c>
     </row>
-    <row r="100" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A100" s="50">
         <v>46157</v>
       </c>
@@ -34704,7 +34731,7 @@
         <v>-17.105</v>
       </c>
     </row>
-    <row r="101" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A101" s="50">
         <v>46161</v>
       </c>
@@ -34715,11 +34742,11 @@
         <f t="shared" si="5"/>
         <v>197.405</v>
       </c>
-      <c r="AM101" s="107">
+      <c r="AM101" s="237">
         <v>197.405</v>
       </c>
     </row>
-    <row r="102" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A102" s="50">
         <v>46162</v>
       </c>
@@ -34728,14 +34755,14 @@
       </c>
       <c r="C102" s="18">
         <f t="shared" si="5"/>
-        <v>-66.085000000000008</v>
-      </c>
-      <c r="AM102" s="107">
+        <v>-66.084999999999994</v>
+      </c>
+      <c r="AM102" s="237">
         <f>-33.07-33.015</f>
-        <v>-66.085000000000008</v>
-      </c>
-    </row>
-    <row r="103" spans="1:94" x14ac:dyDescent="0.25">
+        <v>-66.084999999999994</v>
+      </c>
+    </row>
+    <row r="103" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A103" s="50">
         <v>46162</v>
       </c>
@@ -34746,11 +34773,11 @@
         <f t="shared" si="5"/>
         <v>-66.19</v>
       </c>
-      <c r="AM103" s="107">
+      <c r="AM103" s="237">
         <v>-66.19</v>
       </c>
     </row>
-    <row r="104" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:103" x14ac:dyDescent="0.25">
       <c r="A104" s="50">
         <v>46162</v>
       </c>
@@ -34761,199 +34788,328 @@
         <f t="shared" si="5"/>
         <v>-16.440000000000001</v>
       </c>
-      <c r="AM104" s="107">
+      <c r="AM104" s="237">
         <v>-16.440000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A105" s="50">
+        <v>46163</v>
+      </c>
+      <c r="B105" s="19" t="s">
+        <v>88</v>
+      </c>
       <c r="C105" s="18">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:94" x14ac:dyDescent="0.25">
+        <v>-16.440000000000001</v>
+      </c>
+      <c r="AM105" s="237">
+        <v>-16.440000000000001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A106" s="50">
+        <v>46163</v>
+      </c>
+      <c r="B106" s="19" t="s">
+        <v>89</v>
+      </c>
       <c r="C106" s="18">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:94" x14ac:dyDescent="0.25">
+        <v>-15.75</v>
+      </c>
+      <c r="AM106" s="237">
+        <v>-7.43</v>
+      </c>
+      <c r="AZ106" s="255">
+        <v>-8.32</v>
+      </c>
+    </row>
+    <row r="107" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A107" s="50">
+        <v>46163</v>
+      </c>
+      <c r="B107" s="19" t="s">
+        <v>105</v>
+      </c>
       <c r="C107" s="18">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:94" x14ac:dyDescent="0.25">
+        <v>-16.545000000000002</v>
+      </c>
+      <c r="AM107" s="237">
+        <v>-16.545000000000002</v>
+      </c>
+    </row>
+    <row r="108" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A108" s="50">
+        <v>46165</v>
+      </c>
+      <c r="B108" s="19" t="s">
+        <v>85</v>
+      </c>
       <c r="C108" s="18">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:94" x14ac:dyDescent="0.25">
+        <v>-27.684999999999999</v>
+      </c>
+      <c r="CJ108" s="56">
+        <v>-21</v>
+      </c>
+      <c r="CY108" s="72">
+        <v>-6.6849999999999996</v>
+      </c>
+    </row>
+    <row r="109" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A109" s="50">
+        <v>46175</v>
+      </c>
+      <c r="B109" s="19" t="s">
+        <v>100</v>
+      </c>
       <c r="C109" s="18">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:94" x14ac:dyDescent="0.25">
+        <v>-8.2750000000000004</v>
+      </c>
+      <c r="AM109" s="237">
+        <v>-8.2750000000000004</v>
+      </c>
+    </row>
+    <row r="110" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A110" s="50">
+        <v>46175</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>118</v>
+      </c>
       <c r="C110" s="18">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:94" x14ac:dyDescent="0.25">
+        <v>-8.39</v>
+      </c>
+      <c r="E110" s="230">
+        <v>-8.39</v>
+      </c>
+    </row>
+    <row r="111" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A111" s="50">
+        <v>46175</v>
+      </c>
+      <c r="B111" s="19" t="s">
+        <v>84</v>
+      </c>
       <c r="C111" s="18">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:94" x14ac:dyDescent="0.25">
+        <v>0.85</v>
+      </c>
+      <c r="BE111" s="107">
+        <v>24.32</v>
+      </c>
+      <c r="BK111" s="63">
+        <v>9.77</v>
+      </c>
+      <c r="BY111" s="63">
+        <v>-33.24</v>
+      </c>
+    </row>
+    <row r="112" spans="1:103" x14ac:dyDescent="0.25">
+      <c r="A112" s="50">
+        <v>46175</v>
+      </c>
+      <c r="B112" s="19" t="s">
+        <v>92</v>
+      </c>
       <c r="C112" s="18">
         <f t="shared" si="5"/>
+        <v>-33.685000000000002</v>
+      </c>
+      <c r="BP112" s="255">
+        <v>-8.1549999999999994</v>
+      </c>
+      <c r="BQ112" s="299">
+        <v>-8.59</v>
+      </c>
+      <c r="BT112" s="299">
+        <v>-16.940000000000001</v>
+      </c>
+    </row>
+    <row r="113" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A113" s="50">
+        <v>46176</v>
+      </c>
+      <c r="B113" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C113" s="18">
+        <f t="shared" si="5"/>
+        <v>-8.5749999999999993</v>
+      </c>
+      <c r="BT113" s="299">
+        <v>-8.5749999999999993</v>
+      </c>
+    </row>
+    <row r="114" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A114" s="50">
+        <v>46176</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C114" s="18">
+        <f t="shared" si="5"/>
+        <v>50.515000000000001</v>
+      </c>
+      <c r="E114" s="230">
+        <v>16.315000000000001</v>
+      </c>
+      <c r="BC114" s="323">
+        <v>34.200000000000003</v>
+      </c>
+    </row>
+    <row r="115" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A115" s="50">
+        <v>46176</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C115" s="18">
+        <f t="shared" si="5"/>
+        <v>-33.78</v>
+      </c>
+      <c r="BC115" s="323">
+        <v>-33.78</v>
+      </c>
+    </row>
+    <row r="116" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="A116" s="50">
+        <v>46176</v>
+      </c>
+      <c r="B116" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C116" s="18">
+        <f t="shared" si="5"/>
+        <v>-16.315000000000001</v>
+      </c>
+      <c r="E116" s="230">
+        <v>-16.315000000000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="C117" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C113" s="18">
-        <f t="shared" ref="C113:C144" si="6">SUM(D113:EQ113)</f>
+    <row r="118" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="C118" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C114" s="18">
-        <f t="shared" si="6"/>
+    <row r="119" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="C119" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C115" s="18">
-        <f t="shared" si="6"/>
+    <row r="120" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="C120" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C116" s="18">
-        <f t="shared" si="6"/>
+    <row r="121" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="C121" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C117" s="18">
-        <f t="shared" si="6"/>
+    <row r="122" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="C122" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C118" s="18">
-        <f t="shared" si="6"/>
+    <row r="123" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="C123" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C119" s="18">
-        <f t="shared" si="6"/>
+    <row r="124" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="C124" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C120" s="18">
-        <f t="shared" si="6"/>
+    <row r="125" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="C125" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C121" s="18">
-        <f t="shared" si="6"/>
+    <row r="126" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="C126" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C122" s="18">
-        <f t="shared" si="6"/>
+    <row r="127" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="C127" s="18">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C123" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C124" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C125" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C126" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C127" s="18">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:72" x14ac:dyDescent="0.25">
       <c r="C128" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C129" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C130" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C131" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="132" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C132" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C133" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="134" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C134" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="135" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C135" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="136" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C136" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="C136:C199" si="6">SUM(D136:ER136)</f>
         <v>0</v>
       </c>
     </row>
@@ -35007,811 +35163,817 @@
     </row>
     <row r="145" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C145" s="18">
-        <f t="shared" ref="C145:C176" si="7">SUM(D145:EQ145)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="146" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C146" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C147" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C148" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C149" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C150" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C151" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C152" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C153" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C154" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C155" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C156" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C157" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C158" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C159" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C160" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C161" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C162" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C163" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C164" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C165" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C166" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C167" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C168" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C169" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C170" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C171" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C172" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C173" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C174" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C175" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C176" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C177" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C178" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C179" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C180" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C181" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C182" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C183" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C184" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C185" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C186" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C187" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C188" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C189" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C190" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C191" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C192" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C193" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C194" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C195" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C196" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C197" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C198" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C199" s="18">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C200" s="18">
+        <f t="shared" ref="C200:C263" si="7">SUM(D200:ER200)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C201" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C147" s="18">
+    <row r="202" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C202" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C148" s="18">
+    <row r="203" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C203" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C149" s="18">
+    <row r="204" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C204" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C150" s="18">
+    <row r="205" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C205" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C151" s="18">
+    <row r="206" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C206" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C152" s="18">
+    <row r="207" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C207" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C153" s="18">
+    <row r="208" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C208" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C154" s="18">
+    <row r="209" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C209" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C155" s="18">
+    <row r="210" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C210" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C156" s="18">
+    <row r="211" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C211" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C157" s="18">
+    <row r="212" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C212" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C158" s="18">
+    <row r="213" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C213" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C159" s="18">
+    <row r="214" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C214" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C160" s="18">
+    <row r="215" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C215" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C161" s="18">
+    <row r="216" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C216" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C162" s="18">
+    <row r="217" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C217" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C163" s="18">
+    <row r="218" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C218" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C164" s="18">
+    <row r="219" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C219" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C165" s="18">
+    <row r="220" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C220" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C166" s="18">
+    <row r="221" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C221" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C167" s="18">
+    <row r="222" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C222" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C168" s="18">
+    <row r="223" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C223" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C169" s="18">
+    <row r="224" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C224" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C170" s="18">
+    <row r="225" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C225" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C171" s="18">
+    <row r="226" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C226" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C172" s="18">
+    <row r="227" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C227" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C173" s="18">
+    <row r="228" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C228" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C174" s="18">
+    <row r="229" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C229" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C175" s="18">
+    <row r="230" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C230" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C176" s="18">
+    <row r="231" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C231" s="18">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C177" s="18">
-        <f t="shared" ref="C177:C208" si="8">SUM(D177:EQ177)</f>
+    <row r="232" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C232" s="18">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C178" s="18">
+    <row r="233" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C233" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C234" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C235" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C236" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C237" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C238" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C239" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C240" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C241" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C242" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C243" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C244" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C245" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C246" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C247" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C248" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C249" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C250" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C251" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C252" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C253" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C254" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C255" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C256" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C257" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C258" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C259" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C260" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C261" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C262" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C263" s="18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C264" s="18">
+        <f t="shared" ref="C264:C327" si="8">SUM(D264:ER264)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C265" s="18">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C179" s="18">
+    <row r="266" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C266" s="18">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C180" s="18">
+    <row r="267" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C267" s="18">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C181" s="18">
+    <row r="268" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C268" s="18">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C182" s="18">
+    <row r="269" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C269" s="18">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C183" s="18">
+    <row r="270" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C270" s="18">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C184" s="18">
+    <row r="271" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C271" s="18">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C185" s="18">
+    <row r="272" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C272" s="18">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C186" s="18">
+    <row r="273" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C273" s="18">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C187" s="18">
-        <f t="shared" si="8"/>
+    <row r="274" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C274" s="18">
+        <f t="shared" ref="C274:C280" si="9">SUM(D274:ER274)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C188" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C189" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C190" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C191" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C192" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C193" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C194" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C195" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C196" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C197" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C198" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C199" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C200" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C201" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C202" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C203" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C204" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C205" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C206" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C207" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C208" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C209" s="18">
-        <f t="shared" ref="C209:C240" si="9">SUM(D209:EQ209)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="210" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C210" s="18">
+    <row r="275" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C275" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C211" s="18">
+    <row r="276" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C276" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C212" s="18">
+    <row r="277" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C277" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C213" s="18">
+    <row r="278" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C278" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C214" s="18">
+    <row r="279" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C279" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C215" s="18">
+    <row r="280" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C280" s="18">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C216" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C217" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C218" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C219" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C220" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C221" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C222" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C223" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C224" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C225" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C226" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C227" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C228" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C229" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C230" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C231" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C232" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C233" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C234" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C235" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C236" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C237" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C238" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C239" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C240" s="18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C241" s="18">
-        <f t="shared" ref="C241:C272" si="10">SUM(D241:EQ241)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C242" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C243" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C244" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C245" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C246" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C247" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C248" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C249" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C250" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C251" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C252" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C253" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C254" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C255" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C256" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C257" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C258" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C259" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C260" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C261" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C262" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C263" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C264" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C265" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C266" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C267" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C268" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C269" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C270" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="271" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C271" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C272" s="18">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C273" s="18">
-        <f t="shared" ref="C273:C279" si="11">SUM(D273:EQ273)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C274" s="18">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C275" s="18">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C276" s="18">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C277" s="18">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C278" s="18">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C279" s="18">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -35884,7 +36046,7 @@
       </c>
       <c r="C6" s="91">
         <f>21.6+20.86+3.44+17.62</f>
-        <v>63.519999999999996</v>
+        <v>63.52</v>
       </c>
       <c r="D6" s="89"/>
     </row>
@@ -36114,7 +36276,7 @@
       <c r="D3" s="127"/>
       <c r="E3" s="127">
         <f>'STOK DETAY'!E6</f>
-        <v>8.39</v>
+        <v>0</v>
       </c>
       <c r="F3" s="127"/>
       <c r="G3" s="127"/>
@@ -36122,7 +36284,7 @@
       <c r="I3" s="127"/>
       <c r="J3" s="146">
         <f t="shared" si="0"/>
-        <v>8.39</v>
+        <v>0</v>
       </c>
       <c r="K3" s="74"/>
       <c r="L3" s="74"/>
@@ -36259,7 +36421,7 @@
       </c>
       <c r="D7" s="127">
         <f>'STOK DETAY'!I6</f>
-        <v>2.0999999999999996</v>
+        <v>2.1</v>
       </c>
       <c r="E7" s="127"/>
       <c r="F7" s="127"/>
@@ -36268,7 +36430,7 @@
       <c r="I7" s="127"/>
       <c r="J7" s="146">
         <f t="shared" si="0"/>
-        <v>2.0999999999999996</v>
+        <v>2.1</v>
       </c>
       <c r="K7" s="74"/>
       <c r="L7" s="74"/>
@@ -36562,7 +36724,7 @@
       </c>
       <c r="E15" s="146">
         <f>'STOK DETAY'!S6</f>
-        <v>5.8900000000000006</v>
+        <v>5.89</v>
       </c>
       <c r="F15" s="146"/>
       <c r="G15" s="146"/>
@@ -36570,7 +36732,7 @@
       <c r="I15" s="146"/>
       <c r="J15" s="146">
         <f t="shared" si="0"/>
-        <v>5.8900000000000006</v>
+        <v>5.89</v>
       </c>
       <c r="K15" s="74"/>
       <c r="L15" s="74"/>
@@ -36635,7 +36797,7 @@
       </c>
       <c r="D17" s="146">
         <f>'STOK DETAY'!U6</f>
-        <v>7.9936057773011271E-15</v>
+        <v>0</v>
       </c>
       <c r="E17" s="146">
         <f>'STOK DETAY'!V6</f>
@@ -36650,7 +36812,7 @@
       <c r="I17" s="146"/>
       <c r="J17" s="146">
         <f t="shared" si="0"/>
-        <v>7.9936057773011271E-15</v>
+        <v>0</v>
       </c>
       <c r="K17" s="74"/>
       <c r="L17" s="74"/>
@@ -36893,7 +37055,7 @@
       </c>
       <c r="D23" s="146">
         <f>'STOK DETAY'!AM6</f>
-        <v>48.69</v>
+        <v>0</v>
       </c>
       <c r="E23" s="146">
         <f>'STOK DETAY'!AN6</f>
@@ -36908,7 +37070,7 @@
       <c r="I23" s="146"/>
       <c r="J23" s="146">
         <f t="shared" si="0"/>
-        <v>48.69</v>
+        <v>0</v>
       </c>
       <c r="K23" s="74"/>
       <c r="L23" s="74"/>
@@ -37065,11 +37227,11 @@
       </c>
       <c r="D27" s="146">
         <f>'STOK DETAY'!AY6</f>
-        <v>7.1054273576010019E-15</v>
+        <v>0</v>
       </c>
       <c r="E27" s="146">
         <f>'STOK DETAY'!AZ6</f>
-        <v>8.32</v>
+        <v>0</v>
       </c>
       <c r="F27" s="146">
         <f>'STOK DETAY'!BA6</f>
@@ -37080,7 +37242,7 @@
       <c r="I27" s="146"/>
       <c r="J27" s="146">
         <f t="shared" si="0"/>
-        <v>8.3200000000000074</v>
+        <v>0</v>
       </c>
       <c r="K27" s="74"/>
       <c r="L27" s="74"/>
@@ -37112,7 +37274,7 @@
       </c>
       <c r="E28" s="146">
         <f>'STOK DETAY'!BC6</f>
-        <v>33.25</v>
+        <v>33.67</v>
       </c>
       <c r="F28" s="146">
         <f>'STOK DETAY'!BD6</f>
@@ -37123,7 +37285,7 @@
       <c r="I28" s="146"/>
       <c r="J28" s="146">
         <f t="shared" si="0"/>
-        <v>33.25</v>
+        <v>33.67</v>
       </c>
       <c r="K28" s="74"/>
       <c r="L28" s="74"/>
@@ -37151,7 +37313,7 @@
       </c>
       <c r="D29" s="146">
         <f>'STOK DETAY'!BE6</f>
-        <v>0</v>
+        <v>24.32</v>
       </c>
       <c r="E29" s="146">
         <f>'STOK DETAY'!BF6</f>
@@ -37166,7 +37328,7 @@
       <c r="I29" s="146"/>
       <c r="J29" s="146">
         <f t="shared" si="0"/>
-        <v>8.6549999999999994</v>
+        <v>32.975000000000001</v>
       </c>
       <c r="K29" s="74"/>
       <c r="L29" s="74"/>
@@ -37197,7 +37359,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="146">
-        <f>'STOK DETAY'!BK6</f>
+        <f>'STOK DETAY'!BL6</f>
         <v>0</v>
       </c>
       <c r="F30" s="146">
@@ -37236,15 +37398,15 @@
         <v>501</v>
       </c>
       <c r="D31" s="146">
-        <f>'STOK DETAY'!BK6</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="146">
         <f>'STOK DETAY'!BL6</f>
         <v>0</v>
       </c>
+      <c r="E31" s="146">
+        <f>'STOK DETAY'!BM6</f>
+        <v>0</v>
+      </c>
       <c r="F31" s="146">
-        <f>'STOK DETAY'!BM6</f>
+        <f>'STOK DETAY'!BN6</f>
         <v>16.925000000000001</v>
       </c>
       <c r="G31" s="216"/>
@@ -37279,23 +37441,23 @@
         <v>501</v>
       </c>
       <c r="D32" s="146">
-        <f>'STOK DETAY'!BN6</f>
+        <f>'STOK DETAY'!BO6</f>
         <v>0</v>
       </c>
       <c r="E32" s="146">
-        <f>'STOK DETAY'!BO6</f>
-        <v>8.1550000000000011</v>
+        <f>'STOK DETAY'!BP6</f>
+        <v>0</v>
       </c>
       <c r="F32" s="146">
-        <f>'STOK DETAY'!BP6</f>
-        <v>17.184999999999999</v>
+        <f>'STOK DETAY'!BQ6</f>
+        <v>8.5950000000000006</v>
       </c>
       <c r="G32" s="146"/>
       <c r="H32" s="146"/>
       <c r="I32" s="146"/>
       <c r="J32" s="146">
         <f t="shared" si="0"/>
-        <v>25.34</v>
+        <v>8.5950000000000006</v>
       </c>
       <c r="K32" s="74"/>
       <c r="L32" s="74"/>
@@ -37322,23 +37484,23 @@
         <v>502</v>
       </c>
       <c r="D33" s="146">
-        <f>'STOK DETAY'!BQ6</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="146">
         <f>'STOK DETAY'!BR6</f>
         <v>0</v>
       </c>
+      <c r="E33" s="146">
+        <f>'STOK DETAY'!BS6</f>
+        <v>0</v>
+      </c>
       <c r="F33" s="146">
-        <f>'STOK DETAY'!BS6</f>
-        <v>34.085000000000001</v>
+        <f>'STOK DETAY'!BT6</f>
+        <v>8.57</v>
       </c>
       <c r="G33" s="146"/>
       <c r="H33" s="146"/>
       <c r="I33" s="146"/>
       <c r="J33" s="146">
         <f t="shared" si="0"/>
-        <v>34.085000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="K33" s="74"/>
       <c r="L33" s="74"/>
@@ -37365,23 +37527,23 @@
         <v>502</v>
       </c>
       <c r="D34" s="146">
-        <f>'STOK DETAY'!BT6</f>
-        <v>47.559999999999988</v>
+        <f>'STOK DETAY'!BU6</f>
+        <v>47.56</v>
       </c>
       <c r="E34" s="146"/>
       <c r="F34" s="146"/>
       <c r="G34" s="146"/>
       <c r="H34" s="146">
-        <f>'STOK DETAY'!BU6</f>
+        <f>'STOK DETAY'!BV6</f>
         <v>8.44</v>
       </c>
       <c r="I34" s="146">
-        <f>'STOK DETAY'!BV6</f>
+        <f>'STOK DETAY'!BW6</f>
         <v>1.75</v>
       </c>
       <c r="J34" s="146">
         <f t="shared" ref="J34:J65" si="1">SUM(D34:I34)</f>
-        <v>57.749999999999986</v>
+        <v>57.75</v>
       </c>
       <c r="K34" s="74"/>
       <c r="L34" s="74"/>
@@ -37408,20 +37570,20 @@
         <v>503</v>
       </c>
       <c r="D35" s="146">
-        <f>'STOK DETAY'!BW6</f>
+        <f>'STOK DETAY'!BX6</f>
         <v>0</v>
       </c>
       <c r="E35" s="146"/>
       <c r="F35" s="146"/>
       <c r="G35" s="146"/>
       <c r="H35" s="146">
-        <f>'STOK DETAY'!BX6</f>
-        <v>110.34</v>
+        <f>'STOK DETAY'!BY6</f>
+        <v>77.099999999999994</v>
       </c>
       <c r="I35" s="146"/>
       <c r="J35" s="146">
         <f t="shared" si="1"/>
-        <v>110.34</v>
+        <v>77.099999999999994</v>
       </c>
       <c r="K35" s="74"/>
       <c r="L35" s="74"/>
@@ -37448,14 +37610,14 @@
         <v>503</v>
       </c>
       <c r="D36" s="146">
-        <f>'STOK DETAY'!BY6</f>
+        <f>'STOK DETAY'!BZ6</f>
         <v>16.170000000000002</v>
       </c>
       <c r="E36" s="146"/>
       <c r="F36" s="146"/>
       <c r="G36" s="146"/>
       <c r="H36" s="146">
-        <f>'STOK DETAY'!BZ6</f>
+        <f>'STOK DETAY'!CA6</f>
         <v>0</v>
       </c>
       <c r="I36" s="146"/>
@@ -37490,7 +37652,7 @@
       <c r="F37" s="146"/>
       <c r="G37" s="146"/>
       <c r="H37" s="146">
-        <f>'STOK DETAY'!CA6</f>
+        <f>'STOK DETAY'!CB6</f>
         <v>0</v>
       </c>
       <c r="I37" s="146"/>
@@ -37527,7 +37689,7 @@
       <c r="F38" s="146"/>
       <c r="G38" s="146"/>
       <c r="H38" s="146">
-        <f>'STOK DETAY'!CB6</f>
+        <f>'STOK DETAY'!CC6</f>
         <v>27.65</v>
       </c>
       <c r="I38" s="146"/>
@@ -37558,7 +37720,7 @@
       </c>
       <c r="C39" s="187"/>
       <c r="D39" s="146">
-        <f>'STOK DETAY'!CC6</f>
+        <f>'STOK DETAY'!CD6</f>
         <v>0</v>
       </c>
       <c r="E39" s="146"/>
@@ -37599,7 +37761,7 @@
       <c r="F40" s="146"/>
       <c r="G40" s="146"/>
       <c r="H40" s="146">
-        <f>'STOK DETAY'!CD6</f>
+        <f>'STOK DETAY'!CE6</f>
         <v>28</v>
       </c>
       <c r="I40" s="146"/>
@@ -37632,7 +37794,7 @@
         <v>112</v>
       </c>
       <c r="D41" s="146">
-        <f>'STOK DETAY'!CE6</f>
+        <f>'STOK DETAY'!CF6</f>
         <v>0</v>
       </c>
       <c r="E41" s="146"/>
@@ -37667,7 +37829,7 @@
       </c>
       <c r="C42" s="187"/>
       <c r="D42" s="146">
-        <f>'STOK DETAY'!CF6</f>
+        <f>'STOK DETAY'!CG6</f>
         <v>0</v>
       </c>
       <c r="E42" s="146"/>
@@ -37708,13 +37870,13 @@
       <c r="F43" s="146"/>
       <c r="G43" s="146"/>
       <c r="H43" s="146">
-        <f>'STOK DETAY'!CG6</f>
-        <v>21.650000000000002</v>
+        <f>'STOK DETAY'!CH6</f>
+        <v>21.65</v>
       </c>
       <c r="I43" s="146"/>
       <c r="J43" s="146">
         <f t="shared" si="1"/>
-        <v>21.650000000000002</v>
+        <v>21.65</v>
       </c>
       <c r="K43" s="74"/>
       <c r="L43" s="74"/>
@@ -37777,13 +37939,13 @@
       <c r="F45" s="146"/>
       <c r="G45" s="146"/>
       <c r="H45" s="146">
-        <f>'STOK DETAY'!CI6</f>
-        <v>45.4</v>
+        <f>'STOK DETAY'!CJ6</f>
+        <v>24.4</v>
       </c>
       <c r="I45" s="146"/>
       <c r="J45" s="146">
         <f t="shared" si="1"/>
-        <v>45.4</v>
+        <v>24.4</v>
       </c>
       <c r="K45" s="74"/>
       <c r="L45" s="74"/>
@@ -37813,7 +37975,7 @@
       <c r="E46" s="146"/>
       <c r="F46" s="146"/>
       <c r="G46" s="146">
-        <f>'STOK DETAY'!CJ6</f>
+        <f>'STOK DETAY'!CK6</f>
         <v>9.1999999999999993</v>
       </c>
       <c r="H46" s="146"/>
@@ -37851,7 +38013,7 @@
       <c r="F47" s="146"/>
       <c r="G47" s="146"/>
       <c r="H47" s="146">
-        <f>'STOK DETAY'!CK6</f>
+        <f>'STOK DETAY'!CL6</f>
         <v>89.45</v>
       </c>
       <c r="I47" s="146"/>
@@ -37888,7 +38050,7 @@
       <c r="F48" s="146"/>
       <c r="G48" s="146"/>
       <c r="H48" s="146">
-        <f>'STOK DETAY'!CL6</f>
+        <f>'STOK DETAY'!CM6</f>
         <v>21.45</v>
       </c>
       <c r="I48" s="146"/>
@@ -37921,7 +38083,7 @@
         <v>312</v>
       </c>
       <c r="D49" s="146">
-        <f>'STOK DETAY'!CM6</f>
+        <f>'STOK DETAY'!CN6</f>
         <v>54.058</v>
       </c>
       <c r="E49" s="146"/>
@@ -37956,7 +38118,7 @@
       </c>
       <c r="C50" s="220"/>
       <c r="D50" s="146">
-        <f>'STOK DETAY'!CN6</f>
+        <f>'STOK DETAY'!CO6</f>
         <v>0</v>
       </c>
       <c r="E50" s="146"/>
@@ -37991,7 +38153,7 @@
       </c>
       <c r="C51" s="220"/>
       <c r="D51" s="146">
-        <f>'STOK DETAY'!CO6</f>
+        <f>'STOK DETAY'!CP6</f>
         <v>0</v>
       </c>
       <c r="E51" s="146"/>
@@ -38028,11 +38190,11 @@
         <v>212</v>
       </c>
       <c r="D52" s="146">
-        <f>'STOK DETAY'!CP6</f>
+        <f>'STOK DETAY'!CQ6</f>
         <v>0</v>
       </c>
       <c r="E52" s="146">
-        <f>'STOK DETAY'!CQ6</f>
+        <f>'STOK DETAY'!CR6</f>
         <v>0</v>
       </c>
       <c r="F52" s="146"/>
@@ -38071,7 +38233,7 @@
       <c r="E53" s="146"/>
       <c r="F53" s="146"/>
       <c r="G53" s="146">
-        <f>'STOK DETAY'!CR6</f>
+        <f>'STOK DETAY'!CS6</f>
         <v>0</v>
       </c>
       <c r="H53" s="146"/>
@@ -38103,16 +38265,16 @@
       </c>
       <c r="C54" s="220"/>
       <c r="D54" s="146">
-        <f>'STOK DETAY'!CS6</f>
-        <v>0</v>
-      </c>
-      <c r="E54" s="146">
         <f>'STOK DETAY'!CT6</f>
         <v>0</v>
       </c>
+      <c r="E54" s="146">
+        <f>'STOK DETAY'!CU6</f>
+        <v>0</v>
+      </c>
       <c r="F54" s="146"/>
       <c r="G54" s="146">
-        <f>'STOK DETAY'!CU6</f>
+        <f>'STOK DETAY'!CV6</f>
         <v>0</v>
       </c>
       <c r="H54" s="146"/>
@@ -38144,7 +38306,7 @@
       </c>
       <c r="C55" s="220"/>
       <c r="D55" s="146">
-        <f>'STOK DETAY'!CV6</f>
+        <f>'STOK DETAY'!CW6</f>
         <v>0</v>
       </c>
       <c r="E55" s="146"/>
@@ -38181,12 +38343,12 @@
         <v>311</v>
       </c>
       <c r="D56" s="146">
-        <f>'STOK DETAY'!CW6</f>
+        <f>'STOK DETAY'!CX6</f>
         <v>0</v>
       </c>
       <c r="E56" s="146">
-        <f>'STOK DETAY'!CX6</f>
-        <v>13.32</v>
+        <f>'STOK DETAY'!CY6</f>
+        <v>6.6349999999999998</v>
       </c>
       <c r="F56" s="146"/>
       <c r="G56" s="146"/>
@@ -38194,7 +38356,7 @@
       <c r="I56" s="146"/>
       <c r="J56" s="146">
         <f t="shared" si="1"/>
-        <v>13.32</v>
+        <v>6.6349999999999998</v>
       </c>
       <c r="K56" s="74"/>
       <c r="L56" s="74"/>
@@ -38221,7 +38383,7 @@
         <v>311</v>
       </c>
       <c r="D57" s="146">
-        <f>'STOK DETAY'!CY6</f>
+        <f>'STOK DETAY'!CZ6</f>
         <v>8.9849999999999994</v>
       </c>
       <c r="E57" s="146"/>
@@ -38256,7 +38418,7 @@
       </c>
       <c r="C58" s="220"/>
       <c r="D58" s="146">
-        <f>'STOK DETAY'!CZ6</f>
+        <f>'STOK DETAY'!DA6</f>
         <v>0</v>
       </c>
       <c r="E58" s="146"/>
@@ -38291,7 +38453,7 @@
       </c>
       <c r="C59" s="220"/>
       <c r="D59" s="146">
-        <f>'STOK DETAY'!DA6</f>
+        <f>'STOK DETAY'!DB6</f>
         <v>0</v>
       </c>
       <c r="E59" s="146"/>
@@ -38326,7 +38488,7 @@
       </c>
       <c r="C60" s="220"/>
       <c r="D60" s="146">
-        <f>'STOK DETAY'!DB6</f>
+        <f>'STOK DETAY'!DC6</f>
         <v>0</v>
       </c>
       <c r="E60" s="146"/>
@@ -38366,7 +38528,7 @@
       <c r="E61" s="146"/>
       <c r="F61" s="146"/>
       <c r="G61" s="146">
-        <f>'STOK DETAY'!DD6</f>
+        <f>'STOK DETAY'!DE6</f>
         <v>93.39</v>
       </c>
       <c r="H61" s="146"/>
@@ -38400,7 +38562,7 @@
         <v>213</v>
       </c>
       <c r="D62" s="146">
-        <f>'STOK DETAY'!DE6</f>
+        <f>'STOK DETAY'!DF6</f>
         <v>14.9</v>
       </c>
       <c r="E62" s="146"/>
@@ -38440,7 +38602,7 @@
       <c r="E63" s="146"/>
       <c r="F63" s="146"/>
       <c r="G63" s="146">
-        <f>'STOK DETAY'!DF6</f>
+        <f>'STOK DETAY'!DG6</f>
         <v>6.02</v>
       </c>
       <c r="H63" s="146"/>
@@ -38474,7 +38636,7 @@
         <v>312</v>
       </c>
       <c r="D64" s="146">
-        <f>'STOK DETAY'!DG6</f>
+        <f>'STOK DETAY'!DH6</f>
         <v>2.25</v>
       </c>
       <c r="E64" s="146"/>
@@ -38513,7 +38675,7 @@
       <c r="D65" s="146"/>
       <c r="E65" s="216"/>
       <c r="F65" s="146">
-        <f>'STOK DETAY'!DH6</f>
+        <f>'STOK DETAY'!DI6</f>
         <v>3.28</v>
       </c>
       <c r="G65" s="146"/>
@@ -38550,7 +38712,7 @@
       <c r="D66" s="146"/>
       <c r="E66" s="216"/>
       <c r="F66" s="146">
-        <f>'STOK DETAY'!DI6</f>
+        <f>'STOK DETAY'!DJ6</f>
         <v>63.54</v>
       </c>
       <c r="G66" s="146"/>
@@ -38587,7 +38749,7 @@
       <c r="D67" s="146"/>
       <c r="E67" s="216"/>
       <c r="F67" s="146">
-        <f>'STOK DETAY'!DJ6</f>
+        <f>'STOK DETAY'!DK6</f>
         <v>10.45</v>
       </c>
       <c r="G67" s="146"/>
@@ -38625,7 +38787,7 @@
       <c r="E68" s="146"/>
       <c r="F68" s="146"/>
       <c r="G68" s="146">
-        <f>'STOK DETAY'!DK6</f>
+        <f>'STOK DETAY'!DL6</f>
         <v>0</v>
       </c>
       <c r="H68" s="146"/>
@@ -38660,12 +38822,12 @@
       </c>
       <c r="D69" s="216"/>
       <c r="E69" s="146">
-        <f>'STOK DETAY'!DL6</f>
+        <f>'STOK DETAY'!DM6</f>
         <v>404.44</v>
       </c>
       <c r="F69" s="146"/>
       <c r="G69" s="146">
-        <f>'STOK DETAY'!DM6</f>
+        <f>'STOK DETAY'!DN6</f>
         <v>0</v>
       </c>
       <c r="H69" s="146"/>
@@ -38701,7 +38863,7 @@
       <c r="D70" s="146"/>
       <c r="E70" s="216"/>
       <c r="F70" s="146">
-        <f>'STOK DETAY'!DN6</f>
+        <f>'STOK DETAY'!DO6</f>
         <v>2.5</v>
       </c>
       <c r="G70" s="146"/>
@@ -38738,7 +38900,7 @@
       <c r="D71" s="146"/>
       <c r="E71" s="216"/>
       <c r="F71" s="146">
-        <f>'STOK DETAY'!DO6</f>
+        <f>'STOK DETAY'!DP6</f>
         <v>14.7</v>
       </c>
       <c r="G71" s="146"/>
@@ -38775,7 +38937,7 @@
       <c r="D72" s="146"/>
       <c r="E72" s="216"/>
       <c r="F72" s="146">
-        <f>'STOK DETAY'!DP6</f>
+        <f>'STOK DETAY'!DQ6</f>
         <v>2.85</v>
       </c>
       <c r="G72" s="146"/>
@@ -38812,7 +38974,7 @@
       <c r="D73" s="146"/>
       <c r="E73" s="216"/>
       <c r="F73" s="146">
-        <f>'STOK DETAY'!DQ6</f>
+        <f>'STOK DETAY'!DR6</f>
         <v>6.83</v>
       </c>
       <c r="G73" s="146"/>
@@ -38849,7 +39011,7 @@
       <c r="D74" s="146"/>
       <c r="E74" s="216"/>
       <c r="F74" s="146">
-        <f>'STOK DETAY'!DR6</f>
+        <f>'STOK DETAY'!DS6</f>
         <v>9.2200000000000006</v>
       </c>
       <c r="G74" s="146"/>
@@ -38886,7 +39048,7 @@
       <c r="D75" s="146"/>
       <c r="E75" s="216"/>
       <c r="F75" s="146">
-        <f>'STOK DETAY'!DS6</f>
+        <f>'STOK DETAY'!DT6</f>
         <v>18.5</v>
       </c>
       <c r="G75" s="146"/>
@@ -38923,7 +39085,7 @@
       <c r="D76" s="146"/>
       <c r="E76" s="216"/>
       <c r="F76" s="146">
-        <f>'STOK DETAY'!DT6</f>
+        <f>'STOK DETAY'!DU6</f>
         <v>52.36</v>
       </c>
       <c r="G76" s="146"/>

--- a/STOK.xlsx
+++ b/STOK.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="125">
   <si>
     <t>BAYRAMPAŞA DEPODAKİ ELSAN AYRINTI  DÖKÜMÜ</t>
   </si>
@@ -392,6 +392,9 @@
   </si>
   <si>
     <t>MERT</t>
+  </si>
+  <si>
+    <t>AHMAD OMERAH</t>
   </si>
 </sst>
 </file>
@@ -2488,6 +2491,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="46" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="34" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2506,12 +2524,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2608,26 +2620,17 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="25" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="46" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="34" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -2888,1104 +2891,1104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="319" t="s">
+      <c r="A1" s="324" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="320"/>
-      <c r="C1" s="320"/>
-      <c r="D1" s="320"/>
-      <c r="E1" s="320"/>
-      <c r="F1" s="320"/>
-      <c r="G1" s="320"/>
-      <c r="H1" s="320"/>
-      <c r="I1" s="320"/>
-      <c r="J1" s="320"/>
-      <c r="K1" s="320"/>
-      <c r="L1" s="320"/>
-      <c r="M1" s="320"/>
-      <c r="N1" s="320"/>
-      <c r="O1" s="320"/>
-      <c r="P1" s="320"/>
-      <c r="Q1" s="320"/>
-      <c r="R1" s="320"/>
-      <c r="S1" s="320"/>
-      <c r="T1" s="320"/>
-      <c r="U1" s="320"/>
-      <c r="V1" s="320"/>
-      <c r="W1" s="320"/>
-      <c r="X1" s="320"/>
-      <c r="Y1" s="320"/>
-      <c r="Z1" s="320"/>
-      <c r="AA1" s="320"/>
-      <c r="AB1" s="320"/>
-      <c r="AC1" s="320"/>
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325"/>
+      <c r="G1" s="325"/>
+      <c r="H1" s="325"/>
+      <c r="I1" s="325"/>
+      <c r="J1" s="325"/>
+      <c r="K1" s="325"/>
+      <c r="L1" s="325"/>
+      <c r="M1" s="325"/>
+      <c r="N1" s="325"/>
+      <c r="O1" s="325"/>
+      <c r="P1" s="325"/>
+      <c r="Q1" s="325"/>
+      <c r="R1" s="325"/>
+      <c r="S1" s="325"/>
+      <c r="T1" s="325"/>
+      <c r="U1" s="325"/>
+      <c r="V1" s="325"/>
+      <c r="W1" s="325"/>
+      <c r="X1" s="325"/>
+      <c r="Y1" s="325"/>
+      <c r="Z1" s="325"/>
+      <c r="AA1" s="325"/>
+      <c r="AB1" s="325"/>
+      <c r="AC1" s="325"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A2" s="321"/>
-      <c r="B2" s="318"/>
-      <c r="C2" s="318"/>
-      <c r="D2" s="318"/>
-      <c r="E2" s="318"/>
-      <c r="F2" s="318"/>
-      <c r="G2" s="318"/>
-      <c r="H2" s="318"/>
-      <c r="I2" s="318"/>
-      <c r="J2" s="318"/>
-      <c r="K2" s="318"/>
-      <c r="L2" s="318"/>
-      <c r="M2" s="318"/>
-      <c r="N2" s="318"/>
-      <c r="O2" s="318"/>
-      <c r="P2" s="318"/>
-      <c r="Q2" s="318"/>
-      <c r="R2" s="318"/>
-      <c r="S2" s="318"/>
-      <c r="T2" s="318"/>
-      <c r="U2" s="318"/>
-      <c r="V2" s="318"/>
-      <c r="W2" s="318"/>
-      <c r="X2" s="318"/>
-      <c r="Y2" s="318"/>
-      <c r="Z2" s="318"/>
-      <c r="AA2" s="318"/>
-      <c r="AB2" s="318"/>
-      <c r="AC2" s="318"/>
+      <c r="A2" s="326"/>
+      <c r="B2" s="323"/>
+      <c r="C2" s="323"/>
+      <c r="D2" s="323"/>
+      <c r="E2" s="323"/>
+      <c r="F2" s="323"/>
+      <c r="G2" s="323"/>
+      <c r="H2" s="323"/>
+      <c r="I2" s="323"/>
+      <c r="J2" s="323"/>
+      <c r="K2" s="323"/>
+      <c r="L2" s="323"/>
+      <c r="M2" s="323"/>
+      <c r="N2" s="323"/>
+      <c r="O2" s="323"/>
+      <c r="P2" s="323"/>
+      <c r="Q2" s="323"/>
+      <c r="R2" s="323"/>
+      <c r="S2" s="323"/>
+      <c r="T2" s="323"/>
+      <c r="U2" s="323"/>
+      <c r="V2" s="323"/>
+      <c r="W2" s="323"/>
+      <c r="X2" s="323"/>
+      <c r="Y2" s="323"/>
+      <c r="Z2" s="323"/>
+      <c r="AA2" s="323"/>
+      <c r="AB2" s="323"/>
+      <c r="AC2" s="323"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1.8</v>
       </c>
-      <c r="B3" s="316"/>
+      <c r="B3" s="321"/>
       <c r="C3" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D3" s="316"/>
+      <c r="D3" s="321"/>
       <c r="E3" s="2">
         <v>2.2999999999999998</v>
       </c>
-      <c r="F3" s="316"/>
+      <c r="F3" s="321"/>
       <c r="G3" s="2">
         <v>2.4500000000000002</v>
       </c>
-      <c r="H3" s="316"/>
+      <c r="H3" s="321"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="316"/>
+      <c r="J3" s="321"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="316"/>
+      <c r="L3" s="321"/>
       <c r="M3" s="2"/>
-      <c r="N3" s="316"/>
+      <c r="N3" s="321"/>
       <c r="O3" s="2"/>
-      <c r="P3" s="316"/>
+      <c r="P3" s="321"/>
       <c r="Q3" s="2"/>
-      <c r="R3" s="316"/>
+      <c r="R3" s="321"/>
       <c r="S3" s="2"/>
-      <c r="T3" s="316"/>
+      <c r="T3" s="321"/>
       <c r="U3" s="2"/>
-      <c r="V3" s="316"/>
+      <c r="V3" s="321"/>
       <c r="W3" s="2"/>
-      <c r="X3" s="316"/>
+      <c r="X3" s="321"/>
       <c r="Y3" s="2"/>
-      <c r="Z3" s="316"/>
+      <c r="Z3" s="321"/>
       <c r="AA3" s="2"/>
-      <c r="AB3" s="318"/>
+      <c r="AB3" s="323"/>
     </row>
     <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
-      <c r="B4" s="317"/>
+      <c r="B4" s="322"/>
       <c r="C4" s="5"/>
-      <c r="D4" s="317"/>
+      <c r="D4" s="322"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="317"/>
+      <c r="F4" s="322"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="317"/>
+      <c r="H4" s="322"/>
       <c r="I4" s="5"/>
-      <c r="J4" s="317"/>
+      <c r="J4" s="322"/>
       <c r="K4" s="5"/>
-      <c r="L4" s="317"/>
+      <c r="L4" s="322"/>
       <c r="M4" s="5"/>
-      <c r="N4" s="317"/>
+      <c r="N4" s="322"/>
       <c r="O4" s="5"/>
-      <c r="P4" s="317"/>
+      <c r="P4" s="322"/>
       <c r="Q4" s="5"/>
-      <c r="R4" s="317"/>
+      <c r="R4" s="322"/>
       <c r="S4" s="5"/>
-      <c r="T4" s="317"/>
+      <c r="T4" s="322"/>
       <c r="U4" s="5"/>
-      <c r="V4" s="317"/>
+      <c r="V4" s="322"/>
       <c r="W4" s="5"/>
-      <c r="X4" s="317"/>
+      <c r="X4" s="322"/>
       <c r="Y4" s="5"/>
-      <c r="Z4" s="317"/>
+      <c r="Z4" s="322"/>
       <c r="AA4" s="5"/>
-      <c r="AB4" s="318"/>
+      <c r="AB4" s="323"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>2035.8</v>
       </c>
-      <c r="B5" s="317"/>
+      <c r="B5" s="322"/>
       <c r="C5" s="7">
         <v>2018.1</v>
       </c>
-      <c r="D5" s="317"/>
+      <c r="D5" s="322"/>
       <c r="E5" s="7">
         <v>2056.1</v>
       </c>
-      <c r="F5" s="317"/>
+      <c r="F5" s="322"/>
       <c r="G5" s="7">
         <v>1995.7</v>
       </c>
-      <c r="H5" s="317"/>
+      <c r="H5" s="322"/>
       <c r="I5" s="7"/>
-      <c r="J5" s="317"/>
+      <c r="J5" s="322"/>
       <c r="K5" s="7"/>
-      <c r="L5" s="317"/>
+      <c r="L5" s="322"/>
       <c r="M5" s="7"/>
-      <c r="N5" s="317"/>
+      <c r="N5" s="322"/>
       <c r="O5" s="7"/>
-      <c r="P5" s="317"/>
+      <c r="P5" s="322"/>
       <c r="Q5" s="7"/>
-      <c r="R5" s="317"/>
+      <c r="R5" s="322"/>
       <c r="S5" s="7"/>
-      <c r="T5" s="317"/>
+      <c r="T5" s="322"/>
       <c r="U5" s="7"/>
-      <c r="V5" s="317"/>
+      <c r="V5" s="322"/>
       <c r="W5" s="7"/>
-      <c r="X5" s="317"/>
+      <c r="X5" s="322"/>
       <c r="Y5" s="7"/>
-      <c r="Z5" s="317"/>
+      <c r="Z5" s="322"/>
       <c r="AA5" s="7"/>
-      <c r="AB5" s="318"/>
+      <c r="AB5" s="323"/>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
-      <c r="B6" s="317"/>
+      <c r="B6" s="322"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="317"/>
+      <c r="D6" s="322"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="317"/>
+      <c r="F6" s="322"/>
       <c r="G6" s="7"/>
-      <c r="H6" s="317"/>
+      <c r="H6" s="322"/>
       <c r="I6" s="7"/>
-      <c r="J6" s="317"/>
+      <c r="J6" s="322"/>
       <c r="K6" s="7"/>
-      <c r="L6" s="317"/>
+      <c r="L6" s="322"/>
       <c r="M6" s="7"/>
-      <c r="N6" s="317"/>
+      <c r="N6" s="322"/>
       <c r="O6" s="7"/>
-      <c r="P6" s="317"/>
+      <c r="P6" s="322"/>
       <c r="Q6" s="7"/>
-      <c r="R6" s="317"/>
+      <c r="R6" s="322"/>
       <c r="S6" s="7"/>
-      <c r="T6" s="317"/>
+      <c r="T6" s="322"/>
       <c r="U6" s="7"/>
-      <c r="V6" s="317"/>
+      <c r="V6" s="322"/>
       <c r="W6" s="7"/>
-      <c r="X6" s="317"/>
+      <c r="X6" s="322"/>
       <c r="Y6" s="7"/>
-      <c r="Z6" s="317"/>
+      <c r="Z6" s="322"/>
       <c r="AA6" s="7"/>
-      <c r="AB6" s="318"/>
+      <c r="AB6" s="323"/>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
-      <c r="B7" s="317"/>
+      <c r="B7" s="322"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="317"/>
+      <c r="D7" s="322"/>
       <c r="E7" s="7"/>
-      <c r="F7" s="317"/>
+      <c r="F7" s="322"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="317"/>
+      <c r="H7" s="322"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="317"/>
+      <c r="J7" s="322"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="317"/>
+      <c r="L7" s="322"/>
       <c r="M7" s="7"/>
-      <c r="N7" s="317"/>
+      <c r="N7" s="322"/>
       <c r="O7" s="7"/>
-      <c r="P7" s="317"/>
+      <c r="P7" s="322"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="317"/>
+      <c r="R7" s="322"/>
       <c r="S7" s="7"/>
-      <c r="T7" s="317"/>
+      <c r="T7" s="322"/>
       <c r="U7" s="7"/>
-      <c r="V7" s="317"/>
+      <c r="V7" s="322"/>
       <c r="W7" s="7"/>
-      <c r="X7" s="317"/>
+      <c r="X7" s="322"/>
       <c r="Y7" s="7"/>
-      <c r="Z7" s="317"/>
+      <c r="Z7" s="322"/>
       <c r="AA7" s="7"/>
-      <c r="AB7" s="318"/>
+      <c r="AB7" s="323"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
-      <c r="B8" s="317"/>
+      <c r="B8" s="322"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="317"/>
+      <c r="D8" s="322"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="317"/>
+      <c r="F8" s="322"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="317"/>
+      <c r="H8" s="322"/>
       <c r="I8" s="7"/>
-      <c r="J8" s="317"/>
+      <c r="J8" s="322"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="317"/>
+      <c r="L8" s="322"/>
       <c r="M8" s="7"/>
-      <c r="N8" s="317"/>
+      <c r="N8" s="322"/>
       <c r="O8" s="7"/>
-      <c r="P8" s="317"/>
+      <c r="P8" s="322"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="317"/>
+      <c r="R8" s="322"/>
       <c r="S8" s="7"/>
-      <c r="T8" s="317"/>
+      <c r="T8" s="322"/>
       <c r="U8" s="7"/>
-      <c r="V8" s="317"/>
+      <c r="V8" s="322"/>
       <c r="W8" s="7"/>
-      <c r="X8" s="317"/>
+      <c r="X8" s="322"/>
       <c r="Y8" s="7"/>
-      <c r="Z8" s="317"/>
+      <c r="Z8" s="322"/>
       <c r="AA8" s="7"/>
-      <c r="AB8" s="318"/>
+      <c r="AB8" s="323"/>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
-      <c r="B9" s="317"/>
+      <c r="B9" s="322"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="317"/>
+      <c r="D9" s="322"/>
       <c r="E9" s="7"/>
-      <c r="F9" s="317"/>
+      <c r="F9" s="322"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="317"/>
+      <c r="H9" s="322"/>
       <c r="I9" s="7"/>
-      <c r="J9" s="317"/>
+      <c r="J9" s="322"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="317"/>
+      <c r="L9" s="322"/>
       <c r="M9" s="7"/>
-      <c r="N9" s="317"/>
+      <c r="N9" s="322"/>
       <c r="O9" s="7"/>
-      <c r="P9" s="317"/>
+      <c r="P9" s="322"/>
       <c r="Q9" s="7"/>
-      <c r="R9" s="317"/>
+      <c r="R9" s="322"/>
       <c r="S9" s="7"/>
-      <c r="T9" s="317"/>
+      <c r="T9" s="322"/>
       <c r="U9" s="7"/>
-      <c r="V9" s="317"/>
+      <c r="V9" s="322"/>
       <c r="W9" s="7"/>
-      <c r="X9" s="317"/>
+      <c r="X9" s="322"/>
       <c r="Y9" s="7"/>
-      <c r="Z9" s="317"/>
+      <c r="Z9" s="322"/>
       <c r="AA9" s="7"/>
-      <c r="AB9" s="318"/>
+      <c r="AB9" s="323"/>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
-      <c r="B10" s="317"/>
+      <c r="B10" s="322"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="317"/>
+      <c r="D10" s="322"/>
       <c r="E10" s="7"/>
-      <c r="F10" s="317"/>
+      <c r="F10" s="322"/>
       <c r="G10" s="7"/>
-      <c r="H10" s="317"/>
+      <c r="H10" s="322"/>
       <c r="I10" s="7"/>
-      <c r="J10" s="317"/>
+      <c r="J10" s="322"/>
       <c r="K10" s="7"/>
-      <c r="L10" s="317"/>
+      <c r="L10" s="322"/>
       <c r="M10" s="7"/>
-      <c r="N10" s="317"/>
+      <c r="N10" s="322"/>
       <c r="O10" s="7"/>
-      <c r="P10" s="317"/>
+      <c r="P10" s="322"/>
       <c r="Q10" s="7"/>
-      <c r="R10" s="317"/>
+      <c r="R10" s="322"/>
       <c r="S10" s="7"/>
-      <c r="T10" s="317"/>
+      <c r="T10" s="322"/>
       <c r="U10" s="7"/>
-      <c r="V10" s="317"/>
+      <c r="V10" s="322"/>
       <c r="W10" s="7"/>
-      <c r="X10" s="317"/>
+      <c r="X10" s="322"/>
       <c r="Y10" s="7"/>
-      <c r="Z10" s="317"/>
+      <c r="Z10" s="322"/>
       <c r="AA10" s="7"/>
-      <c r="AB10" s="318"/>
+      <c r="AB10" s="323"/>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
-      <c r="B11" s="317"/>
+      <c r="B11" s="322"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="317"/>
+      <c r="D11" s="322"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="317"/>
+      <c r="F11" s="322"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="317"/>
+      <c r="H11" s="322"/>
       <c r="I11" s="7"/>
-      <c r="J11" s="317"/>
+      <c r="J11" s="322"/>
       <c r="K11" s="7"/>
-      <c r="L11" s="317"/>
+      <c r="L11" s="322"/>
       <c r="M11" s="7"/>
-      <c r="N11" s="317"/>
+      <c r="N11" s="322"/>
       <c r="O11" s="7"/>
-      <c r="P11" s="317"/>
+      <c r="P11" s="322"/>
       <c r="Q11" s="7"/>
-      <c r="R11" s="317"/>
+      <c r="R11" s="322"/>
       <c r="S11" s="7"/>
-      <c r="T11" s="317"/>
+      <c r="T11" s="322"/>
       <c r="U11" s="7"/>
-      <c r="V11" s="317"/>
+      <c r="V11" s="322"/>
       <c r="W11" s="7"/>
-      <c r="X11" s="317"/>
+      <c r="X11" s="322"/>
       <c r="Y11" s="7"/>
-      <c r="Z11" s="317"/>
+      <c r="Z11" s="322"/>
       <c r="AA11" s="7"/>
-      <c r="AB11" s="318"/>
+      <c r="AB11" s="323"/>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
-      <c r="B12" s="317"/>
+      <c r="B12" s="322"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="317"/>
+      <c r="D12" s="322"/>
       <c r="E12" s="7"/>
-      <c r="F12" s="317"/>
+      <c r="F12" s="322"/>
       <c r="G12" s="7"/>
-      <c r="H12" s="317"/>
+      <c r="H12" s="322"/>
       <c r="I12" s="7"/>
-      <c r="J12" s="317"/>
+      <c r="J12" s="322"/>
       <c r="K12" s="7"/>
-      <c r="L12" s="317"/>
+      <c r="L12" s="322"/>
       <c r="M12" s="7"/>
-      <c r="N12" s="317"/>
+      <c r="N12" s="322"/>
       <c r="O12" s="7"/>
-      <c r="P12" s="317"/>
+      <c r="P12" s="322"/>
       <c r="Q12" s="7"/>
-      <c r="R12" s="317"/>
+      <c r="R12" s="322"/>
       <c r="S12" s="7"/>
-      <c r="T12" s="317"/>
+      <c r="T12" s="322"/>
       <c r="U12" s="7"/>
-      <c r="V12" s="317"/>
+      <c r="V12" s="322"/>
       <c r="W12" s="7"/>
-      <c r="X12" s="317"/>
+      <c r="X12" s="322"/>
       <c r="Y12" s="7"/>
-      <c r="Z12" s="317"/>
+      <c r="Z12" s="322"/>
       <c r="AA12" s="7"/>
-      <c r="AB12" s="318"/>
+      <c r="AB12" s="323"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
-      <c r="B13" s="317"/>
+      <c r="B13" s="322"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="317"/>
+      <c r="D13" s="322"/>
       <c r="E13" s="7"/>
-      <c r="F13" s="317"/>
+      <c r="F13" s="322"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="317"/>
+      <c r="H13" s="322"/>
       <c r="I13" s="7"/>
-      <c r="J13" s="317"/>
+      <c r="J13" s="322"/>
       <c r="K13" s="7"/>
-      <c r="L13" s="317"/>
+      <c r="L13" s="322"/>
       <c r="M13" s="7"/>
-      <c r="N13" s="317"/>
+      <c r="N13" s="322"/>
       <c r="O13" s="7"/>
-      <c r="P13" s="317"/>
+      <c r="P13" s="322"/>
       <c r="Q13" s="7"/>
-      <c r="R13" s="317"/>
+      <c r="R13" s="322"/>
       <c r="S13" s="7"/>
-      <c r="T13" s="317"/>
+      <c r="T13" s="322"/>
       <c r="U13" s="7"/>
-      <c r="V13" s="317"/>
+      <c r="V13" s="322"/>
       <c r="W13" s="7"/>
-      <c r="X13" s="317"/>
+      <c r="X13" s="322"/>
       <c r="Y13" s="7"/>
-      <c r="Z13" s="317"/>
+      <c r="Z13" s="322"/>
       <c r="AA13" s="7"/>
-      <c r="AB13" s="318"/>
+      <c r="AB13" s="323"/>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
-      <c r="B14" s="317"/>
+      <c r="B14" s="322"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="317"/>
+      <c r="D14" s="322"/>
       <c r="E14" s="7"/>
-      <c r="F14" s="317"/>
+      <c r="F14" s="322"/>
       <c r="G14" s="7"/>
-      <c r="H14" s="317"/>
+      <c r="H14" s="322"/>
       <c r="I14" s="7"/>
-      <c r="J14" s="317"/>
+      <c r="J14" s="322"/>
       <c r="K14" s="7"/>
-      <c r="L14" s="317"/>
+      <c r="L14" s="322"/>
       <c r="M14" s="7"/>
-      <c r="N14" s="317"/>
+      <c r="N14" s="322"/>
       <c r="O14" s="7"/>
-      <c r="P14" s="317"/>
+      <c r="P14" s="322"/>
       <c r="Q14" s="7"/>
-      <c r="R14" s="317"/>
+      <c r="R14" s="322"/>
       <c r="S14" s="7"/>
-      <c r="T14" s="317"/>
+      <c r="T14" s="322"/>
       <c r="U14" s="7"/>
-      <c r="V14" s="317"/>
+      <c r="V14" s="322"/>
       <c r="W14" s="7"/>
-      <c r="X14" s="317"/>
+      <c r="X14" s="322"/>
       <c r="Y14" s="7"/>
-      <c r="Z14" s="317"/>
+      <c r="Z14" s="322"/>
       <c r="AA14" s="7"/>
-      <c r="AB14" s="318"/>
+      <c r="AB14" s="323"/>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
-      <c r="B15" s="317"/>
+      <c r="B15" s="322"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="317"/>
+      <c r="D15" s="322"/>
       <c r="E15" s="7"/>
-      <c r="F15" s="317"/>
+      <c r="F15" s="322"/>
       <c r="G15" s="7"/>
-      <c r="H15" s="317"/>
+      <c r="H15" s="322"/>
       <c r="I15" s="7"/>
-      <c r="J15" s="317"/>
+      <c r="J15" s="322"/>
       <c r="K15" s="7"/>
-      <c r="L15" s="317"/>
+      <c r="L15" s="322"/>
       <c r="M15" s="7"/>
-      <c r="N15" s="317"/>
+      <c r="N15" s="322"/>
       <c r="O15" s="7"/>
-      <c r="P15" s="317"/>
+      <c r="P15" s="322"/>
       <c r="Q15" s="7"/>
-      <c r="R15" s="317"/>
+      <c r="R15" s="322"/>
       <c r="S15" s="7"/>
-      <c r="T15" s="317"/>
+      <c r="T15" s="322"/>
       <c r="U15" s="7"/>
-      <c r="V15" s="317"/>
+      <c r="V15" s="322"/>
       <c r="W15" s="7"/>
-      <c r="X15" s="317"/>
+      <c r="X15" s="322"/>
       <c r="Y15" s="7"/>
-      <c r="Z15" s="317"/>
+      <c r="Z15" s="322"/>
       <c r="AA15" s="7"/>
-      <c r="AB15" s="318"/>
+      <c r="AB15" s="323"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="317"/>
+      <c r="B16" s="322"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="317"/>
+      <c r="D16" s="322"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="317"/>
+      <c r="F16" s="322"/>
       <c r="G16" s="7"/>
-      <c r="H16" s="317"/>
+      <c r="H16" s="322"/>
       <c r="I16" s="7"/>
-      <c r="J16" s="317"/>
+      <c r="J16" s="322"/>
       <c r="K16" s="7"/>
-      <c r="L16" s="317"/>
+      <c r="L16" s="322"/>
       <c r="M16" s="7"/>
-      <c r="N16" s="317"/>
+      <c r="N16" s="322"/>
       <c r="O16" s="7"/>
-      <c r="P16" s="317"/>
+      <c r="P16" s="322"/>
       <c r="Q16" s="7"/>
-      <c r="R16" s="317"/>
+      <c r="R16" s="322"/>
       <c r="S16" s="7"/>
-      <c r="T16" s="317"/>
+      <c r="T16" s="322"/>
       <c r="U16" s="7"/>
-      <c r="V16" s="317"/>
+      <c r="V16" s="322"/>
       <c r="W16" s="7"/>
-      <c r="X16" s="317"/>
+      <c r="X16" s="322"/>
       <c r="Y16" s="7"/>
-      <c r="Z16" s="317"/>
+      <c r="Z16" s="322"/>
       <c r="AA16" s="7"/>
-      <c r="AB16" s="318"/>
+      <c r="AB16" s="323"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
-      <c r="B17" s="317"/>
+      <c r="B17" s="322"/>
       <c r="C17" s="7"/>
-      <c r="D17" s="317"/>
+      <c r="D17" s="322"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="317"/>
+      <c r="F17" s="322"/>
       <c r="G17" s="7"/>
-      <c r="H17" s="317"/>
+      <c r="H17" s="322"/>
       <c r="I17" s="7"/>
-      <c r="J17" s="317"/>
+      <c r="J17" s="322"/>
       <c r="K17" s="7"/>
-      <c r="L17" s="317"/>
+      <c r="L17" s="322"/>
       <c r="M17" s="7"/>
-      <c r="N17" s="317"/>
+      <c r="N17" s="322"/>
       <c r="O17" s="7"/>
-      <c r="P17" s="317"/>
+      <c r="P17" s="322"/>
       <c r="Q17" s="7"/>
-      <c r="R17" s="317"/>
+      <c r="R17" s="322"/>
       <c r="S17" s="7"/>
-      <c r="T17" s="317"/>
+      <c r="T17" s="322"/>
       <c r="U17" s="7"/>
-      <c r="V17" s="317"/>
+      <c r="V17" s="322"/>
       <c r="W17" s="7"/>
-      <c r="X17" s="317"/>
+      <c r="X17" s="322"/>
       <c r="Y17" s="7"/>
-      <c r="Z17" s="317"/>
+      <c r="Z17" s="322"/>
       <c r="AA17" s="7"/>
-      <c r="AB17" s="318"/>
+      <c r="AB17" s="323"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
-      <c r="B18" s="317"/>
+      <c r="B18" s="322"/>
       <c r="C18" s="7"/>
-      <c r="D18" s="317"/>
+      <c r="D18" s="322"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="317"/>
+      <c r="F18" s="322"/>
       <c r="G18" s="7"/>
-      <c r="H18" s="317"/>
+      <c r="H18" s="322"/>
       <c r="I18" s="7"/>
-      <c r="J18" s="317"/>
+      <c r="J18" s="322"/>
       <c r="K18" s="7"/>
-      <c r="L18" s="317"/>
+      <c r="L18" s="322"/>
       <c r="M18" s="7"/>
-      <c r="N18" s="317"/>
+      <c r="N18" s="322"/>
       <c r="O18" s="7"/>
-      <c r="P18" s="317"/>
+      <c r="P18" s="322"/>
       <c r="Q18" s="7"/>
-      <c r="R18" s="317"/>
+      <c r="R18" s="322"/>
       <c r="S18" s="7"/>
-      <c r="T18" s="317"/>
+      <c r="T18" s="322"/>
       <c r="U18" s="7"/>
-      <c r="V18" s="317"/>
+      <c r="V18" s="322"/>
       <c r="W18" s="7"/>
-      <c r="X18" s="317"/>
+      <c r="X18" s="322"/>
       <c r="Y18" s="7"/>
-      <c r="Z18" s="317"/>
+      <c r="Z18" s="322"/>
       <c r="AA18" s="7"/>
-      <c r="AB18" s="318"/>
+      <c r="AB18" s="323"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
-      <c r="B19" s="317"/>
+      <c r="B19" s="322"/>
       <c r="C19" s="7"/>
-      <c r="D19" s="317"/>
+      <c r="D19" s="322"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="317"/>
+      <c r="F19" s="322"/>
       <c r="G19" s="7"/>
-      <c r="H19" s="317"/>
+      <c r="H19" s="322"/>
       <c r="I19" s="7"/>
-      <c r="J19" s="317"/>
+      <c r="J19" s="322"/>
       <c r="K19" s="7"/>
-      <c r="L19" s="317"/>
+      <c r="L19" s="322"/>
       <c r="M19" s="7"/>
-      <c r="N19" s="317"/>
+      <c r="N19" s="322"/>
       <c r="O19" s="7"/>
-      <c r="P19" s="317"/>
+      <c r="P19" s="322"/>
       <c r="Q19" s="7"/>
-      <c r="R19" s="317"/>
+      <c r="R19" s="322"/>
       <c r="S19" s="7"/>
-      <c r="T19" s="317"/>
+      <c r="T19" s="322"/>
       <c r="U19" s="7"/>
-      <c r="V19" s="317"/>
+      <c r="V19" s="322"/>
       <c r="W19" s="7"/>
-      <c r="X19" s="317"/>
+      <c r="X19" s="322"/>
       <c r="Y19" s="7"/>
-      <c r="Z19" s="317"/>
+      <c r="Z19" s="322"/>
       <c r="AA19" s="7"/>
-      <c r="AB19" s="318"/>
+      <c r="AB19" s="323"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
-      <c r="B20" s="317"/>
+      <c r="B20" s="322"/>
       <c r="C20" s="7"/>
-      <c r="D20" s="317"/>
+      <c r="D20" s="322"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="317"/>
+      <c r="F20" s="322"/>
       <c r="G20" s="7"/>
-      <c r="H20" s="317"/>
+      <c r="H20" s="322"/>
       <c r="I20" s="7"/>
-      <c r="J20" s="317"/>
+      <c r="J20" s="322"/>
       <c r="K20" s="7"/>
-      <c r="L20" s="317"/>
+      <c r="L20" s="322"/>
       <c r="M20" s="7"/>
-      <c r="N20" s="317"/>
+      <c r="N20" s="322"/>
       <c r="O20" s="7"/>
-      <c r="P20" s="317"/>
+      <c r="P20" s="322"/>
       <c r="Q20" s="7"/>
-      <c r="R20" s="317"/>
+      <c r="R20" s="322"/>
       <c r="S20" s="7"/>
-      <c r="T20" s="317"/>
+      <c r="T20" s="322"/>
       <c r="U20" s="7"/>
-      <c r="V20" s="317"/>
+      <c r="V20" s="322"/>
       <c r="W20" s="7"/>
-      <c r="X20" s="317"/>
+      <c r="X20" s="322"/>
       <c r="Y20" s="7"/>
-      <c r="Z20" s="317"/>
+      <c r="Z20" s="322"/>
       <c r="AA20" s="7"/>
-      <c r="AB20" s="318"/>
+      <c r="AB20" s="323"/>
     </row>
     <row r="21" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
-      <c r="B21" s="317"/>
+      <c r="B21" s="322"/>
       <c r="C21" s="7"/>
-      <c r="D21" s="317"/>
+      <c r="D21" s="322"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="317"/>
+      <c r="F21" s="322"/>
       <c r="G21" s="7"/>
-      <c r="H21" s="317"/>
+      <c r="H21" s="322"/>
       <c r="I21" s="7"/>
-      <c r="J21" s="317"/>
+      <c r="J21" s="322"/>
       <c r="K21" s="7"/>
-      <c r="L21" s="317"/>
+      <c r="L21" s="322"/>
       <c r="M21" s="7"/>
-      <c r="N21" s="317"/>
+      <c r="N21" s="322"/>
       <c r="O21" s="7"/>
-      <c r="P21" s="317"/>
+      <c r="P21" s="322"/>
       <c r="Q21" s="7"/>
-      <c r="R21" s="317"/>
+      <c r="R21" s="322"/>
       <c r="S21" s="7"/>
-      <c r="T21" s="317"/>
+      <c r="T21" s="322"/>
       <c r="U21" s="7"/>
-      <c r="V21" s="317"/>
+      <c r="V21" s="322"/>
       <c r="W21" s="7"/>
-      <c r="X21" s="317"/>
+      <c r="X21" s="322"/>
       <c r="Y21" s="7"/>
-      <c r="Z21" s="317"/>
+      <c r="Z21" s="322"/>
       <c r="AA21" s="7"/>
-      <c r="AB21" s="318"/>
+      <c r="AB21" s="323"/>
     </row>
     <row r="22" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
-      <c r="B22" s="317"/>
+      <c r="B22" s="322"/>
       <c r="C22" s="7"/>
-      <c r="D22" s="317"/>
+      <c r="D22" s="322"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="317"/>
+      <c r="F22" s="322"/>
       <c r="G22" s="7"/>
-      <c r="H22" s="317"/>
+      <c r="H22" s="322"/>
       <c r="I22" s="7"/>
-      <c r="J22" s="317"/>
+      <c r="J22" s="322"/>
       <c r="K22" s="7"/>
-      <c r="L22" s="317"/>
+      <c r="L22" s="322"/>
       <c r="M22" s="7"/>
-      <c r="N22" s="317"/>
+      <c r="N22" s="322"/>
       <c r="O22" s="7"/>
-      <c r="P22" s="317"/>
+      <c r="P22" s="322"/>
       <c r="Q22" s="7"/>
-      <c r="R22" s="317"/>
+      <c r="R22" s="322"/>
       <c r="S22" s="7"/>
-      <c r="T22" s="317"/>
+      <c r="T22" s="322"/>
       <c r="U22" s="7"/>
-      <c r="V22" s="317"/>
+      <c r="V22" s="322"/>
       <c r="W22" s="7"/>
-      <c r="X22" s="317"/>
+      <c r="X22" s="322"/>
       <c r="Y22" s="7"/>
-      <c r="Z22" s="317"/>
+      <c r="Z22" s="322"/>
       <c r="AA22" s="7"/>
-      <c r="AB22" s="318"/>
+      <c r="AB22" s="323"/>
     </row>
     <row r="23" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
-      <c r="B23" s="317"/>
+      <c r="B23" s="322"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="317"/>
+      <c r="D23" s="322"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="317"/>
+      <c r="F23" s="322"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="317"/>
+      <c r="H23" s="322"/>
       <c r="I23" s="7"/>
-      <c r="J23" s="317"/>
+      <c r="J23" s="322"/>
       <c r="K23" s="7"/>
-      <c r="L23" s="317"/>
+      <c r="L23" s="322"/>
       <c r="M23" s="7"/>
-      <c r="N23" s="317"/>
+      <c r="N23" s="322"/>
       <c r="O23" s="7"/>
-      <c r="P23" s="317"/>
+      <c r="P23" s="322"/>
       <c r="Q23" s="7"/>
-      <c r="R23" s="317"/>
+      <c r="R23" s="322"/>
       <c r="S23" s="7"/>
-      <c r="T23" s="317"/>
+      <c r="T23" s="322"/>
       <c r="U23" s="7"/>
-      <c r="V23" s="317"/>
+      <c r="V23" s="322"/>
       <c r="W23" s="7"/>
-      <c r="X23" s="317"/>
+      <c r="X23" s="322"/>
       <c r="Y23" s="7"/>
-      <c r="Z23" s="317"/>
+      <c r="Z23" s="322"/>
       <c r="AA23" s="7"/>
-      <c r="AB23" s="318"/>
+      <c r="AB23" s="323"/>
     </row>
     <row r="24" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
-      <c r="B24" s="317"/>
+      <c r="B24" s="322"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="317"/>
+      <c r="D24" s="322"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="317"/>
+      <c r="F24" s="322"/>
       <c r="G24" s="7"/>
-      <c r="H24" s="317"/>
+      <c r="H24" s="322"/>
       <c r="I24" s="7"/>
-      <c r="J24" s="317"/>
+      <c r="J24" s="322"/>
       <c r="K24" s="7"/>
-      <c r="L24" s="317"/>
+      <c r="L24" s="322"/>
       <c r="M24" s="7"/>
-      <c r="N24" s="317"/>
+      <c r="N24" s="322"/>
       <c r="O24" s="7"/>
-      <c r="P24" s="317"/>
+      <c r="P24" s="322"/>
       <c r="Q24" s="7"/>
-      <c r="R24" s="317"/>
+      <c r="R24" s="322"/>
       <c r="S24" s="7"/>
-      <c r="T24" s="317"/>
+      <c r="T24" s="322"/>
       <c r="U24" s="7"/>
-      <c r="V24" s="317"/>
+      <c r="V24" s="322"/>
       <c r="W24" s="7"/>
-      <c r="X24" s="317"/>
+      <c r="X24" s="322"/>
       <c r="Y24" s="7"/>
-      <c r="Z24" s="317"/>
+      <c r="Z24" s="322"/>
       <c r="AA24" s="7"/>
-      <c r="AB24" s="318"/>
+      <c r="AB24" s="323"/>
     </row>
     <row r="25" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
-      <c r="B25" s="317"/>
+      <c r="B25" s="322"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="317"/>
+      <c r="D25" s="322"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="317"/>
+      <c r="F25" s="322"/>
       <c r="G25" s="7"/>
-      <c r="H25" s="317"/>
+      <c r="H25" s="322"/>
       <c r="I25" s="7"/>
-      <c r="J25" s="317"/>
+      <c r="J25" s="322"/>
       <c r="K25" s="7"/>
-      <c r="L25" s="317"/>
+      <c r="L25" s="322"/>
       <c r="M25" s="7"/>
-      <c r="N25" s="317"/>
+      <c r="N25" s="322"/>
       <c r="O25" s="7"/>
-      <c r="P25" s="317"/>
+      <c r="P25" s="322"/>
       <c r="Q25" s="7"/>
-      <c r="R25" s="317"/>
+      <c r="R25" s="322"/>
       <c r="S25" s="7"/>
-      <c r="T25" s="317"/>
+      <c r="T25" s="322"/>
       <c r="U25" s="7"/>
-      <c r="V25" s="317"/>
+      <c r="V25" s="322"/>
       <c r="W25" s="7"/>
-      <c r="X25" s="317"/>
+      <c r="X25" s="322"/>
       <c r="Y25" s="7"/>
-      <c r="Z25" s="317"/>
+      <c r="Z25" s="322"/>
       <c r="AA25" s="7"/>
-      <c r="AB25" s="318"/>
+      <c r="AB25" s="323"/>
     </row>
     <row r="26" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
-      <c r="B26" s="317"/>
+      <c r="B26" s="322"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="317"/>
+      <c r="D26" s="322"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="317"/>
+      <c r="F26" s="322"/>
       <c r="G26" s="7"/>
-      <c r="H26" s="317"/>
+      <c r="H26" s="322"/>
       <c r="I26" s="7"/>
-      <c r="J26" s="317"/>
+      <c r="J26" s="322"/>
       <c r="K26" s="7"/>
-      <c r="L26" s="317"/>
+      <c r="L26" s="322"/>
       <c r="M26" s="7"/>
-      <c r="N26" s="317"/>
+      <c r="N26" s="322"/>
       <c r="O26" s="7"/>
-      <c r="P26" s="317"/>
+      <c r="P26" s="322"/>
       <c r="Q26" s="7"/>
-      <c r="R26" s="317"/>
+      <c r="R26" s="322"/>
       <c r="S26" s="7"/>
-      <c r="T26" s="317"/>
+      <c r="T26" s="322"/>
       <c r="U26" s="7"/>
-      <c r="V26" s="317"/>
+      <c r="V26" s="322"/>
       <c r="W26" s="7"/>
-      <c r="X26" s="317"/>
+      <c r="X26" s="322"/>
       <c r="Y26" s="7"/>
-      <c r="Z26" s="317"/>
+      <c r="Z26" s="322"/>
       <c r="AA26" s="7"/>
-      <c r="AB26" s="318"/>
+      <c r="AB26" s="323"/>
     </row>
     <row r="27" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
-      <c r="B27" s="317"/>
+      <c r="B27" s="322"/>
       <c r="C27" s="7"/>
-      <c r="D27" s="317"/>
+      <c r="D27" s="322"/>
       <c r="E27" s="7"/>
-      <c r="F27" s="317"/>
+      <c r="F27" s="322"/>
       <c r="G27" s="7"/>
-      <c r="H27" s="317"/>
+      <c r="H27" s="322"/>
       <c r="I27" s="7"/>
-      <c r="J27" s="317"/>
+      <c r="J27" s="322"/>
       <c r="K27" s="7"/>
-      <c r="L27" s="317"/>
+      <c r="L27" s="322"/>
       <c r="M27" s="7"/>
-      <c r="N27" s="317"/>
+      <c r="N27" s="322"/>
       <c r="O27" s="7"/>
-      <c r="P27" s="317"/>
+      <c r="P27" s="322"/>
       <c r="Q27" s="7"/>
-      <c r="R27" s="317"/>
+      <c r="R27" s="322"/>
       <c r="S27" s="7"/>
-      <c r="T27" s="317"/>
+      <c r="T27" s="322"/>
       <c r="U27" s="7"/>
-      <c r="V27" s="317"/>
+      <c r="V27" s="322"/>
       <c r="W27" s="7"/>
-      <c r="X27" s="317"/>
+      <c r="X27" s="322"/>
       <c r="Y27" s="7"/>
-      <c r="Z27" s="317"/>
+      <c r="Z27" s="322"/>
       <c r="AA27" s="7"/>
-      <c r="AB27" s="318"/>
+      <c r="AB27" s="323"/>
     </row>
     <row r="28" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
-      <c r="B28" s="317"/>
+      <c r="B28" s="322"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="317"/>
+      <c r="D28" s="322"/>
       <c r="E28" s="7"/>
-      <c r="F28" s="317"/>
+      <c r="F28" s="322"/>
       <c r="G28" s="7"/>
-      <c r="H28" s="317"/>
+      <c r="H28" s="322"/>
       <c r="I28" s="7"/>
-      <c r="J28" s="317"/>
+      <c r="J28" s="322"/>
       <c r="K28" s="7"/>
-      <c r="L28" s="317"/>
+      <c r="L28" s="322"/>
       <c r="M28" s="7"/>
-      <c r="N28" s="317"/>
+      <c r="N28" s="322"/>
       <c r="O28" s="7"/>
-      <c r="P28" s="317"/>
+      <c r="P28" s="322"/>
       <c r="Q28" s="7"/>
-      <c r="R28" s="317"/>
+      <c r="R28" s="322"/>
       <c r="S28" s="7"/>
-      <c r="T28" s="317"/>
+      <c r="T28" s="322"/>
       <c r="U28" s="7"/>
-      <c r="V28" s="317"/>
+      <c r="V28" s="322"/>
       <c r="W28" s="7"/>
-      <c r="X28" s="317"/>
+      <c r="X28" s="322"/>
       <c r="Y28" s="7"/>
-      <c r="Z28" s="317"/>
+      <c r="Z28" s="322"/>
       <c r="AA28" s="7"/>
-      <c r="AB28" s="318"/>
+      <c r="AB28" s="323"/>
     </row>
     <row r="29" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
-      <c r="B29" s="317"/>
+      <c r="B29" s="322"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="317"/>
+      <c r="D29" s="322"/>
       <c r="E29" s="7"/>
-      <c r="F29" s="317"/>
+      <c r="F29" s="322"/>
       <c r="G29" s="7"/>
-      <c r="H29" s="317"/>
+      <c r="H29" s="322"/>
       <c r="I29" s="7"/>
-      <c r="J29" s="317"/>
+      <c r="J29" s="322"/>
       <c r="K29" s="7"/>
-      <c r="L29" s="317"/>
+      <c r="L29" s="322"/>
       <c r="M29" s="7"/>
-      <c r="N29" s="317"/>
+      <c r="N29" s="322"/>
       <c r="O29" s="7"/>
-      <c r="P29" s="317"/>
+      <c r="P29" s="322"/>
       <c r="Q29" s="7"/>
-      <c r="R29" s="317"/>
+      <c r="R29" s="322"/>
       <c r="S29" s="7"/>
-      <c r="T29" s="317"/>
+      <c r="T29" s="322"/>
       <c r="U29" s="7"/>
-      <c r="V29" s="317"/>
+      <c r="V29" s="322"/>
       <c r="W29" s="7"/>
-      <c r="X29" s="317"/>
+      <c r="X29" s="322"/>
       <c r="Y29" s="7"/>
-      <c r="Z29" s="317"/>
+      <c r="Z29" s="322"/>
       <c r="AA29" s="7"/>
-      <c r="AB29" s="318"/>
+      <c r="AB29" s="323"/>
     </row>
     <row r="30" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
-      <c r="B30" s="317"/>
+      <c r="B30" s="322"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="317"/>
+      <c r="D30" s="322"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="317"/>
+      <c r="F30" s="322"/>
       <c r="G30" s="7"/>
-      <c r="H30" s="317"/>
+      <c r="H30" s="322"/>
       <c r="I30" s="7"/>
-      <c r="J30" s="317"/>
+      <c r="J30" s="322"/>
       <c r="K30" s="7"/>
-      <c r="L30" s="317"/>
+      <c r="L30" s="322"/>
       <c r="M30" s="7"/>
-      <c r="N30" s="317"/>
+      <c r="N30" s="322"/>
       <c r="O30" s="7"/>
-      <c r="P30" s="317"/>
+      <c r="P30" s="322"/>
       <c r="Q30" s="7"/>
-      <c r="R30" s="317"/>
+      <c r="R30" s="322"/>
       <c r="S30" s="7"/>
-      <c r="T30" s="317"/>
+      <c r="T30" s="322"/>
       <c r="U30" s="7"/>
-      <c r="V30" s="317"/>
+      <c r="V30" s="322"/>
       <c r="W30" s="7"/>
-      <c r="X30" s="317"/>
+      <c r="X30" s="322"/>
       <c r="Y30" s="7"/>
-      <c r="Z30" s="317"/>
+      <c r="Z30" s="322"/>
       <c r="AA30" s="7"/>
-      <c r="AB30" s="318"/>
+      <c r="AB30" s="323"/>
     </row>
     <row r="31" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
-      <c r="B31" s="317"/>
+      <c r="B31" s="322"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="317"/>
+      <c r="D31" s="322"/>
       <c r="E31" s="7"/>
-      <c r="F31" s="317"/>
+      <c r="F31" s="322"/>
       <c r="G31" s="7"/>
-      <c r="H31" s="317"/>
+      <c r="H31" s="322"/>
       <c r="I31" s="7"/>
-      <c r="J31" s="317"/>
+      <c r="J31" s="322"/>
       <c r="K31" s="7"/>
-      <c r="L31" s="317"/>
+      <c r="L31" s="322"/>
       <c r="M31" s="7"/>
-      <c r="N31" s="317"/>
+      <c r="N31" s="322"/>
       <c r="O31" s="7"/>
-      <c r="P31" s="317"/>
+      <c r="P31" s="322"/>
       <c r="Q31" s="7"/>
-      <c r="R31" s="317"/>
+      <c r="R31" s="322"/>
       <c r="S31" s="7"/>
-      <c r="T31" s="317"/>
+      <c r="T31" s="322"/>
       <c r="U31" s="7"/>
-      <c r="V31" s="317"/>
+      <c r="V31" s="322"/>
       <c r="W31" s="7"/>
-      <c r="X31" s="317"/>
+      <c r="X31" s="322"/>
       <c r="Y31" s="7"/>
-      <c r="Z31" s="317"/>
+      <c r="Z31" s="322"/>
       <c r="AA31" s="7"/>
-      <c r="AB31" s="318"/>
+      <c r="AB31" s="323"/>
     </row>
     <row r="32" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
-      <c r="B32" s="317"/>
+      <c r="B32" s="322"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="317"/>
+      <c r="D32" s="322"/>
       <c r="E32" s="7"/>
-      <c r="F32" s="317"/>
+      <c r="F32" s="322"/>
       <c r="G32" s="7"/>
-      <c r="H32" s="317"/>
+      <c r="H32" s="322"/>
       <c r="I32" s="7"/>
-      <c r="J32" s="317"/>
+      <c r="J32" s="322"/>
       <c r="K32" s="7"/>
-      <c r="L32" s="317"/>
+      <c r="L32" s="322"/>
       <c r="M32" s="7"/>
-      <c r="N32" s="317"/>
+      <c r="N32" s="322"/>
       <c r="O32" s="7"/>
-      <c r="P32" s="317"/>
+      <c r="P32" s="322"/>
       <c r="Q32" s="7"/>
-      <c r="R32" s="317"/>
+      <c r="R32" s="322"/>
       <c r="S32" s="7"/>
-      <c r="T32" s="317"/>
+      <c r="T32" s="322"/>
       <c r="U32" s="7"/>
-      <c r="V32" s="317"/>
+      <c r="V32" s="322"/>
       <c r="W32" s="7"/>
-      <c r="X32" s="317"/>
+      <c r="X32" s="322"/>
       <c r="Y32" s="7"/>
-      <c r="Z32" s="317"/>
+      <c r="Z32" s="322"/>
       <c r="AA32" s="7"/>
-      <c r="AB32" s="318"/>
+      <c r="AB32" s="323"/>
     </row>
     <row r="33" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
-      <c r="B33" s="317"/>
+      <c r="B33" s="322"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="317"/>
+      <c r="D33" s="322"/>
       <c r="E33" s="7"/>
-      <c r="F33" s="317"/>
+      <c r="F33" s="322"/>
       <c r="G33" s="7"/>
-      <c r="H33" s="317"/>
+      <c r="H33" s="322"/>
       <c r="I33" s="7"/>
-      <c r="J33" s="317"/>
+      <c r="J33" s="322"/>
       <c r="K33" s="7"/>
-      <c r="L33" s="317"/>
+      <c r="L33" s="322"/>
       <c r="M33" s="7"/>
-      <c r="N33" s="317"/>
+      <c r="N33" s="322"/>
       <c r="O33" s="7"/>
-      <c r="P33" s="317"/>
+      <c r="P33" s="322"/>
       <c r="Q33" s="7"/>
-      <c r="R33" s="317"/>
+      <c r="R33" s="322"/>
       <c r="S33" s="7"/>
-      <c r="T33" s="317"/>
+      <c r="T33" s="322"/>
       <c r="U33" s="7"/>
-      <c r="V33" s="317"/>
+      <c r="V33" s="322"/>
       <c r="W33" s="7"/>
-      <c r="X33" s="317"/>
+      <c r="X33" s="322"/>
       <c r="Y33" s="7"/>
-      <c r="Z33" s="317"/>
+      <c r="Z33" s="322"/>
       <c r="AA33" s="7"/>
-      <c r="AB33" s="318"/>
+      <c r="AB33" s="323"/>
     </row>
     <row r="34" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
-      <c r="B34" s="317"/>
+      <c r="B34" s="322"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="317"/>
+      <c r="D34" s="322"/>
       <c r="E34" s="7"/>
-      <c r="F34" s="317"/>
+      <c r="F34" s="322"/>
       <c r="G34" s="7"/>
-      <c r="H34" s="317"/>
+      <c r="H34" s="322"/>
       <c r="I34" s="7"/>
-      <c r="J34" s="317"/>
+      <c r="J34" s="322"/>
       <c r="K34" s="7"/>
-      <c r="L34" s="317"/>
+      <c r="L34" s="322"/>
       <c r="M34" s="7"/>
-      <c r="N34" s="317"/>
+      <c r="N34" s="322"/>
       <c r="O34" s="7"/>
-      <c r="P34" s="317"/>
+      <c r="P34" s="322"/>
       <c r="Q34" s="7"/>
-      <c r="R34" s="317"/>
+      <c r="R34" s="322"/>
       <c r="S34" s="7"/>
-      <c r="T34" s="317"/>
+      <c r="T34" s="322"/>
       <c r="U34" s="7"/>
-      <c r="V34" s="317"/>
+      <c r="V34" s="322"/>
       <c r="W34" s="7"/>
-      <c r="X34" s="317"/>
+      <c r="X34" s="322"/>
       <c r="Y34" s="7"/>
-      <c r="Z34" s="317"/>
+      <c r="Z34" s="322"/>
       <c r="AA34" s="7"/>
-      <c r="AB34" s="318"/>
+      <c r="AB34" s="323"/>
     </row>
     <row r="35" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
-      <c r="B35" s="317"/>
+      <c r="B35" s="322"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="317"/>
+      <c r="D35" s="322"/>
       <c r="E35" s="7"/>
-      <c r="F35" s="317"/>
+      <c r="F35" s="322"/>
       <c r="G35" s="7"/>
-      <c r="H35" s="317"/>
+      <c r="H35" s="322"/>
       <c r="I35" s="7"/>
-      <c r="J35" s="317"/>
+      <c r="J35" s="322"/>
       <c r="K35" s="7"/>
-      <c r="L35" s="317"/>
+      <c r="L35" s="322"/>
       <c r="M35" s="7"/>
-      <c r="N35" s="317"/>
+      <c r="N35" s="322"/>
       <c r="O35" s="7"/>
-      <c r="P35" s="317"/>
+      <c r="P35" s="322"/>
       <c r="Q35" s="7"/>
-      <c r="R35" s="317"/>
+      <c r="R35" s="322"/>
       <c r="S35" s="7"/>
-      <c r="T35" s="317"/>
+      <c r="T35" s="322"/>
       <c r="U35" s="7"/>
-      <c r="V35" s="317"/>
+      <c r="V35" s="322"/>
       <c r="W35" s="7"/>
-      <c r="X35" s="317"/>
+      <c r="X35" s="322"/>
       <c r="Y35" s="7"/>
-      <c r="Z35" s="317"/>
+      <c r="Z35" s="322"/>
       <c r="AA35" s="7"/>
-      <c r="AB35" s="318"/>
+      <c r="AB35" s="323"/>
     </row>
     <row r="36" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
-      <c r="B36" s="317"/>
+      <c r="B36" s="322"/>
       <c r="C36" s="5"/>
-      <c r="D36" s="317"/>
+      <c r="D36" s="322"/>
       <c r="E36" s="5"/>
-      <c r="F36" s="317"/>
+      <c r="F36" s="322"/>
       <c r="G36" s="5"/>
-      <c r="H36" s="317"/>
+      <c r="H36" s="322"/>
       <c r="I36" s="5"/>
-      <c r="J36" s="317"/>
+      <c r="J36" s="322"/>
       <c r="K36" s="5"/>
-      <c r="L36" s="317"/>
+      <c r="L36" s="322"/>
       <c r="M36" s="5"/>
-      <c r="N36" s="317"/>
+      <c r="N36" s="322"/>
       <c r="O36" s="5"/>
-      <c r="P36" s="317"/>
+      <c r="P36" s="322"/>
       <c r="Q36" s="5"/>
-      <c r="R36" s="317"/>
+      <c r="R36" s="322"/>
       <c r="S36" s="5"/>
-      <c r="T36" s="317"/>
+      <c r="T36" s="322"/>
       <c r="U36" s="5"/>
-      <c r="V36" s="317"/>
+      <c r="V36" s="322"/>
       <c r="W36" s="5"/>
-      <c r="X36" s="317"/>
+      <c r="X36" s="322"/>
       <c r="Y36" s="5"/>
-      <c r="Z36" s="317"/>
+      <c r="Z36" s="322"/>
       <c r="AA36" s="5"/>
-      <c r="AB36" s="318"/>
+      <c r="AB36" s="323"/>
     </row>
     <row r="37" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
@@ -4143,19 +4146,19 @@
     </row>
     <row r="39" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="310">
+      <c r="A40" s="315">
         <f>SUM(A38:AC38)</f>
         <v>8105.7</v>
       </c>
-      <c r="B40" s="311"/>
-      <c r="C40" s="311"/>
-      <c r="D40" s="312"/>
+      <c r="B40" s="316"/>
+      <c r="C40" s="316"/>
+      <c r="D40" s="317"/>
     </row>
     <row r="41" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="313"/>
-      <c r="B41" s="314"/>
-      <c r="C41" s="314"/>
-      <c r="D41" s="315"/>
+      <c r="A41" s="318"/>
+      <c r="B41" s="319"/>
+      <c r="C41" s="319"/>
+      <c r="D41" s="320"/>
     </row>
     <row r="42" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8544,19 +8547,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="324" t="s">
+      <c r="A1" s="327" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="325"/>
-      <c r="C1" s="325"/>
-      <c r="D1" s="325"/>
-      <c r="E1" s="325"/>
-      <c r="F1" s="325"/>
-      <c r="G1" s="325"/>
-      <c r="H1" s="325"/>
-      <c r="I1" s="325"/>
-      <c r="J1" s="325"/>
-      <c r="K1" s="326"/>
+      <c r="B1" s="328"/>
+      <c r="C1" s="328"/>
+      <c r="D1" s="328"/>
+      <c r="E1" s="328"/>
+      <c r="F1" s="328"/>
+      <c r="G1" s="328"/>
+      <c r="H1" s="328"/>
+      <c r="I1" s="328"/>
+      <c r="J1" s="328"/>
+      <c r="K1" s="329"/>
       <c r="L1" s="60"/>
       <c r="M1" s="60"/>
       <c r="N1" s="60"/>
@@ -8572,11 +8575,11 @@
       <c r="X1" s="60"/>
     </row>
     <row r="2" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="336" t="s">
+      <c r="A2" s="339" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="337"/>
-      <c r="C2" s="338"/>
+      <c r="B2" s="340"/>
+      <c r="C2" s="341"/>
       <c r="D2" s="105" t="s">
         <v>27</v>
       </c>
@@ -8619,10 +8622,10 @@
       <c r="A3" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="342" t="s">
+      <c r="B3" s="345" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="343"/>
+      <c r="C3" s="346"/>
       <c r="D3" s="111">
         <v>102</v>
       </c>
@@ -8657,10 +8660,10 @@
       <c r="A4" s="116" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="344" t="s">
+      <c r="B4" s="347" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="345"/>
+      <c r="C4" s="348"/>
       <c r="D4" s="117">
         <v>102</v>
       </c>
@@ -8695,10 +8698,10 @@
       <c r="A5" s="116" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="344" t="s">
+      <c r="B5" s="347" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="345"/>
+      <c r="C5" s="348"/>
       <c r="D5" s="117">
         <v>102</v>
       </c>
@@ -8733,10 +8736,10 @@
       <c r="A6" s="122" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="349" t="s">
+      <c r="B6" s="352" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="350"/>
+      <c r="C6" s="353"/>
       <c r="D6" s="123"/>
       <c r="E6" s="124">
         <f>SUM(F6:K6)</f>
@@ -8766,12 +8769,12 @@
       <c r="X6" s="69"/>
     </row>
     <row r="7" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="333" t="s">
+      <c r="A7" s="336" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="334"/>
-      <c r="C7" s="334"/>
-      <c r="D7" s="335"/>
+      <c r="B7" s="337"/>
+      <c r="C7" s="337"/>
+      <c r="D7" s="338"/>
       <c r="E7" s="128">
         <f>SUM(F7:K7)</f>
         <v>0</v>
@@ -8815,11 +8818,11 @@
       <c r="X7" s="60"/>
     </row>
     <row r="8" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="351" t="s">
+      <c r="A8" s="354" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="352"/>
-      <c r="C8" s="353"/>
+      <c r="B8" s="355"/>
+      <c r="C8" s="356"/>
       <c r="D8" s="106" t="s">
         <v>27</v>
       </c>
@@ -9205,7 +9208,7 @@
       </c>
       <c r="E17" s="118">
         <f t="shared" si="1"/>
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="F17" s="138">
         <f>'STOK DETAY'!T6</f>
@@ -9213,7 +9216,7 @@
       </c>
       <c r="G17" s="139">
         <f>'STOK DETAY'!U6</f>
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="H17" s="139">
         <f>'STOK DETAY'!V6</f>
@@ -9429,7 +9432,7 @@
       </c>
       <c r="E22" s="118">
         <f t="shared" si="1"/>
-        <v>23.215</v>
+        <v>15.8</v>
       </c>
       <c r="F22" s="138">
         <f>'STOK DETAY'!AG6</f>
@@ -9437,7 +9440,7 @@
       </c>
       <c r="G22" s="139">
         <f>'STOK DETAY'!AH6</f>
-        <v>14.734999999999999</v>
+        <v>7.32</v>
       </c>
       <c r="H22" s="139">
         <f>'STOK DETAY'!AI6</f>
@@ -9613,7 +9616,7 @@
       </c>
       <c r="E26" s="118">
         <f t="shared" si="1"/>
-        <v>34.380000000000003</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="F26" s="138">
         <f>'STOK DETAY'!AS6</f>
@@ -9621,7 +9624,7 @@
       </c>
       <c r="G26" s="139">
         <f>'STOK DETAY'!AT6</f>
-        <v>34.380000000000003</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="H26" s="139">
         <f>'STOK DETAY'!AU6</f>
@@ -9659,7 +9662,7 @@
       </c>
       <c r="E27" s="118">
         <f t="shared" si="1"/>
-        <v>8.4949999999999992</v>
+        <v>0</v>
       </c>
       <c r="F27" s="138">
         <f>'STOK DETAY'!AV6</f>
@@ -9671,7 +9674,7 @@
       </c>
       <c r="H27" s="139">
         <f>'STOK DETAY'!AX6</f>
-        <v>8.4949999999999992</v>
+        <v>0</v>
       </c>
       <c r="I27" s="139"/>
       <c r="J27" s="139"/>
@@ -9705,7 +9708,7 @@
       </c>
       <c r="E28" s="118">
         <f t="shared" si="1"/>
-        <v>24.934999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="F28" s="138">
         <f>'STOK DETAY'!AY6</f>
@@ -9713,11 +9716,11 @@
       </c>
       <c r="G28" s="139">
         <f>'STOK DETAY'!AZ6</f>
-        <v>16.649999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="H28" s="139">
         <f>'STOK DETAY'!BA6</f>
-        <v>8.2850000000000001</v>
+        <v>0</v>
       </c>
       <c r="I28" s="139"/>
       <c r="J28" s="139"/>
@@ -9843,7 +9846,7 @@
       </c>
       <c r="E31" s="118">
         <f t="shared" si="1"/>
-        <v>17.059999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="F31" s="138">
         <f>'STOK DETAY'!BH6</f>
@@ -9851,7 +9854,7 @@
       </c>
       <c r="G31" s="139">
         <f>'STOK DETAY'!BI6</f>
-        <v>17.059999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="H31" s="139">
         <f>'STOK DETAY'!BJ6</f>
@@ -9987,7 +9990,7 @@
       </c>
       <c r="E34" s="118">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8.3650000000000002</v>
       </c>
       <c r="F34" s="138">
         <f>'STOK DETAY'!BS6</f>
@@ -9995,7 +9998,7 @@
       </c>
       <c r="G34" s="139">
         <f>'STOK DETAY'!BT6</f>
-        <v>0</v>
+        <v>8.3650000000000002</v>
       </c>
       <c r="H34" s="139">
         <f>'STOK DETAY'!BV6</f>
@@ -10081,7 +10084,7 @@
       </c>
       <c r="E36" s="118">
         <f t="shared" si="1"/>
-        <v>16.510000000000002</v>
+        <v>8.23</v>
       </c>
       <c r="F36" s="138">
         <f>'STOK DETAY'!BZ6</f>
@@ -10089,7 +10092,7 @@
       </c>
       <c r="G36" s="139">
         <f>'STOK DETAY'!CA6</f>
-        <v>16.510000000000002</v>
+        <v>8.23</v>
       </c>
       <c r="H36" s="139">
         <f>'STOK DETAY'!CB6</f>
@@ -10709,15 +10712,15 @@
       <c r="X51" s="69"/>
     </row>
     <row r="52" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="333" t="s">
+      <c r="A52" s="336" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="334"/>
-      <c r="C52" s="334"/>
-      <c r="D52" s="335"/>
+      <c r="B52" s="337"/>
+      <c r="C52" s="337"/>
+      <c r="D52" s="338"/>
       <c r="E52" s="128">
         <f t="shared" si="1"/>
-        <v>560.05499999999995</v>
+        <v>489.875</v>
       </c>
       <c r="F52" s="129">
         <f t="shared" ref="F52:K52" si="2">SUM(F9:F51)</f>
@@ -10725,11 +10728,11 @@
       </c>
       <c r="G52" s="130">
         <f t="shared" si="2"/>
-        <v>166.095</v>
+        <v>112.69499999999999</v>
       </c>
       <c r="H52" s="130">
         <f>SUM(H9:H51)</f>
-        <v>54.07</v>
+        <v>37.29</v>
       </c>
       <c r="I52" s="130">
         <f t="shared" si="2"/>
@@ -10758,11 +10761,11 @@
       <c r="X52" s="60"/>
     </row>
     <row r="53" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="336" t="s">
+      <c r="A53" s="339" t="s">
         <v>12</v>
       </c>
-      <c r="B53" s="337"/>
-      <c r="C53" s="338"/>
+      <c r="B53" s="340"/>
+      <c r="C53" s="341"/>
       <c r="D53" s="105" t="s">
         <v>27</v>
       </c>
@@ -11443,12 +11446,12 @@
       <c r="X69" s="69"/>
     </row>
     <row r="70" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A70" s="330" t="s">
+      <c r="A70" s="333" t="s">
         <v>4</v>
       </c>
-      <c r="B70" s="331"/>
-      <c r="C70" s="331"/>
-      <c r="D70" s="332"/>
+      <c r="B70" s="334"/>
+      <c r="C70" s="334"/>
+      <c r="D70" s="335"/>
       <c r="E70" s="128">
         <f t="shared" si="3"/>
         <v>159.74799999999999</v>
@@ -11492,11 +11495,11 @@
       <c r="X70" s="60"/>
     </row>
     <row r="71" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A71" s="336" t="s">
+      <c r="A71" s="339" t="s">
         <v>10</v>
       </c>
-      <c r="B71" s="337"/>
-      <c r="C71" s="339"/>
+      <c r="B71" s="340"/>
+      <c r="C71" s="342"/>
       <c r="D71" s="145" t="s">
         <v>27</v>
       </c>
@@ -11539,8 +11542,8 @@
       <c r="A72" s="146">
         <v>0.3</v>
       </c>
-      <c r="B72" s="354"/>
-      <c r="C72" s="355"/>
+      <c r="B72" s="357"/>
+      <c r="C72" s="358"/>
       <c r="D72" s="147">
         <v>511</v>
       </c>
@@ -11575,8 +11578,8 @@
       <c r="A73" s="116">
         <v>0.5</v>
       </c>
-      <c r="B73" s="322"/>
-      <c r="C73" s="323"/>
+      <c r="B73" s="359"/>
+      <c r="C73" s="360"/>
       <c r="D73" s="147">
         <v>511</v>
       </c>
@@ -11611,8 +11614,8 @@
       <c r="A74" s="116">
         <v>0.55000000000000004</v>
       </c>
-      <c r="B74" s="322"/>
-      <c r="C74" s="323"/>
+      <c r="B74" s="359"/>
+      <c r="C74" s="360"/>
       <c r="D74" s="147">
         <v>511</v>
       </c>
@@ -11647,8 +11650,8 @@
       <c r="A75" s="116">
         <v>0.6</v>
       </c>
-      <c r="B75" s="322"/>
-      <c r="C75" s="323"/>
+      <c r="B75" s="359"/>
+      <c r="C75" s="360"/>
       <c r="D75" s="147">
         <v>101</v>
       </c>
@@ -11683,8 +11686,8 @@
       <c r="A76" s="116">
         <v>0.7</v>
       </c>
-      <c r="B76" s="322"/>
-      <c r="C76" s="323"/>
+      <c r="B76" s="359"/>
+      <c r="C76" s="360"/>
       <c r="D76" s="147">
         <v>101</v>
       </c>
@@ -11722,8 +11725,8 @@
       <c r="A77" s="116">
         <v>1</v>
       </c>
-      <c r="B77" s="322"/>
-      <c r="C77" s="323"/>
+      <c r="B77" s="359"/>
+      <c r="C77" s="360"/>
       <c r="D77" s="147">
         <v>511</v>
       </c>
@@ -11758,8 +11761,8 @@
       <c r="A78" s="116">
         <v>1.2</v>
       </c>
-      <c r="B78" s="322"/>
-      <c r="C78" s="323"/>
+      <c r="B78" s="359"/>
+      <c r="C78" s="360"/>
       <c r="D78" s="147">
         <v>511</v>
       </c>
@@ -11794,8 +11797,8 @@
       <c r="A79" s="116">
         <v>1.3</v>
       </c>
-      <c r="B79" s="322"/>
-      <c r="C79" s="323"/>
+      <c r="B79" s="359"/>
+      <c r="C79" s="360"/>
       <c r="D79" s="147">
         <v>511</v>
       </c>
@@ -11830,8 +11833,8 @@
       <c r="A80" s="116">
         <v>1.4</v>
       </c>
-      <c r="B80" s="322"/>
-      <c r="C80" s="323"/>
+      <c r="B80" s="359"/>
+      <c r="C80" s="360"/>
       <c r="D80" s="147">
         <v>511</v>
       </c>
@@ -11866,8 +11869,8 @@
       <c r="A81" s="116">
         <v>1.6</v>
       </c>
-      <c r="B81" s="322"/>
-      <c r="C81" s="323"/>
+      <c r="B81" s="359"/>
+      <c r="C81" s="360"/>
       <c r="D81" s="147">
         <v>511</v>
       </c>
@@ -11902,8 +11905,8 @@
       <c r="A82" s="116">
         <v>1.7</v>
       </c>
-      <c r="B82" s="322"/>
-      <c r="C82" s="323"/>
+      <c r="B82" s="359"/>
+      <c r="C82" s="360"/>
       <c r="D82" s="147">
         <v>511</v>
       </c>
@@ -11938,8 +11941,8 @@
       <c r="A83" s="151">
         <v>3.5</v>
       </c>
-      <c r="B83" s="340"/>
-      <c r="C83" s="341"/>
+      <c r="B83" s="343"/>
+      <c r="C83" s="344"/>
       <c r="D83" s="152">
         <v>511</v>
       </c>
@@ -11971,12 +11974,12 @@
       <c r="X83" s="69"/>
     </row>
     <row r="84" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A84" s="346" t="s">
+      <c r="A84" s="349" t="s">
         <v>4</v>
       </c>
-      <c r="B84" s="347"/>
-      <c r="C84" s="347"/>
-      <c r="D84" s="348"/>
+      <c r="B84" s="350"/>
+      <c r="C84" s="350"/>
+      <c r="D84" s="351"/>
       <c r="E84" s="128">
         <f t="shared" si="5"/>
         <v>184.27</v>
@@ -12020,15 +12023,15 @@
       <c r="X84" s="60"/>
     </row>
     <row r="85" spans="1:24" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A85" s="327" t="s">
+      <c r="A85" s="330" t="s">
         <v>1</v>
       </c>
-      <c r="B85" s="328"/>
-      <c r="C85" s="328"/>
-      <c r="D85" s="329"/>
+      <c r="B85" s="331"/>
+      <c r="C85" s="331"/>
+      <c r="D85" s="332"/>
       <c r="E85" s="154">
         <f t="shared" si="5"/>
-        <v>904.07299999999998</v>
+        <v>833.89300000000003</v>
       </c>
       <c r="F85" s="155">
         <f t="shared" ref="F85:K85" si="7">F7+F52+F70+F84</f>
@@ -12036,11 +12039,11 @@
       </c>
       <c r="G85" s="156">
         <f t="shared" si="7"/>
-        <v>172.73</v>
+        <v>119.33</v>
       </c>
       <c r="H85" s="156">
         <f>H7+H52+H70+H84</f>
-        <v>238.34</v>
+        <v>221.56</v>
       </c>
       <c r="I85" s="156">
         <f t="shared" si="7"/>
@@ -30093,6 +30096,16 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="26">
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A85:D85"/>
     <mergeCell ref="A70:D70"/>
@@ -30109,16 +30122,6 @@
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:K6 F9:K51 F54:K69 F72:K83">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -30168,7 +30171,7 @@
     <col min="31" max="31" width="12.7109375" style="296" customWidth="1"/>
     <col min="32" max="32" width="12.7109375" style="276" customWidth="1"/>
     <col min="33" max="33" width="12.7109375" style="208" customWidth="1"/>
-    <col min="34" max="34" width="12.7109375" style="226" customWidth="1"/>
+    <col min="34" max="34" width="12.7109375" style="296" customWidth="1"/>
     <col min="35" max="35" width="12.7109375" style="270" customWidth="1"/>
     <col min="36" max="36" width="12.7109375" style="208" customWidth="1"/>
     <col min="37" max="37" width="12.7109375" style="296" customWidth="1"/>
@@ -30184,10 +30187,10 @@
     <col min="47" max="47" width="12.7109375" style="276" customWidth="1"/>
     <col min="48" max="48" width="12.7109375" style="208" customWidth="1"/>
     <col min="49" max="49" width="12.7109375" style="226" customWidth="1"/>
-    <col min="50" max="50" width="12.7109375" style="270" customWidth="1"/>
+    <col min="50" max="50" width="12.7109375" style="276" customWidth="1"/>
     <col min="51" max="51" width="12.7109375" style="208" customWidth="1"/>
-    <col min="52" max="52" width="12.7109375" style="226" customWidth="1"/>
-    <col min="53" max="53" width="12.7109375" style="270" customWidth="1"/>
+    <col min="52" max="52" width="12.7109375" style="296" customWidth="1"/>
+    <col min="53" max="53" width="12.7109375" style="276" customWidth="1"/>
     <col min="54" max="54" width="12.7109375" style="208" customWidth="1"/>
     <col min="55" max="55" width="12.7109375" style="226" customWidth="1"/>
     <col min="56" max="56" width="12.7109375" style="276" customWidth="1"/>
@@ -30256,17 +30259,17 @@
     <col min="120" max="120" width="12.7109375" style="96" customWidth="1"/>
     <col min="121" max="122" width="12.7109375" style="91" customWidth="1"/>
     <col min="123" max="123" width="12.7109375" style="253" customWidth="1"/>
-    <col min="124" max="124" width="12.7109375" style="360" customWidth="1"/>
+    <col min="124" max="124" width="12.7109375" style="312" customWidth="1"/>
     <col min="125" max="125" width="12.7109375" style="250" customWidth="1"/>
     <col min="126" max="132" width="12.7109375" style="91" customWidth="1"/>
     <col min="133" max="16384" width="9.140625" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:132" s="19" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="356" t="s">
+      <c r="A1" s="361" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="356"/>
+      <c r="B1" s="361"/>
       <c r="C1" s="44" t="s">
         <v>22</v>
       </c>
@@ -30360,7 +30363,7 @@
       <c r="AG1" s="202" t="s">
         <v>16</v>
       </c>
-      <c r="AH1" s="221" t="s">
+      <c r="AH1" s="291" t="s">
         <v>17</v>
       </c>
       <c r="AI1" s="265" t="s">
@@ -30408,16 +30411,16 @@
       <c r="AW1" s="221" t="s">
         <v>17</v>
       </c>
-      <c r="AX1" s="265" t="s">
+      <c r="AX1" s="271" t="s">
         <v>3</v>
       </c>
       <c r="AY1" s="202" t="s">
         <v>16</v>
       </c>
-      <c r="AZ1" s="221" t="s">
+      <c r="AZ1" s="291" t="s">
         <v>17</v>
       </c>
-      <c r="BA1" s="265" t="s">
+      <c r="BA1" s="271" t="s">
         <v>3</v>
       </c>
       <c r="BB1" s="202" t="s">
@@ -30630,7 +30633,7 @@
       <c r="DS1" s="251" t="s">
         <v>2</v>
       </c>
-      <c r="DT1" s="358" t="s">
+      <c r="DT1" s="310" t="s">
         <v>17</v>
       </c>
       <c r="DU1" s="245" t="s">
@@ -30659,8 +30662,8 @@
       </c>
     </row>
     <row r="2" spans="1:132" s="19" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="356"/>
-      <c r="B2" s="356"/>
+      <c r="A2" s="361"/>
+      <c r="B2" s="361"/>
       <c r="C2" s="44" t="s">
         <v>23</v>
       </c>
@@ -30754,7 +30757,7 @@
       <c r="AG2" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="AH2" s="221" t="s">
+      <c r="AH2" s="291" t="s">
         <v>7</v>
       </c>
       <c r="AI2" s="265" t="s">
@@ -30802,16 +30805,16 @@
       <c r="AW2" s="221" t="s">
         <v>7</v>
       </c>
-      <c r="AX2" s="265" t="s">
+      <c r="AX2" s="271" t="s">
         <v>7</v>
       </c>
       <c r="AY2" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="AZ2" s="221" t="s">
+      <c r="AZ2" s="291" t="s">
         <v>7</v>
       </c>
-      <c r="BA2" s="265" t="s">
+      <c r="BA2" s="271" t="s">
         <v>7</v>
       </c>
       <c r="BB2" s="202" t="s">
@@ -31024,7 +31027,7 @@
       <c r="DS2" s="251" t="s">
         <v>29</v>
       </c>
-      <c r="DT2" s="358" t="s">
+      <c r="DT2" s="310" t="s">
         <v>29</v>
       </c>
       <c r="DU2" s="245" t="s">
@@ -31053,8 +31056,8 @@
       </c>
     </row>
     <row r="3" spans="1:132" s="19" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="356"/>
-      <c r="B3" s="356"/>
+      <c r="A3" s="361"/>
+      <c r="B3" s="361"/>
       <c r="C3" s="44" t="s">
         <v>24</v>
       </c>
@@ -31148,7 +31151,7 @@
       <c r="AG3" s="202" t="s">
         <v>14</v>
       </c>
-      <c r="AH3" s="221" t="s">
+      <c r="AH3" s="291" t="s">
         <v>14</v>
       </c>
       <c r="AI3" s="265" t="s">
@@ -31196,16 +31199,16 @@
       <c r="AW3" s="221" t="s">
         <v>14</v>
       </c>
-      <c r="AX3" s="265" t="s">
+      <c r="AX3" s="271" t="s">
         <v>14</v>
       </c>
       <c r="AY3" s="202" t="s">
         <v>14</v>
       </c>
-      <c r="AZ3" s="221" t="s">
+      <c r="AZ3" s="291" t="s">
         <v>14</v>
       </c>
-      <c r="BA3" s="265" t="s">
+      <c r="BA3" s="271" t="s">
         <v>14</v>
       </c>
       <c r="BB3" s="202" t="s">
@@ -31418,7 +31421,7 @@
       <c r="DS3" s="251" t="s">
         <v>10</v>
       </c>
-      <c r="DT3" s="358" t="s">
+      <c r="DT3" s="310" t="s">
         <v>10</v>
       </c>
       <c r="DU3" s="245" t="s">
@@ -31447,8 +31450,8 @@
       </c>
     </row>
     <row r="4" spans="1:132" s="20" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="356"/>
-      <c r="B4" s="356"/>
+      <c r="A4" s="361"/>
+      <c r="B4" s="361"/>
       <c r="C4" s="44" t="s">
         <v>25</v>
       </c>
@@ -31542,7 +31545,7 @@
       <c r="AG4" s="204">
         <v>0.6</v>
       </c>
-      <c r="AH4" s="222">
+      <c r="AH4" s="292">
         <v>0.6</v>
       </c>
       <c r="AI4" s="266">
@@ -31590,16 +31593,16 @@
       <c r="AW4" s="222">
         <v>0.85</v>
       </c>
-      <c r="AX4" s="266">
+      <c r="AX4" s="272">
         <v>0.85</v>
       </c>
       <c r="AY4" s="204">
         <v>0.9</v>
       </c>
-      <c r="AZ4" s="222">
+      <c r="AZ4" s="292">
         <v>0.9</v>
       </c>
-      <c r="BA4" s="266">
+      <c r="BA4" s="272">
         <v>0.9</v>
       </c>
       <c r="BB4" s="204">
@@ -31812,7 +31815,7 @@
       <c r="DS4" s="252">
         <v>0.6</v>
       </c>
-      <c r="DT4" s="359">
+      <c r="DT4" s="311">
         <v>0.7</v>
       </c>
       <c r="DU4" s="246">
@@ -31841,8 +31844,8 @@
       </c>
     </row>
     <row r="5" spans="1:132" ht="6.75" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A5" s="356"/>
-      <c r="B5" s="356"/>
+      <c r="A5" s="361"/>
+      <c r="B5" s="361"/>
       <c r="C5" s="43"/>
       <c r="D5" s="214"/>
       <c r="E5" s="198"/>
@@ -31874,7 +31877,7 @@
       <c r="AE5" s="293"/>
       <c r="AF5" s="273"/>
       <c r="AG5" s="205"/>
-      <c r="AH5" s="223"/>
+      <c r="AH5" s="293"/>
       <c r="AI5" s="267"/>
       <c r="AJ5" s="205"/>
       <c r="AK5" s="293"/>
@@ -31890,10 +31893,10 @@
       <c r="AU5" s="273"/>
       <c r="AV5" s="205"/>
       <c r="AW5" s="223"/>
-      <c r="AX5" s="267"/>
+      <c r="AX5" s="273"/>
       <c r="AY5" s="205"/>
-      <c r="AZ5" s="223"/>
-      <c r="BA5" s="267"/>
+      <c r="AZ5" s="293"/>
+      <c r="BA5" s="273"/>
       <c r="BB5" s="205"/>
       <c r="BC5" s="223"/>
       <c r="BD5" s="273"/>
@@ -31972,7 +31975,7 @@
       </c>
       <c r="C6" s="72">
         <f>SUM(D6:EB6)</f>
-        <v>904.07299999999998</v>
+        <v>833.89300000000003</v>
       </c>
       <c r="D6" s="199">
         <f t="shared" ref="D6:AI6" si="0">SUM(D8:D1048576)</f>
@@ -32044,7 +32047,7 @@
       </c>
       <c r="U6" s="294">
         <f t="shared" si="0"/>
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="V6" s="274">
         <f t="shared" si="0"/>
@@ -32094,9 +32097,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH6" s="224">
+      <c r="AH6" s="294">
         <f t="shared" si="0"/>
-        <v>14.734999999999999</v>
+        <v>7.32</v>
       </c>
       <c r="AI6" s="268">
         <f t="shared" si="0"/>
@@ -32144,7 +32147,7 @@
       </c>
       <c r="AT6" s="294">
         <f t="shared" si="1"/>
-        <v>34.380000000000003</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="AU6" s="274">
         <f t="shared" si="1"/>
@@ -32158,21 +32161,21 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AX6" s="268">
+      <c r="AX6" s="274">
         <f t="shared" si="1"/>
-        <v>8.4949999999999992</v>
+        <v>0</v>
       </c>
       <c r="AY6" s="206">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AZ6" s="224">
+      <c r="AZ6" s="294">
         <f t="shared" si="1"/>
-        <v>16.649999999999999</v>
-      </c>
-      <c r="BA6" s="268">
+        <v>8.31</v>
+      </c>
+      <c r="BA6" s="274">
         <f t="shared" si="1"/>
-        <v>8.2850000000000001</v>
+        <v>0</v>
       </c>
       <c r="BB6" s="206">
         <f t="shared" si="1"/>
@@ -32204,7 +32207,7 @@
       </c>
       <c r="BI6" s="294">
         <f t="shared" si="1"/>
-        <v>17.059999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="BJ6" s="274">
         <f t="shared" si="1"/>
@@ -32248,7 +32251,7 @@
       </c>
       <c r="BT6" s="224">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8.3650000000000002</v>
       </c>
       <c r="BU6" s="287">
         <f t="shared" si="2"/>
@@ -32276,7 +32279,7 @@
       </c>
       <c r="CA6" s="294">
         <f t="shared" si="2"/>
-        <v>16.510000000000002</v>
+        <v>8.23</v>
       </c>
       <c r="CB6" s="274">
         <f t="shared" si="2"/>
@@ -32454,7 +32457,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="DT6" s="361">
+      <c r="DT6" s="313">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -32525,7 +32528,7 @@
       <c r="AE7" s="295"/>
       <c r="AF7" s="275"/>
       <c r="AG7" s="207"/>
-      <c r="AH7" s="225"/>
+      <c r="AH7" s="295"/>
       <c r="AI7" s="269"/>
       <c r="AJ7" s="207"/>
       <c r="AK7" s="295"/>
@@ -32541,10 +32544,10 @@
       <c r="AU7" s="275"/>
       <c r="AV7" s="207"/>
       <c r="AW7" s="225"/>
-      <c r="AX7" s="269"/>
+      <c r="AX7" s="275"/>
       <c r="AY7" s="207"/>
-      <c r="AZ7" s="225"/>
-      <c r="BA7" s="269"/>
+      <c r="AZ7" s="295"/>
+      <c r="BA7" s="275"/>
       <c r="BB7" s="207"/>
       <c r="BC7" s="225"/>
       <c r="BD7" s="275"/>
@@ -32615,7 +32618,7 @@
       <c r="DQ7" s="94"/>
       <c r="DR7" s="95"/>
       <c r="DS7" s="255"/>
-      <c r="DT7" s="362"/>
+      <c r="DT7" s="314"/>
       <c r="DU7" s="256"/>
       <c r="DV7" s="95"/>
       <c r="DW7" s="95"/>
@@ -32690,7 +32693,7 @@
       <c r="AG8" s="208">
         <v>0</v>
       </c>
-      <c r="AH8" s="226">
+      <c r="AH8" s="296">
         <v>0</v>
       </c>
       <c r="AJ8" s="208">
@@ -32726,7 +32729,7 @@
       <c r="AY8" s="208">
         <v>0</v>
       </c>
-      <c r="AZ8" s="226">
+      <c r="AZ8" s="296">
         <v>0</v>
       </c>
       <c r="BB8" s="208">
@@ -32903,7 +32906,7 @@
       <c r="DS8" s="253">
         <v>0</v>
       </c>
-      <c r="DT8" s="360">
+      <c r="DT8" s="312">
         <v>404.44</v>
       </c>
       <c r="DU8" s="250">
@@ -33264,7 +33267,7 @@
         <f t="shared" si="5"/>
         <v>288.53500000000003</v>
       </c>
-      <c r="AH22" s="226">
+      <c r="AH22" s="296">
         <v>33.28</v>
       </c>
       <c r="AN22" s="296">
@@ -33279,7 +33282,7 @@
       <c r="AW22" s="226">
         <v>33.39</v>
       </c>
-      <c r="AZ22" s="226">
+      <c r="AZ22" s="296">
         <v>33.700000000000003</v>
       </c>
       <c r="BC22" s="226">
@@ -33306,7 +33309,7 @@
       <c r="T23" s="208">
         <v>-7.89</v>
       </c>
-      <c r="AH23" s="226">
+      <c r="AH23" s="296">
         <v>-8.2200000000000006</v>
       </c>
       <c r="AN23" s="296">
@@ -33336,7 +33339,7 @@
         <f t="shared" si="5"/>
         <v>-98.23</v>
       </c>
-      <c r="AH24" s="226">
+      <c r="AH24" s="296">
         <v>-16.72</v>
       </c>
       <c r="AN24" s="296">
@@ -33348,7 +33351,7 @@
       <c r="AW24" s="226">
         <v>-16.649999999999999</v>
       </c>
-      <c r="AZ24" s="226">
+      <c r="AZ24" s="296">
         <v>-16.79</v>
       </c>
       <c r="BC24" s="226">
@@ -33378,7 +33381,7 @@
       <c r="AW25" s="226">
         <v>-8.36</v>
       </c>
-      <c r="AZ25" s="226">
+      <c r="AZ25" s="296">
         <v>-16.91</v>
       </c>
     </row>
@@ -33531,7 +33534,7 @@
         <f t="shared" si="5"/>
         <v>-159.1</v>
       </c>
-      <c r="DT34" s="360">
+      <c r="DT34" s="312">
         <v>-159.1</v>
       </c>
     </row>
@@ -33591,7 +33594,7 @@
         <f t="shared" si="5"/>
         <v>193.27</v>
       </c>
-      <c r="AH38" s="226">
+      <c r="AH38" s="296">
         <v>33.79</v>
       </c>
       <c r="AK38" s="296">
@@ -33606,7 +33609,7 @@
       <c r="AT38" s="296">
         <v>32.604999999999997</v>
       </c>
-      <c r="AZ38" s="226">
+      <c r="AZ38" s="296">
         <v>31.09</v>
       </c>
     </row>
@@ -33654,7 +33657,7 @@
         <f t="shared" si="5"/>
         <v>-96.424999999999997</v>
       </c>
-      <c r="AH41" s="226">
+      <c r="AH41" s="296">
         <v>-16.93</v>
       </c>
       <c r="AK41" s="296">
@@ -33669,7 +33672,7 @@
       <c r="AT41" s="296">
         <v>-16.285</v>
       </c>
-      <c r="AZ41" s="226">
+      <c r="AZ41" s="296">
         <v>-15.1</v>
       </c>
     </row>
@@ -33702,7 +33705,7 @@
         <f t="shared" si="5"/>
         <v>-42.534999999999997</v>
       </c>
-      <c r="AH43" s="226">
+      <c r="AH43" s="296">
         <v>-8.4450000000000003</v>
       </c>
       <c r="AN43" s="296">
@@ -33730,7 +33733,7 @@
       <c r="AT44" s="296">
         <v>-8.1050000000000004</v>
       </c>
-      <c r="AZ44" s="226">
+      <c r="AZ44" s="296">
         <v>-8.59</v>
       </c>
     </row>
@@ -33763,7 +33766,7 @@
         <f t="shared" si="5"/>
         <v>-16.754999999999999</v>
       </c>
-      <c r="AH46" s="226">
+      <c r="AH46" s="296">
         <v>-16.754999999999999</v>
       </c>
     </row>
@@ -33789,7 +33792,7 @@
         <f>8.38+8.365</f>
         <v>16.745000000000001</v>
       </c>
-      <c r="AX47" s="270">
+      <c r="AX47" s="276">
         <v>33.494999999999997</v>
       </c>
       <c r="BD47" s="276">
@@ -33871,7 +33874,7 @@
       <c r="AO51" s="276">
         <v>-16.745000000000001</v>
       </c>
-      <c r="AX51" s="270">
+      <c r="AX51" s="276">
         <v>-16.79</v>
       </c>
     </row>
@@ -33889,7 +33892,7 @@
       <c r="Q52" s="208">
         <v>-8.5299999999999994</v>
       </c>
-      <c r="AX52" s="270">
+      <c r="AX52" s="276">
         <v>-8.4</v>
       </c>
     </row>
@@ -33925,10 +33928,10 @@
       <c r="AL54" s="276">
         <v>33.950000000000003</v>
       </c>
-      <c r="AX54" s="270">
+      <c r="AX54" s="276">
         <v>32.505000000000003</v>
       </c>
-      <c r="BA54" s="270">
+      <c r="BA54" s="276">
         <v>34.045000000000002</v>
       </c>
       <c r="BG54" s="276">
@@ -33949,7 +33952,7 @@
         <f t="shared" si="5"/>
         <v>-82.89</v>
       </c>
-      <c r="AX55" s="270">
+      <c r="AX55" s="276">
         <v>-16.8</v>
       </c>
       <c r="BG55" s="276">
@@ -33997,10 +34000,10 @@
       <c r="AQ57" s="296">
         <v>-8.4649999999999999</v>
       </c>
-      <c r="AX57" s="270">
+      <c r="AX57" s="276">
         <v>-16.664999999999999</v>
       </c>
-      <c r="AZ57" s="226">
+      <c r="AZ57" s="296">
         <v>-7.4</v>
       </c>
     </row>
@@ -34021,7 +34024,7 @@
       <c r="AL58" s="276">
         <v>-8.4749999999999996</v>
       </c>
-      <c r="BA58" s="270">
+      <c r="BA58" s="276">
         <v>-8.5749999999999993</v>
       </c>
       <c r="BK58" s="208">
@@ -34039,7 +34042,7 @@
         <f t="shared" si="5"/>
         <v>-15.93</v>
       </c>
-      <c r="AX59" s="270">
+      <c r="AX59" s="276">
         <v>-7.3449999999999998</v>
       </c>
       <c r="BD59" s="276">
@@ -34057,7 +34060,7 @@
         <f t="shared" si="5"/>
         <v>-49.765000000000001</v>
       </c>
-      <c r="BA60" s="270">
+      <c r="BA60" s="276">
         <f>-8.525-8.385</f>
         <v>-16.91</v>
       </c>
@@ -34104,7 +34107,7 @@
       <c r="AR62" s="276">
         <v>8.5050000000000008</v>
       </c>
-      <c r="BA62" s="270">
+      <c r="BA62" s="276">
         <v>34.090000000000003</v>
       </c>
       <c r="BD62" s="276">
@@ -34161,7 +34164,7 @@
       <c r="AR64" s="276">
         <v>-8.5050000000000008</v>
       </c>
-      <c r="BA64" s="270">
+      <c r="BA64" s="276">
         <v>-8.56</v>
       </c>
       <c r="BD64" s="276">
@@ -34287,7 +34290,7 @@
         <f t="shared" si="5"/>
         <v>-17.14</v>
       </c>
-      <c r="BA71" s="270">
+      <c r="BA71" s="276">
         <v>-8.5649999999999995</v>
       </c>
       <c r="BD71" s="276">
@@ -34339,7 +34342,7 @@
         <f t="shared" si="6"/>
         <v>-25.524999999999999</v>
       </c>
-      <c r="BA74" s="270">
+      <c r="BA74" s="276">
         <v>-25.524999999999999</v>
       </c>
     </row>
@@ -34503,7 +34506,7 @@
       <c r="AL83" s="276">
         <v>33.695</v>
       </c>
-      <c r="BA83" s="270">
+      <c r="BA83" s="276">
         <v>33.86</v>
       </c>
       <c r="BD83" s="276">
@@ -34528,7 +34531,7 @@
       <c r="AU84" s="276">
         <v>8.4</v>
       </c>
-      <c r="AX84" s="270">
+      <c r="AX84" s="276">
         <v>8.3949999999999996</v>
       </c>
     </row>
@@ -34699,7 +34702,7 @@
         <f t="shared" si="6"/>
         <v>-33.755000000000003</v>
       </c>
-      <c r="BA92" s="270">
+      <c r="BA92" s="276">
         <v>-16.965</v>
       </c>
       <c r="BF92" s="226">
@@ -34753,7 +34756,7 @@
       <c r="AO94" s="276">
         <v>-8.42</v>
       </c>
-      <c r="AX94" s="270">
+      <c r="AX94" s="276">
         <v>-8.3949999999999996</v>
       </c>
     </row>
@@ -34846,7 +34849,7 @@
       <c r="AT99" s="296">
         <v>-8.24</v>
       </c>
-      <c r="BA99" s="270">
+      <c r="BA99" s="276">
         <v>-16.895</v>
       </c>
       <c r="BD99" s="276">
@@ -35178,7 +35181,7 @@
         <f t="shared" si="6"/>
         <v>-164.51</v>
       </c>
-      <c r="DT119" s="360">
+      <c r="DT119" s="312">
         <v>-164.51</v>
       </c>
     </row>
@@ -35229,7 +35232,7 @@
       <c r="AU121" s="276">
         <v>33.774999999999999</v>
       </c>
-      <c r="AX121" s="270">
+      <c r="AX121" s="276">
         <v>34.034999999999997</v>
       </c>
       <c r="BD121" s="276">
@@ -35273,7 +35276,7 @@
       <c r="AR123" s="276">
         <v>-8.41</v>
       </c>
-      <c r="AX123" s="270">
+      <c r="AX123" s="276">
         <f>-8.51-8.515</f>
         <v>-17.024999999999999</v>
       </c>
@@ -35308,7 +35311,7 @@
         <f>-8.41-8.47</f>
         <v>-16.88</v>
       </c>
-      <c r="AX124" s="270">
+      <c r="AX124" s="276">
         <v>-8.5150000000000006</v>
       </c>
       <c r="BG124" s="276">
@@ -35451,7 +35454,7 @@
       <c r="AU131" s="276">
         <v>-8.4450000000000003</v>
       </c>
-      <c r="AX131" s="270">
+      <c r="AX131" s="276">
         <v>-8.4949999999999992</v>
       </c>
     </row>
@@ -35525,7 +35528,7 @@
         <f>8.455+8.48</f>
         <v>16.934999999999999</v>
       </c>
-      <c r="AX134" s="270">
+      <c r="AX134" s="276">
         <f>34.08+8.505+8.495+8.515+8.5</f>
         <v>68.094999999999999</v>
       </c>
@@ -35573,7 +35576,7 @@
       <c r="AE136" s="296">
         <v>14.21</v>
       </c>
-      <c r="AH136" s="226">
+      <c r="AH136" s="296">
         <v>17.364999999999998</v>
       </c>
       <c r="AK136" s="296">
@@ -35588,7 +35591,7 @@
       <c r="AT136" s="296">
         <v>35.380000000000003</v>
       </c>
-      <c r="AZ136" s="226">
+      <c r="AZ136" s="296">
         <v>33.64</v>
       </c>
       <c r="BI136" s="296">
@@ -35609,7 +35612,7 @@
         <f t="shared" si="7"/>
         <v>-67.004999999999995</v>
       </c>
-      <c r="AH137" s="226">
+      <c r="AH137" s="296">
         <v>-8.625</v>
       </c>
       <c r="AK137" s="296">
@@ -35621,7 +35624,7 @@
       <c r="AT137" s="296">
         <v>-8.8450000000000006</v>
       </c>
-      <c r="AX137" s="270">
+      <c r="AX137" s="276">
         <v>-8.5050000000000008</v>
       </c>
       <c r="BI137" s="296">
@@ -35646,7 +35649,7 @@
       <c r="AC138" s="270">
         <v>-8.3849999999999998</v>
       </c>
-      <c r="AH138" s="226">
+      <c r="AH138" s="296">
         <v>-8.74</v>
       </c>
       <c r="AK138" s="296">
@@ -35682,10 +35685,10 @@
       <c r="AT139" s="296">
         <v>-8.8450000000000006</v>
       </c>
-      <c r="AX139" s="270">
+      <c r="AX139" s="276">
         <v>-17.015000000000001</v>
       </c>
-      <c r="AZ139" s="226">
+      <c r="AZ139" s="296">
         <v>-25.254999999999999</v>
       </c>
       <c r="BD139" s="276">
@@ -35703,7 +35706,7 @@
         <f t="shared" si="7"/>
         <v>-17.14</v>
       </c>
-      <c r="AX140" s="270">
+      <c r="AX140" s="276">
         <v>-8.5850000000000009</v>
       </c>
       <c r="BD140" s="276">
@@ -35751,7 +35754,7 @@
       <c r="AE142" s="296">
         <v>-7.1050000000000004</v>
       </c>
-      <c r="AZ142" s="226">
+      <c r="AZ142" s="296">
         <v>-8.3849999999999998</v>
       </c>
     </row>
@@ -35769,7 +35772,7 @@
       <c r="M143" s="270">
         <v>-3.02</v>
       </c>
-      <c r="AX143" s="270">
+      <c r="AX143" s="276">
         <v>-8.5050000000000008</v>
       </c>
       <c r="BD143" s="276">
@@ -35854,7 +35857,7 @@
         <f>-8.42-8.43</f>
         <v>-16.850000000000001</v>
       </c>
-      <c r="AX147" s="270">
+      <c r="AX147" s="276">
         <f>-8.49-8.5</f>
         <v>-16.989999999999998</v>
       </c>
@@ -35897,7 +35900,7 @@
         <f>33.94+33.44</f>
         <v>67.38</v>
       </c>
-      <c r="AX149" s="270">
+      <c r="AX149" s="276">
         <v>34.21</v>
       </c>
     </row>
@@ -35945,7 +35948,7 @@
       <c r="AI152" s="270">
         <v>-8.4499999999999993</v>
       </c>
-      <c r="AX152" s="270">
+      <c r="AX152" s="276">
         <f>-8.53-8.465</f>
         <v>-16.995000000000001</v>
       </c>
@@ -35995,7 +35998,7 @@
         <f>-8.465-8.475</f>
         <v>-16.940000000000001</v>
       </c>
-      <c r="AX155" s="270">
+      <c r="AX155" s="276">
         <f>-8.64-8.575</f>
         <v>-17.215</v>
       </c>
@@ -36017,7 +36020,7 @@
       <c r="AQ156" s="296">
         <v>-8.4</v>
       </c>
-      <c r="AX156" s="270">
+      <c r="AX156" s="276">
         <v>-8.4949999999999992</v>
       </c>
     </row>
@@ -36152,10 +36155,10 @@
       <c r="AU163" s="276">
         <v>33.634999999999998</v>
       </c>
-      <c r="AX163" s="270">
+      <c r="AX163" s="276">
         <v>34.270000000000003</v>
       </c>
-      <c r="BA163" s="270">
+      <c r="BA163" s="276">
         <f>33.9+33.96</f>
         <v>67.86</v>
       </c>
@@ -36184,10 +36187,10 @@
       <c r="AU164" s="276">
         <v>-25.19</v>
       </c>
-      <c r="AX164" s="270">
+      <c r="AX164" s="276">
         <v>-17.135000000000002</v>
       </c>
-      <c r="BA164" s="270">
+      <c r="BA164" s="276">
         <v>-33.9</v>
       </c>
       <c r="BG164" s="276">
@@ -36205,7 +36208,7 @@
         <f t="shared" si="7"/>
         <v>-8.5</v>
       </c>
-      <c r="BA165" s="270">
+      <c r="BA165" s="276">
         <v>-8.5</v>
       </c>
     </row>
@@ -36223,7 +36226,7 @@
       <c r="AU166" s="276">
         <v>-8.4450000000000003</v>
       </c>
-      <c r="BA166" s="270">
+      <c r="BA166" s="276">
         <v>-8.49</v>
       </c>
     </row>
@@ -36306,10 +36309,10 @@
         <f t="shared" si="7"/>
         <v>-17.03</v>
       </c>
-      <c r="AX171" s="270">
+      <c r="AX171" s="276">
         <v>-8.5500000000000007</v>
       </c>
-      <c r="BA171" s="270">
+      <c r="BA171" s="276">
         <v>-8.48</v>
       </c>
     </row>
@@ -36330,7 +36333,7 @@
       <c r="AO172" s="276">
         <v>-8.51</v>
       </c>
-      <c r="BA172" s="270">
+      <c r="BA172" s="276">
         <v>-8.49</v>
       </c>
     </row>
@@ -36348,7 +36351,7 @@
       <c r="AR173" s="276">
         <v>-8.4600000000000009</v>
       </c>
-      <c r="AX173" s="270">
+      <c r="AX173" s="276">
         <v>-8.5850000000000009</v>
       </c>
     </row>
@@ -36408,7 +36411,7 @@
       <c r="CU176" s="35">
         <v>-26.49</v>
       </c>
-      <c r="DT176" s="360">
+      <c r="DT176" s="312">
         <v>-80.83</v>
       </c>
     </row>
@@ -36437,7 +36440,7 @@
         <f>8.425+8.435</f>
         <v>16.86</v>
       </c>
-      <c r="BA177" s="270">
+      <c r="BA177" s="276">
         <v>33.549999999999997</v>
       </c>
       <c r="BD177" s="276">
@@ -36477,7 +36480,7 @@
         <f t="shared" si="7"/>
         <v>-50.465000000000003</v>
       </c>
-      <c r="BA179" s="270">
+      <c r="BA179" s="276">
         <f>-8.09-8.475-8.505</f>
         <v>-25.07</v>
       </c>
@@ -36584,7 +36587,7 @@
       <c r="AN185" s="296">
         <v>-34.33</v>
       </c>
-      <c r="BA185" s="270">
+      <c r="BA185" s="276">
         <v>-8.48</v>
       </c>
     </row>
@@ -36654,7 +36657,7 @@
       <c r="AL189" s="276">
         <v>8.4600000000000009</v>
       </c>
-      <c r="BA189" s="270">
+      <c r="BA189" s="276">
         <f>8.48+8.43</f>
         <v>16.91</v>
       </c>
@@ -36763,7 +36766,7 @@
         <f t="shared" si="7"/>
         <v>-8.43</v>
       </c>
-      <c r="BA195" s="270">
+      <c r="BA195" s="276">
         <v>-8.43</v>
       </c>
     </row>
@@ -36898,7 +36901,7 @@
       <c r="AW202" s="226">
         <v>32.76</v>
       </c>
-      <c r="AZ202" s="226">
+      <c r="AZ202" s="296">
         <v>33.96</v>
       </c>
       <c r="BF202" s="226">
@@ -36931,7 +36934,7 @@
       <c r="AW203" s="226">
         <v>-32.76</v>
       </c>
-      <c r="AZ203" s="226">
+      <c r="AZ203" s="296">
         <v>-17.02</v>
       </c>
       <c r="BF203" s="226">
@@ -37102,13 +37105,13 @@
       <c r="AU212" s="276">
         <v>-25.245000000000001</v>
       </c>
-      <c r="AX212" s="270">
+      <c r="AX212" s="276">
         <v>-25.434999999999999</v>
       </c>
-      <c r="AZ212" s="226">
+      <c r="AZ212" s="296">
         <v>-16.940000000000001</v>
       </c>
-      <c r="BA212" s="270">
+      <c r="BA212" s="276">
         <v>-8.48</v>
       </c>
     </row>
@@ -37165,7 +37168,7 @@
       <c r="AU214" s="276">
         <v>25.245000000000001</v>
       </c>
-      <c r="AX214" s="270">
+      <c r="AX214" s="276">
         <v>25.434999999999999</v>
       </c>
       <c r="BM214" s="308">
@@ -37186,7 +37189,7 @@
       <c r="D215" s="201">
         <v>33.61</v>
       </c>
-      <c r="AH215" s="226">
+      <c r="AH215" s="296">
         <v>30.425000000000001</v>
       </c>
       <c r="AN215" s="296">
@@ -37198,7 +37201,7 @@
       <c r="AT215" s="296">
         <v>51.96</v>
       </c>
-      <c r="AZ215" s="226">
+      <c r="AZ215" s="296">
         <v>33.83</v>
       </c>
       <c r="BF215" s="226">
@@ -37228,7 +37231,7 @@
         <f t="shared" si="8"/>
         <v>-94.685000000000002</v>
       </c>
-      <c r="AH217" s="226">
+      <c r="AH217" s="296">
         <v>-15.2</v>
       </c>
       <c r="AN217" s="296">
@@ -37237,7 +37240,7 @@
       <c r="AT217" s="296">
         <v>-34.630000000000003</v>
       </c>
-      <c r="AZ217" s="226">
+      <c r="AZ217" s="296">
         <v>-1.33</v>
       </c>
       <c r="BF217" s="226">
@@ -37255,7 +37258,7 @@
         <f t="shared" si="8"/>
         <v>-40</v>
       </c>
-      <c r="AZ218" s="226">
+      <c r="AZ218" s="296">
         <v>-24</v>
       </c>
       <c r="BF218" s="226">
@@ -37291,7 +37294,7 @@
       <c r="AF220" s="276">
         <v>-8.3949999999999996</v>
       </c>
-      <c r="AH220" s="226">
+      <c r="AH220" s="296">
         <v>-7.6349999999999998</v>
       </c>
       <c r="AK220" s="296">
@@ -37321,7 +37324,7 @@
         <f t="shared" si="8"/>
         <v>-63.954999999999998</v>
       </c>
-      <c r="AH221" s="226">
+      <c r="AH221" s="296">
         <v>-7.59</v>
       </c>
       <c r="AQ221" s="296">
@@ -37330,7 +37333,7 @@
       <c r="AT221" s="296">
         <v>-8.6150000000000002</v>
       </c>
-      <c r="AZ221" s="226">
+      <c r="AZ221" s="296">
         <v>-8.5</v>
       </c>
       <c r="BJ221" s="276">
@@ -37396,7 +37399,7 @@
         <f t="shared" si="8"/>
         <v>-33</v>
       </c>
-      <c r="AX225" s="270">
+      <c r="AX225" s="276">
         <v>-33</v>
       </c>
     </row>
@@ -37432,10 +37435,10 @@
       <c r="AU226" s="276">
         <v>33.825000000000003</v>
       </c>
-      <c r="AX226" s="270">
+      <c r="AX226" s="276">
         <v>84.52</v>
       </c>
-      <c r="BA226" s="270">
+      <c r="BA226" s="276">
         <v>83.834999999999994</v>
       </c>
       <c r="BD226" s="276">
@@ -37489,10 +37492,10 @@
         <f t="shared" si="8"/>
         <v>-33.86</v>
       </c>
-      <c r="AX228" s="270">
+      <c r="AX228" s="276">
         <v>-8.4949999999999992</v>
       </c>
-      <c r="BA228" s="270">
+      <c r="BA228" s="276">
         <v>-16.809999999999999</v>
       </c>
       <c r="BD228" s="276">
@@ -37531,10 +37534,10 @@
       <c r="AU229" s="276">
         <v>-16.905000000000001</v>
       </c>
-      <c r="AX229" s="270">
+      <c r="AX229" s="276">
         <v>-16.824999999999999</v>
       </c>
-      <c r="BA229" s="270">
+      <c r="BA229" s="276">
         <v>-25.13</v>
       </c>
       <c r="BD229" s="276">
@@ -37567,10 +37570,10 @@
       <c r="AO230" s="276">
         <v>-8.41</v>
       </c>
-      <c r="AX230" s="270">
+      <c r="AX230" s="276">
         <v>-25.465</v>
       </c>
-      <c r="BA230" s="270">
+      <c r="BA230" s="276">
         <v>-16.79</v>
       </c>
       <c r="BJ230" s="276">
@@ -37594,7 +37597,7 @@
         <f t="shared" si="8"/>
         <v>-34.594999999999999</v>
       </c>
-      <c r="AX231" s="270">
+      <c r="AX231" s="276">
         <v>-0.73499999999999999</v>
       </c>
       <c r="BG231" s="276">
@@ -37630,7 +37633,7 @@
       <c r="AU232" s="276">
         <v>-8.4600000000000009</v>
       </c>
-      <c r="BA232" s="270">
+      <c r="BA232" s="276">
         <v>-8.39</v>
       </c>
       <c r="BJ232" s="276">
@@ -37663,7 +37666,7 @@
         <f t="shared" si="8"/>
         <v>-102</v>
       </c>
-      <c r="BA234" s="270">
+      <c r="BA234" s="276">
         <v>-8.4</v>
       </c>
       <c r="CF234" s="58">
@@ -37692,7 +37695,7 @@
         <f t="shared" si="8"/>
         <v>-8.3149999999999995</v>
       </c>
-      <c r="BA235" s="270">
+      <c r="BA235" s="276">
         <v>-8.3149999999999995</v>
       </c>
     </row>
@@ -37715,11 +37718,11 @@
         <f>8.43+8.43</f>
         <v>16.86</v>
       </c>
-      <c r="AX236" s="270">
+      <c r="AX236" s="276">
         <f>33.99+33.88</f>
         <v>67.87</v>
       </c>
-      <c r="BA236" s="270">
+      <c r="BA236" s="276">
         <f>8.465+8.285+33.375</f>
         <v>50.125</v>
       </c>
@@ -37756,7 +37759,7 @@
       <c r="AL237" s="276">
         <v>-8.43</v>
       </c>
-      <c r="AX237" s="270">
+      <c r="AX237" s="276">
         <v>-8.4049999999999994</v>
       </c>
     </row>
@@ -37774,10 +37777,10 @@
       <c r="AL238" s="276">
         <v>-7.43</v>
       </c>
-      <c r="AX238" s="270">
+      <c r="AX238" s="276">
         <v>-32.99</v>
       </c>
-      <c r="BA238" s="270">
+      <c r="BA238" s="276">
         <v>-24.234999999999999</v>
       </c>
     </row>
@@ -37795,10 +37798,10 @@
       <c r="AL239" s="276">
         <v>-1</v>
       </c>
-      <c r="AX239" s="270">
+      <c r="AX239" s="276">
         <v>-1</v>
       </c>
-      <c r="BA239" s="270">
+      <c r="BA239" s="276">
         <v>-1</v>
       </c>
     </row>
@@ -37828,7 +37831,7 @@
         <f t="shared" si="8"/>
         <v>-17.024999999999999</v>
       </c>
-      <c r="BA241" s="270">
+      <c r="BA241" s="276">
         <v>-8.4649999999999999</v>
       </c>
       <c r="BD241" s="276">
@@ -37871,7 +37874,7 @@
       <c r="AI243" s="270">
         <v>-8.4550000000000001</v>
       </c>
-      <c r="BA243" s="270">
+      <c r="BA243" s="276">
         <v>-8.14</v>
       </c>
     </row>
@@ -37886,7 +37889,7 @@
         <f t="shared" si="8"/>
         <v>-8.5</v>
       </c>
-      <c r="AX244" s="270">
+      <c r="AX244" s="276">
         <v>-8.5</v>
       </c>
     </row>
@@ -37940,7 +37943,7 @@
       <c r="AE247" s="296">
         <v>16.46</v>
       </c>
-      <c r="AH247" s="226">
+      <c r="AH247" s="296">
         <v>14.734999999999999</v>
       </c>
       <c r="AK247" s="296">
@@ -37955,7 +37958,7 @@
       <c r="AT247" s="296">
         <v>70.275000000000006</v>
       </c>
-      <c r="AZ247" s="226">
+      <c r="AZ247" s="296">
         <v>33.299999999999997</v>
       </c>
       <c r="BF247" s="226">
@@ -38078,10 +38081,10 @@
       <c r="AQ252" s="296">
         <v>-9</v>
       </c>
-      <c r="AX252" s="270">
+      <c r="AX252" s="276">
         <v>-8.48</v>
       </c>
-      <c r="AZ252" s="226">
+      <c r="AZ252" s="296">
         <v>-8.33</v>
       </c>
     </row>
@@ -38096,7 +38099,7 @@
         <f t="shared" si="8"/>
         <v>-16.885000000000002</v>
       </c>
-      <c r="AZ253" s="226">
+      <c r="AZ253" s="296">
         <v>-8.32</v>
       </c>
       <c r="BD253" s="276">
@@ -38104,114 +38107,246 @@
       </c>
     </row>
     <row r="254" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A254" s="45">
+        <v>46256</v>
+      </c>
+      <c r="B254" s="19" t="s">
+        <v>109</v>
+      </c>
       <c r="C254" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-28.85</v>
+      </c>
+      <c r="U254" s="296">
+        <v>-3.57</v>
+      </c>
+      <c r="AX254" s="276">
+        <v>-8.4949999999999992</v>
+      </c>
+      <c r="BA254" s="276">
+        <v>-8.2850000000000001</v>
+      </c>
+      <c r="BI254" s="296">
+        <v>-8.5</v>
       </c>
     </row>
     <row r="255" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A255" s="45">
+        <v>46258</v>
+      </c>
+      <c r="B255" s="19" t="s">
+        <v>84</v>
+      </c>
       <c r="C255" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>-16.864999999999998</v>
+      </c>
+      <c r="AT255" s="296">
+        <v>-8.5250000000000004</v>
+      </c>
+      <c r="AZ255" s="296">
+        <v>-8.34</v>
       </c>
     </row>
     <row r="256" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A256" s="45">
+        <v>46258</v>
+      </c>
+      <c r="B256" s="19" t="s">
+        <v>83</v>
+      </c>
       <c r="C256" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" spans="3:3" x14ac:dyDescent="0.25">
+        <f>SUM(D256:EY256)</f>
+        <v>-80.924999999999997</v>
+      </c>
+      <c r="BT256" s="226">
+        <v>-25.17</v>
+      </c>
+      <c r="BX256" s="226">
+        <v>-14.715</v>
+      </c>
+      <c r="CA256" s="296">
+        <v>-41.04</v>
+      </c>
+    </row>
+    <row r="257" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A257" s="45">
+        <v>46258</v>
+      </c>
+      <c r="B257" s="19" t="s">
+        <v>83</v>
+      </c>
       <c r="C257" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" spans="3:3" x14ac:dyDescent="0.25">
+        <f>SUM(D257:EY257)</f>
+        <v>-17.754999999999999</v>
+      </c>
+      <c r="BX257" s="226">
+        <v>-17.754999999999999</v>
+      </c>
+    </row>
+    <row r="258" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A258" s="45">
+        <v>46258</v>
+      </c>
+      <c r="B258" s="19" t="s">
+        <v>17</v>
+      </c>
       <c r="C258" s="18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259" spans="3:3" x14ac:dyDescent="0.25">
+        <f>SUM(D258:EY258)</f>
+        <v>113.89</v>
+      </c>
+      <c r="U258" s="296">
+        <v>7.52</v>
+      </c>
+      <c r="X258" s="226">
+        <v>7.6050000000000004</v>
+      </c>
+      <c r="BT258" s="226">
+        <v>33.534999999999997</v>
+      </c>
+      <c r="BX258" s="226">
+        <v>32.47</v>
+      </c>
+      <c r="CA258" s="296">
+        <v>32.76</v>
+      </c>
+    </row>
+    <row r="259" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A259" s="45">
+        <v>46259</v>
+      </c>
+      <c r="B259" s="19" t="s">
+        <v>105</v>
+      </c>
       <c r="C259" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260" spans="3:3" x14ac:dyDescent="0.25">
+        <v>-15.98</v>
+      </c>
+      <c r="AH259" s="296">
+        <v>-7.415</v>
+      </c>
+      <c r="AT259" s="296">
+        <v>-8.5649999999999995</v>
+      </c>
+    </row>
+    <row r="260" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A260" s="45">
+        <v>46259</v>
+      </c>
+      <c r="B260" s="19" t="s">
+        <v>124</v>
+      </c>
       <c r="C260" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261" spans="3:3" x14ac:dyDescent="0.25">
+        <v>-8.57</v>
+      </c>
+      <c r="AT260" s="296">
+        <v>-8.57</v>
+      </c>
+    </row>
+    <row r="261" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A261" s="45">
+        <v>46259</v>
+      </c>
+      <c r="B261" s="19" t="s">
+        <v>92</v>
+      </c>
       <c r="C261" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="3:3" x14ac:dyDescent="0.25">
+        <v>-15.125</v>
+      </c>
+      <c r="U261" s="296">
+        <v>-7.52</v>
+      </c>
+      <c r="X261" s="226">
+        <v>-7.6050000000000004</v>
+      </c>
+    </row>
+    <row r="262" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A262" s="45">
+        <v>46259</v>
+      </c>
+      <c r="B262" s="19" t="s">
+        <v>17</v>
+      </c>
       <c r="C262" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263" spans="3:3" x14ac:dyDescent="0.25">
+        <v>67.62</v>
+      </c>
+      <c r="BF262" s="226">
+        <v>33.634999999999998</v>
+      </c>
+      <c r="BI262" s="296">
+        <v>33.984999999999999</v>
+      </c>
+    </row>
+    <row r="263" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="A263" s="45">
+        <v>46259</v>
+      </c>
+      <c r="B263" s="19" t="s">
+        <v>92</v>
+      </c>
       <c r="C263" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264" spans="3:3" x14ac:dyDescent="0.25">
+        <v>-67.62</v>
+      </c>
+      <c r="BF263" s="226">
+        <v>-33.634999999999998</v>
+      </c>
+      <c r="BI263" s="296">
+        <v>-33.984999999999999</v>
+      </c>
+    </row>
+    <row r="264" spans="1:79" x14ac:dyDescent="0.25">
       <c r="C264" s="18">
         <f t="shared" ref="C264:C278" si="9">SUM(D264:EY264)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:79" x14ac:dyDescent="0.25">
       <c r="C265" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:79" x14ac:dyDescent="0.25">
       <c r="C266" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:79" x14ac:dyDescent="0.25">
       <c r="C267" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:79" x14ac:dyDescent="0.25">
       <c r="C268" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:79" x14ac:dyDescent="0.25">
       <c r="C269" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:79" x14ac:dyDescent="0.25">
       <c r="C270" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:79" x14ac:dyDescent="0.25">
       <c r="C271" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:79" x14ac:dyDescent="0.25">
       <c r="C272" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
@@ -38398,8 +38533,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A194:EA200">
-    <sortCondition ref="A194:A200"/>
+  <sortState ref="A256:EB258">
+    <sortCondition ref="A256:A258"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A1:B5"/>
@@ -38437,16 +38572,16 @@
     </row>
     <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="82"/>
-      <c r="B3" s="357" t="s">
+      <c r="B3" s="362" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="357"/>
+      <c r="C3" s="362"/>
       <c r="D3" s="82"/>
     </row>
     <row r="4" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="82"/>
-      <c r="B4" s="357"/>
-      <c r="C4" s="357"/>
+      <c r="B4" s="362"/>
+      <c r="C4" s="362"/>
       <c r="D4" s="82"/>
     </row>
     <row r="5" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -39116,7 +39251,7 @@
       </c>
       <c r="E14" s="139">
         <f>'STOK DETAY'!U6</f>
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="F14" s="139">
         <f>'STOK DETAY'!V6</f>
@@ -39127,7 +39262,7 @@
       <c r="I14" s="139"/>
       <c r="J14" s="139">
         <f t="shared" si="0"/>
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="K14" s="69"/>
       <c r="L14" s="69"/>
@@ -39325,7 +39460,7 @@
       </c>
       <c r="E19" s="139">
         <f>'STOK DETAY'!AH6</f>
-        <v>14.734999999999999</v>
+        <v>7.32</v>
       </c>
       <c r="F19" s="139">
         <f>'STOK DETAY'!AI6</f>
@@ -39336,7 +39471,7 @@
       <c r="I19" s="139"/>
       <c r="J19" s="139">
         <f t="shared" si="0"/>
-        <v>23.215</v>
+        <v>15.8</v>
       </c>
       <c r="K19" s="69"/>
       <c r="L19" s="69"/>
@@ -39497,7 +39632,7 @@
       </c>
       <c r="E23" s="139">
         <f>'STOK DETAY'!AT6</f>
-        <v>34.380000000000003</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="F23" s="139">
         <f>'STOK DETAY'!AU6</f>
@@ -39508,7 +39643,7 @@
       <c r="I23" s="139"/>
       <c r="J23" s="139">
         <f t="shared" si="0"/>
-        <v>34.380000000000003</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="K23" s="69"/>
       <c r="L23" s="69"/>
@@ -39544,14 +39679,14 @@
       </c>
       <c r="F24" s="139">
         <f>'STOK DETAY'!AX6</f>
-        <v>8.4949999999999992</v>
+        <v>0</v>
       </c>
       <c r="G24" s="139"/>
       <c r="H24" s="139"/>
       <c r="I24" s="139"/>
       <c r="J24" s="139">
         <f t="shared" si="0"/>
-        <v>8.4949999999999992</v>
+        <v>0</v>
       </c>
       <c r="K24" s="69"/>
       <c r="L24" s="69"/>
@@ -39583,18 +39718,18 @@
       </c>
       <c r="E25" s="139">
         <f>'STOK DETAY'!AZ6</f>
-        <v>16.649999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="F25" s="139">
         <f>'STOK DETAY'!BA6</f>
-        <v>8.2850000000000001</v>
+        <v>0</v>
       </c>
       <c r="G25" s="139"/>
       <c r="H25" s="139"/>
       <c r="I25" s="139"/>
       <c r="J25" s="139">
         <f t="shared" si="0"/>
-        <v>24.934999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="K25" s="69"/>
       <c r="L25" s="69"/>
@@ -39712,7 +39847,7 @@
       </c>
       <c r="E28" s="139">
         <f>'STOK DETAY'!BI6</f>
-        <v>17.059999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="F28" s="139">
         <f>'STOK DETAY'!BJ6</f>
@@ -39723,7 +39858,7 @@
       <c r="I28" s="139"/>
       <c r="J28" s="139">
         <f t="shared" si="0"/>
-        <v>17.059999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="K28" s="69"/>
       <c r="L28" s="69"/>
@@ -39847,7 +39982,7 @@
       </c>
       <c r="E31" s="139">
         <f>'STOK DETAY'!BT6</f>
-        <v>0</v>
+        <v>8.3650000000000002</v>
       </c>
       <c r="F31" s="139">
         <f>'STOK DETAY'!BV6</f>
@@ -39858,7 +39993,7 @@
       <c r="I31" s="139"/>
       <c r="J31" s="139">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.3650000000000002</v>
       </c>
       <c r="K31" s="69"/>
       <c r="L31" s="69"/>
@@ -39933,7 +40068,7 @@
       </c>
       <c r="E33" s="139">
         <f>'STOK DETAY'!CA6</f>
-        <v>16.510000000000002</v>
+        <v>8.23</v>
       </c>
       <c r="F33" s="139">
         <f>'STOK DETAY'!CB6</f>
@@ -39944,7 +40079,7 @@
       <c r="I33" s="139"/>
       <c r="J33" s="139">
         <f t="shared" si="0"/>
-        <v>16.510000000000002</v>
+        <v>8.23</v>
       </c>
       <c r="K33" s="69"/>
       <c r="L33" s="69"/>
